--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/Stocks/Data/Stocks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1CC872-E08D-2C4B-935C-7352EB8593D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227D1EEF-6F9B-A84D-A9AC-23E842B8602B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -1740,20 +1740,19 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
+      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="8">
           <cell r="C8">
-            <v>134.36000000000001</v>
+            <v>136.19999999999999</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2226,7 +2225,7 @@
       </c>
       <c r="C3" s="38">
         <f>[1]Sheet1!$C$8</f>
-        <v>134.36000000000001</v>
+        <v>136.19999999999999</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -2246,7 +2245,7 @@
       </c>
       <c r="C9" s="159">
         <f>C3/'Statement Q'!N27</f>
-        <v>27.366615097856481</v>
+        <v>27.741388630009318</v>
       </c>
       <c r="E9" s="159"/>
     </row>
@@ -2256,7 +2255,7 @@
       </c>
       <c r="C10" s="159">
         <f>C3/Statements!W20</f>
-        <v>13.130199427651583</v>
+        <v>13.310011625827221</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2265,7 +2264,7 @@
       </c>
       <c r="C12" s="163">
         <f>C3*'Statement Q'!J141</f>
-        <v>143362.12000000002</v>
+        <v>145325.4</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2283,7 +2282,7 @@
       </c>
       <c r="C14" s="163">
         <f>C12+C13</f>
-        <v>146357.12000000002</v>
+        <v>148320.4</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -24426,7 +24425,7 @@
       </c>
       <c r="C70" s="132">
         <f>(C69-Overview!C3)/Overview!C3</f>
-        <v>0.26990135197903997</v>
+        <v>0.25274556278930865</v>
       </c>
       <c r="E70" s="107"/>
     </row>
@@ -24507,7 +24506,7 @@
       </c>
       <c r="C80" s="132">
         <f>(C79-Overview!C3)/Overview!C3</f>
-        <v>-0.11921563433043328</v>
+        <v>-0.13111463016620406</v>
       </c>
     </row>
   </sheetData>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227D1EEF-6F9B-A84D-A9AC-23E842B8602B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DE208B-6276-6640-9F75-46C6014A2BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -1748,7 +1748,7 @@
       <sheetData sheetId="0">
         <row r="8">
           <cell r="C8">
-            <v>136.19999999999999</v>
+            <v>133.245</v>
           </cell>
         </row>
       </sheetData>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C3" s="38">
         <f>[1]Sheet1!$C$8</f>
-        <v>136.19999999999999</v>
+        <v>133.245</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C9" s="159">
         <f>C3/'Statement Q'!N27</f>
-        <v>27.741388630009318</v>
+        <v>27.139510484622555</v>
       </c>
       <c r="E9" s="159"/>
     </row>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C10" s="159">
         <f>C3/Statements!W20</f>
-        <v>13.310011625827221</v>
+        <v>13.021237144517976</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C12" s="163">
         <f>C3*'Statement Q'!J141</f>
-        <v>145325.4</v>
+        <v>142172.41500000001</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="C14" s="163">
         <f>C12+C13</f>
-        <v>148320.4</v>
+        <v>145167.41500000001</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -24425,7 +24425,7 @@
       </c>
       <c r="C70" s="132">
         <f>(C69-Overview!C3)/Overview!C3</f>
-        <v>0.25274556278930865</v>
+        <v>0.28052794215095367</v>
       </c>
       <c r="E70" s="107"/>
     </row>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="C80" s="132">
         <f>(C79-Overview!C3)/Overview!C3</f>
-        <v>-0.13111463016620406</v>
+        <v>-0.11184519215457997</v>
       </c>
     </row>
   </sheetData>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DE208B-6276-6640-9F75-46C6014A2BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3402EBFB-70AB-0546-96A4-C320A44F2876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1740,6 +1740,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
       <sheetName val="1. List_AutomaticData"/>
@@ -1748,7 +1751,7 @@
       <sheetData sheetId="0">
         <row r="8">
           <cell r="C8">
-            <v>133.245</v>
+            <v>150.53</v>
           </cell>
         </row>
       </sheetData>
@@ -2225,7 +2228,7 @@
       </c>
       <c r="C3" s="38">
         <f>[1]Sheet1!$C$8</f>
-        <v>133.245</v>
+        <v>150.53</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -2245,7 +2248,7 @@
       </c>
       <c r="C9" s="159">
         <f>C3/'Statement Q'!N27</f>
-        <v>27.139510484622555</v>
+        <v>30.660141192917056</v>
       </c>
       <c r="E9" s="159"/>
     </row>
@@ -2255,7 +2258,7 @@
       </c>
       <c r="C10" s="159">
         <f>C3/Statements!W20</f>
-        <v>13.021237144517976</v>
+        <v>14.710396843140762</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2264,7 +2267,7 @@
       </c>
       <c r="C12" s="163">
         <f>C3*'Statement Q'!J141</f>
-        <v>142172.41500000001</v>
+        <v>160615.51</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2282,7 +2285,7 @@
       </c>
       <c r="C14" s="163">
         <f>C12+C13</f>
-        <v>145167.41500000001</v>
+        <v>163610.51</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -24425,7 +24428,7 @@
       </c>
       <c r="C70" s="132">
         <f>(C69-Overview!C3)/Overview!C3</f>
-        <v>0.28052794215095367</v>
+        <v>0.13348798014949725</v>
       </c>
       <c r="E70" s="107"/>
     </row>
@@ -24506,7 +24509,7 @@
       </c>
       <c r="C80" s="132">
         <f>(C79-Overview!C3)/Overview!C3</f>
-        <v>-0.11184519215457997</v>
+        <v>-0.21382988526298416</v>
       </c>
     </row>
   </sheetData>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3402EBFB-70AB-0546-96A4-C320A44F2876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFB08C0-8ACE-5942-B7A8-F3FBDB9F01DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1693,15 +1693,6 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="1" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1712,6 +1703,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1751,7 +1751,7 @@
       <sheetData sheetId="0">
         <row r="8">
           <cell r="C8">
-            <v>150.53</v>
+            <v>185.85</v>
           </cell>
         </row>
       </sheetData>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C3" s="38">
         <f>[1]Sheet1!$C$8</f>
-        <v>150.53</v>
+        <v>185.85</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="C9" s="159">
         <f>C3/'Statement Q'!N27</f>
-        <v>30.660141192917056</v>
+        <v>37.854163560111836</v>
       </c>
       <c r="E9" s="159"/>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C10" s="159">
         <f>C3/Statements!W20</f>
-        <v>14.710396843140762</v>
+        <v>18.162009255947055</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C12" s="163">
         <f>C3*'Statement Q'!J141</f>
-        <v>160615.51</v>
+        <v>198301.94999999998</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="C14" s="163">
         <f>C12+C13</f>
-        <v>163610.51</v>
+        <v>201296.94999999998</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -8654,11 +8654,11 @@
         <v>156</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="165" t="s">
+      <c r="P4" s="169" t="s">
         <v>157</v>
       </c>
-      <c r="Q4" s="166"/>
-      <c r="R4" s="167"/>
+      <c r="Q4" s="170"/>
+      <c r="R4" s="171"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -21514,36 +21514,36 @@
   <sheetData>
     <row r="5" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B5" s="93"/>
-      <c r="C5" s="168" t="s">
+      <c r="C5" s="165" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="168"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="169"/>
-      <c r="H5" s="170" t="s">
+      <c r="D5" s="165"/>
+      <c r="E5" s="165"/>
+      <c r="F5" s="165"/>
+      <c r="G5" s="166"/>
+      <c r="H5" s="167" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="168"/>
-      <c r="J5" s="168"/>
-      <c r="K5" s="168"/>
-      <c r="L5" s="168"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="165"/>
+      <c r="K5" s="165"/>
+      <c r="L5" s="165"/>
       <c r="N5" s="93"/>
-      <c r="O5" s="168" t="s">
+      <c r="O5" s="165" t="s">
         <v>178</v>
       </c>
-      <c r="P5" s="168"/>
-      <c r="Q5" s="168"/>
-      <c r="R5" s="168"/>
-      <c r="S5" s="168"/>
-      <c r="T5" s="168"/>
-      <c r="U5" s="168"/>
-      <c r="V5" s="168"/>
-      <c r="W5" s="171" t="s">
+      <c r="P5" s="165"/>
+      <c r="Q5" s="165"/>
+      <c r="R5" s="165"/>
+      <c r="S5" s="165"/>
+      <c r="T5" s="165"/>
+      <c r="U5" s="165"/>
+      <c r="V5" s="165"/>
+      <c r="W5" s="168" t="s">
         <v>179</v>
       </c>
-      <c r="X5" s="171"/>
-      <c r="Y5" s="171"/>
+      <c r="X5" s="168"/>
+      <c r="Y5" s="168"/>
       <c r="Z5" s="135"/>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.2">
@@ -24428,7 +24428,7 @@
       </c>
       <c r="C70" s="132">
         <f>(C69-Overview!C3)/Overview!C3</f>
-        <v>0.13348798014949725</v>
+        <v>-8.1926577068045042E-2</v>
       </c>
       <c r="E70" s="107"/>
     </row>
@@ -24509,7 +24509,7 @@
       </c>
       <c r="C80" s="132">
         <f>(C79-Overview!C3)/Overview!C3</f>
-        <v>-0.21382988526298416</v>
+        <v>-0.36323816318879204</v>
       </c>
     </row>
   </sheetData>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B7FB4F-CB29-2B48-9194-B6A81122EB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A143A51A-F17C-9A4A-9468-2622C6E64C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1753,7 +1753,7 @@
       <sheetData sheetId="0">
         <row r="8">
           <cell r="C8">
-            <v>177.035</v>
+            <v>192.66200000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C3" s="38">
         <f>[1]Sheet1!$C$8</f>
-        <v>177.035</v>
+        <v>192.66200000000001</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="C9" s="159">
         <f>C3/'Statement Q'!N27</f>
-        <v>19.303826463771038</v>
+        <v>21.007788370452484</v>
       </c>
       <c r="E9" s="159"/>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C10" s="159">
         <f>C3/Statements!W20</f>
-        <v>19.922191367654705</v>
+        <v>21.68073676547062</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C12" s="162">
         <f>C3*'Statement Q'!J141</f>
-        <v>186594.88999999998</v>
+        <v>203065.74799999999</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="C14" s="162">
         <f>C12+C13</f>
-        <v>192065.88999999998</v>
+        <v>208536.74799999999</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="C70" s="132">
         <f>(C69-Overview!C3)/Overview!C3</f>
-        <v>0.12720570895112801</v>
+        <v>3.5776970467258383E-2</v>
       </c>
       <c r="E70" s="107"/>
     </row>
@@ -24510,7 +24510,7 @@
       </c>
       <c r="C80" s="132">
         <f>(C79-Overview!C3)/Overview!C3</f>
-        <v>-1.7169275371822862E-2</v>
+        <v>-9.6887620109054551E-2</v>
       </c>
     </row>
   </sheetData>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FC421B-7C2C-D849-9FE5-A7D79D457E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED3FD35-8126-EE49-BDF8-166D16C43CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="14" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2404,6 +2404,24 @@
     <xf numFmtId="166" fontId="0" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="12" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="12" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2414,24 +2432,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2547,15 +2547,15 @@
       <sheetData sheetId="0">
         <row r="8">
           <cell r="C8">
-            <v>219.09</v>
+            <v>201.79</v>
           </cell>
           <cell r="F8">
-            <v>1.5152000000000001</v>
+            <v>1.5168999999999999</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>43.64</v>
+            <v>44.81</v>
           </cell>
         </row>
       </sheetData>
@@ -3114,8 +3114,8 @@
         <v>153</v>
       </c>
       <c r="C3" s="38">
-        <f ca="1">[1]Sheet1!$C$8</f>
-        <v>219.09</v>
+        <f>[1]Sheet1!$C$8</f>
+        <v>201.79</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -3142,8 +3142,8 @@
         <v>234</v>
       </c>
       <c r="C11" s="159">
-        <f ca="1">C3/'Statement Q'!N27</f>
-        <v>23.889487050287212</v>
+        <f>C3/'Statement Q'!N27</f>
+        <v>22.00310188451073</v>
       </c>
       <c r="E11" s="159"/>
     </row>
@@ -3152,8 +3152,8 @@
         <v>235</v>
       </c>
       <c r="C12" s="159">
-        <f ca="1">C3/Statements!W20</f>
-        <v>24.654745709828394</v>
+        <f>C3/Statements!W20</f>
+        <v>22.707933437337491</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -3161,8 +3161,8 @@
         <v>266</v>
       </c>
       <c r="C13" s="165">
-        <f ca="1">C3/(Statements!W5/Statements!W19)</f>
-        <v>5.3287636559816569</v>
+        <f>C3/(Statements!W5/Statements!W19)</f>
+        <v>4.9079885806770669</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -3170,8 +3170,8 @@
         <v>257</v>
       </c>
       <c r="C15" s="162">
-        <f ca="1">C3*'Statement Q'!J141</f>
-        <v>230920.86000000002</v>
+        <f>C3*'Statement Q'!J141</f>
+        <v>212686.66</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -3188,8 +3188,8 @@
         <v>259</v>
       </c>
       <c r="C17" s="162">
-        <f ca="1">C15+C16</f>
-        <v>236391.86000000002</v>
+        <f>C15+C16</f>
+        <v>218157.66</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -3434,60 +3434,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="S2" s="245"/>
-      <c r="T2" s="245"/>
-      <c r="U2" s="245"/>
-      <c r="V2" s="245"/>
-      <c r="W2" s="245"/>
-      <c r="X2" s="245"/>
-      <c r="Y2" s="245"/>
-      <c r="Z2" s="245"/>
-      <c r="AA2" s="245"/>
-      <c r="AB2" s="245"/>
-      <c r="AC2" s="245"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="S2" s="251"/>
+      <c r="T2" s="251"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="251"/>
+      <c r="X2" s="251"/>
+      <c r="Y2" s="251"/>
+      <c r="Z2" s="251"/>
+      <c r="AA2" s="251"/>
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="251"/>
       <c r="AE2" s="186"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="245" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="S4" s="245"/>
-      <c r="T4" s="245"/>
-      <c r="U4" s="245"/>
-      <c r="V4" s="245"/>
-      <c r="W4" s="245"/>
-      <c r="X4" s="245"/>
-      <c r="Y4" s="245"/>
-      <c r="Z4" s="245"/>
-      <c r="AA4" s="245"/>
-      <c r="AB4" s="245"/>
-      <c r="AC4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="S4" s="251"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
+      <c r="AA4" s="251"/>
+      <c r="AB4" s="251"/>
+      <c r="AC4" s="251"/>
       <c r="AE4" s="187"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3974,18 +3974,18 @@
       <c r="AE12" s="147"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C15" s="246" t="s">
+      <c r="C15" s="245" t="s">
         <v>319</v>
       </c>
-      <c r="D15" s="246"/>
-      <c r="E15" s="246"/>
-      <c r="F15" s="246"/>
-      <c r="G15" s="246"/>
-      <c r="H15" s="246"/>
-      <c r="I15" s="246"/>
-      <c r="J15" s="246"/>
-      <c r="K15" s="246"/>
-      <c r="L15" s="246"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="245"/>
+      <c r="H15" s="245"/>
+      <c r="I15" s="245"/>
+      <c r="J15" s="245"/>
+      <c r="K15" s="245"/>
+      <c r="L15" s="245"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C16" s="66">
@@ -4070,18 +4070,18 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C20" s="246" t="s">
+      <c r="C20" s="245" t="s">
         <v>320</v>
       </c>
-      <c r="D20" s="246"/>
-      <c r="E20" s="246"/>
-      <c r="F20" s="246"/>
-      <c r="G20" s="246"/>
-      <c r="H20" s="246"/>
-      <c r="I20" s="246"/>
-      <c r="J20" s="246"/>
-      <c r="K20" s="246"/>
-      <c r="L20" s="246"/>
+      <c r="D20" s="245"/>
+      <c r="E20" s="245"/>
+      <c r="F20" s="245"/>
+      <c r="G20" s="245"/>
+      <c r="H20" s="245"/>
+      <c r="I20" s="245"/>
+      <c r="J20" s="245"/>
+      <c r="K20" s="245"/>
+      <c r="L20" s="245"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -4273,18 +4273,18 @@
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="246" t="s">
+      <c r="C27" s="245" t="s">
         <v>323</v>
       </c>
-      <c r="D27" s="246"/>
-      <c r="E27" s="246"/>
-      <c r="F27" s="246"/>
-      <c r="G27" s="246"/>
-      <c r="H27" s="246"/>
-      <c r="I27" s="246"/>
-      <c r="J27" s="246"/>
-      <c r="K27" s="246"/>
-      <c r="L27" s="246"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="245"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
+      <c r="K27" s="245"/>
+      <c r="L27" s="245"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
@@ -4491,10 +4491,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="248" t="s">
         <v>326</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="248"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4510,8 +4510,8 @@
         <v>153</v>
       </c>
       <c r="C6" s="209">
-        <f ca="1">Overview!C3</f>
-        <v>219.09</v>
+        <f>Overview!C3</f>
+        <v>201.79</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4519,8 +4519,8 @@
         <v>274</v>
       </c>
       <c r="C7" s="210">
-        <f ca="1">C5*C6</f>
-        <v>230920.86000000002</v>
+        <f>C5*C6</f>
+        <v>212686.66</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4537,8 +4537,8 @@
         <v>328</v>
       </c>
       <c r="C9" s="211">
-        <f ca="1">[1]Sheet1!$C$10/1000</f>
-        <v>4.3639999999999998E-2</v>
+        <f>[1]Sheet1!$C$10/1000</f>
+        <v>4.4810000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4546,8 +4546,8 @@
         <v>329</v>
       </c>
       <c r="C10" s="209">
-        <f ca="1">[1]Sheet1!$F$8</f>
-        <v>1.5152000000000001</v>
+        <f>[1]Sheet1!$F$8</f>
+        <v>1.5168999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4576,18 +4576,18 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="248" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="242"/>
+      <c r="C15" s="248"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>333</v>
       </c>
       <c r="C16" s="140">
-        <f ca="1">C8/(C8+C7)</f>
-        <v>6.2025048371007759E-2</v>
+        <f>C8/(C8+C7)</f>
+        <v>6.6986417505853962E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4595,8 +4595,8 @@
         <v>334</v>
       </c>
       <c r="C17" s="140">
-        <f ca="1">C7/(C8+C7)</f>
-        <v>0.93797495162899225</v>
+        <f>C7/(C8+C7)</f>
+        <v>0.93301358249414601</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4613,8 +4613,8 @@
         <v>336</v>
       </c>
       <c r="C19" s="140">
-        <f ca="1">C9+C10*C11</f>
-        <v>0.11940000000000001</v>
+        <f>C9+C10*C11</f>
+        <v>0.120655</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4622,8 +4622,8 @@
         <v>325</v>
       </c>
       <c r="C20" s="140">
-        <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11464019778800887</v>
+        <f>(C17*C19)+(C16*C18)</f>
+        <v>0.11543039436663093</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4677,60 +4677,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="167"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="243"/>
-      <c r="H3" s="244" t="s">
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="245"/>
-      <c r="R3" s="245"/>
-      <c r="S3" s="245"/>
-      <c r="T3" s="245"/>
-      <c r="U3" s="245"/>
-      <c r="V3" s="245"/>
-      <c r="W3" s="245"/>
-      <c r="X3" s="245"/>
-      <c r="Y3" s="245"/>
-      <c r="Z3" s="245"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="186"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="172"/>
       <c r="B5" s="173"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="245" t="s">
         <v>339</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="245"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="245"/>
-      <c r="U5" s="245"/>
-      <c r="V5" s="245"/>
-      <c r="W5" s="245"/>
-      <c r="X5" s="245"/>
-      <c r="Y5" s="245"/>
-      <c r="Z5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="187"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4882,8 +4882,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="143">
-        <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>144642.58832036113</v>
+        <f>L7*(1+C14)/(C15-C14)</f>
+        <v>143444.89780286545</v>
       </c>
       <c r="N8" s="134"/>
       <c r="O8" s="7"/>
@@ -4936,24 +4936,24 @@
       <c r="F10" s="212"/>
       <c r="G10" s="213"/>
       <c r="H10" s="143">
-        <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>9280.4004770962238</v>
+        <f>H7/(1+$C$15)^H9</f>
+        <v>9273.8260276798555</v>
       </c>
       <c r="I10" s="143">
-        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>8252.0700278921486</v>
+        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
+        <v>8240.3822564128714</v>
       </c>
       <c r="J10" s="143">
-        <f t="shared" ca="1" si="0"/>
-        <v>7767.3866373982864</v>
+        <f t="shared" si="0"/>
+        <v>7750.8905424256318</v>
       </c>
       <c r="K10" s="143">
-        <f t="shared" ca="1" si="0"/>
-        <v>7344.6968741967612</v>
+        <f t="shared" si="0"/>
+        <v>7323.9063703244765</v>
       </c>
       <c r="L10" s="143">
-        <f t="shared" ca="1" si="0"/>
-        <v>7800.0636455013946</v>
+        <f t="shared" si="0"/>
+        <v>7772.4740398567101</v>
       </c>
       <c r="N10" s="134"/>
     </row>
@@ -4971,15 +4971,15 @@
       <c r="J11" s="212"/>
       <c r="K11" s="212"/>
       <c r="L11" s="143">
-        <f ca="1">L8/(1+C15)^L9</f>
-        <v>84066.444326677796</v>
+        <f>L8/(1+C15)^L9</f>
+        <v>83075.455920215667</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="242" t="s">
+      <c r="B13" s="248" t="s">
         <v>344</v>
       </c>
-      <c r="C13" s="242"/>
+      <c r="C13" s="248"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4994,23 +4994,23 @@
         <v>325</v>
       </c>
       <c r="C15" s="160">
-        <f ca="1">WACC!C20</f>
-        <v>0.11464019778800887</v>
+        <f>WACC!C20</f>
+        <v>0.11543039436663093</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="242" t="s">
+      <c r="B18" s="248" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="242"/>
+      <c r="C18" s="248"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>346</v>
       </c>
       <c r="C19" s="147">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>40444.617662084813</v>
+        <f>SUM(H10:L10)</f>
+        <v>40361.479236699539</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -5018,8 +5018,8 @@
         <v>343</v>
       </c>
       <c r="C20" s="147">
-        <f ca="1">L11</f>
-        <v>84066.444326677796</v>
+        <f>L11</f>
+        <v>83075.455920215667</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -5027,8 +5027,8 @@
         <v>347</v>
       </c>
       <c r="C21" s="178">
-        <f ca="1">C19+C20</f>
-        <v>124511.06198876261</v>
+        <f>C19+C20</f>
+        <v>123436.93515691521</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -5054,8 +5054,8 @@
         <v>350</v>
       </c>
       <c r="C24" s="178">
-        <f ca="1">C21+C22-C23</f>
-        <v>119040.06198876261</v>
+        <f>C21+C22-C23</f>
+        <v>117965.93515691522</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -5072,8 +5072,8 @@
         <v>351</v>
       </c>
       <c r="C26" s="216">
-        <f ca="1">C24/C25</f>
-        <v>112.94123528345598</v>
+        <f>C24/C25</f>
+        <v>111.92213961756663</v>
       </c>
     </row>
   </sheetData>
@@ -5116,37 +5116,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="245" t="s">
         <v>353</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -5335,18 +5335,18 @@
       <c r="N9" s="134"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="246" t="s">
+      <c r="C10" s="245" t="s">
         <v>283</v>
       </c>
-      <c r="D10" s="246"/>
-      <c r="E10" s="246"/>
-      <c r="F10" s="246"/>
-      <c r="G10" s="246"/>
-      <c r="H10" s="246"/>
-      <c r="I10" s="246"/>
-      <c r="J10" s="246"/>
-      <c r="K10" s="246"/>
-      <c r="L10" s="246"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="245"/>
+      <c r="G10" s="245"/>
+      <c r="H10" s="245"/>
+      <c r="I10" s="245"/>
+      <c r="J10" s="245"/>
+      <c r="K10" s="245"/>
+      <c r="L10" s="245"/>
       <c r="N10" s="134"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5528,18 +5528,18 @@
       <c r="N15" s="134"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="246" t="s">
+      <c r="C16" s="245" t="s">
         <v>355</v>
       </c>
-      <c r="D16" s="246"/>
-      <c r="E16" s="246"/>
-      <c r="F16" s="246"/>
-      <c r="G16" s="246"/>
-      <c r="H16" s="246"/>
-      <c r="I16" s="246"/>
-      <c r="J16" s="246"/>
-      <c r="K16" s="246"/>
-      <c r="L16" s="246"/>
+      <c r="D16" s="245"/>
+      <c r="E16" s="245"/>
+      <c r="F16" s="245"/>
+      <c r="G16" s="245"/>
+      <c r="H16" s="245"/>
+      <c r="I16" s="245"/>
+      <c r="J16" s="245"/>
+      <c r="K16" s="245"/>
+      <c r="L16" s="245"/>
       <c r="N16" s="134"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5673,18 +5673,18 @@
       <c r="N20" s="134"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="246" t="s">
+      <c r="C21" s="245" t="s">
         <v>356</v>
       </c>
-      <c r="D21" s="246"/>
-      <c r="E21" s="246"/>
-      <c r="F21" s="246"/>
-      <c r="G21" s="246"/>
-      <c r="H21" s="246"/>
-      <c r="I21" s="246"/>
-      <c r="J21" s="246"/>
-      <c r="K21" s="246"/>
-      <c r="L21" s="246"/>
+      <c r="D21" s="245"/>
+      <c r="E21" s="245"/>
+      <c r="F21" s="245"/>
+      <c r="G21" s="245"/>
+      <c r="H21" s="245"/>
+      <c r="I21" s="245"/>
+      <c r="J21" s="245"/>
+      <c r="K21" s="245"/>
+      <c r="L21" s="245"/>
       <c r="N21" s="134"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5768,18 +5768,18 @@
       <c r="N25" s="134"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="246" t="s">
+      <c r="C26" s="245" t="s">
         <v>357</v>
       </c>
-      <c r="D26" s="246"/>
-      <c r="E26" s="246"/>
-      <c r="F26" s="246"/>
-      <c r="G26" s="246"/>
-      <c r="H26" s="246"/>
-      <c r="I26" s="246"/>
-      <c r="J26" s="246"/>
-      <c r="K26" s="246"/>
-      <c r="L26" s="246"/>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+      <c r="K26" s="245"/>
+      <c r="L26" s="245"/>
       <c r="N26" s="134"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -6049,10 +6049,10 @@
       <c r="N36" s="134"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="242" t="s">
+      <c r="B37" s="248" t="s">
         <v>361</v>
       </c>
-      <c r="C37" s="242"/>
+      <c r="C37" s="248"/>
       <c r="N37" s="134"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -6069,8 +6069,8 @@
         <v>325</v>
       </c>
       <c r="C39" s="226">
-        <f ca="1">WACC!C20</f>
-        <v>0.11464019778800887</v>
+        <f>WACC!C20</f>
+        <v>0.11543039436663093</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -6113,15 +6113,15 @@
         <v>365</v>
       </c>
       <c r="C44" s="216">
-        <f ca="1">C43/(1+C48)^5</f>
-        <v>139.6718871329802</v>
+        <f>C43/(1+C48)^5</f>
+        <v>139.17785369161589</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="242" t="s">
+      <c r="B46" s="248" t="s">
         <v>213</v>
       </c>
-      <c r="C46" s="242"/>
+      <c r="C46" s="248"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -6137,8 +6137,8 @@
         <v>325</v>
       </c>
       <c r="C48" s="226">
-        <f ca="1">WACC!C20</f>
-        <v>0.11464019778800887</v>
+        <f>WACC!C20</f>
+        <v>0.11543039436663093</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6172,15 +6172,15 @@
         <v>365</v>
       </c>
       <c r="C52" s="216">
-        <f ca="1">C51/(1+C48)^5</f>
-        <v>130.8750335048324</v>
+        <f>C51/(1+C48)^5</f>
+        <v>130.41211541502736</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="242" t="s">
+      <c r="B54" s="248" t="s">
         <v>367</v>
       </c>
-      <c r="C54" s="242"/>
+      <c r="C54" s="248"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -6196,8 +6196,8 @@
         <v>325</v>
       </c>
       <c r="C56" s="226">
-        <f ca="1">WACC!C20</f>
-        <v>0.11464019778800887</v>
+        <f>WACC!C20</f>
+        <v>0.11543039436663093</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6240,8 +6240,8 @@
         <v>365</v>
       </c>
       <c r="C61" s="216">
-        <f ca="1">C60/(1+C56)^5</f>
-        <v>135.08163706882186</v>
+        <f>C60/(1+C56)^5</f>
+        <v>134.60383980126792</v>
       </c>
     </row>
   </sheetData>
@@ -6290,10 +6290,10 @@
       <c r="N3" s="134"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="248" t="s">
         <v>371</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="248"/>
       <c r="N4" s="134"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6301,8 +6301,8 @@
         <v>372</v>
       </c>
       <c r="C5" s="228">
-        <f ca="1">DCF!C26</f>
-        <v>112.94123528345598</v>
+        <f>DCF!C26</f>
+        <v>111.92213961756663</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6310,8 +6310,8 @@
         <v>373</v>
       </c>
       <c r="C6" s="228">
-        <f ca="1">Multiples!C44</f>
-        <v>139.6718871329802</v>
+        <f>Multiples!C44</f>
+        <v>139.17785369161589</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6319,8 +6319,8 @@
         <v>374</v>
       </c>
       <c r="C7" s="228">
-        <f ca="1">Multiples!C52</f>
-        <v>130.8750335048324</v>
+        <f>Multiples!C52</f>
+        <v>130.41211541502736</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6328,8 +6328,8 @@
         <v>375</v>
       </c>
       <c r="C8" s="228">
-        <f ca="1">Multiples!C61</f>
-        <v>135.08163706882186</v>
+        <f>Multiples!C61</f>
+        <v>134.60383980126792</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6337,8 +6337,8 @@
         <v>376</v>
       </c>
       <c r="C9" s="216">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>129.64244824752262</v>
+        <f>AVERAGE(C5:C8)</f>
+        <v>129.02898713136946</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6346,8 +6346,8 @@
         <v>377</v>
       </c>
       <c r="C10" s="38">
-        <f ca="1">Overview!C3</f>
-        <v>219.09</v>
+        <f>Overview!C3</f>
+        <v>201.79</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6355,8 +6355,8 @@
         <v>378</v>
       </c>
       <c r="C11" s="122">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>-0.40826852778528178</v>
+        <f>(C9-C10)/C10</f>
+        <v>-0.36057789220789205</v>
       </c>
     </row>
   </sheetData>
@@ -6400,60 +6400,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="167"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="243"/>
-      <c r="H3" s="244" t="s">
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="245"/>
-      <c r="R3" s="245"/>
-      <c r="S3" s="245"/>
-      <c r="T3" s="245"/>
-      <c r="U3" s="245"/>
-      <c r="V3" s="245"/>
-      <c r="W3" s="245"/>
-      <c r="X3" s="245"/>
-      <c r="Y3" s="245"/>
-      <c r="Z3" s="245"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="186"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="172"/>
       <c r="B5" s="173"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="245" t="s">
         <v>339</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="245"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="245"/>
-      <c r="U5" s="245"/>
-      <c r="V5" s="245"/>
-      <c r="W5" s="245"/>
-      <c r="X5" s="245"/>
-      <c r="Y5" s="245"/>
-      <c r="Z5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="187"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6540,23 +6540,23 @@
       </c>
       <c r="H7" s="143">
         <f>G7*(1+$C$17)</f>
-        <v>8423.2671708126036</v>
+        <v>8628.8646683250408</v>
       </c>
       <c r="I7" s="143">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>11388.25721493864</v>
+        <v>11950.977565630181</v>
       </c>
       <c r="J7" s="143">
         <f t="shared" si="0"/>
-        <v>15396.923754597039</v>
+        <v>16552.103928397799</v>
       </c>
       <c r="K7" s="143">
         <f t="shared" si="0"/>
-        <v>20816.640916215194</v>
+        <v>22924.663940830953</v>
       </c>
       <c r="L7" s="143">
         <f t="shared" si="0"/>
-        <v>28144.098518722938</v>
+        <v>31750.659558050869</v>
       </c>
       <c r="N7" s="134"/>
       <c r="O7" s="7"/>
@@ -6587,8 +6587,8 @@
       <c r="J8" s="212"/>
       <c r="K8" s="212"/>
       <c r="L8" s="143">
-        <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>303327.56228384213</v>
+        <f>L7*(1+C20)/(C21-C20)</f>
+        <v>339364.33946600312</v>
       </c>
       <c r="N8" s="134"/>
       <c r="O8" s="7"/>
@@ -6641,24 +6641,24 @@
       <c r="F10" s="212"/>
       <c r="G10" s="213"/>
       <c r="H10" s="143">
-        <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7556.9382725730538</v>
+        <f>H7/(1+$C$21)^H9</f>
+        <v>7735.9059892076239</v>
       </c>
       <c r="I10" s="143">
-        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>9166.1691053258746</v>
+        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
+        <v>9605.4669562203962</v>
       </c>
       <c r="J10" s="143">
-        <f t="shared" ca="1" si="1"/>
-        <v>11118.081561201254</v>
+        <f t="shared" si="1"/>
+        <v>11926.850659219617</v>
       </c>
       <c r="K10" s="143">
-        <f t="shared" ca="1" si="1"/>
-        <v>13485.648822439949</v>
+        <f t="shared" si="1"/>
+        <v>14809.250533646155</v>
       </c>
       <c r="L10" s="143">
-        <f t="shared" ca="1" si="1"/>
-        <v>16357.383525303674</v>
+        <f t="shared" si="1"/>
+        <v>18388.24913924501</v>
       </c>
       <c r="N10" s="134"/>
     </row>
@@ -6676,8 +6676,8 @@
       <c r="J11" s="212"/>
       <c r="K11" s="212"/>
       <c r="L11" s="143">
-        <f ca="1">L8/(1+C21)^L9</f>
-        <v>176294.33988697472</v>
+        <f>L8/(1+C21)^L9</f>
+        <v>196541.30370636209</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6692,8 +6692,8 @@
         <v>381</v>
       </c>
       <c r="C15" s="230">
-        <f ca="1">Overview!C3</f>
-        <v>219.09</v>
+        <f>Overview!C3</f>
+        <v>201.79</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6701,8 +6701,8 @@
         <v>382</v>
       </c>
       <c r="C16" s="230">
-        <f ca="1">C36</f>
-        <v>216.80034266965706</v>
+        <f>C36</f>
+        <v>240.5465151649914</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6710,7 +6710,7 @@
         <v>383</v>
       </c>
       <c r="C17" s="231">
-        <v>0.35199999999999998</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="E17" s="254" t="s">
         <v>384</v>
@@ -6740,8 +6740,8 @@
         <v>325</v>
       </c>
       <c r="C21" s="233">
-        <f ca="1">WACC!C20</f>
-        <v>0.11464019778800887</v>
+        <f>WACC!C20</f>
+        <v>0.11543039436663093</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6758,8 +6758,8 @@
         <v>257</v>
       </c>
       <c r="C23" s="234">
-        <f ca="1">C15*C22</f>
-        <v>230920.86000000002</v>
+        <f>C15*C22</f>
+        <v>212686.66</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6785,8 +6785,8 @@
         <v>385</v>
       </c>
       <c r="C26" s="235">
-        <f ca="1">C23+C25-C24</f>
-        <v>236391.86000000002</v>
+        <f>C23+C25-C24</f>
+        <v>218157.66</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6801,8 +6801,8 @@
         <v>346</v>
       </c>
       <c r="C29" s="234">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>57684.221286843807</v>
+        <f>SUM(H10:L10)</f>
+        <v>62465.723277538804</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6810,8 +6810,8 @@
         <v>343</v>
       </c>
       <c r="C30" s="234">
-        <f ca="1">L11</f>
-        <v>176294.33988697472</v>
+        <f>L11</f>
+        <v>196541.30370636209</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6819,8 +6819,8 @@
         <v>347</v>
       </c>
       <c r="C31" s="237">
-        <f ca="1">C29+C30</f>
-        <v>233978.56117381854</v>
+        <f>C29+C30</f>
+        <v>259007.0269839009</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6846,8 +6846,8 @@
         <v>350</v>
       </c>
       <c r="C34" s="237">
-        <f ca="1">C31+C32-C33</f>
-        <v>228507.56117381854</v>
+        <f>C31+C32-C33</f>
+        <v>253536.02698390093</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6864,23 +6864,23 @@
         <v>351</v>
       </c>
       <c r="C36" s="239">
-        <f ca="1">C34/C35</f>
-        <v>216.80034266965706</v>
+        <f>C34/C35</f>
+        <v>240.5465151649914</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="246" t="s">
+      <c r="C39" s="245" t="s">
         <v>386</v>
       </c>
-      <c r="D39" s="246"/>
-      <c r="E39" s="246"/>
-      <c r="F39" s="246"/>
-      <c r="G39" s="246"/>
-      <c r="H39" s="246"/>
-      <c r="I39" s="246"/>
-      <c r="J39" s="246"/>
-      <c r="K39" s="246"/>
-      <c r="L39" s="246"/>
+      <c r="D39" s="245"/>
+      <c r="E39" s="245"/>
+      <c r="F39" s="245"/>
+      <c r="G39" s="245"/>
+      <c r="H39" s="245"/>
+      <c r="I39" s="245"/>
+      <c r="J39" s="245"/>
+      <c r="K39" s="245"/>
+      <c r="L39" s="245"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="66">
@@ -6950,23 +6950,23 @@
       </c>
       <c r="H41" s="162">
         <f t="shared" si="2"/>
-        <v>8423.2671708126036</v>
+        <v>8628.8646683250408</v>
       </c>
       <c r="I41" s="162">
         <f t="shared" si="2"/>
-        <v>11388.25721493864</v>
+        <v>11950.977565630181</v>
       </c>
       <c r="J41" s="162">
         <f t="shared" si="2"/>
-        <v>15396.923754597039</v>
+        <v>16552.103928397799</v>
       </c>
       <c r="K41" s="162">
         <f t="shared" si="2"/>
-        <v>20816.640916215194</v>
+        <v>22924.663940830953</v>
       </c>
       <c r="L41" s="162">
         <f t="shared" si="2"/>
-        <v>28144.098518722938</v>
+        <v>31750.659558050869</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -6995,23 +6995,23 @@
       </c>
       <c r="H42" s="162">
         <f>H41/H43</f>
-        <v>9359.1857453473367</v>
+        <v>9587.6274092500444</v>
       </c>
       <c r="I42" s="162">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>12653.619127709599</v>
+        <v>13278.863961811312</v>
       </c>
       <c r="J42" s="162">
         <f t="shared" si="3"/>
-        <v>17107.693060663376</v>
+        <v>18391.226587108664</v>
       </c>
       <c r="K42" s="162">
         <f t="shared" si="3"/>
-        <v>23129.601018016881</v>
+        <v>25471.848823145501</v>
       </c>
       <c r="L42" s="162">
         <f t="shared" si="3"/>
-        <v>31271.220576358821</v>
+        <v>35278.510620056521</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -7080,23 +7080,23 @@
       </c>
       <c r="H44" s="162">
         <f>H41/H45</f>
-        <v>33693.068683250414</v>
+        <v>34515.458673300163</v>
       </c>
       <c r="I44" s="162">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>45553.028859754559</v>
+        <v>47803.910262520723</v>
       </c>
       <c r="J44" s="162">
         <f t="shared" si="5"/>
-        <v>61587.695018388156</v>
+        <v>66208.415713591196</v>
       </c>
       <c r="K44" s="162">
         <f t="shared" si="5"/>
-        <v>83266.563664860776</v>
+        <v>91698.655763323812</v>
       </c>
       <c r="L44" s="162">
         <f t="shared" si="5"/>
-        <v>112576.39407489175</v>
+        <v>127002.63823220348</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -7162,23 +7162,23 @@
       </c>
       <c r="H46" s="241">
         <f t="shared" si="7"/>
-        <v>0.35199999999999987</v>
+        <v>0.38499999999999979</v>
       </c>
       <c r="I46" s="241">
         <f t="shared" si="7"/>
-        <v>0.35199999999999987</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="J46" s="241">
         <f t="shared" si="7"/>
-        <v>0.35199999999999987</v>
+        <v>0.38499999999999979</v>
       </c>
       <c r="K46" s="241">
         <f t="shared" si="7"/>
-        <v>0.35199999999999987</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="L46" s="241">
         <f t="shared" si="7"/>
-        <v>0.35199999999999987</v>
+        <v>0.38500000000000001</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
@@ -7204,23 +7204,23 @@
       </c>
       <c r="H47" s="241">
         <f t="shared" si="7"/>
-        <v>-0.24247788382457813</v>
+        <v>-0.22398806885875799</v>
       </c>
       <c r="I47" s="241">
         <f t="shared" si="7"/>
-        <v>0.35199999999999987</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="J47" s="241">
         <f t="shared" si="7"/>
-        <v>0.35199999999999987</v>
+        <v>0.38499999999999979</v>
       </c>
       <c r="K47" s="241">
         <f t="shared" si="7"/>
-        <v>0.35199999999999987</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="L47" s="241">
         <f t="shared" si="7"/>
-        <v>0.35199999999999987</v>
+        <v>0.38500000000000001</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
@@ -7246,23 +7246,23 @@
       </c>
       <c r="H48" s="241">
         <f t="shared" si="8"/>
-        <v>-0.23915931977123983</v>
+        <v>-0.22058850435145505</v>
       </c>
       <c r="I48" s="241">
         <f t="shared" si="8"/>
-        <v>0.35199999999999987</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="J48" s="241">
         <f t="shared" si="8"/>
-        <v>0.35199999999999987</v>
+        <v>0.38499999999999979</v>
       </c>
       <c r="K48" s="241">
         <f t="shared" si="8"/>
-        <v>0.35199999999999987</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="L48" s="241">
         <f t="shared" si="8"/>
-        <v>0.35199999999999987</v>
+        <v>0.38500000000000001</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
@@ -7295,15 +7295,15 @@
       </c>
       <c r="I49" s="241">
         <f t="shared" si="9"/>
-        <v>0.27777777777777773</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="J49" s="241">
         <f t="shared" si="9"/>
-        <v>0.27777777777777779</v>
+        <v>0.27777777777777773</v>
       </c>
       <c r="K49" s="241">
         <f t="shared" si="9"/>
-        <v>0.27777777777777779</v>
+        <v>0.27777777777777773</v>
       </c>
       <c r="L49" s="241">
         <f t="shared" si="9"/>
@@ -7312,17 +7312,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7345,31 +7345,31 @@
   <sheetData>
     <row r="5" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B5" s="93"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="243"/>
-      <c r="H5" s="244" t="s">
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
       <c r="N5" s="93"/>
-      <c r="O5" s="242" t="s">
+      <c r="O5" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="P5" s="242"/>
-      <c r="Q5" s="242"/>
-      <c r="R5" s="242"/>
-      <c r="S5" s="242"/>
-      <c r="T5" s="242"/>
-      <c r="U5" s="242"/>
-      <c r="V5" s="242"/>
+      <c r="P5" s="248"/>
+      <c r="Q5" s="248"/>
+      <c r="R5" s="248"/>
+      <c r="S5" s="248"/>
+      <c r="T5" s="248"/>
+      <c r="U5" s="248"/>
+      <c r="V5" s="248"/>
       <c r="W5" s="255" t="s">
         <v>177</v>
       </c>
@@ -10250,8 +10250,8 @@
         <v>212</v>
       </c>
       <c r="C70" s="132">
-        <f ca="1">(C69-Overview!C3)/Overview!C3</f>
-        <v>-8.9164897146547364E-2</v>
+        <f>(C69-Overview!C3)/Overview!C3</f>
+        <v>-1.107655144376357E-2</v>
       </c>
       <c r="E70" s="107"/>
     </row>
@@ -10331,8 +10331,8 @@
         <v>212</v>
       </c>
       <c r="C80" s="132">
-        <f ca="1">(C79-Overview!C3)/Overview!C3</f>
-        <v>-0.20582665874960365</v>
+        <f>(C79-Overview!C3)/Overview!C3</f>
+        <v>-0.13774003996952602</v>
       </c>
     </row>
   </sheetData>
@@ -16599,11 +16599,11 @@
         <v>154</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="247" t="s">
+      <c r="P4" s="242" t="s">
         <v>155</v>
       </c>
-      <c r="Q4" s="248"/>
-      <c r="R4" s="249"/>
+      <c r="Q4" s="243"/>
+      <c r="R4" s="244"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -29506,36 +29506,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
       <c r="O2" s="120"/>
-      <c r="S2" s="242" t="s">
+      <c r="S2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242" t="s">
+      <c r="T2" s="248"/>
+      <c r="U2" s="248"/>
+      <c r="V2" s="248"/>
+      <c r="W2" s="248"/>
+      <c r="X2" s="248"/>
+      <c r="Y2" s="248"/>
+      <c r="Z2" s="248"/>
+      <c r="AA2" s="248" t="s">
         <v>177</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
+      <c r="AB2" s="248"/>
+      <c r="AC2" s="248"/>
       <c r="AE2" s="171" t="s">
         <v>154</v>
       </c>
@@ -29546,32 +29546,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
       <c r="O4" s="120"/>
-      <c r="S4" s="250" t="s">
+      <c r="S4" s="246" t="s">
         <v>178</v>
       </c>
-      <c r="T4" s="251"/>
-      <c r="U4" s="251"/>
-      <c r="V4" s="251"/>
-      <c r="W4" s="251"/>
-      <c r="X4" s="251"/>
-      <c r="Y4" s="251"/>
-      <c r="Z4" s="251"/>
-      <c r="AA4" s="251"/>
-      <c r="AB4" s="251"/>
-      <c r="AC4" s="251"/>
+      <c r="T4" s="247"/>
+      <c r="U4" s="247"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="247"/>
+      <c r="X4" s="247"/>
+      <c r="Y4" s="247"/>
+      <c r="Z4" s="247"/>
+      <c r="AA4" s="247"/>
+      <c r="AB4" s="247"/>
+      <c r="AC4" s="247"/>
       <c r="AE4" s="174" t="s">
         <v>285</v>
       </c>
@@ -30241,33 +30241,33 @@
       <c r="Q12" s="134"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="246" t="s">
+      <c r="C13" s="245" t="s">
         <v>283</v>
       </c>
-      <c r="D13" s="246"/>
-      <c r="E13" s="246"/>
-      <c r="F13" s="246"/>
-      <c r="G13" s="246"/>
-      <c r="H13" s="246"/>
-      <c r="I13" s="246"/>
-      <c r="J13" s="246"/>
-      <c r="K13" s="246"/>
-      <c r="L13" s="246"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
+      <c r="I13" s="245"/>
+      <c r="J13" s="245"/>
+      <c r="K13" s="245"/>
+      <c r="L13" s="245"/>
       <c r="O13" s="120"/>
       <c r="Q13" s="134"/>
-      <c r="S13" s="250" t="s">
+      <c r="S13" s="246" t="s">
         <v>283</v>
       </c>
-      <c r="T13" s="251"/>
-      <c r="U13" s="251"/>
-      <c r="V13" s="251"/>
-      <c r="W13" s="251"/>
-      <c r="X13" s="251"/>
-      <c r="Y13" s="251"/>
-      <c r="Z13" s="251"/>
-      <c r="AA13" s="251"/>
-      <c r="AB13" s="251"/>
-      <c r="AC13" s="251"/>
+      <c r="T13" s="247"/>
+      <c r="U13" s="247"/>
+      <c r="V13" s="247"/>
+      <c r="W13" s="247"/>
+      <c r="X13" s="247"/>
+      <c r="Y13" s="247"/>
+      <c r="Z13" s="247"/>
+      <c r="AA13" s="247"/>
+      <c r="AB13" s="247"/>
+      <c r="AC13" s="247"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
@@ -30889,35 +30889,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="244" t="s">
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="P2" s="242" t="s">
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="P2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242" t="s">
+      <c r="Q2" s="248"/>
+      <c r="R2" s="248"/>
+      <c r="S2" s="248"/>
+      <c r="T2" s="248"/>
+      <c r="U2" s="248"/>
+      <c r="V2" s="248"/>
+      <c r="W2" s="248"/>
+      <c r="X2" s="248" t="s">
         <v>177</v>
       </c>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
+      <c r="Y2" s="248"/>
+      <c r="Z2" s="248"/>
       <c r="AB2" s="171" t="s">
         <v>154</v>
       </c>
@@ -30926,31 +30926,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="P4" s="251" t="s">
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="P4" s="247" t="s">
         <v>178</v>
       </c>
-      <c r="Q4" s="251"/>
-      <c r="R4" s="251"/>
-      <c r="S4" s="251"/>
-      <c r="T4" s="251"/>
-      <c r="U4" s="251"/>
-      <c r="V4" s="251"/>
-      <c r="W4" s="251"/>
-      <c r="X4" s="251"/>
-      <c r="Y4" s="251"/>
-      <c r="Z4" s="251"/>
+      <c r="Q4" s="247"/>
+      <c r="R4" s="247"/>
+      <c r="S4" s="247"/>
+      <c r="T4" s="247"/>
+      <c r="U4" s="247"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="247"/>
+      <c r="X4" s="247"/>
+      <c r="Y4" s="247"/>
+      <c r="Z4" s="247"/>
       <c r="AB4" s="174" t="str">
         <f>Revenue!AE4</f>
         <v>Q4-Q1-Q2</v>
@@ -31153,32 +31153,32 @@
       <c r="N8" s="134"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="246" t="s">
+      <c r="C9" s="245" t="s">
         <v>287</v>
       </c>
-      <c r="D9" s="246"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="246"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="246"/>
-      <c r="K9" s="246"/>
-      <c r="L9" s="246"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="245"/>
+      <c r="G9" s="245"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="245"/>
+      <c r="J9" s="245"/>
+      <c r="K9" s="245"/>
+      <c r="L9" s="245"/>
       <c r="N9" s="134"/>
-      <c r="P9" s="251" t="s">
+      <c r="P9" s="247" t="s">
         <v>288</v>
       </c>
-      <c r="Q9" s="251"/>
-      <c r="R9" s="251"/>
-      <c r="S9" s="251"/>
-      <c r="T9" s="251"/>
-      <c r="U9" s="251"/>
-      <c r="V9" s="251"/>
-      <c r="W9" s="251"/>
-      <c r="X9" s="251"/>
-      <c r="Y9" s="251"/>
-      <c r="Z9" s="251"/>
+      <c r="Q9" s="247"/>
+      <c r="R9" s="247"/>
+      <c r="S9" s="247"/>
+      <c r="T9" s="247"/>
+      <c r="U9" s="247"/>
+      <c r="V9" s="247"/>
+      <c r="W9" s="247"/>
+      <c r="X9" s="247"/>
+      <c r="Y9" s="247"/>
+      <c r="Z9" s="247"/>
       <c r="AB9" s="174" t="str">
         <f>AB4</f>
         <v>Q4-Q1-Q2</v>
@@ -31652,31 +31652,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="246" t="s">
+      <c r="C17" s="245" t="s">
         <v>291</v>
       </c>
-      <c r="D17" s="246"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="246"/>
-      <c r="G17" s="246"/>
-      <c r="H17" s="246"/>
-      <c r="I17" s="246"/>
-      <c r="J17" s="246"/>
-      <c r="K17" s="246"/>
-      <c r="L17" s="246"/>
-      <c r="P17" s="251" t="s">
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
+      <c r="H17" s="245"/>
+      <c r="I17" s="245"/>
+      <c r="J17" s="245"/>
+      <c r="K17" s="245"/>
+      <c r="L17" s="245"/>
+      <c r="P17" s="247" t="s">
         <v>291</v>
       </c>
-      <c r="Q17" s="251"/>
-      <c r="R17" s="251"/>
-      <c r="S17" s="251"/>
-      <c r="T17" s="251"/>
-      <c r="U17" s="251"/>
-      <c r="V17" s="251"/>
-      <c r="W17" s="251"/>
-      <c r="X17" s="251"/>
-      <c r="Y17" s="251"/>
-      <c r="Z17" s="251"/>
+      <c r="Q17" s="247"/>
+      <c r="R17" s="247"/>
+      <c r="S17" s="247"/>
+      <c r="T17" s="247"/>
+      <c r="U17" s="247"/>
+      <c r="V17" s="247"/>
+      <c r="W17" s="247"/>
+      <c r="X17" s="247"/>
+      <c r="Y17" s="247"/>
+      <c r="Z17" s="247"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
@@ -32066,60 +32066,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="167"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="243"/>
-      <c r="H3" s="244" t="s">
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="245"/>
-      <c r="R3" s="245"/>
-      <c r="S3" s="245"/>
-      <c r="T3" s="245"/>
-      <c r="U3" s="245"/>
-      <c r="V3" s="245"/>
-      <c r="W3" s="245"/>
-      <c r="X3" s="245"/>
-      <c r="Y3" s="245"/>
-      <c r="Z3" s="245"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="186"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="172"/>
       <c r="B5" s="173"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="245"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="245"/>
-      <c r="U5" s="245"/>
-      <c r="V5" s="245"/>
-      <c r="W5" s="245"/>
-      <c r="X5" s="245"/>
-      <c r="Y5" s="245"/>
-      <c r="Z5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="187"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -32305,30 +32305,30 @@
       <c r="N10" s="134"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="246" t="s">
+      <c r="C11" s="245" t="s">
         <v>293</v>
       </c>
-      <c r="D11" s="246"/>
-      <c r="E11" s="246"/>
-      <c r="F11" s="246"/>
-      <c r="G11" s="246"/>
-      <c r="H11" s="246"/>
-      <c r="I11" s="246"/>
-      <c r="J11" s="246"/>
-      <c r="K11" s="246"/>
-      <c r="L11" s="246"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
       <c r="N11" s="134"/>
-      <c r="P11" s="245"/>
-      <c r="Q11" s="245"/>
-      <c r="R11" s="245"/>
-      <c r="S11" s="245"/>
-      <c r="T11" s="245"/>
-      <c r="U11" s="245"/>
-      <c r="V11" s="245"/>
-      <c r="W11" s="245"/>
-      <c r="X11" s="245"/>
-      <c r="Y11" s="245"/>
-      <c r="Z11" s="245"/>
+      <c r="P11" s="251"/>
+      <c r="Q11" s="251"/>
+      <c r="R11" s="251"/>
+      <c r="S11" s="251"/>
+      <c r="T11" s="251"/>
+      <c r="U11" s="251"/>
+      <c r="V11" s="251"/>
+      <c r="W11" s="251"/>
+      <c r="X11" s="251"/>
+      <c r="Y11" s="251"/>
+      <c r="Z11" s="251"/>
       <c r="AB11" s="187"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -32570,18 +32570,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="246" t="s">
+      <c r="C18" s="245" t="s">
         <v>298</v>
       </c>
-      <c r="D18" s="246"/>
-      <c r="E18" s="246"/>
-      <c r="F18" s="246"/>
-      <c r="G18" s="246"/>
-      <c r="H18" s="246"/>
-      <c r="I18" s="246"/>
-      <c r="J18" s="246"/>
-      <c r="K18" s="246"/>
-      <c r="L18" s="246"/>
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
+      <c r="G18" s="245"/>
+      <c r="H18" s="245"/>
+      <c r="I18" s="245"/>
+      <c r="J18" s="245"/>
+      <c r="K18" s="245"/>
+      <c r="L18" s="245"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -32794,23 +32794,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="245"/>
-      <c r="C25" s="245"/>
+      <c r="B25" s="251"/>
+      <c r="C25" s="251"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="186"/>
-      <c r="C26" s="246" t="s">
+      <c r="C26" s="245" t="s">
         <v>304</v>
       </c>
-      <c r="D26" s="246"/>
-      <c r="E26" s="246"/>
-      <c r="F26" s="246"/>
-      <c r="G26" s="246"/>
-      <c r="H26" s="246"/>
-      <c r="I26" s="246"/>
-      <c r="J26" s="246"/>
-      <c r="K26" s="246"/>
-      <c r="L26" s="246"/>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+      <c r="K26" s="245"/>
+      <c r="L26" s="245"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -33002,18 +33002,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="186"/>
-      <c r="C33" s="246" t="s">
+      <c r="C33" s="245" t="s">
         <v>308</v>
       </c>
-      <c r="D33" s="246"/>
-      <c r="E33" s="246"/>
-      <c r="F33" s="246"/>
-      <c r="G33" s="246"/>
-      <c r="H33" s="246"/>
-      <c r="I33" s="246"/>
-      <c r="J33" s="246"/>
-      <c r="K33" s="246"/>
-      <c r="L33" s="246"/>
+      <c r="D33" s="245"/>
+      <c r="E33" s="245"/>
+      <c r="F33" s="245"/>
+      <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
+      <c r="I33" s="245"/>
+      <c r="J33" s="245"/>
+      <c r="K33" s="245"/>
+      <c r="L33" s="245"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -33197,18 +33197,18 @@
       <c r="C39" s="202"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="246" t="s">
+      <c r="C40" s="245" t="s">
         <v>311</v>
       </c>
-      <c r="D40" s="246"/>
-      <c r="E40" s="246"/>
-      <c r="F40" s="246"/>
-      <c r="G40" s="246"/>
-      <c r="H40" s="246"/>
-      <c r="I40" s="246"/>
-      <c r="J40" s="246"/>
-      <c r="K40" s="246"/>
-      <c r="L40" s="246"/>
+      <c r="D40" s="245"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -33472,6 +33472,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -33479,12 +33485,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED3FD35-8126-EE49-BDF8-166D16C43CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0104743C-DFB4-4C48-9394-4BA9BC302284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="14" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2404,6 +2404,9 @@
     <xf numFmtId="166" fontId="0" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="12" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="12" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2420,9 +2423,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2547,15 +2547,15 @@
       <sheetData sheetId="0">
         <row r="8">
           <cell r="C8">
-            <v>201.79</v>
+            <v>228.99</v>
           </cell>
           <cell r="F8">
-            <v>1.5168999999999999</v>
+            <v>1.5985</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>44.81</v>
+            <v>44.53</v>
           </cell>
         </row>
       </sheetData>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C3" s="38">
         <f>[1]Sheet1!$C$8</f>
-        <v>201.79</v>
+        <v>228.99</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="C11" s="159">
         <f>C3/'Statement Q'!N27</f>
-        <v>22.00310188451073</v>
+        <v>24.968979139373175</v>
       </c>
       <c r="E11" s="159"/>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="C12" s="159">
         <f>C3/Statements!W20</f>
-        <v>22.707933437337491</v>
+        <v>25.76881747269891</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C13" s="165">
         <f>C3/(Statements!W5/Statements!W19)</f>
-        <v>4.9079885806770669</v>
+        <v>5.5695540169941111</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C15" s="162">
         <f>C3*'Statement Q'!J141</f>
-        <v>212686.66</v>
+        <v>241355.46000000002</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="C17" s="162">
         <f>C15+C16</f>
-        <v>218157.66</v>
+        <v>246826.46000000002</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -3434,20 +3434,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="S2" s="251"/>
       <c r="T2" s="251"/>
       <c r="U2" s="251"/>
@@ -3465,18 +3465,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="245" t="s">
+      <c r="C4" s="246" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
-      <c r="J4" s="245"/>
-      <c r="K4" s="245"/>
-      <c r="L4" s="245"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
       <c r="S4" s="251"/>
       <c r="T4" s="251"/>
       <c r="U4" s="251"/>
@@ -3974,18 +3974,18 @@
       <c r="AE12" s="147"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C15" s="245" t="s">
+      <c r="C15" s="246" t="s">
         <v>319</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="E15" s="245"/>
-      <c r="F15" s="245"/>
-      <c r="G15" s="245"/>
-      <c r="H15" s="245"/>
-      <c r="I15" s="245"/>
-      <c r="J15" s="245"/>
-      <c r="K15" s="245"/>
-      <c r="L15" s="245"/>
+      <c r="D15" s="246"/>
+      <c r="E15" s="246"/>
+      <c r="F15" s="246"/>
+      <c r="G15" s="246"/>
+      <c r="H15" s="246"/>
+      <c r="I15" s="246"/>
+      <c r="J15" s="246"/>
+      <c r="K15" s="246"/>
+      <c r="L15" s="246"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C16" s="66">
@@ -4070,18 +4070,18 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C20" s="245" t="s">
+      <c r="C20" s="246" t="s">
         <v>320</v>
       </c>
-      <c r="D20" s="245"/>
-      <c r="E20" s="245"/>
-      <c r="F20" s="245"/>
-      <c r="G20" s="245"/>
-      <c r="H20" s="245"/>
-      <c r="I20" s="245"/>
-      <c r="J20" s="245"/>
-      <c r="K20" s="245"/>
-      <c r="L20" s="245"/>
+      <c r="D20" s="246"/>
+      <c r="E20" s="246"/>
+      <c r="F20" s="246"/>
+      <c r="G20" s="246"/>
+      <c r="H20" s="246"/>
+      <c r="I20" s="246"/>
+      <c r="J20" s="246"/>
+      <c r="K20" s="246"/>
+      <c r="L20" s="246"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -4273,18 +4273,18 @@
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="245" t="s">
+      <c r="C27" s="246" t="s">
         <v>323</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="E27" s="245"/>
-      <c r="F27" s="245"/>
-      <c r="G27" s="245"/>
-      <c r="H27" s="245"/>
-      <c r="I27" s="245"/>
-      <c r="J27" s="245"/>
-      <c r="K27" s="245"/>
-      <c r="L27" s="245"/>
+      <c r="D27" s="246"/>
+      <c r="E27" s="246"/>
+      <c r="F27" s="246"/>
+      <c r="G27" s="246"/>
+      <c r="H27" s="246"/>
+      <c r="I27" s="246"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="246"/>
+      <c r="L27" s="246"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
@@ -4491,10 +4491,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="248" t="s">
+      <c r="B4" s="242" t="s">
         <v>326</v>
       </c>
-      <c r="C4" s="248"/>
+      <c r="C4" s="242"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C6" s="209">
         <f>Overview!C3</f>
-        <v>201.79</v>
+        <v>228.99</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C7" s="210">
         <f>C5*C6</f>
-        <v>212686.66</v>
+        <v>241355.46000000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C9" s="211">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.4810000000000003E-2</v>
+        <v>4.453E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C10" s="209">
         <f>[1]Sheet1!$F$8</f>
-        <v>1.5168999999999999</v>
+        <v>1.5985</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4576,10 +4576,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="248" t="s">
+      <c r="B15" s="242" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="248"/>
+      <c r="C15" s="242"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C16" s="140">
         <f>C8/(C8+C7)</f>
-        <v>6.6986417505853962E-2</v>
+        <v>5.9503059439231003E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="C17" s="140">
         <f>C7/(C8+C7)</f>
-        <v>0.93301358249414601</v>
+        <v>0.94049694056076905</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C19" s="140">
         <f>C9+C10*C11</f>
-        <v>0.120655</v>
+        <v>0.12445500000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="C20" s="140">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>0.11543039436663093</v>
+        <v>0.11958794725316811</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4677,20 +4677,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="167"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="248"/>
-      <c r="J3" s="248"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -4708,18 +4708,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="172"/>
       <c r="B5" s="173"/>
-      <c r="C5" s="245" t="s">
+      <c r="C5" s="246" t="s">
         <v>339</v>
       </c>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="245"/>
-      <c r="G5" s="245"/>
-      <c r="H5" s="245"/>
-      <c r="I5" s="245"/>
-      <c r="J5" s="245"/>
-      <c r="K5" s="245"/>
-      <c r="L5" s="245"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
       <c r="P5" s="251"/>
       <c r="Q5" s="251"/>
       <c r="R5" s="251"/>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="L8" s="143">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>143444.89780286545</v>
+        <v>137456.42464553402</v>
       </c>
       <c r="N8" s="134"/>
       <c r="O8" s="7"/>
@@ -4937,23 +4937,23 @@
       <c r="G10" s="213"/>
       <c r="H10" s="143">
         <f>H7/(1+$C$15)^H9</f>
-        <v>9273.8260276798555</v>
+        <v>9239.3879808384081</v>
       </c>
       <c r="I10" s="143">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>8240.3822564128714</v>
+        <v>8179.2951149238825</v>
       </c>
       <c r="J10" s="143">
         <f t="shared" si="0"/>
-        <v>7750.8905424256318</v>
+        <v>7664.8627675121143</v>
       </c>
       <c r="K10" s="143">
         <f t="shared" si="0"/>
-        <v>7323.9063703244765</v>
+        <v>7215.7225061695699</v>
       </c>
       <c r="L10" s="143">
         <f t="shared" si="0"/>
-        <v>7772.4740398567101</v>
+        <v>7629.2277496552952</v>
       </c>
       <c r="N10" s="134"/>
     </row>
@@ -4972,14 +4972,14 @@
       <c r="K11" s="212"/>
       <c r="L11" s="143">
         <f>L8/(1+C15)^L9</f>
-        <v>83075.455920215667</v>
+        <v>78140.101481013757</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="248" t="s">
+      <c r="B13" s="242" t="s">
         <v>344</v>
       </c>
-      <c r="C13" s="248"/>
+      <c r="C13" s="242"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4995,14 +4995,14 @@
       </c>
       <c r="C15" s="160">
         <f>WACC!C20</f>
-        <v>0.11543039436663093</v>
+        <v>0.11958794725316811</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="248" t="s">
+      <c r="B18" s="242" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="248"/>
+      <c r="C18" s="242"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="C19" s="147">
         <f>SUM(H10:L10)</f>
-        <v>40361.479236699539</v>
+        <v>39928.496119099269</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C20" s="147">
         <f>L11</f>
-        <v>83075.455920215667</v>
+        <v>78140.101481013757</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C21" s="178">
         <f>C19+C20</f>
-        <v>123436.93515691521</v>
+        <v>118068.59760011302</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C24" s="178">
         <f>C21+C22-C23</f>
-        <v>117965.93515691522</v>
+        <v>112597.59760011302</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="C26" s="216">
         <f>C24/C25</f>
-        <v>111.92213961756663</v>
+        <v>106.82884022781121</v>
       </c>
     </row>
   </sheetData>
@@ -5116,37 +5116,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="245" t="s">
+      <c r="C4" s="246" t="s">
         <v>353</v>
       </c>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
-      <c r="J4" s="245"/>
-      <c r="K4" s="245"/>
-      <c r="L4" s="245"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -5335,18 +5335,18 @@
       <c r="N9" s="134"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="245" t="s">
+      <c r="C10" s="246" t="s">
         <v>283</v>
       </c>
-      <c r="D10" s="245"/>
-      <c r="E10" s="245"/>
-      <c r="F10" s="245"/>
-      <c r="G10" s="245"/>
-      <c r="H10" s="245"/>
-      <c r="I10" s="245"/>
-      <c r="J10" s="245"/>
-      <c r="K10" s="245"/>
-      <c r="L10" s="245"/>
+      <c r="D10" s="246"/>
+      <c r="E10" s="246"/>
+      <c r="F10" s="246"/>
+      <c r="G10" s="246"/>
+      <c r="H10" s="246"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
       <c r="N10" s="134"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5528,18 +5528,18 @@
       <c r="N15" s="134"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="245" t="s">
+      <c r="C16" s="246" t="s">
         <v>355</v>
       </c>
-      <c r="D16" s="245"/>
-      <c r="E16" s="245"/>
-      <c r="F16" s="245"/>
-      <c r="G16" s="245"/>
-      <c r="H16" s="245"/>
-      <c r="I16" s="245"/>
-      <c r="J16" s="245"/>
-      <c r="K16" s="245"/>
-      <c r="L16" s="245"/>
+      <c r="D16" s="246"/>
+      <c r="E16" s="246"/>
+      <c r="F16" s="246"/>
+      <c r="G16" s="246"/>
+      <c r="H16" s="246"/>
+      <c r="I16" s="246"/>
+      <c r="J16" s="246"/>
+      <c r="K16" s="246"/>
+      <c r="L16" s="246"/>
       <c r="N16" s="134"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5673,18 +5673,18 @@
       <c r="N20" s="134"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="245" t="s">
+      <c r="C21" s="246" t="s">
         <v>356</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="E21" s="245"/>
-      <c r="F21" s="245"/>
-      <c r="G21" s="245"/>
-      <c r="H21" s="245"/>
-      <c r="I21" s="245"/>
-      <c r="J21" s="245"/>
-      <c r="K21" s="245"/>
-      <c r="L21" s="245"/>
+      <c r="D21" s="246"/>
+      <c r="E21" s="246"/>
+      <c r="F21" s="246"/>
+      <c r="G21" s="246"/>
+      <c r="H21" s="246"/>
+      <c r="I21" s="246"/>
+      <c r="J21" s="246"/>
+      <c r="K21" s="246"/>
+      <c r="L21" s="246"/>
       <c r="N21" s="134"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5768,18 +5768,18 @@
       <c r="N25" s="134"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="245" t="s">
+      <c r="C26" s="246" t="s">
         <v>357</v>
       </c>
-      <c r="D26" s="245"/>
-      <c r="E26" s="245"/>
-      <c r="F26" s="245"/>
-      <c r="G26" s="245"/>
-      <c r="H26" s="245"/>
-      <c r="I26" s="245"/>
-      <c r="J26" s="245"/>
-      <c r="K26" s="245"/>
-      <c r="L26" s="245"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246"/>
       <c r="N26" s="134"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -6049,10 +6049,10 @@
       <c r="N36" s="134"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="248" t="s">
+      <c r="B37" s="242" t="s">
         <v>361</v>
       </c>
-      <c r="C37" s="248"/>
+      <c r="C37" s="242"/>
       <c r="N37" s="134"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="C39" s="226">
         <f>WACC!C20</f>
-        <v>0.11543039436663093</v>
+        <v>0.11958794725316811</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -6114,14 +6114,14 @@
       </c>
       <c r="C44" s="216">
         <f>C43/(1+C48)^5</f>
-        <v>139.17785369161589</v>
+        <v>136.61281312444444</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="248" t="s">
+      <c r="B46" s="242" t="s">
         <v>213</v>
       </c>
-      <c r="C46" s="248"/>
+      <c r="C46" s="242"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="C48" s="226">
         <f>WACC!C20</f>
-        <v>0.11543039436663093</v>
+        <v>0.11958794725316811</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6173,14 +6173,14 @@
       </c>
       <c r="C52" s="216">
         <f>C51/(1+C48)^5</f>
-        <v>130.41211541502736</v>
+        <v>128.00862694601142</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="248" t="s">
+      <c r="B54" s="242" t="s">
         <v>367</v>
       </c>
-      <c r="C54" s="248"/>
+      <c r="C54" s="242"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="C56" s="226">
         <f>WACC!C20</f>
-        <v>0.11543039436663093</v>
+        <v>0.11958794725316811</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="C61" s="216">
         <f>C60/(1+C56)^5</f>
-        <v>134.60383980126792</v>
+        <v>132.12309807096136</v>
       </c>
     </row>
   </sheetData>
@@ -6290,10 +6290,10 @@
       <c r="N3" s="134"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="248" t="s">
+      <c r="B4" s="242" t="s">
         <v>371</v>
       </c>
-      <c r="C4" s="248"/>
+      <c r="C4" s="242"/>
       <c r="N4" s="134"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="C5" s="228">
         <f>DCF!C26</f>
-        <v>111.92213961756663</v>
+        <v>106.82884022781121</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C6" s="228">
         <f>Multiples!C44</f>
-        <v>139.17785369161589</v>
+        <v>136.61281312444444</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C7" s="228">
         <f>Multiples!C52</f>
-        <v>130.41211541502736</v>
+        <v>128.00862694601142</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="C8" s="228">
         <f>Multiples!C61</f>
-        <v>134.60383980126792</v>
+        <v>132.12309807096136</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C9" s="216">
         <f>AVERAGE(C5:C8)</f>
-        <v>129.02898713136946</v>
+        <v>125.89334459230712</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="C10" s="38">
         <f>Overview!C3</f>
-        <v>201.79</v>
+        <v>228.99</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="C11" s="122">
         <f>(C9-C10)/C10</f>
-        <v>-0.36057789220789205</v>
+        <v>-0.45022339581507004</v>
       </c>
     </row>
   </sheetData>
@@ -6400,20 +6400,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="167"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="248"/>
-      <c r="J3" s="248"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -6431,18 +6431,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="172"/>
       <c r="B5" s="173"/>
-      <c r="C5" s="245" t="s">
+      <c r="C5" s="246" t="s">
         <v>339</v>
       </c>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="245"/>
-      <c r="G5" s="245"/>
-      <c r="H5" s="245"/>
-      <c r="I5" s="245"/>
-      <c r="J5" s="245"/>
-      <c r="K5" s="245"/>
-      <c r="L5" s="245"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
       <c r="P5" s="251"/>
       <c r="Q5" s="251"/>
       <c r="R5" s="251"/>
@@ -6588,7 +6588,7 @@
       <c r="K8" s="212"/>
       <c r="L8" s="143">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>339364.33946600312</v>
+        <v>325196.70946608082</v>
       </c>
       <c r="N8" s="134"/>
       <c r="O8" s="7"/>
@@ -6642,23 +6642,23 @@
       <c r="G10" s="213"/>
       <c r="H10" s="143">
         <f>H7/(1+$C$21)^H9</f>
-        <v>7735.9059892076239</v>
+        <v>7707.1789576650644</v>
       </c>
       <c r="I10" s="143">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>9605.4669562203962</v>
+        <v>9534.2602450795621</v>
       </c>
       <c r="J10" s="143">
         <f t="shared" si="1"/>
-        <v>11926.850659219617</v>
+        <v>11794.473557734013</v>
       </c>
       <c r="K10" s="143">
         <f t="shared" si="1"/>
-        <v>14809.250533646155</v>
+        <v>14590.498153842453</v>
       </c>
       <c r="L10" s="143">
         <f t="shared" si="1"/>
-        <v>18388.24913924501</v>
+        <v>18049.354668965796</v>
       </c>
       <c r="N10" s="134"/>
     </row>
@@ -6677,7 +6677,7 @@
       <c r="K11" s="212"/>
       <c r="L11" s="143">
         <f>L8/(1+C21)^L9</f>
-        <v>196541.30370636209</v>
+        <v>184865.15959148301</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="C15" s="230">
         <f>Overview!C3</f>
-        <v>201.79</v>
+        <v>228.99</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="C16" s="230">
         <f>C36</f>
-        <v>240.5465151649914</v>
+        <v>228.71909409370957</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C21" s="233">
         <f>WACC!C20</f>
-        <v>0.11543039436663093</v>
+        <v>0.11958794725316811</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="C23" s="234">
         <f>C15*C22</f>
-        <v>212686.66</v>
+        <v>241355.46000000002</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="C26" s="235">
         <f>C23+C25-C24</f>
-        <v>218157.66</v>
+        <v>246826.46000000002</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="C29" s="234">
         <f>SUM(H10:L10)</f>
-        <v>62465.723277538804</v>
+        <v>61675.765583286891</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C30" s="234">
         <f>L11</f>
-        <v>196541.30370636209</v>
+        <v>184865.15959148301</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="C31" s="237">
         <f>C29+C30</f>
-        <v>259007.0269839009</v>
+        <v>246540.92517476989</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="C34" s="237">
         <f>C31+C32-C33</f>
-        <v>253536.02698390093</v>
+        <v>241069.92517476989</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="C36" s="239">
         <f>C34/C35</f>
-        <v>240.5465151649914</v>
+        <v>228.71909409370957</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="245" t="s">
+      <c r="C39" s="246" t="s">
         <v>386</v>
       </c>
-      <c r="D39" s="245"/>
-      <c r="E39" s="245"/>
-      <c r="F39" s="245"/>
-      <c r="G39" s="245"/>
-      <c r="H39" s="245"/>
-      <c r="I39" s="245"/>
-      <c r="J39" s="245"/>
-      <c r="K39" s="245"/>
-      <c r="L39" s="245"/>
+      <c r="D39" s="246"/>
+      <c r="E39" s="246"/>
+      <c r="F39" s="246"/>
+      <c r="G39" s="246"/>
+      <c r="H39" s="246"/>
+      <c r="I39" s="246"/>
+      <c r="J39" s="246"/>
+      <c r="K39" s="246"/>
+      <c r="L39" s="246"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="66">
@@ -7312,17 +7312,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7345,31 +7345,31 @@
   <sheetData>
     <row r="5" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B5" s="93"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
       <c r="G5" s="249"/>
       <c r="H5" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
+      <c r="I5" s="242"/>
+      <c r="J5" s="242"/>
+      <c r="K5" s="242"/>
+      <c r="L5" s="242"/>
       <c r="N5" s="93"/>
-      <c r="O5" s="248" t="s">
+      <c r="O5" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="P5" s="248"/>
-      <c r="Q5" s="248"/>
-      <c r="R5" s="248"/>
-      <c r="S5" s="248"/>
-      <c r="T5" s="248"/>
-      <c r="U5" s="248"/>
-      <c r="V5" s="248"/>
+      <c r="P5" s="242"/>
+      <c r="Q5" s="242"/>
+      <c r="R5" s="242"/>
+      <c r="S5" s="242"/>
+      <c r="T5" s="242"/>
+      <c r="U5" s="242"/>
+      <c r="V5" s="242"/>
       <c r="W5" s="255" t="s">
         <v>177</v>
       </c>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="C70" s="132">
         <f>(C69-Overview!C3)/Overview!C3</f>
-        <v>-1.107655144376357E-2</v>
+        <v>-0.1285433307822921</v>
       </c>
       <c r="E70" s="107"/>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="C80" s="132">
         <f>(C79-Overview!C3)/Overview!C3</f>
-        <v>-0.13774003996952602</v>
+        <v>-0.24016141606817185</v>
       </c>
     </row>
   </sheetData>
@@ -16599,11 +16599,11 @@
         <v>154</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="242" t="s">
+      <c r="P4" s="243" t="s">
         <v>155</v>
       </c>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="244"/>
+      <c r="Q4" s="244"/>
+      <c r="R4" s="245"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -29506,36 +29506,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="O2" s="120"/>
-      <c r="S2" s="248" t="s">
+      <c r="S2" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="T2" s="248"/>
-      <c r="U2" s="248"/>
-      <c r="V2" s="248"/>
-      <c r="W2" s="248"/>
-      <c r="X2" s="248"/>
-      <c r="Y2" s="248"/>
-      <c r="Z2" s="248"/>
-      <c r="AA2" s="248" t="s">
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="242" t="s">
         <v>177</v>
       </c>
-      <c r="AB2" s="248"/>
-      <c r="AC2" s="248"/>
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="242"/>
       <c r="AE2" s="171" t="s">
         <v>154</v>
       </c>
@@ -29546,32 +29546,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="245" t="s">
+      <c r="C4" s="246" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
-      <c r="J4" s="245"/>
-      <c r="K4" s="245"/>
-      <c r="L4" s="245"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
       <c r="O4" s="120"/>
-      <c r="S4" s="246" t="s">
+      <c r="S4" s="247" t="s">
         <v>178</v>
       </c>
-      <c r="T4" s="247"/>
-      <c r="U4" s="247"/>
-      <c r="V4" s="247"/>
-      <c r="W4" s="247"/>
-      <c r="X4" s="247"/>
-      <c r="Y4" s="247"/>
-      <c r="Z4" s="247"/>
-      <c r="AA4" s="247"/>
-      <c r="AB4" s="247"/>
-      <c r="AC4" s="247"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
+      <c r="AA4" s="248"/>
+      <c r="AB4" s="248"/>
+      <c r="AC4" s="248"/>
       <c r="AE4" s="174" t="s">
         <v>285</v>
       </c>
@@ -30241,33 +30241,33 @@
       <c r="Q12" s="134"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="245" t="s">
+      <c r="C13" s="246" t="s">
         <v>283</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="E13" s="245"/>
-      <c r="F13" s="245"/>
-      <c r="G13" s="245"/>
-      <c r="H13" s="245"/>
-      <c r="I13" s="245"/>
-      <c r="J13" s="245"/>
-      <c r="K13" s="245"/>
-      <c r="L13" s="245"/>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="246"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="246"/>
+      <c r="I13" s="246"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
+      <c r="L13" s="246"/>
       <c r="O13" s="120"/>
       <c r="Q13" s="134"/>
-      <c r="S13" s="246" t="s">
+      <c r="S13" s="247" t="s">
         <v>283</v>
       </c>
-      <c r="T13" s="247"/>
-      <c r="U13" s="247"/>
-      <c r="V13" s="247"/>
-      <c r="W13" s="247"/>
-      <c r="X13" s="247"/>
-      <c r="Y13" s="247"/>
-      <c r="Z13" s="247"/>
-      <c r="AA13" s="247"/>
-      <c r="AB13" s="247"/>
-      <c r="AC13" s="247"/>
+      <c r="T13" s="248"/>
+      <c r="U13" s="248"/>
+      <c r="V13" s="248"/>
+      <c r="W13" s="248"/>
+      <c r="X13" s="248"/>
+      <c r="Y13" s="248"/>
+      <c r="Z13" s="248"/>
+      <c r="AA13" s="248"/>
+      <c r="AB13" s="248"/>
+      <c r="AC13" s="248"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
@@ -30889,35 +30889,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="P2" s="248" t="s">
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="P2" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="Q2" s="248"/>
-      <c r="R2" s="248"/>
-      <c r="S2" s="248"/>
-      <c r="T2" s="248"/>
-      <c r="U2" s="248"/>
-      <c r="V2" s="248"/>
-      <c r="W2" s="248"/>
-      <c r="X2" s="248" t="s">
+      <c r="Q2" s="242"/>
+      <c r="R2" s="242"/>
+      <c r="S2" s="242"/>
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242" t="s">
         <v>177</v>
       </c>
-      <c r="Y2" s="248"/>
-      <c r="Z2" s="248"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
       <c r="AB2" s="171" t="s">
         <v>154</v>
       </c>
@@ -30926,31 +30926,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="245" t="s">
+      <c r="C4" s="246" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
-      <c r="J4" s="245"/>
-      <c r="K4" s="245"/>
-      <c r="L4" s="245"/>
-      <c r="P4" s="247" t="s">
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="P4" s="248" t="s">
         <v>178</v>
       </c>
-      <c r="Q4" s="247"/>
-      <c r="R4" s="247"/>
-      <c r="S4" s="247"/>
-      <c r="T4" s="247"/>
-      <c r="U4" s="247"/>
-      <c r="V4" s="247"/>
-      <c r="W4" s="247"/>
-      <c r="X4" s="247"/>
-      <c r="Y4" s="247"/>
-      <c r="Z4" s="247"/>
+      <c r="Q4" s="248"/>
+      <c r="R4" s="248"/>
+      <c r="S4" s="248"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
       <c r="AB4" s="174" t="str">
         <f>Revenue!AE4</f>
         <v>Q4-Q1-Q2</v>
@@ -31153,32 +31153,32 @@
       <c r="N8" s="134"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="245" t="s">
+      <c r="C9" s="246" t="s">
         <v>287</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="E9" s="245"/>
-      <c r="F9" s="245"/>
-      <c r="G9" s="245"/>
-      <c r="H9" s="245"/>
-      <c r="I9" s="245"/>
-      <c r="J9" s="245"/>
-      <c r="K9" s="245"/>
-      <c r="L9" s="245"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
       <c r="N9" s="134"/>
-      <c r="P9" s="247" t="s">
+      <c r="P9" s="248" t="s">
         <v>288</v>
       </c>
-      <c r="Q9" s="247"/>
-      <c r="R9" s="247"/>
-      <c r="S9" s="247"/>
-      <c r="T9" s="247"/>
-      <c r="U9" s="247"/>
-      <c r="V9" s="247"/>
-      <c r="W9" s="247"/>
-      <c r="X9" s="247"/>
-      <c r="Y9" s="247"/>
-      <c r="Z9" s="247"/>
+      <c r="Q9" s="248"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
       <c r="AB9" s="174" t="str">
         <f>AB4</f>
         <v>Q4-Q1-Q2</v>
@@ -31652,31 +31652,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="245" t="s">
+      <c r="C17" s="246" t="s">
         <v>291</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="E17" s="245"/>
-      <c r="F17" s="245"/>
-      <c r="G17" s="245"/>
-      <c r="H17" s="245"/>
-      <c r="I17" s="245"/>
-      <c r="J17" s="245"/>
-      <c r="K17" s="245"/>
-      <c r="L17" s="245"/>
-      <c r="P17" s="247" t="s">
+      <c r="D17" s="246"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="246"/>
+      <c r="G17" s="246"/>
+      <c r="H17" s="246"/>
+      <c r="I17" s="246"/>
+      <c r="J17" s="246"/>
+      <c r="K17" s="246"/>
+      <c r="L17" s="246"/>
+      <c r="P17" s="248" t="s">
         <v>291</v>
       </c>
-      <c r="Q17" s="247"/>
-      <c r="R17" s="247"/>
-      <c r="S17" s="247"/>
-      <c r="T17" s="247"/>
-      <c r="U17" s="247"/>
-      <c r="V17" s="247"/>
-      <c r="W17" s="247"/>
-      <c r="X17" s="247"/>
-      <c r="Y17" s="247"/>
-      <c r="Z17" s="247"/>
+      <c r="Q17" s="248"/>
+      <c r="R17" s="248"/>
+      <c r="S17" s="248"/>
+      <c r="T17" s="248"/>
+      <c r="U17" s="248"/>
+      <c r="V17" s="248"/>
+      <c r="W17" s="248"/>
+      <c r="X17" s="248"/>
+      <c r="Y17" s="248"/>
+      <c r="Z17" s="248"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
@@ -32066,20 +32066,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="167"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="248"/>
-      <c r="J3" s="248"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -32097,18 +32097,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="172"/>
       <c r="B5" s="173"/>
-      <c r="C5" s="245" t="s">
+      <c r="C5" s="246" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="245"/>
-      <c r="G5" s="245"/>
-      <c r="H5" s="245"/>
-      <c r="I5" s="245"/>
-      <c r="J5" s="245"/>
-      <c r="K5" s="245"/>
-      <c r="L5" s="245"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
       <c r="P5" s="251"/>
       <c r="Q5" s="251"/>
       <c r="R5" s="251"/>
@@ -32305,18 +32305,18 @@
       <c r="N10" s="134"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="245" t="s">
+      <c r="C11" s="246" t="s">
         <v>293</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="E11" s="245"/>
-      <c r="F11" s="245"/>
-      <c r="G11" s="245"/>
-      <c r="H11" s="245"/>
-      <c r="I11" s="245"/>
-      <c r="J11" s="245"/>
-      <c r="K11" s="245"/>
-      <c r="L11" s="245"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
       <c r="N11" s="134"/>
       <c r="P11" s="251"/>
       <c r="Q11" s="251"/>
@@ -32570,18 +32570,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="245" t="s">
+      <c r="C18" s="246" t="s">
         <v>298</v>
       </c>
-      <c r="D18" s="245"/>
-      <c r="E18" s="245"/>
-      <c r="F18" s="245"/>
-      <c r="G18" s="245"/>
-      <c r="H18" s="245"/>
-      <c r="I18" s="245"/>
-      <c r="J18" s="245"/>
-      <c r="K18" s="245"/>
-      <c r="L18" s="245"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -32799,18 +32799,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="186"/>
-      <c r="C26" s="245" t="s">
+      <c r="C26" s="246" t="s">
         <v>304</v>
       </c>
-      <c r="D26" s="245"/>
-      <c r="E26" s="245"/>
-      <c r="F26" s="245"/>
-      <c r="G26" s="245"/>
-      <c r="H26" s="245"/>
-      <c r="I26" s="245"/>
-      <c r="J26" s="245"/>
-      <c r="K26" s="245"/>
-      <c r="L26" s="245"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -33002,18 +33002,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="186"/>
-      <c r="C33" s="245" t="s">
+      <c r="C33" s="246" t="s">
         <v>308</v>
       </c>
-      <c r="D33" s="245"/>
-      <c r="E33" s="245"/>
-      <c r="F33" s="245"/>
-      <c r="G33" s="245"/>
-      <c r="H33" s="245"/>
-      <c r="I33" s="245"/>
-      <c r="J33" s="245"/>
-      <c r="K33" s="245"/>
-      <c r="L33" s="245"/>
+      <c r="D33" s="246"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246"/>
+      <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
+      <c r="I33" s="246"/>
+      <c r="J33" s="246"/>
+      <c r="K33" s="246"/>
+      <c r="L33" s="246"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -33197,18 +33197,18 @@
       <c r="C39" s="202"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="245" t="s">
+      <c r="C40" s="246" t="s">
         <v>311</v>
       </c>
-      <c r="D40" s="245"/>
-      <c r="E40" s="245"/>
-      <c r="F40" s="245"/>
-      <c r="G40" s="245"/>
-      <c r="H40" s="245"/>
-      <c r="I40" s="245"/>
-      <c r="J40" s="245"/>
-      <c r="K40" s="245"/>
-      <c r="L40" s="245"/>
+      <c r="D40" s="246"/>
+      <c r="E40" s="246"/>
+      <c r="F40" s="246"/>
+      <c r="G40" s="246"/>
+      <c r="H40" s="246"/>
+      <c r="I40" s="246"/>
+      <c r="J40" s="246"/>
+      <c r="K40" s="246"/>
+      <c r="L40" s="246"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -33472,12 +33472,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -33485,6 +33479,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0104743C-DFB4-4C48-9394-4BA9BC302284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D40E9A-F16E-AD4B-A534-7C36DE678E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2404,9 +2404,6 @@
     <xf numFmtId="166" fontId="0" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="12" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="12" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2423,6 +2420,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2547,15 +2547,15 @@
       <sheetData sheetId="0">
         <row r="8">
           <cell r="C8">
-            <v>228.99</v>
+            <v>249.125</v>
           </cell>
           <cell r="F8">
-            <v>1.5985</v>
+            <v>1.5984</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>44.53</v>
+            <v>44.55</v>
           </cell>
         </row>
       </sheetData>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C3" s="38">
         <f>[1]Sheet1!$C$8</f>
-        <v>228.99</v>
+        <v>249.125</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="C11" s="159">
         <f>C3/'Statement Q'!N27</f>
-        <v>24.968979139373175</v>
+        <v>27.164491585206086</v>
       </c>
       <c r="E11" s="159"/>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="C12" s="159">
         <f>C3/Statements!W20</f>
-        <v>25.76881747269891</v>
+        <v>28.034659386375456</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C13" s="165">
         <f>C3/(Statements!W5/Statements!W19)</f>
-        <v>5.5695540169941111</v>
+        <v>6.0592826956795394</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C15" s="162">
         <f>C3*'Statement Q'!J141</f>
-        <v>241355.46000000002</v>
+        <v>262577.75</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="C17" s="162">
         <f>C15+C16</f>
-        <v>246826.46000000002</v>
+        <v>268048.75</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -3434,20 +3434,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
       <c r="S2" s="251"/>
       <c r="T2" s="251"/>
       <c r="U2" s="251"/>
@@ -3465,18 +3465,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="245" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
       <c r="S4" s="251"/>
       <c r="T4" s="251"/>
       <c r="U4" s="251"/>
@@ -3974,18 +3974,18 @@
       <c r="AE12" s="147"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C15" s="246" t="s">
+      <c r="C15" s="245" t="s">
         <v>319</v>
       </c>
-      <c r="D15" s="246"/>
-      <c r="E15" s="246"/>
-      <c r="F15" s="246"/>
-      <c r="G15" s="246"/>
-      <c r="H15" s="246"/>
-      <c r="I15" s="246"/>
-      <c r="J15" s="246"/>
-      <c r="K15" s="246"/>
-      <c r="L15" s="246"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="245"/>
+      <c r="H15" s="245"/>
+      <c r="I15" s="245"/>
+      <c r="J15" s="245"/>
+      <c r="K15" s="245"/>
+      <c r="L15" s="245"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C16" s="66">
@@ -4070,18 +4070,18 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C20" s="246" t="s">
+      <c r="C20" s="245" t="s">
         <v>320</v>
       </c>
-      <c r="D20" s="246"/>
-      <c r="E20" s="246"/>
-      <c r="F20" s="246"/>
-      <c r="G20" s="246"/>
-      <c r="H20" s="246"/>
-      <c r="I20" s="246"/>
-      <c r="J20" s="246"/>
-      <c r="K20" s="246"/>
-      <c r="L20" s="246"/>
+      <c r="D20" s="245"/>
+      <c r="E20" s="245"/>
+      <c r="F20" s="245"/>
+      <c r="G20" s="245"/>
+      <c r="H20" s="245"/>
+      <c r="I20" s="245"/>
+      <c r="J20" s="245"/>
+      <c r="K20" s="245"/>
+      <c r="L20" s="245"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -4273,18 +4273,18 @@
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="246" t="s">
+      <c r="C27" s="245" t="s">
         <v>323</v>
       </c>
-      <c r="D27" s="246"/>
-      <c r="E27" s="246"/>
-      <c r="F27" s="246"/>
-      <c r="G27" s="246"/>
-      <c r="H27" s="246"/>
-      <c r="I27" s="246"/>
-      <c r="J27" s="246"/>
-      <c r="K27" s="246"/>
-      <c r="L27" s="246"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="245"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
+      <c r="K27" s="245"/>
+      <c r="L27" s="245"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
@@ -4491,10 +4491,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="248" t="s">
         <v>326</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="248"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C6" s="209">
         <f>Overview!C3</f>
-        <v>228.99</v>
+        <v>249.125</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C7" s="210">
         <f>C5*C6</f>
-        <v>241355.46000000002</v>
+        <v>262577.75</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C9" s="211">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.453E-2</v>
+        <v>4.4549999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C10" s="209">
         <f>[1]Sheet1!$F$8</f>
-        <v>1.5985</v>
+        <v>1.5984</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4576,10 +4576,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="248" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="242"/>
+      <c r="C15" s="248"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C16" s="140">
         <f>C8/(C8+C7)</f>
-        <v>5.9503059439231003E-2</v>
+        <v>5.4958156040493401E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="C17" s="140">
         <f>C7/(C8+C7)</f>
-        <v>0.94049694056076905</v>
+        <v>0.94504184395950663</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C19" s="140">
         <f>C9+C10*C11</f>
-        <v>0.12445500000000001</v>
+        <v>0.12447</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="C20" s="140">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>0.11958794725316811</v>
+        <v>0.11997387325432723</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4677,20 +4677,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="167"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -4708,18 +4708,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="172"/>
       <c r="B5" s="173"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="245" t="s">
         <v>339</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
       <c r="P5" s="251"/>
       <c r="Q5" s="251"/>
       <c r="R5" s="251"/>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="L8" s="143">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>137456.42464553402</v>
+        <v>136925.80592916068</v>
       </c>
       <c r="N8" s="134"/>
       <c r="O8" s="7"/>
@@ -4937,23 +4937,23 @@
       <c r="G10" s="213"/>
       <c r="H10" s="143">
         <f>H7/(1+$C$15)^H9</f>
-        <v>9239.3879808384081</v>
+        <v>9236.2042279476009</v>
       </c>
       <c r="I10" s="143">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>8179.2951149238825</v>
+        <v>8173.6591641705918</v>
       </c>
       <c r="J10" s="143">
         <f t="shared" si="0"/>
-        <v>7664.8627675121143</v>
+        <v>7656.9419113590793</v>
       </c>
       <c r="K10" s="143">
         <f t="shared" si="0"/>
-        <v>7215.7225061695699</v>
+        <v>7205.7819317927006</v>
       </c>
       <c r="L10" s="143">
         <f t="shared" si="0"/>
-        <v>7629.2277496552952</v>
+        <v>7616.0922248339284</v>
       </c>
       <c r="N10" s="134"/>
     </row>
@@ -4972,14 +4972,14 @@
       <c r="K11" s="212"/>
       <c r="L11" s="143">
         <f>L8/(1+C15)^L9</f>
-        <v>78140.101481013757</v>
+        <v>77704.442335331463</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="242" t="s">
+      <c r="B13" s="248" t="s">
         <v>344</v>
       </c>
-      <c r="C13" s="242"/>
+      <c r="C13" s="248"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4995,14 +4995,14 @@
       </c>
       <c r="C15" s="160">
         <f>WACC!C20</f>
-        <v>0.11958794725316811</v>
+        <v>0.11997387325432723</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="242" t="s">
+      <c r="B18" s="248" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="242"/>
+      <c r="C18" s="248"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="C19" s="147">
         <f>SUM(H10:L10)</f>
-        <v>39928.496119099269</v>
+        <v>39888.6794601039</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C20" s="147">
         <f>L11</f>
-        <v>78140.101481013757</v>
+        <v>77704.442335331463</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C21" s="178">
         <f>C19+C20</f>
-        <v>118068.59760011302</v>
+        <v>117593.12179543536</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C24" s="178">
         <f>C21+C22-C23</f>
-        <v>112597.59760011302</v>
+        <v>112122.12179543536</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="C26" s="216">
         <f>C24/C25</f>
-        <v>106.82884022781121</v>
+        <v>106.37772466360092</v>
       </c>
     </row>
   </sheetData>
@@ -5116,37 +5116,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="245" t="s">
         <v>353</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -5335,18 +5335,18 @@
       <c r="N9" s="134"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="246" t="s">
+      <c r="C10" s="245" t="s">
         <v>283</v>
       </c>
-      <c r="D10" s="246"/>
-      <c r="E10" s="246"/>
-      <c r="F10" s="246"/>
-      <c r="G10" s="246"/>
-      <c r="H10" s="246"/>
-      <c r="I10" s="246"/>
-      <c r="J10" s="246"/>
-      <c r="K10" s="246"/>
-      <c r="L10" s="246"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="245"/>
+      <c r="G10" s="245"/>
+      <c r="H10" s="245"/>
+      <c r="I10" s="245"/>
+      <c r="J10" s="245"/>
+      <c r="K10" s="245"/>
+      <c r="L10" s="245"/>
       <c r="N10" s="134"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5528,18 +5528,18 @@
       <c r="N15" s="134"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="246" t="s">
+      <c r="C16" s="245" t="s">
         <v>355</v>
       </c>
-      <c r="D16" s="246"/>
-      <c r="E16" s="246"/>
-      <c r="F16" s="246"/>
-      <c r="G16" s="246"/>
-      <c r="H16" s="246"/>
-      <c r="I16" s="246"/>
-      <c r="J16" s="246"/>
-      <c r="K16" s="246"/>
-      <c r="L16" s="246"/>
+      <c r="D16" s="245"/>
+      <c r="E16" s="245"/>
+      <c r="F16" s="245"/>
+      <c r="G16" s="245"/>
+      <c r="H16" s="245"/>
+      <c r="I16" s="245"/>
+      <c r="J16" s="245"/>
+      <c r="K16" s="245"/>
+      <c r="L16" s="245"/>
       <c r="N16" s="134"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5673,18 +5673,18 @@
       <c r="N20" s="134"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="246" t="s">
+      <c r="C21" s="245" t="s">
         <v>356</v>
       </c>
-      <c r="D21" s="246"/>
-      <c r="E21" s="246"/>
-      <c r="F21" s="246"/>
-      <c r="G21" s="246"/>
-      <c r="H21" s="246"/>
-      <c r="I21" s="246"/>
-      <c r="J21" s="246"/>
-      <c r="K21" s="246"/>
-      <c r="L21" s="246"/>
+      <c r="D21" s="245"/>
+      <c r="E21" s="245"/>
+      <c r="F21" s="245"/>
+      <c r="G21" s="245"/>
+      <c r="H21" s="245"/>
+      <c r="I21" s="245"/>
+      <c r="J21" s="245"/>
+      <c r="K21" s="245"/>
+      <c r="L21" s="245"/>
       <c r="N21" s="134"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5768,18 +5768,18 @@
       <c r="N25" s="134"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="246" t="s">
+      <c r="C26" s="245" t="s">
         <v>357</v>
       </c>
-      <c r="D26" s="246"/>
-      <c r="E26" s="246"/>
-      <c r="F26" s="246"/>
-      <c r="G26" s="246"/>
-      <c r="H26" s="246"/>
-      <c r="I26" s="246"/>
-      <c r="J26" s="246"/>
-      <c r="K26" s="246"/>
-      <c r="L26" s="246"/>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+      <c r="K26" s="245"/>
+      <c r="L26" s="245"/>
       <c r="N26" s="134"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -6049,10 +6049,10 @@
       <c r="N36" s="134"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="242" t="s">
+      <c r="B37" s="248" t="s">
         <v>361</v>
       </c>
-      <c r="C37" s="242"/>
+      <c r="C37" s="248"/>
       <c r="N37" s="134"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="C39" s="226">
         <f>WACC!C20</f>
-        <v>0.11958794725316811</v>
+        <v>0.11997387325432723</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -6114,14 +6114,14 @@
       </c>
       <c r="C44" s="216">
         <f>C43/(1+C48)^5</f>
-        <v>136.61281312444444</v>
+        <v>136.37760176929859</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="242" t="s">
+      <c r="B46" s="248" t="s">
         <v>213</v>
       </c>
-      <c r="C46" s="242"/>
+      <c r="C46" s="248"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="C48" s="226">
         <f>WACC!C20</f>
-        <v>0.11958794725316811</v>
+        <v>0.11997387325432723</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6173,14 +6173,14 @@
       </c>
       <c r="C52" s="216">
         <f>C51/(1+C48)^5</f>
-        <v>128.00862694601142</v>
+        <v>127.78822973783076</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="242" t="s">
+      <c r="B54" s="248" t="s">
         <v>367</v>
       </c>
-      <c r="C54" s="242"/>
+      <c r="C54" s="248"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="C56" s="226">
         <f>WACC!C20</f>
-        <v>0.11958794725316811</v>
+        <v>0.11997387325432723</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="C61" s="216">
         <f>C60/(1+C56)^5</f>
-        <v>132.12309807096136</v>
+        <v>131.8956168250036</v>
       </c>
     </row>
   </sheetData>
@@ -6290,10 +6290,10 @@
       <c r="N3" s="134"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="248" t="s">
         <v>371</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="248"/>
       <c r="N4" s="134"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="C5" s="228">
         <f>DCF!C26</f>
-        <v>106.82884022781121</v>
+        <v>106.37772466360092</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C6" s="228">
         <f>Multiples!C44</f>
-        <v>136.61281312444444</v>
+        <v>136.37760176929859</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C7" s="228">
         <f>Multiples!C52</f>
-        <v>128.00862694601142</v>
+        <v>127.78822973783076</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="C8" s="228">
         <f>Multiples!C61</f>
-        <v>132.12309807096136</v>
+        <v>131.8956168250036</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C9" s="216">
         <f>AVERAGE(C5:C8)</f>
-        <v>125.89334459230712</v>
+        <v>125.60979324893347</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="C10" s="38">
         <f>Overview!C3</f>
-        <v>228.99</v>
+        <v>249.125</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="C11" s="122">
         <f>(C9-C10)/C10</f>
-        <v>-0.45022339581507004</v>
+        <v>-0.49579611340117019</v>
       </c>
     </row>
   </sheetData>
@@ -6400,20 +6400,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="167"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -6431,18 +6431,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="172"/>
       <c r="B5" s="173"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="245" t="s">
         <v>339</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
       <c r="P5" s="251"/>
       <c r="Q5" s="251"/>
       <c r="R5" s="251"/>
@@ -6588,7 +6588,7 @@
       <c r="K8" s="212"/>
       <c r="L8" s="143">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>325196.70946608082</v>
+        <v>323941.3628281139</v>
       </c>
       <c r="N8" s="134"/>
       <c r="O8" s="7"/>
@@ -6642,23 +6642,23 @@
       <c r="G10" s="213"/>
       <c r="H10" s="143">
         <f>H7/(1+$C$21)^H9</f>
-        <v>7707.1789576650644</v>
+        <v>7704.5231807524242</v>
       </c>
       <c r="I10" s="143">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>9534.2602450795621</v>
+        <v>9527.6906543684654</v>
       </c>
       <c r="J10" s="143">
         <f t="shared" si="1"/>
-        <v>11794.473557734013</v>
+        <v>11782.28516881105</v>
       </c>
       <c r="K10" s="143">
         <f t="shared" si="1"/>
-        <v>14590.498153842453</v>
+        <v>14570.397889181522</v>
       </c>
       <c r="L10" s="143">
         <f t="shared" si="1"/>
-        <v>18049.354668965796</v>
+        <v>18018.278424548451</v>
       </c>
       <c r="N10" s="134"/>
     </row>
@@ -6677,7 +6677,7 @@
       <c r="K11" s="212"/>
       <c r="L11" s="143">
         <f>L8/(1+C21)^L9</f>
-        <v>184865.15959148301</v>
+        <v>183834.46989480252</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="C15" s="230">
         <f>Overview!C3</f>
-        <v>228.99</v>
+        <v>249.125</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="C16" s="230">
         <f>C36</f>
-        <v>228.71909409370957</v>
+        <v>227.67233891125659</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C21" s="233">
         <f>WACC!C20</f>
-        <v>0.11958794725316811</v>
+        <v>0.11997387325432723</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="C23" s="234">
         <f>C15*C22</f>
-        <v>241355.46000000002</v>
+        <v>262577.75</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="C26" s="235">
         <f>C23+C25-C24</f>
-        <v>246826.46000000002</v>
+        <v>268048.75</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="C29" s="234">
         <f>SUM(H10:L10)</f>
-        <v>61675.765583286891</v>
+        <v>61603.17531766191</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C30" s="234">
         <f>L11</f>
-        <v>184865.15959148301</v>
+        <v>183834.46989480252</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="C31" s="237">
         <f>C29+C30</f>
-        <v>246540.92517476989</v>
+        <v>245437.64521246444</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="C34" s="237">
         <f>C31+C32-C33</f>
-        <v>241069.92517476989</v>
+        <v>239966.64521246444</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="C36" s="239">
         <f>C34/C35</f>
-        <v>228.71909409370957</v>
+        <v>227.67233891125659</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="246" t="s">
+      <c r="C39" s="245" t="s">
         <v>386</v>
       </c>
-      <c r="D39" s="246"/>
-      <c r="E39" s="246"/>
-      <c r="F39" s="246"/>
-      <c r="G39" s="246"/>
-      <c r="H39" s="246"/>
-      <c r="I39" s="246"/>
-      <c r="J39" s="246"/>
-      <c r="K39" s="246"/>
-      <c r="L39" s="246"/>
+      <c r="D39" s="245"/>
+      <c r="E39" s="245"/>
+      <c r="F39" s="245"/>
+      <c r="G39" s="245"/>
+      <c r="H39" s="245"/>
+      <c r="I39" s="245"/>
+      <c r="J39" s="245"/>
+      <c r="K39" s="245"/>
+      <c r="L39" s="245"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="66">
@@ -7312,17 +7312,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7345,31 +7345,31 @@
   <sheetData>
     <row r="5" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B5" s="93"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
       <c r="G5" s="249"/>
       <c r="H5" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
       <c r="N5" s="93"/>
-      <c r="O5" s="242" t="s">
+      <c r="O5" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="P5" s="242"/>
-      <c r="Q5" s="242"/>
-      <c r="R5" s="242"/>
-      <c r="S5" s="242"/>
-      <c r="T5" s="242"/>
-      <c r="U5" s="242"/>
-      <c r="V5" s="242"/>
+      <c r="P5" s="248"/>
+      <c r="Q5" s="248"/>
+      <c r="R5" s="248"/>
+      <c r="S5" s="248"/>
+      <c r="T5" s="248"/>
+      <c r="U5" s="248"/>
+      <c r="V5" s="248"/>
       <c r="W5" s="255" t="s">
         <v>177</v>
       </c>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="C70" s="132">
         <f>(C69-Overview!C3)/Overview!C3</f>
-        <v>-0.1285433307822921</v>
+        <v>-0.19897696865363595</v>
       </c>
       <c r="E70" s="107"/>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="C80" s="132">
         <f>(C79-Overview!C3)/Overview!C3</f>
-        <v>-0.24016141606817185</v>
+        <v>-0.30157375881766446</v>
       </c>
     </row>
   </sheetData>
@@ -16599,11 +16599,11 @@
         <v>154</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="243" t="s">
+      <c r="P4" s="242" t="s">
         <v>155</v>
       </c>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="245"/>
+      <c r="Q4" s="243"/>
+      <c r="R4" s="244"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -29506,36 +29506,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
       <c r="O2" s="120"/>
-      <c r="S2" s="242" t="s">
+      <c r="S2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242" t="s">
+      <c r="T2" s="248"/>
+      <c r="U2" s="248"/>
+      <c r="V2" s="248"/>
+      <c r="W2" s="248"/>
+      <c r="X2" s="248"/>
+      <c r="Y2" s="248"/>
+      <c r="Z2" s="248"/>
+      <c r="AA2" s="248" t="s">
         <v>177</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
+      <c r="AB2" s="248"/>
+      <c r="AC2" s="248"/>
       <c r="AE2" s="171" t="s">
         <v>154</v>
       </c>
@@ -29546,32 +29546,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
       <c r="O4" s="120"/>
-      <c r="S4" s="247" t="s">
+      <c r="S4" s="246" t="s">
         <v>178</v>
       </c>
-      <c r="T4" s="248"/>
-      <c r="U4" s="248"/>
-      <c r="V4" s="248"/>
-      <c r="W4" s="248"/>
-      <c r="X4" s="248"/>
-      <c r="Y4" s="248"/>
-      <c r="Z4" s="248"/>
-      <c r="AA4" s="248"/>
-      <c r="AB4" s="248"/>
-      <c r="AC4" s="248"/>
+      <c r="T4" s="247"/>
+      <c r="U4" s="247"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="247"/>
+      <c r="X4" s="247"/>
+      <c r="Y4" s="247"/>
+      <c r="Z4" s="247"/>
+      <c r="AA4" s="247"/>
+      <c r="AB4" s="247"/>
+      <c r="AC4" s="247"/>
       <c r="AE4" s="174" t="s">
         <v>285</v>
       </c>
@@ -30241,33 +30241,33 @@
       <c r="Q12" s="134"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="246" t="s">
+      <c r="C13" s="245" t="s">
         <v>283</v>
       </c>
-      <c r="D13" s="246"/>
-      <c r="E13" s="246"/>
-      <c r="F13" s="246"/>
-      <c r="G13" s="246"/>
-      <c r="H13" s="246"/>
-      <c r="I13" s="246"/>
-      <c r="J13" s="246"/>
-      <c r="K13" s="246"/>
-      <c r="L13" s="246"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
+      <c r="I13" s="245"/>
+      <c r="J13" s="245"/>
+      <c r="K13" s="245"/>
+      <c r="L13" s="245"/>
       <c r="O13" s="120"/>
       <c r="Q13" s="134"/>
-      <c r="S13" s="247" t="s">
+      <c r="S13" s="246" t="s">
         <v>283</v>
       </c>
-      <c r="T13" s="248"/>
-      <c r="U13" s="248"/>
-      <c r="V13" s="248"/>
-      <c r="W13" s="248"/>
-      <c r="X13" s="248"/>
-      <c r="Y13" s="248"/>
-      <c r="Z13" s="248"/>
-      <c r="AA13" s="248"/>
-      <c r="AB13" s="248"/>
-      <c r="AC13" s="248"/>
+      <c r="T13" s="247"/>
+      <c r="U13" s="247"/>
+      <c r="V13" s="247"/>
+      <c r="W13" s="247"/>
+      <c r="X13" s="247"/>
+      <c r="Y13" s="247"/>
+      <c r="Z13" s="247"/>
+      <c r="AA13" s="247"/>
+      <c r="AB13" s="247"/>
+      <c r="AC13" s="247"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
@@ -30889,35 +30889,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="167"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="P2" s="242" t="s">
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="P2" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242" t="s">
+      <c r="Q2" s="248"/>
+      <c r="R2" s="248"/>
+      <c r="S2" s="248"/>
+      <c r="T2" s="248"/>
+      <c r="U2" s="248"/>
+      <c r="V2" s="248"/>
+      <c r="W2" s="248"/>
+      <c r="X2" s="248" t="s">
         <v>177</v>
       </c>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
+      <c r="Y2" s="248"/>
+      <c r="Z2" s="248"/>
       <c r="AB2" s="171" t="s">
         <v>154</v>
       </c>
@@ -30926,31 +30926,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="172"/>
       <c r="B4" s="173"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="P4" s="248" t="s">
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="P4" s="247" t="s">
         <v>178</v>
       </c>
-      <c r="Q4" s="248"/>
-      <c r="R4" s="248"/>
-      <c r="S4" s="248"/>
-      <c r="T4" s="248"/>
-      <c r="U4" s="248"/>
-      <c r="V4" s="248"/>
-      <c r="W4" s="248"/>
-      <c r="X4" s="248"/>
-      <c r="Y4" s="248"/>
-      <c r="Z4" s="248"/>
+      <c r="Q4" s="247"/>
+      <c r="R4" s="247"/>
+      <c r="S4" s="247"/>
+      <c r="T4" s="247"/>
+      <c r="U4" s="247"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="247"/>
+      <c r="X4" s="247"/>
+      <c r="Y4" s="247"/>
+      <c r="Z4" s="247"/>
       <c r="AB4" s="174" t="str">
         <f>Revenue!AE4</f>
         <v>Q4-Q1-Q2</v>
@@ -31153,32 +31153,32 @@
       <c r="N8" s="134"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="246" t="s">
+      <c r="C9" s="245" t="s">
         <v>287</v>
       </c>
-      <c r="D9" s="246"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="246"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="246"/>
-      <c r="K9" s="246"/>
-      <c r="L9" s="246"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="245"/>
+      <c r="G9" s="245"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="245"/>
+      <c r="J9" s="245"/>
+      <c r="K9" s="245"/>
+      <c r="L9" s="245"/>
       <c r="N9" s="134"/>
-      <c r="P9" s="248" t="s">
+      <c r="P9" s="247" t="s">
         <v>288</v>
       </c>
-      <c r="Q9" s="248"/>
-      <c r="R9" s="248"/>
-      <c r="S9" s="248"/>
-      <c r="T9" s="248"/>
-      <c r="U9" s="248"/>
-      <c r="V9" s="248"/>
-      <c r="W9" s="248"/>
-      <c r="X9" s="248"/>
-      <c r="Y9" s="248"/>
-      <c r="Z9" s="248"/>
+      <c r="Q9" s="247"/>
+      <c r="R9" s="247"/>
+      <c r="S9" s="247"/>
+      <c r="T9" s="247"/>
+      <c r="U9" s="247"/>
+      <c r="V9" s="247"/>
+      <c r="W9" s="247"/>
+      <c r="X9" s="247"/>
+      <c r="Y9" s="247"/>
+      <c r="Z9" s="247"/>
       <c r="AB9" s="174" t="str">
         <f>AB4</f>
         <v>Q4-Q1-Q2</v>
@@ -31652,31 +31652,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="246" t="s">
+      <c r="C17" s="245" t="s">
         <v>291</v>
       </c>
-      <c r="D17" s="246"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="246"/>
-      <c r="G17" s="246"/>
-      <c r="H17" s="246"/>
-      <c r="I17" s="246"/>
-      <c r="J17" s="246"/>
-      <c r="K17" s="246"/>
-      <c r="L17" s="246"/>
-      <c r="P17" s="248" t="s">
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
+      <c r="H17" s="245"/>
+      <c r="I17" s="245"/>
+      <c r="J17" s="245"/>
+      <c r="K17" s="245"/>
+      <c r="L17" s="245"/>
+      <c r="P17" s="247" t="s">
         <v>291</v>
       </c>
-      <c r="Q17" s="248"/>
-      <c r="R17" s="248"/>
-      <c r="S17" s="248"/>
-      <c r="T17" s="248"/>
-      <c r="U17" s="248"/>
-      <c r="V17" s="248"/>
-      <c r="W17" s="248"/>
-      <c r="X17" s="248"/>
-      <c r="Y17" s="248"/>
-      <c r="Z17" s="248"/>
+      <c r="Q17" s="247"/>
+      <c r="R17" s="247"/>
+      <c r="S17" s="247"/>
+      <c r="T17" s="247"/>
+      <c r="U17" s="247"/>
+      <c r="V17" s="247"/>
+      <c r="W17" s="247"/>
+      <c r="X17" s="247"/>
+      <c r="Y17" s="247"/>
+      <c r="Z17" s="247"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
@@ -32066,20 +32066,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="167"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -32097,18 +32097,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="172"/>
       <c r="B5" s="173"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
       <c r="P5" s="251"/>
       <c r="Q5" s="251"/>
       <c r="R5" s="251"/>
@@ -32305,18 +32305,18 @@
       <c r="N10" s="134"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="246" t="s">
+      <c r="C11" s="245" t="s">
         <v>293</v>
       </c>
-      <c r="D11" s="246"/>
-      <c r="E11" s="246"/>
-      <c r="F11" s="246"/>
-      <c r="G11" s="246"/>
-      <c r="H11" s="246"/>
-      <c r="I11" s="246"/>
-      <c r="J11" s="246"/>
-      <c r="K11" s="246"/>
-      <c r="L11" s="246"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
       <c r="N11" s="134"/>
       <c r="P11" s="251"/>
       <c r="Q11" s="251"/>
@@ -32570,18 +32570,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="246" t="s">
+      <c r="C18" s="245" t="s">
         <v>298</v>
       </c>
-      <c r="D18" s="246"/>
-      <c r="E18" s="246"/>
-      <c r="F18" s="246"/>
-      <c r="G18" s="246"/>
-      <c r="H18" s="246"/>
-      <c r="I18" s="246"/>
-      <c r="J18" s="246"/>
-      <c r="K18" s="246"/>
-      <c r="L18" s="246"/>
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
+      <c r="G18" s="245"/>
+      <c r="H18" s="245"/>
+      <c r="I18" s="245"/>
+      <c r="J18" s="245"/>
+      <c r="K18" s="245"/>
+      <c r="L18" s="245"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -32799,18 +32799,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="186"/>
-      <c r="C26" s="246" t="s">
+      <c r="C26" s="245" t="s">
         <v>304</v>
       </c>
-      <c r="D26" s="246"/>
-      <c r="E26" s="246"/>
-      <c r="F26" s="246"/>
-      <c r="G26" s="246"/>
-      <c r="H26" s="246"/>
-      <c r="I26" s="246"/>
-      <c r="J26" s="246"/>
-      <c r="K26" s="246"/>
-      <c r="L26" s="246"/>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+      <c r="K26" s="245"/>
+      <c r="L26" s="245"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -33002,18 +33002,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="186"/>
-      <c r="C33" s="246" t="s">
+      <c r="C33" s="245" t="s">
         <v>308</v>
       </c>
-      <c r="D33" s="246"/>
-      <c r="E33" s="246"/>
-      <c r="F33" s="246"/>
-      <c r="G33" s="246"/>
-      <c r="H33" s="246"/>
-      <c r="I33" s="246"/>
-      <c r="J33" s="246"/>
-      <c r="K33" s="246"/>
-      <c r="L33" s="246"/>
+      <c r="D33" s="245"/>
+      <c r="E33" s="245"/>
+      <c r="F33" s="245"/>
+      <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
+      <c r="I33" s="245"/>
+      <c r="J33" s="245"/>
+      <c r="K33" s="245"/>
+      <c r="L33" s="245"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -33197,18 +33197,18 @@
       <c r="C39" s="202"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="246" t="s">
+      <c r="C40" s="245" t="s">
         <v>311</v>
       </c>
-      <c r="D40" s="246"/>
-      <c r="E40" s="246"/>
-      <c r="F40" s="246"/>
-      <c r="G40" s="246"/>
-      <c r="H40" s="246"/>
-      <c r="I40" s="246"/>
-      <c r="J40" s="246"/>
-      <c r="K40" s="246"/>
-      <c r="L40" s="246"/>
+      <c r="D40" s="245"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -33472,6 +33472,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -33479,12 +33485,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D40E9A-F16E-AD4B-A534-7C36DE678E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2840191-F312-1547-A563-46C45B48FD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="14" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -7312,17 +7312,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33472,12 +33472,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -33485,6 +33479,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105057DF-C07C-CF47-9982-105DDDAD4EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693C712B-05C1-F444-AFFD-59CCCFBF1F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="406">
   <si>
     <t>Ticker</t>
   </si>
@@ -1130,12 +1130,6 @@
     <t>Valuation</t>
   </si>
   <si>
-    <t>30.04.2026</t>
-  </si>
-  <si>
-    <t>Q1 2027</t>
-  </si>
-  <si>
     <t>Non-controlling interest</t>
   </si>
   <si>
@@ -1205,24 +1199,6 @@
     <t>Q2 2025</t>
   </si>
   <si>
-    <t>Gross Margin Lower</t>
-  </si>
-  <si>
-    <t>Gross Margin Upper</t>
-  </si>
-  <si>
-    <t>Actual Gross Margin</t>
-  </si>
-  <si>
-    <t>OpEx Lower</t>
-  </si>
-  <si>
-    <t>OpEx Upper</t>
-  </si>
-  <si>
-    <t>Actual OpEx</t>
-  </si>
-  <si>
     <t>PwC</t>
   </si>
   <si>
@@ -1374,6 +1350,24 @@
   </si>
   <si>
     <t>QTL Growth Rate</t>
+  </si>
+  <si>
+    <t>QCT Revenue Lower</t>
+  </si>
+  <si>
+    <t>QCT Revenue Upper</t>
+  </si>
+  <si>
+    <t>Actual QCT Revenue</t>
+  </si>
+  <si>
+    <t>QTL Revenue Lower</t>
+  </si>
+  <si>
+    <t>QTL Revenue Upper</t>
+  </si>
+  <si>
+    <t>Actual QTL Revenue</t>
   </si>
 </sst>
 </file>
@@ -2272,7 +2266,6 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -2286,9 +2279,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2298,6 +2289,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2305,12 +2305,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2819,6 +2813,301 @@
         </a:p>
       </c:txPr>
     </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>FCFE</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Quarter'!$C$66:$J$66</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_);\(#,##0\)</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3551</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1638</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1922</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2926</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3528</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1055</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2537-A641-96D5-AEFA40A2B2D6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1163393471"/>
+        <c:axId val="1163381375"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1163393471"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1163381375"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1163381375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);\(#,##0\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1163393471"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -4696,6 +4985,368 @@
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Price 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$72:$L$72</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90.521362414102185</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80.430236032267715</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>127.07648640573647</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>126.38183447863757</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8918-6343-9993-B2D9E1A85BD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Revenue 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$73:$L$73</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>131.68086754453913</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>106.71512840374189</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>116.07579097896681</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>131.93112077697671</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8918-6343-9993-B2D9E1A85BD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>EPS 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$74:$L$74</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>144.98094027954255</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82.846251588310025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>113.59593392630241</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>129.26112679457472</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8918-6343-9993-B2D9E1A85BD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1761086079"/>
+        <c:axId val="1761092351"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1761086079"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1761092351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1761092351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1761086079"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -5130,7 +5781,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5581,7 +6232,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6131,302 +6782,47 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>FCFE</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="34925" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>'Graphs Quarter'!$C$66:$J$66</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0_);\(#,##0\)</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3551</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1638</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1922</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2926</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3528</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1055</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2537-A641-96D5-AEFA40A2B2D6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1163393471"/>
-        <c:axId val="1163381375"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1163393471"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1163381375"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1163381375"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="#,##0_);\(#,##0\)" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1163393471"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7277,6 +7673,502 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -9267,7 +10159,7 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9289,11 +10181,11 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
             <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9370,7 +10262,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
@@ -9380,7 +10272,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -9390,7 +10282,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="34925" cap="rnd">
@@ -9410,7 +10302,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9429,7 +10321,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -9466,7 +10358,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9490,7 +10382,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9509,7 +10401,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -9527,7 +10419,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -9535,7 +10427,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -9554,7 +10446,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
@@ -9572,7 +10464,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9591,7 +10483,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9620,7 +10512,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -9628,7 +10520,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -9698,7 +10590,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -9724,7 +10616,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9756,7 +10648,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -10755,7 +11647,7 @@
 </file>
 
 <file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -10777,11 +11669,11 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
             <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -10858,7 +11750,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
@@ -10868,7 +11760,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -10878,7 +11770,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="34925" cap="rnd">
@@ -10898,7 +11790,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -10917,7 +11809,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -10954,7 +11846,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -10978,7 +11870,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -10997,7 +11889,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -11015,7 +11907,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -11023,7 +11915,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -11042,7 +11934,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
@@ -11060,7 +11952,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -11079,7 +11971,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -11108,7 +12000,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -11116,7 +12008,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -11186,7 +12078,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -11212,7 +12104,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -11244,7 +12136,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -11427,6 +12319,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>741234</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>50162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>377008</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>197450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CFB7AC8-5677-A22B-6F2A-337F1094351C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -12723,18 +13651,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="231" t="s">
+      <c r="B2" s="230" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="232"/>
-      <c r="E2" s="231" t="s">
+      <c r="C2" s="231"/>
+      <c r="E2" s="230" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="232"/>
-      <c r="H2" s="231" t="s">
+      <c r="F2" s="231"/>
+      <c r="H2" s="230" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="232"/>
+      <c r="I2" s="231"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -12795,7 +13723,7 @@
       <c r="E5" s="185" t="s">
         <v>240</v>
       </c>
-      <c r="F5" s="189">
+      <c r="F5" s="190">
         <f>Statement!AC26</f>
         <v>9.418342702074046</v>
       </c>
@@ -12805,7 +13733,7 @@
       </c>
       <c r="I5" s="211">
         <f>'AVG target price'!C7</f>
-        <v>184.98583880894876</v>
+        <v>190.70675093537938</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -12853,7 +13781,7 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>163.59667794270533</v>
+        <v>165.026905974313</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -12877,7 +13805,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.27647305319222804</v>
+        <v>-0.27014768929143784</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12995,10 +13923,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="233" t="s">
+      <c r="B17" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="233"/>
+      <c r="C17" s="232"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -13012,7 +13940,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="69" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E18" s="185" t="s">
         <v>294</v>
@@ -13067,18 +13995,18 @@
         <v>87</v>
       </c>
       <c r="C22" s="69" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="233" t="s">
+      <c r="B25" s="232" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="233"/>
-      <c r="E25" s="231" t="s">
-        <v>340</v>
-      </c>
-      <c r="F25" s="232"/>
+      <c r="C25" s="232"/>
+      <c r="E25" s="230" t="s">
+        <v>338</v>
+      </c>
+      <c r="F25" s="231"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13103,7 +14031,7 @@
         <v>4.65E-2</v>
       </c>
       <c r="E27" s="186" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
@@ -13112,7 +14040,7 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" s="184" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C28" s="221">
         <v>0</v>
@@ -13120,249 +14048,249 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="184" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C29" s="221">
         <v>0.12</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="230" t="s">
-        <v>335</v>
-      </c>
-      <c r="C33" s="230"/>
-      <c r="D33" s="230"/>
-      <c r="E33" s="230"/>
-      <c r="F33" s="230"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="230"/>
+      <c r="B33" s="233" t="s">
+        <v>333</v>
+      </c>
+      <c r="C33" s="233"/>
+      <c r="D33" s="233"/>
+      <c r="E33" s="233"/>
+      <c r="F33" s="233"/>
+      <c r="G33" s="233"/>
+      <c r="H33" s="233"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="230"/>
-      <c r="C39" s="230"/>
-      <c r="D39" s="230"/>
-      <c r="E39" s="230"/>
-      <c r="F39" s="230"/>
-      <c r="G39" s="230"/>
-      <c r="H39" s="230"/>
+      <c r="B39" s="233"/>
+      <c r="C39" s="233"/>
+      <c r="D39" s="233"/>
+      <c r="E39" s="233"/>
+      <c r="F39" s="233"/>
+      <c r="G39" s="233"/>
+      <c r="H39" s="233"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="230" t="s">
-        <v>338</v>
-      </c>
-      <c r="C42" s="230"/>
-      <c r="D42" s="230"/>
-      <c r="E42" s="230"/>
-      <c r="F42" s="230"/>
-      <c r="G42" s="230"/>
-      <c r="H42" s="230"/>
+      <c r="B42" s="233" t="s">
+        <v>336</v>
+      </c>
+      <c r="C42" s="233"/>
+      <c r="D42" s="233"/>
+      <c r="E42" s="233"/>
+      <c r="F42" s="233"/>
+      <c r="G42" s="233"/>
+      <c r="H42" s="233"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C44" s="41" t="s">
-        <v>326</v>
+        <v>377</v>
       </c>
       <c r="D44" s="41"/>
       <c r="E44" s="41" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="230"/>
-      <c r="C49" s="230"/>
-      <c r="D49" s="230"/>
-      <c r="E49" s="230"/>
-      <c r="F49" s="230"/>
-      <c r="G49" s="230"/>
-      <c r="H49" s="230"/>
+      <c r="B49" s="233"/>
+      <c r="C49" s="233"/>
+      <c r="D49" s="233"/>
+      <c r="E49" s="233"/>
+      <c r="F49" s="233"/>
+      <c r="G49" s="233"/>
+      <c r="H49" s="233"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="230" t="s">
+      <c r="B52" s="233" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="230"/>
-      <c r="D52" s="230"/>
-      <c r="E52" s="230"/>
-      <c r="F52" s="230"/>
-      <c r="G52" s="230"/>
-      <c r="H52" s="230"/>
+      <c r="C52" s="233"/>
+      <c r="D52" s="233"/>
+      <c r="E52" s="233"/>
+      <c r="F52" s="233"/>
+      <c r="G52" s="233"/>
+      <c r="H52" s="233"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C54" s="41" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="D54" s="41"/>
       <c r="E54" s="41" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" s="41" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C59" s="41" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="D59" s="41"/>
       <c r="E59" s="41" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64" s="41" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C64" s="41" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="D64" s="41"/>
       <c r="E64" s="41" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="230"/>
-      <c r="C69" s="230"/>
-      <c r="D69" s="230"/>
-      <c r="E69" s="230"/>
-      <c r="F69" s="230"/>
-      <c r="G69" s="230"/>
-      <c r="H69" s="230"/>
+      <c r="B69" s="233"/>
+      <c r="C69" s="233"/>
+      <c r="D69" s="233"/>
+      <c r="E69" s="233"/>
+      <c r="F69" s="233"/>
+      <c r="G69" s="233"/>
+      <c r="H69" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -13432,36 +14360,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="230" t="s">
+      <c r="S2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230"/>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
-      <c r="AA2" s="230" t="s">
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="230"/>
-      <c r="AC2" s="230"/>
+      <c r="AB2" s="233"/>
+      <c r="AC2" s="233"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -13595,7 +14523,7 @@
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B6" s="224" t="str">
+      <c r="B6" s="223" t="str">
         <f>Statement!B190</f>
         <v>Handset</v>
       </c>
@@ -13620,33 +14548,33 @@
         <v>27793</v>
       </c>
       <c r="H6" s="64">
-        <f>G6+G6*H15</f>
+        <f t="shared" ref="H6:L7" si="1">G6+G6*H15</f>
         <v>24457.84</v>
       </c>
       <c r="I6" s="64">
-        <f>H6+H6*I15</f>
+        <f t="shared" si="1"/>
         <v>23234.948</v>
       </c>
       <c r="J6" s="64">
-        <f>I6+I6*J15</f>
+        <f t="shared" si="1"/>
         <v>25326.09332</v>
       </c>
       <c r="K6" s="64">
-        <f>J6+J6*K15</f>
+        <f t="shared" si="1"/>
         <v>28365.224518399998</v>
       </c>
       <c r="L6" s="64">
-        <f>K6+K6*L15</f>
+        <f t="shared" si="1"/>
         <v>32620.008196159997</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="O6" s="5"/>
       <c r="Q6" s="90" t="s">
-        <v>404</v>
-      </c>
-      <c r="R6" s="224" t="str">
+        <v>396</v>
+      </c>
+      <c r="R6" s="223" t="str">
         <f>B6</f>
         <v>Handset</v>
       </c>
@@ -13694,7 +14622,7 @@
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B7" s="224" t="str">
+      <c r="B7" s="223" t="str">
         <f>Statement!B191</f>
         <v>Automotive</v>
       </c>
@@ -13719,34 +14647,34 @@
         <v>3957</v>
       </c>
       <c r="H7" s="64">
-        <f>G7+G7*H16</f>
+        <f t="shared" si="1"/>
         <v>4154.8500000000004</v>
       </c>
       <c r="I7" s="64">
-        <f>H7+H7*I16</f>
+        <f t="shared" si="1"/>
         <v>4778.0775000000003</v>
       </c>
       <c r="J7" s="64">
-        <f>I7+I7*J16</f>
+        <f t="shared" si="1"/>
         <v>5733.6930000000002</v>
       </c>
       <c r="K7" s="64">
-        <f>J7+J7*K16</f>
+        <f t="shared" si="1"/>
         <v>7740.4855500000003</v>
       </c>
       <c r="L7" s="64">
-        <f>K7+K7*L16</f>
+        <f t="shared" si="1"/>
         <v>10062.631215000001</v>
       </c>
       <c r="N7" s="90" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="O7" s="5"/>
       <c r="Q7" s="90" t="s">
-        <v>405</v>
-      </c>
-      <c r="R7" s="224" t="str">
-        <f t="shared" ref="R7:R10" si="1">B7</f>
+        <v>397</v>
+      </c>
+      <c r="R7" s="223" t="str">
+        <f t="shared" ref="R7:R10" si="2">B7</f>
         <v>Automotive</v>
       </c>
       <c r="S7" s="88">
@@ -13788,12 +14716,12 @@
       <c r="AB7" s="64"/>
       <c r="AC7" s="64"/>
       <c r="AE7" s="64">
-        <f t="shared" ref="AE7:AE10" si="2">SUM(X7:AA7)</f>
+        <f t="shared" ref="AE7:AE10" si="3">SUM(X7:AA7)</f>
         <v>5270.1</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B8" s="224" t="str">
+      <c r="B8" s="223" t="str">
         <f>Statement!B192</f>
         <v>IoT</v>
       </c>
@@ -13826,26 +14754,26 @@
         <v>7505.0014000000001</v>
       </c>
       <c r="J8" s="64">
-        <f t="shared" ref="J8:L8" si="3">I8+I8*J17</f>
+        <f t="shared" ref="J8:L8" si="4">I8+I8*J17</f>
         <v>8030.351498</v>
       </c>
       <c r="K8" s="64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8592.4761028600005</v>
       </c>
       <c r="L8" s="64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9193.9494300602</v>
       </c>
       <c r="N8" s="90" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="O8" s="5"/>
       <c r="Q8" s="90" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="R8" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>IoT</v>
       </c>
       <c r="S8" s="88">
@@ -13887,7 +14815,7 @@
       <c r="AB8" s="64"/>
       <c r="AC8" s="64"/>
       <c r="AE8" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7067.82</v>
       </c>
     </row>
@@ -13921,26 +14849,26 @@
         <v>35626.710000000006</v>
       </c>
       <c r="I9" s="64">
-        <f t="shared" ref="I9:L9" si="4">SUM(I6:I8)</f>
+        <f t="shared" ref="I9:L9" si="5">SUM(I6:I8)</f>
         <v>35518.026899999997</v>
       </c>
       <c r="J9" s="64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39090.137818000003</v>
       </c>
       <c r="K9" s="64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>44698.186171259993</v>
       </c>
       <c r="L9" s="64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>51876.588841220197</v>
       </c>
       <c r="N9" s="90"/>
       <c r="O9" s="5"/>
       <c r="Q9" s="90"/>
       <c r="R9" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>QCT</v>
       </c>
       <c r="S9" s="88">
@@ -13982,7 +14910,7 @@
       <c r="AB9" s="64"/>
       <c r="AC9" s="64"/>
       <c r="AE9" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>37664.92</v>
       </c>
     </row>
@@ -14016,30 +14944,30 @@
         <v>5247.08</v>
       </c>
       <c r="I10" s="64">
-        <f t="shared" ref="I10:L10" si="5">H10+H10*I19</f>
+        <f t="shared" ref="I10:L10" si="6">H10+H10*I19</f>
         <v>5089.6675999999998</v>
       </c>
       <c r="J10" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5191.4609519999995</v>
       </c>
       <c r="K10" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5347.2047805599996</v>
       </c>
       <c r="L10" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5507.6209239767995</v>
       </c>
       <c r="N10" s="90" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="O10" s="5"/>
       <c r="Q10" s="90" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="R10" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>QTL</v>
       </c>
       <c r="S10" s="88">
@@ -14081,7 +15009,7 @@
       <c r="AB10" s="64"/>
       <c r="AC10" s="64"/>
       <c r="AE10" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5626.8</v>
       </c>
     </row>
@@ -14114,19 +15042,19 @@
         <v>40873.790000000008</v>
       </c>
       <c r="I11" s="94">
-        <f t="shared" ref="I11:L11" si="6">I9+I10</f>
+        <f t="shared" ref="I11:L11" si="7">I9+I10</f>
         <v>40607.694499999998</v>
       </c>
       <c r="J11" s="94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>44281.598770000004</v>
       </c>
       <c r="K11" s="94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50045.390951819994</v>
       </c>
       <c r="L11" s="94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>57384.209765196996</v>
       </c>
       <c r="O11" s="5"/>
@@ -14214,43 +15142,43 @@
         <v>115</v>
       </c>
       <c r="C14" s="12">
-        <f t="shared" ref="C14:L14" si="7">C5</f>
+        <f t="shared" ref="C14:L14" si="8">C5</f>
         <v>2021</v>
       </c>
       <c r="D14" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2022</v>
       </c>
       <c r="E14" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2023</v>
       </c>
       <c r="F14" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2024</v>
       </c>
       <c r="G14" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2025</v>
       </c>
       <c r="H14" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2026</v>
       </c>
       <c r="I14" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2027</v>
       </c>
       <c r="J14" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2028</v>
       </c>
       <c r="K14" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2029</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2030</v>
       </c>
       <c r="O14" s="5"/>
@@ -14259,70 +15187,70 @@
         <v>115</v>
       </c>
       <c r="S14" s="12" t="str">
-        <f t="shared" ref="S14:AC14" si="8">S5</f>
+        <f t="shared" ref="S14:AC14" si="9">S5</f>
         <v>Q3 2024</v>
       </c>
       <c r="T14" s="12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Q4 2024</v>
       </c>
       <c r="U14" s="12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Q1 2025</v>
       </c>
       <c r="V14" s="12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Q2 2025</v>
       </c>
       <c r="W14" s="12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Q3 2025</v>
       </c>
       <c r="X14" s="12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Q4 2025</v>
       </c>
       <c r="Y14" s="12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Q1 2026</v>
       </c>
       <c r="Z14" s="12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Q2 2026</v>
       </c>
       <c r="AA14" s="12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>FQ1</v>
       </c>
       <c r="AB14" s="12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>FQ2</v>
       </c>
       <c r="AC14" s="12" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>FQ3</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B15" s="224" t="str">
+      <c r="B15" s="223" t="str">
         <f>B6</f>
         <v>Handset</v>
       </c>
       <c r="C15" s="47"/>
       <c r="D15" s="95">
-        <f t="shared" ref="D15:G15" si="9">D6/C6-1</f>
+        <f t="shared" ref="D15:G15" si="10">D6/C6-1</f>
         <v>0.48704693998811655</v>
       </c>
       <c r="E15" s="95">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-9.8173972110121022E-2</v>
       </c>
       <c r="F15" s="95">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.1015950376606114</v>
       </c>
       <c r="G15" s="96">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.11784579495636094</v>
       </c>
       <c r="H15" s="97">
@@ -14342,37 +15270,37 @@
       </c>
       <c r="O15" s="5"/>
       <c r="Q15" s="91"/>
-      <c r="R15" s="224" t="str">
-        <f>R6</f>
+      <c r="R15" s="223" t="str">
+        <f t="shared" ref="R15:R20" si="11">R6</f>
         <v>Handset</v>
       </c>
       <c r="S15" s="47"/>
       <c r="T15" s="95">
-        <f>T6/S6-1</f>
+        <f t="shared" ref="T15:Z17" si="12">T6/S6-1</f>
         <v>3.3395490761146007E-2</v>
       </c>
       <c r="U15" s="95">
-        <f>U6/T6-1</f>
+        <f t="shared" si="12"/>
         <v>0.24245406824146976</v>
       </c>
       <c r="V15" s="95">
-        <f>V6/U6-1</f>
+        <f t="shared" si="12"/>
         <v>-8.5159757063638764E-2</v>
       </c>
       <c r="W15" s="95">
-        <f>W6/V6-1</f>
+        <f t="shared" si="12"/>
         <v>-8.673690287198732E-2</v>
       </c>
       <c r="X15" s="95">
-        <f>X6/W6-1</f>
+        <f t="shared" si="12"/>
         <v>0.10003160556257895</v>
       </c>
       <c r="Y15" s="95">
-        <f>Y6/X6-1</f>
+        <f t="shared" si="12"/>
         <v>0.12397644016664278</v>
       </c>
       <c r="Z15" s="96">
-        <f>Z6/Y6-1</f>
+        <f t="shared" si="12"/>
         <v>-0.23006134969325154</v>
       </c>
       <c r="AA15" s="97">
@@ -14382,25 +15310,25 @@
       <c r="AC15" s="95"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B16" s="224" t="str">
+      <c r="B16" s="223" t="str">
         <f>B7</f>
         <v>Automotive</v>
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="95">
-        <f t="shared" ref="D16:G16" si="10">D7/C7-1</f>
+        <f t="shared" ref="D16:G16" si="13">D7/C7-1</f>
         <v>0.40717948717948715</v>
       </c>
       <c r="E16" s="95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.36443148688046656</v>
       </c>
       <c r="F16" s="95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.55448717948717952</v>
       </c>
       <c r="G16" s="96">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.35979381443298974</v>
       </c>
       <c r="H16" s="97">
@@ -14420,37 +15348,37 @@
       </c>
       <c r="O16" s="5"/>
       <c r="Q16" s="91"/>
-      <c r="R16" s="224" t="str">
-        <f>R7</f>
+      <c r="R16" s="223" t="str">
+        <f t="shared" si="11"/>
         <v>Automotive</v>
       </c>
       <c r="S16" s="47"/>
       <c r="T16" s="95">
-        <f>T7/S7-1</f>
+        <f t="shared" si="12"/>
         <v>0.10850801479654737</v>
       </c>
       <c r="U16" s="95">
-        <f>U7/T7-1</f>
+        <f t="shared" si="12"/>
         <v>6.8965517241379226E-2</v>
       </c>
       <c r="V16" s="95">
-        <f>V7/U7-1</f>
+        <f t="shared" si="12"/>
         <v>-2.0811654526534662E-3</v>
       </c>
       <c r="W16" s="95">
-        <f>W7/V7-1</f>
+        <f t="shared" si="12"/>
         <v>2.6068821689259725E-2</v>
       </c>
       <c r="X16" s="95">
-        <f>X7/W7-1</f>
+        <f t="shared" si="12"/>
         <v>7.0121951219512146E-2</v>
       </c>
       <c r="Y16" s="95">
-        <f>Y7/X7-1</f>
+        <f t="shared" si="12"/>
         <v>4.5584045584045496E-2</v>
       </c>
       <c r="Z16" s="96">
-        <f>Z7/Y7-1</f>
+        <f t="shared" si="12"/>
         <v>0.20435967302452318</v>
       </c>
       <c r="AA16" s="97">
@@ -14460,7 +15388,7 @@
       <c r="AC16" s="95"/>
     </row>
     <row r="17" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B17" s="224" t="str">
+      <c r="B17" s="223" t="str">
         <f>B8</f>
         <v>IoT</v>
       </c>
@@ -14499,36 +15427,36 @@
       <c r="O17" s="5"/>
       <c r="Q17" s="91"/>
       <c r="R17" s="1" t="str">
-        <f>R8</f>
+        <f t="shared" si="11"/>
         <v>IoT</v>
       </c>
       <c r="S17" s="47"/>
       <c r="T17" s="95">
-        <f>T8/S8-1</f>
+        <f t="shared" si="12"/>
         <v>0.23841059602649017</v>
       </c>
       <c r="U17" s="95">
-        <f>U8/T8-1</f>
+        <f t="shared" si="12"/>
         <v>-7.9619726678550218E-2</v>
       </c>
       <c r="V17" s="95">
-        <f>V8/U8-1</f>
+        <f t="shared" si="12"/>
         <v>2.0658489347966436E-2</v>
       </c>
       <c r="W17" s="95">
-        <f>W8/V8-1</f>
+        <f t="shared" si="12"/>
         <v>6.3251106894370634E-2</v>
       </c>
       <c r="X17" s="95">
-        <f>X8/W8-1</f>
+        <f t="shared" si="12"/>
         <v>7.4955383700178402E-2</v>
       </c>
       <c r="Y17" s="95">
-        <f>Y8/X8-1</f>
+        <f t="shared" si="12"/>
         <v>-6.585500830105151E-2</v>
       </c>
       <c r="Z17" s="96">
-        <f>Z8/Y8-1</f>
+        <f t="shared" si="12"/>
         <v>2.2511848341232321E-2</v>
       </c>
       <c r="AA17" s="97">
@@ -14548,15 +15476,15 @@
         <v>0.39446315555720046</v>
       </c>
       <c r="E18" s="95">
-        <f t="shared" ref="E18:E19" si="11">E9/D9-1</f>
+        <f t="shared" ref="E18:E19" si="14">E9/D9-1</f>
         <v>-0.19361944953154442</v>
       </c>
       <c r="F18" s="95">
-        <f t="shared" ref="F18:F19" si="12">F9/E9-1</f>
+        <f t="shared" ref="F18:F19" si="15">F9/E9-1</f>
         <v>9.2620630636561119E-2</v>
       </c>
       <c r="G18" s="96">
-        <f t="shared" ref="G18:G19" si="13">G9/F9-1</f>
+        <f t="shared" ref="G18:G19" si="16">G9/F9-1</f>
         <v>0.15577177973249778</v>
       </c>
       <c r="H18" s="95">
@@ -14564,25 +15492,25 @@
         <v>-7.1423097974821936E-2</v>
       </c>
       <c r="I18" s="95">
-        <f t="shared" ref="I18:L18" si="14">I9/H9-1</f>
+        <f t="shared" ref="I18:L18" si="17">I9/H9-1</f>
         <v>-3.0506072550625651E-3</v>
       </c>
       <c r="J18" s="95">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.10057177241453141</v>
       </c>
       <c r="K18" s="95">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.14346453264939951</v>
       </c>
       <c r="L18" s="95">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.16059718044164772</v>
       </c>
       <c r="O18" s="5"/>
       <c r="Q18" s="91"/>
       <c r="R18" s="1" t="str">
-        <f>R9</f>
+        <f t="shared" si="11"/>
         <v>QCT</v>
       </c>
       <c r="S18" s="47"/>
@@ -14591,23 +15519,23 @@
         <v>7.5474036435741798E-2</v>
       </c>
       <c r="U18" s="95">
-        <f t="shared" ref="U18:Y18" si="15">U9/T9-1</f>
+        <f t="shared" ref="U18:Y18" si="18">U9/T9-1</f>
         <v>0.16201889836367833</v>
       </c>
       <c r="V18" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-6.0987703292344264E-2</v>
       </c>
       <c r="W18" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-5.0269299820466795E-2</v>
       </c>
       <c r="X18" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>9.2071611253196961E-2</v>
       </c>
       <c r="Y18" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>8.0643518989919505E-2</v>
       </c>
       <c r="Z18" s="96">
@@ -14622,7 +15550,7 @@
     </row>
     <row r="19" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C19" s="47"/>
       <c r="D19" s="95">
@@ -14630,15 +15558,15 @@
         <v>6.0126582278481333E-3</v>
       </c>
       <c r="E19" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-0.16546083674111356</v>
       </c>
       <c r="F19" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>5.0131926121371961E-2</v>
       </c>
       <c r="G19" s="96">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1.7946877243359971E-3</v>
       </c>
       <c r="H19" s="97">
@@ -14659,7 +15587,7 @@
       <c r="O19" s="5"/>
       <c r="Q19" s="91"/>
       <c r="R19" s="1" t="str">
-        <f>R10</f>
+        <f t="shared" si="11"/>
         <v>QTL</v>
       </c>
       <c r="S19" s="47"/>
@@ -14668,27 +15596,27 @@
         <v>-0.20267085624509029</v>
       </c>
       <c r="U19" s="95">
-        <f t="shared" ref="U19:Z19" si="16">U10/T10-1</f>
+        <f t="shared" ref="U19:Z19" si="19">U10/T10-1</f>
         <v>0.51231527093596063</v>
       </c>
       <c r="V19" s="95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>-0.14071661237785016</v>
       </c>
       <c r="W19" s="95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>-7.5815011372248886E-4</v>
       </c>
       <c r="X19" s="95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>6.9044006069802766E-2</v>
       </c>
       <c r="Y19" s="95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.12987934705464865</v>
       </c>
       <c r="Z19" s="96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>-0.13190954773869346</v>
       </c>
       <c r="AA19" s="97">
@@ -14704,78 +15632,78 @@
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="103">
-        <f t="shared" ref="D20:L20" si="17">D11/C11-1</f>
+        <f t="shared" ref="D20:L20" si="20">D11/C11-1</f>
         <v>0.31680867544539115</v>
       </c>
       <c r="E20" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>-0.18959276018099547</v>
       </c>
       <c r="F20" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>8.7716359575656044E-2</v>
       </c>
       <c r="G20" s="104">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.13659463066577682</v>
       </c>
       <c r="H20" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>-7.700772287959512E-2</v>
       </c>
       <c r="I20" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>-6.5101743684646829E-3</v>
       </c>
       <c r="J20" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>9.047310651925855E-2</v>
       </c>
       <c r="K20" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.13016224214842165</v>
       </c>
       <c r="L20" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.14664325073296514</v>
       </c>
       <c r="O20" s="5"/>
       <c r="Q20" s="91"/>
       <c r="R20" s="16" t="str">
-        <f>R11</f>
+        <f t="shared" si="11"/>
         <v>Total</v>
       </c>
       <c r="S20" s="47"/>
       <c r="T20" s="103">
-        <f t="shared" ref="T20:AA20" si="18">T11/S11-1</f>
+        <f t="shared" ref="T20:AA20" si="21">T11/S11-1</f>
         <v>9.0599382518897098E-2</v>
       </c>
       <c r="U20" s="103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0.13910581803982813</v>
       </c>
       <c r="V20" s="103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-5.9131030936669826E-2</v>
       </c>
       <c r="W20" s="103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-4.681664996812096E-2</v>
       </c>
       <c r="X20" s="103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>7.6923076923076872E-2</v>
       </c>
       <c r="Y20" s="103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>8.7133984028394007E-2</v>
       </c>
       <c r="Z20" s="104">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-0.13491674828599409</v>
       </c>
       <c r="AA20" s="103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-0.11324464572129456</v>
       </c>
       <c r="AB20" s="103"/>
@@ -14831,35 +15759,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
-      <c r="P2" s="230" t="s">
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
+      <c r="P2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="230"/>
-      <c r="R2" s="230"/>
-      <c r="S2" s="230"/>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230" t="s">
+      <c r="Q2" s="233"/>
+      <c r="R2" s="233"/>
+      <c r="S2" s="233"/>
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16090,20 +17018,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -17496,6 +18424,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -17503,12 +18437,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17546,20 +18474,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="S2" s="244"/>
       <c r="T2" s="244"/>
       <c r="U2" s="244"/>
@@ -18433,7 +19361,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C32" s="12">
         <f>C5</f>
@@ -18568,16 +19496,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -18640,10 +19568,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="230"/>
+      <c r="C4" s="233"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -18728,10 +19656,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
+      <c r="B15" s="233" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="230"/>
+      <c r="C15" s="233"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -18820,20 +19748,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -19119,10 +20047,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="230" t="s">
+      <c r="B13" s="233" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="230"/>
+      <c r="C13" s="233"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19142,10 +20070,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="230" t="s">
+      <c r="B18" s="233" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="230"/>
+      <c r="C18" s="233"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19259,20 +20187,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -19766,23 +20694,23 @@
       </c>
       <c r="H18" s="143">
         <f>G18*(1+H19)</f>
-        <v>1088.425</v>
+        <v>1077.375</v>
       </c>
       <c r="I18" s="143">
         <f t="shared" ref="I18:L18" si="5">H18*(1+I19)</f>
-        <v>1077.5407499999999</v>
+        <v>1055.8274999999999</v>
       </c>
       <c r="J18" s="143">
         <f t="shared" si="5"/>
-        <v>1066.7653424999999</v>
+        <v>1039.9900874999998</v>
       </c>
       <c r="K18" s="143">
         <f t="shared" si="5"/>
-        <v>1061.4315157874998</v>
+        <v>1029.5901866249999</v>
       </c>
       <c r="L18" s="143">
         <f t="shared" si="5"/>
-        <v>1056.1243582085624</v>
+        <v>1024.4422356918749</v>
       </c>
       <c r="N18" s="91"/>
     </row>
@@ -19808,16 +20736,16 @@
         <v>-2.2123893805309769E-2</v>
       </c>
       <c r="H19" s="146">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="I19" s="97">
+        <v>-0.02</v>
+      </c>
+      <c r="J19" s="97">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="I19" s="97">
+      <c r="K19" s="97">
         <v>-0.01</v>
-      </c>
-      <c r="J19" s="97">
-        <v>-0.01</v>
-      </c>
-      <c r="K19" s="97">
-        <v>-5.0000000000000001E-3</v>
       </c>
       <c r="L19" s="97">
         <v>-5.0000000000000001E-3</v>
@@ -20204,10 +21132,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="230" t="s">
+      <c r="B37" s="233" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="230"/>
+      <c r="C37" s="233"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20247,7 +21175,7 @@
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
@@ -20273,10 +21201,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="230" t="s">
+      <c r="B46" s="233" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="230"/>
+      <c r="C46" s="233"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -20289,7 +21217,7 @@
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C48" s="135">
         <f>Overview!C29</f>
@@ -20310,7 +21238,7 @@
       </c>
       <c r="C50" s="24">
         <f>L18</f>
-        <v>1056.1243582085624</v>
+        <v>1024.4422356918749</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
@@ -20319,7 +21247,7 @@
       </c>
       <c r="C51" s="24">
         <f>(C47*C49)/C50</f>
-        <v>326.00825453472675</v>
+        <v>336.09045644105976</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -20328,14 +21256,14 @@
       </c>
       <c r="C52" s="142">
         <f>C51/(1+C48)^5</f>
-        <v>184.98583880894876</v>
+        <v>190.70675093537938</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="230" t="s">
+      <c r="B54" s="233" t="s">
         <v>319</v>
       </c>
-      <c r="C54" s="230"/>
+      <c r="C54" s="233"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -20357,7 +21285,7 @@
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" s="39" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C57" s="105">
         <v>25</v>
@@ -20374,7 +21302,7 @@
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C59" s="24">
         <f ca="1">C58/(1+C56)^5-G30+G31</f>
@@ -20448,10 +21376,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="230"/>
+      <c r="C4" s="233"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -20478,7 +21406,7 @@
       </c>
       <c r="C7" s="133">
         <f>Multiples!C52</f>
-        <v>184.98583880894876</v>
+        <v>190.70675093537938</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -20496,7 +21424,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>163.59667794270533</v>
+        <v>165.026905974313</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -20514,7 +21442,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.27647305319222804</v>
+        <v>-0.27014768929143784</v>
       </c>
     </row>
   </sheetData>
@@ -20579,20 +21507,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -20918,7 +21846,7 @@
       <c r="B21" s="159" t="s">
         <v>157</v>
       </c>
-      <c r="C21" s="226">
+      <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.11214224057861526</v>
       </c>
@@ -20927,7 +21855,7 @@
       <c r="B22" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="227">
+      <c r="C22" s="226">
         <f>Statement!AC75</f>
         <v>1054</v>
       </c>
@@ -20945,7 +21873,7 @@
       <c r="B24" s="159" t="s">
         <v>170</v>
       </c>
-      <c r="C24" s="227">
+      <c r="C24" s="226">
         <f>Statement!AC106</f>
         <v>9799</v>
       </c>
@@ -20954,7 +21882,7 @@
       <c r="B25" s="159" t="s">
         <v>161</v>
       </c>
-      <c r="C25" s="227">
+      <c r="C25" s="226">
         <f>Statement!AC107</f>
         <v>15270</v>
       </c>
@@ -21491,17 +22419,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -21548,45 +22476,45 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="M2" s="10" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="10" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="X2" s="10" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="Y2" s="10" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -21615,28 +22543,28 @@
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="10" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="X3" s="10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Y3" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="AA3" s="10" t="s">
         <v>347</v>
-      </c>
-      <c r="Z3" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="AA3" s="10" t="s">
-        <v>349</v>
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="59" t="s">
@@ -21945,7 +22873,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -22003,7 +22931,7 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
@@ -22464,7 +23392,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B17" s="23" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -23126,6 +24054,8 @@
         <f>Q25/Q$85</f>
         <v>10.172850678733031</v>
       </c>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
       <c r="T26" s="66">
         <f t="shared" ref="T26:AA26" si="11">T25/T$85</f>
         <v>1.86</v>
@@ -23504,7 +24434,7 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -24198,7 +25128,7 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -24314,7 +25244,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -24372,7 +25302,7 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
@@ -25239,7 +26169,7 @@
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C65" s="62"/>
       <c r="D65" s="62"/>
@@ -26752,7 +27682,7 @@
     </row>
     <row r="93" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B93" s="20" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C93" s="49"/>
       <c r="D93" s="50"/>
@@ -27780,7 +28710,7 @@
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B110" s="20" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C110" s="25"/>
       <c r="D110" s="25"/>
@@ -27851,7 +28781,7 @@
     </row>
     <row r="111" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B111" s="20" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C111" s="25"/>
       <c r="D111" s="25"/>
@@ -27989,7 +28919,7 @@
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B116" s="20" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C116" s="26"/>
       <c r="D116" s="26"/>
@@ -28303,28 +29233,28 @@
       <c r="P128" s="49"/>
       <c r="Q128" s="49"/>
       <c r="T128" s="21">
-        <v>31800</v>
+        <v>9500</v>
       </c>
       <c r="U128" s="21">
-        <v>36300</v>
+        <v>10500</v>
       </c>
       <c r="V128" s="21">
-        <v>42000</v>
+        <v>10300</v>
       </c>
       <c r="W128" s="21">
-        <v>44000</v>
+        <v>9900</v>
       </c>
       <c r="X128" s="21">
-        <v>53000</v>
+        <v>10300</v>
       </c>
       <c r="Y128" s="21">
-        <v>63700</v>
+        <v>11800</v>
       </c>
       <c r="Z128" s="21">
-        <v>76500</v>
+        <v>10200</v>
       </c>
       <c r="AA128" s="21">
-        <v>89000</v>
+        <v>9200</v>
       </c>
       <c r="AC128" s="49"/>
     </row>
@@ -28348,28 +29278,28 @@
       <c r="P129" s="49"/>
       <c r="Q129" s="49"/>
       <c r="T129" s="21">
-        <v>33500</v>
+        <v>10300</v>
       </c>
       <c r="U129" s="21">
-        <v>38300</v>
+        <v>11300</v>
       </c>
       <c r="V129" s="21">
-        <v>44000</v>
+        <v>11200</v>
       </c>
       <c r="W129" s="21">
-        <v>46000</v>
+        <v>10700</v>
       </c>
       <c r="X129" s="21">
-        <v>55000</v>
+        <v>11100</v>
       </c>
       <c r="Y129" s="21">
-        <v>66300</v>
+        <v>12600</v>
       </c>
       <c r="Z129" s="21">
-        <v>79500</v>
+        <v>11000</v>
       </c>
       <c r="AA129" s="21">
-        <v>93000</v>
+        <v>10000</v>
       </c>
       <c r="AC129" s="49"/>
     </row>
@@ -28445,43 +29375,43 @@
       <c r="O131" s="49"/>
       <c r="P131" s="49"/>
       <c r="Q131" s="49"/>
-      <c r="T131" s="228" t="str">
+      <c r="T131" s="227" t="str">
         <f t="shared" ref="T131:AA131" si="73">IF(T130&gt;T129, "BEAT", IF(T130&lt;T128, "MISSED", "MET"))</f>
-        <v>MISSED</v>
-      </c>
-      <c r="U131" s="228" t="str">
+        <v>MET</v>
+      </c>
+      <c r="U131" s="227" t="str">
+        <f t="shared" si="73"/>
+        <v>BEAT</v>
+      </c>
+      <c r="V131" s="227" t="str">
+        <f t="shared" si="73"/>
+        <v>MET</v>
+      </c>
+      <c r="W131" s="227" t="str">
+        <f t="shared" si="73"/>
+        <v>MET</v>
+      </c>
+      <c r="X131" s="227" t="str">
+        <f t="shared" si="73"/>
+        <v>BEAT</v>
+      </c>
+      <c r="Y131" s="227" t="str">
+        <f t="shared" si="73"/>
+        <v>MET</v>
+      </c>
+      <c r="Z131" s="227" t="str">
+        <f t="shared" si="73"/>
+        <v>MET</v>
+      </c>
+      <c r="AA131" s="227" t="str">
         <f t="shared" si="73"/>
         <v>MISSED</v>
       </c>
-      <c r="V131" s="228" t="str">
-        <f t="shared" si="73"/>
-        <v>MISSED</v>
-      </c>
-      <c r="W131" s="228" t="str">
-        <f t="shared" si="73"/>
-        <v>MISSED</v>
-      </c>
-      <c r="X131" s="228" t="str">
-        <f t="shared" si="73"/>
-        <v>MISSED</v>
-      </c>
-      <c r="Y131" s="228" t="str">
-        <f t="shared" si="73"/>
-        <v>MISSED</v>
-      </c>
-      <c r="Z131" s="228" t="str">
-        <f t="shared" si="73"/>
-        <v>MISSED</v>
-      </c>
-      <c r="AA131" s="228" t="str">
-        <f t="shared" si="73"/>
-        <v>MISSED</v>
-      </c>
       <c r="AC131" s="49"/>
     </row>
     <row r="132" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B132" s="20" t="s">
-        <v>351</v>
+        <v>400</v>
       </c>
       <c r="C132" s="49"/>
       <c r="D132" s="49"/>
@@ -28498,35 +29428,35 @@
       <c r="O132" s="49"/>
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
-      <c r="T132" s="222">
-        <v>0.73899999999999999</v>
-      </c>
-      <c r="U132" s="222">
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="V132" s="222">
-        <v>0.70099999999999996</v>
-      </c>
-      <c r="W132" s="222">
-        <v>0.71299999999999997</v>
-      </c>
-      <c r="X132" s="222">
-        <v>0.72799999999999998</v>
-      </c>
-      <c r="Y132" s="222">
-        <v>0.74299999999999999</v>
-      </c>
-      <c r="Z132" s="222">
-        <v>0.745</v>
-      </c>
-      <c r="AA132" s="222">
-        <v>0.745</v>
+      <c r="T132" s="21">
+        <v>8100</v>
+      </c>
+      <c r="U132" s="21">
+        <v>9000</v>
+      </c>
+      <c r="V132" s="21">
+        <v>8900</v>
+      </c>
+      <c r="W132" s="21">
+        <v>8700</v>
+      </c>
+      <c r="X132" s="21">
+        <v>9000</v>
+      </c>
+      <c r="Y132" s="21">
+        <v>10300</v>
+      </c>
+      <c r="Z132" s="21">
+        <v>8800</v>
+      </c>
+      <c r="AA132" s="21">
+        <v>7900</v>
       </c>
       <c r="AC132" s="49"/>
     </row>
     <row r="133" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B133" s="20" t="s">
-        <v>352</v>
+        <v>401</v>
       </c>
       <c r="C133" s="49"/>
       <c r="D133" s="49"/>
@@ -28543,35 +29473,35 @@
       <c r="O133" s="49"/>
       <c r="P133" s="49"/>
       <c r="Q133" s="49"/>
-      <c r="T133" s="222">
-        <v>0.749</v>
-      </c>
-      <c r="U133" s="222">
-        <v>0.73499999999999999</v>
-      </c>
-      <c r="V133" s="222">
-        <v>0.71099999999999997</v>
-      </c>
-      <c r="W133" s="222">
-        <v>0.72299999999999998</v>
-      </c>
-      <c r="X133" s="222">
-        <v>0.73799999999999999</v>
-      </c>
-      <c r="Y133" s="222">
-        <v>0.754</v>
-      </c>
-      <c r="Z133" s="222">
-        <v>0.754</v>
-      </c>
-      <c r="AA133" s="222">
-        <v>0.754</v>
+      <c r="T133" s="21">
+        <v>8700</v>
+      </c>
+      <c r="U133" s="21">
+        <v>9600</v>
+      </c>
+      <c r="V133" s="21">
+        <v>9500</v>
+      </c>
+      <c r="W133" s="21">
+        <v>9300</v>
+      </c>
+      <c r="X133" s="21">
+        <v>9600</v>
+      </c>
+      <c r="Y133" s="21">
+        <v>10900</v>
+      </c>
+      <c r="Z133" s="21">
+        <v>9400</v>
+      </c>
+      <c r="AA133" s="21">
+        <v>8500</v>
       </c>
       <c r="AC133" s="49"/>
     </row>
     <row r="134" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B134" s="20" t="s">
-        <v>353</v>
+        <v>402</v>
       </c>
       <c r="C134" s="49"/>
       <c r="D134" s="49"/>
@@ -28588,36 +29518,36 @@
       <c r="O134" s="49"/>
       <c r="P134" s="49"/>
       <c r="Q134" s="49"/>
-      <c r="T134" s="81">
-        <f t="shared" ref="T134:AA134" si="74">U100</f>
-        <v>0.56393986723935963</v>
-      </c>
-      <c r="U134" s="81">
+      <c r="T134" s="25">
+        <f t="shared" ref="T134:Y134" si="74">U193</f>
+        <v>8678</v>
+      </c>
+      <c r="U134" s="25">
         <f t="shared" si="74"/>
-        <v>0.55771702802296685</v>
-      </c>
-      <c r="V134" s="81">
+        <v>10084</v>
+      </c>
+      <c r="V134" s="25">
         <f t="shared" si="74"/>
-        <v>0.55032334456690046</v>
-      </c>
-      <c r="W134" s="81">
+        <v>9469</v>
+      </c>
+      <c r="W134" s="25">
         <f t="shared" si="74"/>
-        <v>0.55986622073578596</v>
-      </c>
-      <c r="X134" s="81">
+        <v>8993</v>
+      </c>
+      <c r="X134" s="25">
         <f t="shared" si="74"/>
-        <v>0.55341614906832293</v>
-      </c>
-      <c r="Y134" s="81">
+        <v>9821</v>
+      </c>
+      <c r="Y134" s="25">
         <f t="shared" si="74"/>
-        <v>0.54554358472086195</v>
-      </c>
-      <c r="Z134" s="81">
-        <f t="shared" si="74"/>
-        <v>0.53769223511652042</v>
-      </c>
-      <c r="AA134" s="81">
-        <f t="shared" si="74"/>
+        <v>10613</v>
+      </c>
+      <c r="Z134" s="25">
+        <f>AA193</f>
+        <v>9076</v>
+      </c>
+      <c r="AA134" s="25">
+        <f>AB193</f>
         <v>0</v>
       </c>
       <c r="AC134" s="49"/>
@@ -28641,43 +29571,43 @@
       <c r="O135" s="49"/>
       <c r="P135" s="49"/>
       <c r="Q135" s="49"/>
-      <c r="T135" s="228" t="str">
+      <c r="T135" s="227" t="str">
         <f t="shared" ref="T135:AA135" si="75">IF(T134&gt;T133, "BEAT", IF(T134&lt;T132, "MISSED", "MET"))</f>
-        <v>MISSED</v>
-      </c>
-      <c r="U135" s="228" t="str">
+        <v>MET</v>
+      </c>
+      <c r="U135" s="227" t="str">
+        <f t="shared" si="75"/>
+        <v>BEAT</v>
+      </c>
+      <c r="V135" s="227" t="str">
+        <f t="shared" si="75"/>
+        <v>MET</v>
+      </c>
+      <c r="W135" s="227" t="str">
+        <f t="shared" si="75"/>
+        <v>MET</v>
+      </c>
+      <c r="X135" s="227" t="str">
+        <f t="shared" si="75"/>
+        <v>BEAT</v>
+      </c>
+      <c r="Y135" s="227" t="str">
+        <f t="shared" si="75"/>
+        <v>MET</v>
+      </c>
+      <c r="Z135" s="227" t="str">
+        <f t="shared" si="75"/>
+        <v>MET</v>
+      </c>
+      <c r="AA135" s="227" t="str">
         <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
-      <c r="V135" s="228" t="str">
-        <f t="shared" si="75"/>
-        <v>MISSED</v>
-      </c>
-      <c r="W135" s="228" t="str">
-        <f t="shared" si="75"/>
-        <v>MISSED</v>
-      </c>
-      <c r="X135" s="228" t="str">
-        <f t="shared" si="75"/>
-        <v>MISSED</v>
-      </c>
-      <c r="Y135" s="228" t="str">
-        <f t="shared" si="75"/>
-        <v>MISSED</v>
-      </c>
-      <c r="Z135" s="228" t="str">
-        <f t="shared" si="75"/>
-        <v>MISSED</v>
-      </c>
-      <c r="AA135" s="228" t="str">
-        <f t="shared" si="75"/>
-        <v>MISSED</v>
-      </c>
       <c r="AC135" s="49"/>
     </row>
     <row r="136" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B136" s="20" t="s">
-        <v>354</v>
+        <v>403</v>
       </c>
       <c r="C136" s="49"/>
       <c r="D136" s="49"/>
@@ -28695,34 +29625,34 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="21">
-        <v>4300</v>
+        <v>1350</v>
       </c>
       <c r="U136" s="21">
-        <v>4800</v>
+        <v>1450</v>
       </c>
       <c r="V136" s="21">
-        <v>5200</v>
+        <v>1250</v>
       </c>
       <c r="W136" s="21">
-        <v>5700</v>
+        <v>1150</v>
       </c>
       <c r="X136" s="21">
-        <v>5900</v>
+        <v>1250</v>
       </c>
       <c r="Y136" s="21">
-        <v>6700</v>
+        <v>1400</v>
       </c>
       <c r="Z136" s="21">
-        <v>7700</v>
+        <v>1200</v>
       </c>
       <c r="AA136" s="21">
-        <v>8500</v>
+        <v>1150</v>
       </c>
       <c r="AC136" s="49"/>
     </row>
     <row r="137" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B137" s="20" t="s">
-        <v>355</v>
+        <v>404</v>
       </c>
       <c r="C137" s="49"/>
       <c r="D137" s="49"/>
@@ -28740,34 +29670,34 @@
       <c r="P137" s="49"/>
       <c r="Q137" s="49"/>
       <c r="T137" s="21">
-        <v>4300</v>
+        <v>1550</v>
       </c>
       <c r="U137" s="21">
-        <v>4800</v>
+        <v>1650</v>
       </c>
       <c r="V137" s="21">
-        <v>5200</v>
+        <v>1450</v>
       </c>
       <c r="W137" s="21">
-        <v>5700</v>
+        <v>1350</v>
       </c>
       <c r="X137" s="21">
-        <v>5900</v>
+        <v>1450</v>
       </c>
       <c r="Y137" s="21">
-        <v>6700</v>
+        <v>1600</v>
       </c>
       <c r="Z137" s="21">
-        <v>7700</v>
+        <v>1400</v>
       </c>
       <c r="AA137" s="21">
-        <v>8500</v>
+        <v>1350</v>
       </c>
       <c r="AC137" s="49"/>
     </row>
     <row r="138" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B138" s="20" t="s">
-        <v>356</v>
+        <v>405</v>
       </c>
       <c r="C138" s="49"/>
       <c r="D138" s="49"/>
@@ -28785,35 +29715,35 @@
       <c r="P138" s="49"/>
       <c r="Q138" s="49"/>
       <c r="T138" s="25">
-        <f t="shared" ref="T138:AA138" si="76">U11</f>
-        <v>3196</v>
+        <f t="shared" ref="T138:Y138" si="76">U194</f>
+        <v>1015</v>
       </c>
       <c r="U138" s="25">
         <f t="shared" si="76"/>
-        <v>2953</v>
+        <v>1535</v>
       </c>
       <c r="V138" s="25">
         <f t="shared" si="76"/>
-        <v>2922</v>
+        <v>1319</v>
       </c>
       <c r="W138" s="25">
         <f t="shared" si="76"/>
-        <v>2997</v>
+        <v>1318</v>
       </c>
       <c r="X138" s="25">
         <f t="shared" si="76"/>
-        <v>3319</v>
+        <v>1409</v>
       </c>
       <c r="Y138" s="25">
         <f t="shared" si="76"/>
-        <v>3318</v>
+        <v>1592</v>
       </c>
       <c r="Z138" s="25">
-        <f t="shared" si="76"/>
-        <v>3390</v>
+        <f>AA194</f>
+        <v>1382</v>
       </c>
       <c r="AA138" s="25">
-        <f t="shared" si="76"/>
+        <f>AB194</f>
         <v>0</v>
       </c>
       <c r="AC138" s="49"/>
@@ -28837,35 +29767,35 @@
       <c r="O139" s="49"/>
       <c r="P139" s="49"/>
       <c r="Q139" s="49"/>
-      <c r="T139" s="228" t="str">
+      <c r="T139" s="227" t="str">
         <f t="shared" ref="T139:AA139" si="77">IF(T138&gt;T137, "BEAT", IF(T138&lt;T136, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
-      <c r="U139" s="228" t="str">
+      <c r="U139" s="227" t="str">
         <f t="shared" si="77"/>
-        <v>MISSED</v>
-      </c>
-      <c r="V139" s="228" t="str">
+        <v>MET</v>
+      </c>
+      <c r="V139" s="227" t="str">
         <f t="shared" si="77"/>
-        <v>MISSED</v>
-      </c>
-      <c r="W139" s="228" t="str">
+        <v>MET</v>
+      </c>
+      <c r="W139" s="227" t="str">
         <f t="shared" si="77"/>
-        <v>MISSED</v>
-      </c>
-      <c r="X139" s="228" t="str">
+        <v>MET</v>
+      </c>
+      <c r="X139" s="227" t="str">
         <f t="shared" si="77"/>
-        <v>MISSED</v>
-      </c>
-      <c r="Y139" s="228" t="str">
+        <v>MET</v>
+      </c>
+      <c r="Y139" s="227" t="str">
         <f t="shared" si="77"/>
-        <v>MISSED</v>
-      </c>
-      <c r="Z139" s="228" t="str">
+        <v>MET</v>
+      </c>
+      <c r="Z139" s="227" t="str">
         <f t="shared" si="77"/>
-        <v>MISSED</v>
-      </c>
-      <c r="AA139" s="228" t="str">
+        <v>MET</v>
+      </c>
+      <c r="AA139" s="227" t="str">
         <f t="shared" si="77"/>
         <v>MISSED</v>
       </c>
@@ -30117,25 +31047,25 @@
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B169" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="M169" s="225">
+        <v>351</v>
+      </c>
+      <c r="M169" s="224">
         <f>M161/M5</f>
         <v>0.23384112648821215</v>
       </c>
-      <c r="N169" s="225">
+      <c r="N169" s="224">
         <f>N161/N5</f>
         <v>0.11905795584207608</v>
       </c>
-      <c r="O169" s="225">
+      <c r="O169" s="224">
         <f>O161/O5</f>
         <v>0.31463370639754373</v>
       </c>
-      <c r="P169" s="225">
+      <c r="P169" s="224">
         <f>P161/P5</f>
         <v>0.28735163264579622</v>
       </c>
-      <c r="Q169" s="225">
+      <c r="Q169" s="224">
         <f>Q161/Q5</f>
         <v>0.26627195069724097</v>
       </c>
@@ -30154,25 +31084,25 @@
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B170" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="M170" s="225">
+        <v>352</v>
+      </c>
+      <c r="M170" s="224">
         <f>M160/M5</f>
         <v>0.20809747959244473</v>
       </c>
-      <c r="N170" s="225">
+      <c r="N170" s="224">
         <f>N160/N5</f>
         <v>0.10866515837104072</v>
       </c>
-      <c r="O170" s="225">
+      <c r="O170" s="224">
         <f>O160/O5</f>
         <v>0.20561139028475711</v>
       </c>
-      <c r="P170" s="225">
+      <c r="P170" s="224">
         <f>P160/P5</f>
         <v>0.21849494379138648</v>
       </c>
-      <c r="Q170" s="225">
+      <c r="Q170" s="224">
         <f>Q160/Q5</f>
         <v>0.22665070905970552</v>
       </c>
@@ -30803,7 +31733,7 @@
     </row>
     <row r="183" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B183" s="20" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="M183" s="72">
         <f>M5/M37</f>
@@ -30840,7 +31770,7 @@
     </row>
     <row r="184" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B184" s="20" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="M184" s="72">
         <f>IF(AND(M12&gt;0,M107&gt;0),M107/M12,"N/A")</f>
@@ -30877,25 +31807,25 @@
     </row>
     <row r="185" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B185" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="M185" s="229">
+        <v>363</v>
+      </c>
+      <c r="M185" s="228">
         <f>IF(AND(M12&gt;0,M107&gt;0),(M107-M106)/M12,"N/A")</f>
         <v>0.34027990601695779</v>
       </c>
-      <c r="N185" s="229">
+      <c r="N185" s="228">
         <f t="shared" ref="N185:Q185" si="113">IF(AND(N12&gt;0,N107&gt;0),(N107-N106)/N12,"N/A")</f>
         <v>0.57377049180327866</v>
       </c>
-      <c r="O185" s="229">
+      <c r="O185" s="228">
         <f t="shared" si="113"/>
         <v>0.52311248073959937</v>
       </c>
-      <c r="P185" s="229">
+      <c r="P185" s="228">
         <f t="shared" si="113"/>
         <v>0.13245953728527454</v>
       </c>
-      <c r="Q185" s="229">
+      <c r="Q185" s="228">
         <f t="shared" si="113"/>
         <v>0.37685147713476325</v>
       </c>
@@ -30907,32 +31837,32 @@
       <c r="Y185" s="49"/>
       <c r="Z185" s="49"/>
       <c r="AA185" s="49"/>
-      <c r="AC185" s="229">
+      <c r="AC185" s="228">
         <f t="shared" ref="AC185" si="114">IF(AND(AC12&gt;0,AC107&gt;0),(AC107-AC106)/AC12,"N/A")</f>
         <v>0.48181417877586968</v>
       </c>
     </row>
     <row r="186" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B186" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="M186" s="229">
+        <v>364</v>
+      </c>
+      <c r="M186" s="228">
         <f>M5/(M107+M111-M106)</f>
         <v>2.5273699269633312</v>
       </c>
-      <c r="N186" s="229">
+      <c r="N186" s="228">
         <f t="shared" ref="N186:Q186" si="115">N5/(N107+N111-N106)</f>
         <v>1.6302142883487627</v>
       </c>
-      <c r="O186" s="229">
+      <c r="O186" s="228">
         <f t="shared" si="115"/>
         <v>1.3962190606119664</v>
       </c>
-      <c r="P186" s="229">
+      <c r="P186" s="228">
         <f t="shared" si="115"/>
         <v>1.4112576064908722</v>
       </c>
-      <c r="Q186" s="229">
+      <c r="Q186" s="228">
         <f t="shared" si="115"/>
         <v>1.7123192328512875</v>
       </c>
@@ -30944,7 +31874,7 @@
       <c r="Y186" s="49"/>
       <c r="Z186" s="49"/>
       <c r="AA186" s="49"/>
-      <c r="AC186" s="229">
+      <c r="AC186" s="228">
         <f t="shared" ref="AC186" si="116">AC5/(AC107+AC111-AC106)</f>
         <v>1.3614461510275122</v>
       </c>
@@ -30964,8 +31894,8 @@
       <c r="AE189" s="1"/>
     </row>
     <row r="190" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B190" s="223" t="s">
-        <v>395</v>
+      <c r="B190" s="222" t="s">
+        <v>387</v>
       </c>
       <c r="C190" s="62"/>
       <c r="D190" s="62"/>
@@ -31022,8 +31952,8 @@
       </c>
     </row>
     <row r="191" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B191" s="223" t="s">
-        <v>396</v>
+      <c r="B191" s="222" t="s">
+        <v>388</v>
       </c>
       <c r="C191" s="62"/>
       <c r="D191" s="62"/>
@@ -31080,8 +32010,8 @@
       </c>
     </row>
     <row r="192" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B192" s="223" t="s">
-        <v>397</v>
+      <c r="B192" s="222" t="s">
+        <v>389</v>
       </c>
       <c r="C192" s="62"/>
       <c r="D192" s="62"/>
@@ -31139,7 +32069,7 @@
     </row>
     <row r="193" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B193" s="20" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C193" s="21"/>
       <c r="D193" s="21"/>
@@ -31199,7 +32129,7 @@
     </row>
     <row r="194" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B194" s="20" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C194" s="21"/>
       <c r="D194" s="21"/>
@@ -31303,8 +32233,8 @@
       <c r="AC197" s="171"/>
     </row>
     <row r="198" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B198" s="223" t="s">
-        <v>395</v>
+      <c r="B198" s="222" t="s">
+        <v>387</v>
       </c>
       <c r="C198" s="81"/>
       <c r="D198" s="81"/>
@@ -31377,8 +32307,8 @@
       <c r="AC198" s="49"/>
     </row>
     <row r="199" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B199" s="223" t="s">
-        <v>396</v>
+      <c r="B199" s="222" t="s">
+        <v>388</v>
       </c>
       <c r="M199" s="81">
         <f t="shared" si="118"/>
@@ -31435,8 +32365,8 @@
       <c r="AC199" s="49"/>
     </row>
     <row r="200" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B200" s="223" t="s">
-        <v>397</v>
+      <c r="B200" s="222" t="s">
+        <v>389</v>
       </c>
       <c r="M200" s="81">
         <f t="shared" si="118"/>
@@ -31494,7 +32424,7 @@
     </row>
     <row r="201" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B201" s="20" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="M201" s="81">
         <f t="shared" si="118"/>
@@ -31552,7 +32482,7 @@
     </row>
     <row r="202" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B202" s="20" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="M202" s="81">
         <f t="shared" ref="M202" si="120">IF(L194=0,
@@ -31743,7 +32673,7 @@
     </row>
     <row r="209" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B209" s="14" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C209" s="171"/>
       <c r="D209" s="171"/>
@@ -31772,7 +32702,7 @@
     </row>
     <row r="210" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B210" s="20" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="M210" s="143">
         <v>100</v>
@@ -31805,7 +32735,7 @@
     </row>
     <row r="211" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B211" s="20" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="M211" s="143">
         <v>100</v>
@@ -31838,7 +32768,7 @@
     </row>
     <row r="212" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B212" s="20" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="M212" s="143">
         <v>100</v>
@@ -31937,15 +32867,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="230"/>
-      <c r="E4" s="230" t="s">
+      <c r="C4" s="233"/>
+      <c r="E4" s="233" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32082,14 +33012,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
+      <c r="B15" s="233" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="230"/>
-      <c r="E15" s="230" t="s">
+      <c r="C15" s="233"/>
+      <c r="E15" s="233" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="230"/>
+      <c r="F15" s="233"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -32140,14 +33070,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="230" t="s">
+      <c r="B21" s="233" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="230"/>
-      <c r="E21" s="230" t="s">
+      <c r="C21" s="233"/>
+      <c r="E21" s="233" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="230"/>
+      <c r="F21" s="233"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -32216,14 +33146,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="230" t="s">
+      <c r="B29" s="233" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="230"/>
-      <c r="E29" s="230" t="s">
+      <c r="C29" s="233"/>
+      <c r="E29" s="233" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="230"/>
+      <c r="F29" s="233"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -32299,14 +33229,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="230" t="s">
+      <c r="B37" s="233" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="230"/>
-      <c r="E37" s="230" t="s">
+      <c r="C37" s="233"/>
+      <c r="E37" s="233" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="230"/>
+      <c r="F37" s="233"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -32375,14 +33305,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="230" t="s">
+      <c r="B45" s="233" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="230"/>
-      <c r="E45" s="230" t="s">
+      <c r="C45" s="233"/>
+      <c r="E45" s="233" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="230"/>
+      <c r="F45" s="233"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -32419,14 +33349,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="230" t="s">
+      <c r="B51" s="233" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="230"/>
-      <c r="E51" s="230" t="s">
+      <c r="C51" s="233"/>
+      <c r="E51" s="233" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="230"/>
+      <c r="F51" s="233"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34272,8 +35202,8 @@
       <c r="I88" s="14"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="223" t="s">
-        <v>395</v>
+      <c r="B89" s="222" t="s">
+        <v>387</v>
       </c>
       <c r="C89" s="175">
         <f>Statement!M198</f>
@@ -34298,8 +35228,8 @@
       <c r="I89" s="197"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="223" t="s">
-        <v>396</v>
+      <c r="B90" s="222" t="s">
+        <v>388</v>
       </c>
       <c r="C90" s="175">
         <f>Statement!M199</f>
@@ -34324,8 +35254,8 @@
       <c r="I90" s="197"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B91" s="223" t="s">
-        <v>397</v>
+      <c r="B91" s="222" t="s">
+        <v>389</v>
       </c>
       <c r="C91" s="175">
         <f>Statement!M200</f>
@@ -34351,7 +35281,7 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C92" s="175">
         <f>Statement!M201</f>
@@ -34377,7 +35307,7 @@
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B93" s="20" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C93" s="175">
         <f>Statement!M202</f>
@@ -34461,14 +35391,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="236" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="F3" s="236" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="235"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -34535,19 +35465,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="237">
+      <c r="C7" s="234">
         <f>Statement!AA89</f>
         <v>-0.13491674828599412</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="F7" s="237">
+      <c r="D7" s="235"/>
+      <c r="F7" s="234">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-3.4611531104836508E-2</v>
       </c>
-      <c r="G7" s="238"/>
+      <c r="G7" s="235"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -34574,19 +35504,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="237">
+      <c r="C9" s="234">
         <f>Statement!AA90</f>
         <v>-0.11997126436781609</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="F9" s="237">
+      <c r="D9" s="235"/>
+      <c r="F9" s="234">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>-7.4944298156775372E-3</v>
       </c>
-      <c r="G9" s="238"/>
+      <c r="G9" s="235"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -34613,19 +35543,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="237">
+      <c r="C11" s="234">
         <f>Statement!AA91</f>
         <v>-0.1473668461998803</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="F11" s="237">
+      <c r="D11" s="235"/>
+      <c r="F11" s="234">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-5.6769281694803046E-2</v>
       </c>
-      <c r="G11" s="238"/>
+      <c r="G11" s="235"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -34652,19 +35582,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="237">
+      <c r="C13" s="234">
         <f>Statement!AA94</f>
         <v>2.1699819168173599E-2</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="F13" s="237">
+      <c r="D13" s="235"/>
+      <c r="F13" s="234">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.16016427104722791</v>
       </c>
-      <c r="G13" s="238"/>
+      <c r="G13" s="235"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -34691,19 +35621,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="237">
+      <c r="C15" s="234">
         <f>Statement!AA95</f>
         <v>-0.31402257872846107</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="F15" s="237">
+      <c r="D15" s="235"/>
+      <c r="F15" s="234">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.25993589743589746</v>
       </c>
-      <c r="G15" s="238"/>
+      <c r="G15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -34730,19 +35660,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="237">
+      <c r="C17" s="234">
         <f>Statement!AA97</f>
         <v>-0.35685752330226367</v>
       </c>
-      <c r="D17" s="238"/>
-      <c r="F17" s="237">
+      <c r="D17" s="235"/>
+      <c r="F17" s="234">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.31294452347083929</v>
       </c>
-      <c r="G17" s="238"/>
+      <c r="G17" s="235"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -34769,22 +35699,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="237">
+      <c r="C19" s="234">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-6.4874884151992582E-3</v>
       </c>
-      <c r="D19" s="238"/>
-      <c r="F19" s="237">
+      <c r="D19" s="235"/>
+      <c r="F19" s="234">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.8565022421524667E-2</v>
       </c>
-      <c r="G19" s="238"/>
+      <c r="G19" s="235"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -34811,22 +35741,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="237">
+      <c r="C21" s="234">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.35171265972296784</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="F21" s="237">
+      <c r="D21" s="235"/>
+      <c r="F21" s="234">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.28482587064676618</v>
       </c>
-      <c r="G21" s="238"/>
+      <c r="G21" s="235"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -34850,8 +35780,8 @@
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="223" t="s">
-        <v>395</v>
+      <c r="B24" s="222" t="s">
+        <v>387</v>
       </c>
       <c r="C24" s="200">
         <f>Statement!Z190</f>
@@ -34874,26 +35804,26 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="237">
+      <c r="C25" s="234">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.23006134969325154</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="F25" s="237">
+      <c r="D25" s="235"/>
+      <c r="F25" s="234">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.13061047770241016</v>
       </c>
-      <c r="G25" s="238"/>
+      <c r="G25" s="235"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="223" t="s">
-        <v>396</v>
+      <c r="B26" s="222" t="s">
+        <v>388</v>
       </c>
       <c r="C26" s="200">
         <f>Statement!Z191</f>
@@ -34916,26 +35846,26 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="237">
+      <c r="C27" s="234">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.20435967302452315</v>
       </c>
-      <c r="D27" s="238"/>
-      <c r="F27" s="237">
+      <c r="D27" s="235"/>
+      <c r="F27" s="234">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.38269030239833157</v>
       </c>
-      <c r="G27" s="238"/>
+      <c r="G27" s="235"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B28" s="223" t="s">
-        <v>397</v>
+      <c r="B28" s="222" t="s">
+        <v>389</v>
       </c>
       <c r="C28" s="200">
         <f>Statement!Z192</f>
@@ -34958,26 +35888,26 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="237">
+      <c r="C29" s="234">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.2511848341232227E-2</v>
       </c>
-      <c r="D29" s="238"/>
-      <c r="F29" s="237">
+      <c r="D29" s="235"/>
+      <c r="F29" s="234">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>9.1714104996837451E-2</v>
       </c>
-      <c r="G29" s="238"/>
+      <c r="G29" s="235"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C30" s="200">
         <f>Statement!Z193</f>
@@ -35000,26 +35930,26 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="237">
+      <c r="C31" s="234">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.1448223876378027</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="F31" s="237">
+      <c r="D31" s="235"/>
+      <c r="F31" s="234">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-4.1503854683704718E-2</v>
       </c>
-      <c r="G31" s="238"/>
+      <c r="G31" s="235"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C32" s="200">
         <f>Statement!Z194</f>
@@ -35042,25 +35972,43 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="237">
+      <c r="C33" s="234">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.13190954773869346</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="F33" s="237">
+      <c r="D33" s="235"/>
+      <c r="F33" s="234">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>4.7763457164518575E-2</v>
       </c>
-      <c r="G33" s="238"/>
+      <c r="G33" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -35071,24 +36019,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -35099,7 +36029,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59D4CD5-3D15-DF4B-A135-ED758F2E1A8D}">
-  <dimension ref="B55:L71"/>
+  <dimension ref="B55:L74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -35555,7 +36485,7 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!H190</f>
@@ -35600,7 +36530,7 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!H191</f>
@@ -35645,7 +36575,7 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C67" s="64">
         <f>Statement!H192</f>
@@ -35690,7 +36620,7 @@
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C68" s="64">
         <f>Statement!H194</f>
@@ -35866,6 +36796,141 @@
       <c r="L71" s="218">
         <f>Statement!Q143</f>
         <v>0.42408116405060003</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B72" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="C72" s="229">
+        <f>Statement!H210</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="229">
+        <f>Statement!I210</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="229">
+        <f>Statement!J210</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="229">
+        <f>Statement!K210</f>
+        <v>0</v>
+      </c>
+      <c r="G72" s="229">
+        <f>Statement!L210</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="229">
+        <f>Statement!M210</f>
+        <v>100</v>
+      </c>
+      <c r="I72" s="229">
+        <f>Statement!N210</f>
+        <v>90.521362414102185</v>
+      </c>
+      <c r="J72" s="229">
+        <f>Statement!O210</f>
+        <v>80.430236032267715</v>
+      </c>
+      <c r="K72" s="229">
+        <f>Statement!P210</f>
+        <v>127.07648640573647</v>
+      </c>
+      <c r="L72" s="229">
+        <f>Statement!Q210</f>
+        <v>126.38183447863757</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B73" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="C73" s="229">
+        <f>Statement!H211</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="229">
+        <f>Statement!I211</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="229">
+        <f>Statement!J211</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="229">
+        <f>Statement!K211</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="229">
+        <f>Statement!L211</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="229">
+        <f>Statement!M211</f>
+        <v>100</v>
+      </c>
+      <c r="I73" s="229">
+        <f>Statement!N211</f>
+        <v>131.68086754453913</v>
+      </c>
+      <c r="J73" s="229">
+        <f>Statement!O211</f>
+        <v>106.71512840374189</v>
+      </c>
+      <c r="K73" s="229">
+        <f>Statement!P211</f>
+        <v>116.07579097896681</v>
+      </c>
+      <c r="L73" s="229">
+        <f>Statement!Q211</f>
+        <v>131.93112077697671</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B74" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="C74" s="229">
+        <f>Statement!H212</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="229">
+        <f>Statement!I212</f>
+        <v>0</v>
+      </c>
+      <c r="E74" s="229">
+        <f>Statement!J212</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="229">
+        <f>Statement!K212</f>
+        <v>0</v>
+      </c>
+      <c r="G74" s="229">
+        <f>Statement!L212</f>
+        <v>0</v>
+      </c>
+      <c r="H74" s="229">
+        <f>Statement!M212</f>
+        <v>100</v>
+      </c>
+      <c r="I74" s="229">
+        <f>Statement!N212</f>
+        <v>144.98094027954255</v>
+      </c>
+      <c r="J74" s="229">
+        <f>Statement!O212</f>
+        <v>82.846251588310025</v>
+      </c>
+      <c r="K74" s="229">
+        <f>Statement!P212</f>
+        <v>113.59593392630241</v>
+      </c>
+      <c r="L74" s="229">
+        <f>Statement!Q212</f>
+        <v>129.26112679457472</v>
       </c>
     </row>
   </sheetData>
@@ -36178,7 +37243,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C63" s="64">
         <f>Statement!T190</f>
@@ -36215,7 +37280,7 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C64" s="64">
         <f>Statement!T191</f>
@@ -36252,7 +37317,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!T194</f>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693C712B-05C1-F444-AFFD-59CCCFBF1F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D77732D-C01C-C840-8561-138183494884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -4352,43 +4352,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="57930431"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -6590,43 +6558,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="1156723391"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -12755,11 +12691,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6096999999999999</v>
-    <v>13.14</v>
-    <v>6.1699000000000004E-2</v>
-    <v>0.39</v>
-    <v>1.725E-3</v>
+    <v>1.6483000000000001</v>
+    <v>7.49</v>
+    <v>3.7940999999999996E-2</v>
+    <v>7.0000000000000007E-2</v>
+    <v>3.4160000000000001E-4</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12767,26 +12703,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>229.42</v>
+    <v>219.43</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.999934085157</v>
+    <v>46198.90999325156</v>
     <v>4</v>
-    <v>214.73</v>
-    <v>238319940000</v>
+    <v>199.82</v>
+    <v>215964600000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>220.71</v>
-    <v>23.165500000000002</v>
-    <v>212.97</v>
-    <v>226.11</v>
-    <v>226.5</v>
+    <v>219.43</v>
+    <v>22.287700000000001</v>
+    <v>197.41</v>
+    <v>204.9</v>
+    <v>204.97</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>47081544</v>
-    <v>21727556</v>
+    <v>34778719</v>
+    <v>22388233</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -12810,17 +12746,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.12</v>
-    <v>-2.6889999999999996E-3</v>
+    <v>-0.91</v>
+    <v>-2.0253999999999998E-2</v>
     <v>US</v>
-    <v>44.53</v>
+    <v>44.55</v>
     <v>Index</v>
     <v>7</v>
-    <v>44.2</v>
+    <v>43.98</v>
     <v>10 Y TSY YLD NDX</v>
     <v>44.53</v>
-    <v>44.63</v>
-    <v>44.51</v>
+    <v>44.93</v>
+    <v>44.02</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13062,9 +12998,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13677,7 +13613,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>239676.6</v>
+        <v>217194</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13685,7 +13621,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>115.4962120112572</v>
+        <v>114.49922479469299</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13701,7 +13637,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>245147.6</v>
+        <v>222665</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13709,7 +13645,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>180.15703874400484</v>
+        <v>179.57697255026278</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13718,7 +13654,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>226.11</v>
+        <v>204.9</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13742,14 +13678,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>226.5</v>
+        <v>204.97</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>24.007408431868544</v>
+        <v>21.755419873910327</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13757,7 +13693,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>173.74762220661054</v>
+        <v>173.1877017516795</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13766,14 +13702,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>13.14</v>
+        <v>7.49</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>5.4871713093796259</v>
+        <v>4.9724532364419325</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13781,7 +13717,7 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>165.026905974313</v>
+        <v>164.49266250800366</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13790,14 +13726,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.39</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.9348855916681059E-2</v>
+        <v>4.3422009816109101E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13805,7 +13741,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.27014768929143784</v>
+        <v>-0.19720516101511149</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13814,14 +13750,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.1699000000000004E-2</v>
+        <v>3.7940999999999996E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>4.1653808774817766E-2</v>
+        <v>4.59655573551686E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13830,14 +13766,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.725E-3</v>
+        <v>3.4160000000000001E-4</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>4.4789520545601862E-2</v>
+        <v>4.9425858909546302E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13853,7 +13789,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.5744549113263454E-2</v>
+        <v>1.7374328940946804E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13878,7 +13814,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6096999999999999</v>
+        <v>1.6483000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13894,7 +13830,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>21727556</v>
+        <v>22388233</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13910,7 +13846,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-2.2826592166277391E-2</v>
+        <v>-2.5189461955670966E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14020,7 +13956,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.51</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14035,7 +13971,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.4020000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -19588,7 +19524,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>226.11</v>
+        <v>204.9</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19597,7 +19533,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>239676.6</v>
+        <v>217194</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19615,7 +19551,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.4020000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19624,7 +19560,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6096999999999999</v>
+        <v>1.6483000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19667,7 +19603,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.9894895636968683E-2</v>
+        <v>6.568759033656825E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19676,7 +19612,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9401051043630313</v>
+        <v>0.93431240966343176</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19694,7 +19630,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11694649999999998</v>
+        <v>0.11819350000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19703,7 +19639,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11214224057861526</v>
+        <v>0.11284268742256866</v>
       </c>
     </row>
   </sheetData>
@@ -19954,7 +19890,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>151155.62428396993</v>
+        <v>149950.32782638099</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20008,23 +19944,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>8957.8878281537309</v>
+        <v>8952.2495431304869</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7960.7270853195414</v>
+        <v>7950.70893742101</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7499.6831001759474</v>
+        <v>7485.5306318713192</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7082.6670955794298</v>
+        <v>7064.8519992799374</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7553.1391815602874</v>
+        <v>7529.3985542712098</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20043,7 +19979,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>88842.880441143687</v>
+        <v>87857.438616400599</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20066,7 +20002,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11214224057861526</v>
+        <v>0.11284268742256866</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20081,7 +20017,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>39054.104290788935</v>
+        <v>38982.739665973961</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20090,7 +20026,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>88842.880441143687</v>
+        <v>87857.438616400599</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20099,7 +20035,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>127896.98473193262</v>
+        <v>126840.17828237456</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20126,7 +20062,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>122425.98473193264</v>
+        <v>121369.17828237457</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20144,7 +20080,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>115.4962120112572</v>
+        <v>114.49922479469299</v>
       </c>
     </row>
   </sheetData>
@@ -21153,7 +21089,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11214224057861526</v>
+        <v>0.11284268742256866</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21179,7 +21115,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>190966.46106864512</v>
+        <v>190351.59090327856</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21197,7 +21133,7 @@
       </c>
       <c r="C44" s="142">
         <f ca="1">C42/C43</f>
-        <v>180.15703874400484</v>
+        <v>179.57697255026278</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21280,7 +21216,7 @@
       </c>
       <c r="C56" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11214224057861526</v>
+        <v>0.11284268742256866</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -21306,7 +21242,7 @@
       </c>
       <c r="C59" s="24">
         <f ca="1">C58/(1+C56)^5-G30+G31</f>
-        <v>184172.47953900718</v>
+        <v>183578.96385678026</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21324,7 +21260,7 @@
       </c>
       <c r="C61" s="142">
         <f ca="1">C59/C60</f>
-        <v>173.74762220661054</v>
+        <v>173.1877017516795</v>
       </c>
     </row>
   </sheetData>
@@ -21388,7 +21324,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>115.4962120112572</v>
+        <v>114.49922479469299</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21397,7 +21333,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C44</f>
-        <v>180.15703874400484</v>
+        <v>179.57697255026278</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21415,7 +21351,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C61</f>
-        <v>173.74762220661054</v>
+        <v>173.1877017516795</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21424,7 +21360,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>165.026905974313</v>
+        <v>164.49266250800366</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21433,7 +21369,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>226.11</v>
+        <v>204.9</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21442,7 +21378,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.27014768929143784</v>
+        <v>-0.19720516101511149</v>
       </c>
     </row>
   </sheetData>
@@ -21695,7 +21631,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>300207.601973582</v>
+        <v>297813.78327901429</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21749,23 +21685,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12373.221340211194</v>
+        <v>12365.433371673285</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12983.545428967778</v>
+        <v>12967.206333686574</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13623.974490639219</v>
+        <v>13598.26502204083</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14295.99348937964</v>
+        <v>14260.034648271723</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>15001.160636993825</v>
+        <v>14954.00978288857</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21784,7 +21720,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>176449.32642106054</v>
+        <v>174492.1572552291</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21800,7 +21736,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>226.11</v>
+        <v>204.9</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21809,7 +21745,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>226.99831291010645</v>
+        <v>225.01528122750483</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -21848,7 +21784,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11214224057861526</v>
+        <v>0.11284268742256866</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -21866,7 +21802,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>238319.94</v>
+        <v>215964.6</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21893,7 +21829,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>243790.94</v>
+        <v>221435.6</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21909,7 +21845,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>68277.895386191653</v>
+        <v>68144.949158560979</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -21918,7 +21854,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>176449.32642106054</v>
+        <v>174492.1572552291</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -21927,7 +21863,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>244727.22180725221</v>
+        <v>242637.10641379008</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -21954,7 +21890,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>239256.22180725221</v>
+        <v>237166.10641379008</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -21972,7 +21908,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>226.99831291010645</v>
+        <v>225.01528122750483</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -28914,7 +28850,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>226.11</v>
+        <v>204.9</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -28961,7 +28897,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>226.11</v>
+        <v>204.9</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -30463,7 +30399,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>24.007408431868544</v>
+        <v>21.755419873910327</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30500,7 +30436,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>5.4871713093796259</v>
+        <v>4.9724532364419325</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30537,7 +30473,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>8.7367087029840906</v>
+        <v>7.9171713468729381</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30574,7 +30510,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>239676.6</v>
+        <v>217194</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30611,7 +30547,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>245147.6</v>
+        <v>222665</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30648,7 +30584,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>5.4983088861974609</v>
+        <v>4.9940564302695911</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30685,7 +30621,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>21.589396741523558</v>
+        <v>19.60942316160282</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30820,7 +30756,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="98">AC156/AC160</f>
-        <v>25.413699501643517</v>
+        <v>23.029795355741705</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30857,7 +30793,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="98"/>
-        <v>20.500747166174794</v>
+        <v>18.620614143301054</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30894,7 +30830,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="101">AC160/AC156</f>
-        <v>3.9348855916681059E-2</v>
+        <v>4.3422009816109101E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30931,7 +30867,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>4.1653808774817766E-2</v>
+        <v>4.59655573551686E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30968,7 +30904,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>1.5744549113263454E-2</v>
+        <v>1.7374328940946804E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31005,7 +30941,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>4.4789520545601862E-2</v>
+        <v>4.9425858909546302E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31042,7 +30978,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>6.0727663860385202E-2</v>
+        <v>6.7013821744615412E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -31545,7 +31481,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-2.2826592166277391E-2</v>
+        <v>-2.5189461955670966E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -32883,7 +32819,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>226.11</v>
+        <v>204.9</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -32899,7 +32835,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>239676.6</v>
+        <v>217194</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32919,7 +32855,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>245147.6</v>
+        <v>222665</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32939,7 +32875,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>24.007408431868544</v>
+        <v>21.755419873910327</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32959,7 +32895,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>5.4871713093796259</v>
+        <v>4.9724532364419325</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32979,7 +32915,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>8.7367087029840906</v>
+        <v>7.9171713468729381</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32999,7 +32935,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>5.4983088861974609</v>
+        <v>4.9940564302695911</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33008,7 +32944,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>21.589396741523558</v>
+        <v>19.60942316160282</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33244,7 +33180,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>4.1653808774817766E-2</v>
+        <v>4.59655573551686E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33260,7 +33196,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>3.9348855916681059E-2</v>
+        <v>4.3422009816109101E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33276,7 +33212,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.5744549113263454E-2</v>
+        <v>1.7374328940946804E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33292,7 +33228,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>4.4789520545601862E-2</v>
+        <v>4.9425858909546302E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33301,7 +33237,7 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>6.0727663860385202E-2</v>
+        <v>6.7013821744615412E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33345,7 +33281,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-2.2826592166277391E-2</v>
+        <v>-2.5189461955670966E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33525,7 +33461,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>226.11</v>
+        <v>204.9</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33554,7 +33490,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>239676.6</v>
+        <v>217194</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33583,7 +33519,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>245147.6</v>
+        <v>222665</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33612,7 +33548,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>24.007408431868544</v>
+        <v>21.755419873910327</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33641,7 +33577,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>5.4871713093796259</v>
+        <v>4.9724532364419325</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33670,7 +33606,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>8.7367087029840906</v>
+        <v>7.9171713468729381</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33699,7 +33635,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>5.4983088861974609</v>
+        <v>4.9940564302695911</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33728,7 +33664,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>21.589396741523558</v>
+        <v>19.60942316160282</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34501,7 +34437,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>4.1653808774817766E-2</v>
+        <v>4.59655573551686E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34530,7 +34466,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>3.9348855916681059E-2</v>
+        <v>4.3422009816109101E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34559,7 +34495,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.5744549113263454E-2</v>
+        <v>1.7374328940946804E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34588,7 +34524,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>4.4789520545601862E-2</v>
+        <v>4.9425858909546302E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34617,7 +34553,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>6.0727663860385202E-2</v>
+        <v>6.7013821744615412E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34853,7 +34789,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-2.2826592166277391E-2</v>
+        <v>-2.5189461955670966E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D77732D-C01C-C840-8561-138183494884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC33F33-3B86-234B-B9D0-E3975A634FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2280,6 +2280,9 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2289,15 +2292,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2305,6 +2299,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12691,11 +12691,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6483000000000001</v>
-    <v>7.49</v>
-    <v>3.7940999999999996E-2</v>
-    <v>7.0000000000000007E-2</v>
-    <v>3.4160000000000001E-4</v>
+    <v>1.6463000000000001</v>
+    <v>-3.93</v>
+    <v>-2.0825E-2</v>
+    <v>0.81</v>
+    <v>4.3830000000000006E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12703,26 +12703,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>219.43</v>
+    <v>193.5</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46198.90999325156</v>
+    <v>46203.949436168747</v>
     <v>4</v>
-    <v>199.82</v>
-    <v>215964600000</v>
+    <v>183.5</v>
+    <v>194768660000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>219.43</v>
-    <v>22.287700000000001</v>
-    <v>197.41</v>
-    <v>204.9</v>
-    <v>204.97</v>
+    <v>188.99</v>
+    <v>20.100300000000001</v>
+    <v>188.72</v>
+    <v>184.79</v>
+    <v>185.6</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>34778719</v>
-    <v>22388233</v>
+    <v>22030054</v>
+    <v>23460284</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -12746,17 +12746,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.91</v>
-    <v>-2.0253999999999998E-2</v>
+    <v>0.02</v>
+    <v>4.5750000000000001E-4</v>
     <v>US</v>
-    <v>44.55</v>
+    <v>43.9</v>
     <v>Index</v>
     <v>7</v>
-    <v>43.98</v>
+    <v>43.67</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.53</v>
-    <v>44.93</v>
-    <v>44.02</v>
+    <v>43.78</v>
+    <v>43.72</v>
+    <v>43.74</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13587,18 +13587,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="230" t="s">
+      <c r="B2" s="231" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="231"/>
-      <c r="E2" s="230" t="s">
+      <c r="C2" s="232"/>
+      <c r="E2" s="231" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="231"/>
-      <c r="H2" s="230" t="s">
+      <c r="F2" s="232"/>
+      <c r="H2" s="231" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="231"/>
+      <c r="I2" s="232"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>217194</v>
+        <v>195877.4</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>114.49922479469299</v>
+        <v>115.75933916247121</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>222665</v>
+        <v>201348.4</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>179.57697255026278</v>
+        <v>180.30894250214121</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>204.9</v>
+        <v>184.79</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13678,14 +13678,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>204.97</v>
+        <v>185.6</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>21.755419873910327</v>
+        <v>19.620224687651973</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>173.1877017516795</v>
+        <v>173.89425033677753</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13702,14 +13702,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>7.49</v>
+        <v>-3.93</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>4.9724532364419325</v>
+        <v>4.4844296415915306</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13717,7 +13717,7 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>164.49266250800366</v>
+        <v>165.16732073419234</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13726,14 +13726,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>7.0000000000000007E-2</v>
+        <v>0.81</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.3422009816109101E-2</v>
+        <v>4.8147463668600871E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.19720516101511149</v>
+        <v>-0.10618907552252638</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13750,14 +13750,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.7940999999999996E-2</v>
+        <v>-2.0825E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>4.59655573551686E-2</v>
+        <v>5.0967815910352543E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13766,14 +13766,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.4160000000000001E-4</v>
+        <v>4.3830000000000006E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>4.9425858909546302E-2</v>
+        <v>5.4804689055501045E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.7374328940946804E-2</v>
+        <v>1.9265111748471238E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6483000000000001</v>
+        <v>1.6463000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>22388233</v>
+        <v>23460284</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-2.5189461955670966E-2</v>
+        <v>-2.7930736266664761E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13859,10 +13859,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="232" t="s">
+      <c r="B17" s="233" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="232"/>
+      <c r="C17" s="233"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -13935,14 +13935,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="232" t="s">
+      <c r="B25" s="233" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="232"/>
-      <c r="E25" s="230" t="s">
+      <c r="C25" s="233"/>
+      <c r="E25" s="231" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="231"/>
+      <c r="F25" s="232"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.02</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.4020000000000004E-2</v>
+        <v>4.3740000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13991,15 +13991,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="233" t="s">
+      <c r="B33" s="230" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="233"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
+      <c r="C33" s="230"/>
+      <c r="D33" s="230"/>
+      <c r="E33" s="230"/>
+      <c r="F33" s="230"/>
+      <c r="G33" s="230"/>
+      <c r="H33" s="230"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14018,24 +14018,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="233"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="233"/>
+      <c r="B39" s="230"/>
+      <c r="C39" s="230"/>
+      <c r="D39" s="230"/>
+      <c r="E39" s="230"/>
+      <c r="F39" s="230"/>
+      <c r="G39" s="230"/>
+      <c r="H39" s="230"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="233" t="s">
+      <c r="B42" s="230" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="233"/>
-      <c r="D42" s="233"/>
-      <c r="E42" s="233"/>
-      <c r="F42" s="233"/>
-      <c r="G42" s="233"/>
-      <c r="H42" s="233"/>
+      <c r="C42" s="230"/>
+      <c r="D42" s="230"/>
+      <c r="E42" s="230"/>
+      <c r="F42" s="230"/>
+      <c r="G42" s="230"/>
+      <c r="H42" s="230"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14050,24 +14050,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="233"/>
-      <c r="C49" s="233"/>
-      <c r="D49" s="233"/>
-      <c r="E49" s="233"/>
-      <c r="F49" s="233"/>
-      <c r="G49" s="233"/>
-      <c r="H49" s="233"/>
+      <c r="B49" s="230"/>
+      <c r="C49" s="230"/>
+      <c r="D49" s="230"/>
+      <c r="E49" s="230"/>
+      <c r="F49" s="230"/>
+      <c r="G49" s="230"/>
+      <c r="H49" s="230"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="233" t="s">
+      <c r="B52" s="230" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="233"/>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="233"/>
-      <c r="H52" s="233"/>
+      <c r="C52" s="230"/>
+      <c r="D52" s="230"/>
+      <c r="E52" s="230"/>
+      <c r="F52" s="230"/>
+      <c r="G52" s="230"/>
+      <c r="H52" s="230"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14205,28 +14205,28 @@
       </c>
     </row>
     <row r="69" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="233"/>
-      <c r="C69" s="233"/>
-      <c r="D69" s="233"/>
-      <c r="E69" s="233"/>
-      <c r="F69" s="233"/>
-      <c r="G69" s="233"/>
-      <c r="H69" s="233"/>
+      <c r="B69" s="230"/>
+      <c r="C69" s="230"/>
+      <c r="D69" s="230"/>
+      <c r="E69" s="230"/>
+      <c r="F69" s="230"/>
+      <c r="G69" s="230"/>
+      <c r="H69" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14296,36 +14296,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="233" t="s">
+      <c r="S2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233" t="s">
+      <c r="T2" s="230"/>
+      <c r="U2" s="230"/>
+      <c r="V2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="230"/>
+      <c r="Y2" s="230"/>
+      <c r="Z2" s="230"/>
+      <c r="AA2" s="230" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
+      <c r="AB2" s="230"/>
+      <c r="AC2" s="230"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15695,35 +15695,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="P2" s="233" t="s">
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
+      <c r="P2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233" t="s">
+      <c r="Q2" s="230"/>
+      <c r="R2" s="230"/>
+      <c r="S2" s="230"/>
+      <c r="T2" s="230"/>
+      <c r="U2" s="230"/>
+      <c r="V2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="230" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
+      <c r="Y2" s="230"/>
+      <c r="Z2" s="230"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16954,20 +16954,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -18360,12 +18360,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18373,6 +18367,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18410,20 +18410,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
       <c r="S2" s="244"/>
       <c r="T2" s="244"/>
       <c r="U2" s="244"/>
@@ -19432,16 +19432,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19504,10 +19504,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="230" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="230"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>204.9</v>
+        <v>184.79</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>217194</v>
+        <v>195877.4</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.4020000000000004E-2</v>
+        <v>4.3740000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6483000000000001</v>
+        <v>1.6463000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19592,10 +19592,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="230" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="233"/>
+      <c r="C15" s="230"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.568759033656825E-2</v>
+        <v>7.2319147666511638E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93431240966343176</v>
+        <v>0.9276808523334884</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19630,7 +19630,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11819350000000001</v>
+        <v>0.1178235</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11284268742256866</v>
+        <v>0.11195924879444408</v>
       </c>
     </row>
   </sheetData>
@@ -19684,20 +19684,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -19890,7 +19890,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>149950.32782638099</v>
+        <v>151473.70703834851</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19944,23 +19944,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>8952.2495431304869</v>
+        <v>8959.3620007709869</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7950.70893742101</v>
+        <v>7963.3474466691287</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7485.5306318713192</v>
+        <v>7503.3863103078038</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7064.8519992799374</v>
+        <v>7087.3305393539886</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7529.3985542712098</v>
+        <v>7559.3562142793662</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19979,14 +19979,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>87857.438616400599</v>
+        <v>89103.117000838203</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="233" t="s">
+      <c r="B13" s="230" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="233"/>
+      <c r="C13" s="230"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20002,14 +20002,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11284268742256866</v>
+        <v>0.11195924879444408</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="230" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="233"/>
+      <c r="C18" s="230"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20017,7 +20017,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>38982.739665973961</v>
+        <v>39072.782511381272</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20026,7 +20026,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>87857.438616400599</v>
+        <v>89103.117000838203</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>126840.17828237456</v>
+        <v>128175.89951221948</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20062,7 +20062,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>121369.17828237457</v>
+        <v>122704.89951221948</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>114.49922479469299</v>
+        <v>115.75933916247121</v>
       </c>
     </row>
   </sheetData>
@@ -20123,20 +20123,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21068,10 +21068,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="230" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="233"/>
+      <c r="C37" s="230"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11284268742256866</v>
+        <v>0.11195924879444408</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>190351.59090327856</v>
+        <v>191127.47905226969</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21133,14 +21133,14 @@
       </c>
       <c r="C44" s="142">
         <f ca="1">C42/C43</f>
-        <v>179.57697255026278</v>
+        <v>180.30894250214121</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="233" t="s">
+      <c r="B46" s="230" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="233"/>
+      <c r="C46" s="230"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -21196,10 +21196,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="233" t="s">
+      <c r="B54" s="230" t="s">
         <v>319</v>
       </c>
-      <c r="C54" s="233"/>
+      <c r="C54" s="230"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -21216,7 +21216,7 @@
       </c>
       <c r="C56" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11284268742256866</v>
+        <v>0.11195924879444408</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C59" s="24">
         <f ca="1">C58/(1+C56)^5-G30+G31</f>
-        <v>183578.96385678026</v>
+        <v>184327.90535698418</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="C61" s="142">
         <f ca="1">C59/C60</f>
-        <v>173.1877017516795</v>
+        <v>173.89425033677753</v>
       </c>
     </row>
   </sheetData>
@@ -21312,10 +21312,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="230" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="230"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21324,7 +21324,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>114.49922479469299</v>
+        <v>115.75933916247121</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C44</f>
-        <v>179.57697255026278</v>
+        <v>180.30894250214121</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C61</f>
-        <v>173.1877017516795</v>
+        <v>173.89425033677753</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21360,7 +21360,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>164.49266250800366</v>
+        <v>165.16732073419234</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21369,7 +21369,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>204.9</v>
+        <v>184.79</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.19720516101511149</v>
+        <v>-0.10618907552252638</v>
       </c>
     </row>
   </sheetData>
@@ -21443,20 +21443,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -21631,7 +21631,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>297813.78327901429</v>
+        <v>300839.3406956672</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21685,23 +21685,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12365.433371673285</v>
+        <v>12375.257563976988</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12967.206333686574</v>
+        <v>12987.819106517336</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13598.26502204083</v>
+        <v>13630.701766938228</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14260.034648271723</v>
+        <v>14305.406406990973</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14954.00978288857</v>
+        <v>15013.508179421222</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21720,7 +21720,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>174492.1572552291</v>
+        <v>176966.17780453918</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21736,7 +21736,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>204.9</v>
+        <v>184.79</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>225.01528122750483</v>
+        <v>227.52169907816312</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11284268742256866</v>
+        <v>0.11195924879444408</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>215964.6</v>
+        <v>194768.66</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21829,7 +21829,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>221435.6</v>
+        <v>200239.66</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>68144.949158560979</v>
+        <v>68312.693023844738</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>174492.1572552291</v>
+        <v>176966.17780453918</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>242637.10641379008</v>
+        <v>245278.87082838392</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>237166.10641379008</v>
+        <v>239807.87082838392</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>225.01528122750483</v>
+        <v>227.52169907816312</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22355,17 +22355,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28850,7 +28850,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>204.9</v>
+        <v>184.79</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -28897,7 +28897,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>204.9</v>
+        <v>184.79</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -30399,7 +30399,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>21.755419873910327</v>
+        <v>19.620224687651973</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30436,7 +30436,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.9724532364419325</v>
+        <v>4.4844296415915306</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30473,7 +30473,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>7.9171713468729381</v>
+        <v>7.140137106826014</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30510,7 +30510,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>217194</v>
+        <v>195877.4</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30547,7 +30547,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>222665</v>
+        <v>201348.4</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30584,7 +30584,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>4.9940564302695911</v>
+        <v>4.5159556811555195</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30621,7 +30621,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>19.60942316160282</v>
+        <v>17.732135623073535</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30756,7 +30756,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="98">AC156/AC160</f>
-        <v>23.029795355741705</v>
+        <v>20.76952603117379</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30793,7 +30793,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="98"/>
-        <v>18.620614143301054</v>
+        <v>16.837989197992673</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30830,7 +30830,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="101">AC160/AC156</f>
-        <v>4.3422009816109101E-2</v>
+        <v>4.8147463668600871E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30867,7 +30867,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>4.59655573551686E-2</v>
+        <v>5.0967815910352543E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30904,7 +30904,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>1.7374328940946804E-2</v>
+        <v>1.9265111748471238E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -30941,7 +30941,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>4.9425858909546302E-2</v>
+        <v>5.4804689055501045E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -30978,7 +30978,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>6.7013821744615412E-2</v>
+        <v>7.4306683670500015E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -31481,7 +31481,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-2.5189461955670966E-2</v>
+        <v>-2.7930736266664761E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -32803,15 +32803,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="230" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="233"/>
-      <c r="E4" s="233" t="s">
+      <c r="C4" s="230"/>
+      <c r="E4" s="230" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32819,7 +32819,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>204.9</v>
+        <v>184.79</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -32835,7 +32835,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>217194</v>
+        <v>195877.4</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32855,7 +32855,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>222665</v>
+        <v>201348.4</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32875,7 +32875,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>21.755419873910327</v>
+        <v>19.620224687651973</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.9724532364419325</v>
+        <v>4.4844296415915306</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32915,7 +32915,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.9171713468729381</v>
+        <v>7.140137106826014</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32935,7 +32935,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.9940564302695911</v>
+        <v>4.5159556811555195</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32944,18 +32944,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>19.60942316160282</v>
+        <v>17.732135623073535</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="233"/>
-      <c r="E15" s="233" t="s">
+      <c r="C15" s="230"/>
+      <c r="E15" s="230" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="233"/>
+      <c r="F15" s="230"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33006,14 +33006,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="233" t="s">
+      <c r="B21" s="230" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="233"/>
-      <c r="E21" s="233" t="s">
+      <c r="C21" s="230"/>
+      <c r="E21" s="230" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="233"/>
+      <c r="F21" s="230"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33082,14 +33082,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="233" t="s">
+      <c r="B29" s="230" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="233"/>
-      <c r="E29" s="233" t="s">
+      <c r="C29" s="230"/>
+      <c r="E29" s="230" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="233"/>
+      <c r="F29" s="230"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33165,14 +33165,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="230" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="233"/>
-      <c r="E37" s="233" t="s">
+      <c r="C37" s="230"/>
+      <c r="E37" s="230" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="233"/>
+      <c r="F37" s="230"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33180,7 +33180,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>4.59655573551686E-2</v>
+        <v>5.0967815910352543E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33196,7 +33196,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>4.3422009816109101E-2</v>
+        <v>4.8147463668600871E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33212,7 +33212,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.7374328940946804E-2</v>
+        <v>1.9265111748471238E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>4.9425858909546302E-2</v>
+        <v>5.4804689055501045E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33237,18 +33237,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>6.7013821744615412E-2</v>
+        <v>7.4306683670500015E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="233" t="s">
+      <c r="B45" s="230" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="233"/>
-      <c r="E45" s="233" t="s">
+      <c r="C45" s="230"/>
+      <c r="E45" s="230" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="233"/>
+      <c r="F45" s="230"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33281,18 +33281,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-2.5189461955670966E-2</v>
+        <v>-2.7930736266664761E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="233" t="s">
+      <c r="B51" s="230" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="233"/>
-      <c r="E51" s="233" t="s">
+      <c r="C51" s="230"/>
+      <c r="E51" s="230" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="233"/>
+      <c r="F51" s="230"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33461,7 +33461,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>204.9</v>
+        <v>184.79</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33490,7 +33490,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>217194</v>
+        <v>195877.4</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>222665</v>
+        <v>201348.4</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33548,7 +33548,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>21.755419873910327</v>
+        <v>19.620224687651973</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33577,7 +33577,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.9724532364419325</v>
+        <v>4.4844296415915306</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33606,7 +33606,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.9171713468729381</v>
+        <v>7.140137106826014</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33635,7 +33635,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.9940564302695911</v>
+        <v>4.5159556811555195</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33664,7 +33664,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>19.60942316160282</v>
+        <v>17.732135623073535</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34437,7 +34437,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>4.59655573551686E-2</v>
+        <v>5.0967815910352543E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34466,7 +34466,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>4.3422009816109101E-2</v>
+        <v>4.8147463668600871E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34495,7 +34495,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.7374328940946804E-2</v>
+        <v>1.9265111748471238E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>4.9425858909546302E-2</v>
+        <v>5.4804689055501045E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34553,7 +34553,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>6.7013821744615412E-2</v>
+        <v>7.4306683670500015E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34789,7 +34789,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-2.5189461955670966E-2</v>
+        <v>-2.7930736266664761E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35327,14 +35327,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="234" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="235"/>
+      <c r="F3" s="236" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="235"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35401,19 +35401,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="234">
+      <c r="C7" s="237">
         <f>Statement!AA89</f>
         <v>-0.13491674828599412</v>
       </c>
-      <c r="D7" s="235"/>
-      <c r="F7" s="234">
+      <c r="D7" s="238"/>
+      <c r="F7" s="237">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-3.4611531104836508E-2</v>
       </c>
-      <c r="G7" s="235"/>
+      <c r="G7" s="238"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35440,19 +35440,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="234">
+      <c r="C9" s="237">
         <f>Statement!AA90</f>
         <v>-0.11997126436781609</v>
       </c>
-      <c r="D9" s="235"/>
-      <c r="F9" s="234">
+      <c r="D9" s="238"/>
+      <c r="F9" s="237">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>-7.4944298156775372E-3</v>
       </c>
-      <c r="G9" s="235"/>
+      <c r="G9" s="238"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35479,19 +35479,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="234">
+      <c r="C11" s="237">
         <f>Statement!AA91</f>
         <v>-0.1473668461998803</v>
       </c>
-      <c r="D11" s="235"/>
-      <c r="F11" s="234">
+      <c r="D11" s="238"/>
+      <c r="F11" s="237">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-5.6769281694803046E-2</v>
       </c>
-      <c r="G11" s="235"/>
+      <c r="G11" s="238"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35518,19 +35518,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="234">
+      <c r="C13" s="237">
         <f>Statement!AA94</f>
         <v>2.1699819168173599E-2</v>
       </c>
-      <c r="D13" s="235"/>
-      <c r="F13" s="234">
+      <c r="D13" s="238"/>
+      <c r="F13" s="237">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.16016427104722791</v>
       </c>
-      <c r="G13" s="235"/>
+      <c r="G13" s="238"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -35557,19 +35557,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="234">
+      <c r="C15" s="237">
         <f>Statement!AA95</f>
         <v>-0.31402257872846107</v>
       </c>
-      <c r="D15" s="235"/>
-      <c r="F15" s="234">
+      <c r="D15" s="238"/>
+      <c r="F15" s="237">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.25993589743589746</v>
       </c>
-      <c r="G15" s="235"/>
+      <c r="G15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35596,19 +35596,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="234">
+      <c r="C17" s="237">
         <f>Statement!AA97</f>
         <v>-0.35685752330226367</v>
       </c>
-      <c r="D17" s="235"/>
-      <c r="F17" s="234">
+      <c r="D17" s="238"/>
+      <c r="F17" s="237">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.31294452347083929</v>
       </c>
-      <c r="G17" s="235"/>
+      <c r="G17" s="238"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -35635,22 +35635,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="234">
+      <c r="C19" s="237">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-6.4874884151992582E-3</v>
       </c>
-      <c r="D19" s="235"/>
-      <c r="F19" s="234">
+      <c r="D19" s="238"/>
+      <c r="F19" s="237">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.8565022421524667E-2</v>
       </c>
-      <c r="G19" s="235"/>
+      <c r="G19" s="238"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35677,22 +35677,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="234">
+      <c r="C21" s="237">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.35171265972296784</v>
       </c>
-      <c r="D21" s="235"/>
-      <c r="F21" s="234">
+      <c r="D21" s="238"/>
+      <c r="F21" s="237">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.28482587064676618</v>
       </c>
-      <c r="G21" s="235"/>
+      <c r="G21" s="238"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35740,22 +35740,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="234">
+      <c r="C25" s="237">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.23006134969325154</v>
       </c>
-      <c r="D25" s="235"/>
-      <c r="F25" s="234">
+      <c r="D25" s="238"/>
+      <c r="F25" s="237">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.13061047770241016</v>
       </c>
-      <c r="G25" s="235"/>
+      <c r="G25" s="238"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -35782,22 +35782,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="234">
+      <c r="C27" s="237">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.20435967302452315</v>
       </c>
-      <c r="D27" s="235"/>
-      <c r="F27" s="234">
+      <c r="D27" s="238"/>
+      <c r="F27" s="237">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.38269030239833157</v>
       </c>
-      <c r="G27" s="235"/>
+      <c r="G27" s="238"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -35824,22 +35824,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="234">
+      <c r="C29" s="237">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.2511848341232227E-2</v>
       </c>
-      <c r="D29" s="235"/>
-      <c r="F29" s="234">
+      <c r="D29" s="238"/>
+      <c r="F29" s="237">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>9.1714104996837451E-2</v>
       </c>
-      <c r="G29" s="235"/>
+      <c r="G29" s="238"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35866,22 +35866,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="234">
+      <c r="C31" s="237">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.1448223876378027</v>
       </c>
-      <c r="D31" s="235"/>
-      <c r="F31" s="234">
+      <c r="D31" s="238"/>
+      <c r="F31" s="237">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-4.1503854683704718E-2</v>
       </c>
-      <c r="G31" s="235"/>
+      <c r="G31" s="238"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -35908,43 +35908,25 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="234">
+      <c r="C33" s="237">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.13190954773869346</v>
       </c>
-      <c r="D33" s="235"/>
-      <c r="F33" s="234">
+      <c r="D33" s="238"/>
+      <c r="F33" s="237">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>4.7763457164518575E-2</v>
       </c>
-      <c r="G33" s="235"/>
+      <c r="G33" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -35955,6 +35937,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC33F33-3B86-234B-B9D0-E3975A634FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D667B5C1-6036-E141-A5F6-DC5DA9C2643A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2280,9 +2280,6 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2292,6 +2289,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2299,12 +2305,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12691,11 +12691,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6463000000000001</v>
-    <v>-3.93</v>
-    <v>-2.0825E-2</v>
-    <v>0.81</v>
-    <v>4.3830000000000006E-3</v>
+    <v>1.6396999999999999</v>
+    <v>-5.67</v>
+    <v>-3.1168000000000001E-2</v>
+    <v>0.77</v>
+    <v>4.3690000000000005E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12703,26 +12703,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>193.5</v>
+    <v>185.79900000000001</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46203.949436168747</v>
+    <v>46205.999901481249</v>
     <v>4</v>
-    <v>183.5</v>
-    <v>194768660000</v>
+    <v>172.12</v>
+    <v>185767500000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>188.99</v>
-    <v>20.100300000000001</v>
-    <v>188.72</v>
-    <v>184.79</v>
-    <v>185.6</v>
+    <v>182.17</v>
+    <v>19.788</v>
+    <v>181.92</v>
+    <v>176.25</v>
+    <v>177.02</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>22030054</v>
-    <v>23460284</v>
+    <v>18682459</v>
+    <v>22834174</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -12746,17 +12746,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.02</v>
-    <v>4.5750000000000001E-4</v>
+    <v>0.1</v>
+    <v>2.235E-3</v>
     <v>US</v>
-    <v>43.9</v>
+    <v>45.05</v>
     <v>Index</v>
     <v>7</v>
-    <v>43.67</v>
+    <v>44.53</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>43.78</v>
-    <v>43.72</v>
-    <v>43.74</v>
+    <v>45.03</v>
+    <v>44.75</v>
+    <v>44.85</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12998,9 +12998,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13587,18 +13587,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="231" t="s">
+      <c r="B2" s="230" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="232"/>
-      <c r="E2" s="231" t="s">
+      <c r="C2" s="231"/>
+      <c r="E2" s="230" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="232"/>
-      <c r="H2" s="231" t="s">
+      <c r="F2" s="231"/>
+      <c r="H2" s="230" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="232"/>
+      <c r="I2" s="231"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>195877.4</v>
+        <v>186825</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>115.75933916247121</v>
+        <v>115.05882450274875</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>201348.4</v>
+        <v>192296</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>180.30894250214121</v>
+        <v>179.90343954741238</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>184.79</v>
+        <v>176.25</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13678,14 +13678,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>185.6</v>
+        <v>177.02</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>19.620224687651973</v>
+        <v>18.71348342009124</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>173.89425033677753</v>
+        <v>173.50283052756066</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13702,14 +13702,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-3.93</v>
+        <v>-5.67</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>4.4844296415915306</v>
+        <v>4.2771834208047368</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13717,7 +13717,7 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>165.16732073419234</v>
+        <v>164.79296137827529</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13726,14 +13726,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.8147463668600871E-2</v>
+        <v>5.0480396092600029E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.10618907552252638</v>
+        <v>-6.5004474449501873E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13750,14 +13750,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.0825E-2</v>
+        <v>-3.1168000000000001E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>5.0967815910352543E-2</v>
+        <v>5.3437405401838556E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13766,14 +13766,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>4.3830000000000006E-3</v>
+        <v>4.3690000000000005E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>5.4804689055501045E-2</v>
+        <v>5.7460190017395961E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.9265111748471238E-2</v>
+        <v>2.0198581560283688E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6463000000000001</v>
+        <v>1.6396999999999999</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>23460284</v>
+        <v>22834174</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-2.7930736266664761E-2</v>
+        <v>-2.9284089388465141E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13859,10 +13859,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="233" t="s">
+      <c r="B17" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="233"/>
+      <c r="C17" s="232"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -13935,14 +13935,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="233" t="s">
+      <c r="B25" s="232" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="233"/>
-      <c r="E25" s="231" t="s">
+      <c r="C25" s="232"/>
+      <c r="E25" s="230" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="232"/>
+      <c r="F25" s="231"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>43.74</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.3740000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13991,15 +13991,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="230" t="s">
+      <c r="B33" s="233" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="230"/>
-      <c r="D33" s="230"/>
-      <c r="E33" s="230"/>
-      <c r="F33" s="230"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="230"/>
+      <c r="C33" s="233"/>
+      <c r="D33" s="233"/>
+      <c r="E33" s="233"/>
+      <c r="F33" s="233"/>
+      <c r="G33" s="233"/>
+      <c r="H33" s="233"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14018,24 +14018,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="230"/>
-      <c r="C39" s="230"/>
-      <c r="D39" s="230"/>
-      <c r="E39" s="230"/>
-      <c r="F39" s="230"/>
-      <c r="G39" s="230"/>
-      <c r="H39" s="230"/>
+      <c r="B39" s="233"/>
+      <c r="C39" s="233"/>
+      <c r="D39" s="233"/>
+      <c r="E39" s="233"/>
+      <c r="F39" s="233"/>
+      <c r="G39" s="233"/>
+      <c r="H39" s="233"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="230" t="s">
+      <c r="B42" s="233" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="230"/>
-      <c r="D42" s="230"/>
-      <c r="E42" s="230"/>
-      <c r="F42" s="230"/>
-      <c r="G42" s="230"/>
-      <c r="H42" s="230"/>
+      <c r="C42" s="233"/>
+      <c r="D42" s="233"/>
+      <c r="E42" s="233"/>
+      <c r="F42" s="233"/>
+      <c r="G42" s="233"/>
+      <c r="H42" s="233"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14050,24 +14050,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="230"/>
-      <c r="C49" s="230"/>
-      <c r="D49" s="230"/>
-      <c r="E49" s="230"/>
-      <c r="F49" s="230"/>
-      <c r="G49" s="230"/>
-      <c r="H49" s="230"/>
+      <c r="B49" s="233"/>
+      <c r="C49" s="233"/>
+      <c r="D49" s="233"/>
+      <c r="E49" s="233"/>
+      <c r="F49" s="233"/>
+      <c r="G49" s="233"/>
+      <c r="H49" s="233"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="230" t="s">
+      <c r="B52" s="233" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="230"/>
-      <c r="D52" s="230"/>
-      <c r="E52" s="230"/>
-      <c r="F52" s="230"/>
-      <c r="G52" s="230"/>
-      <c r="H52" s="230"/>
+      <c r="C52" s="233"/>
+      <c r="D52" s="233"/>
+      <c r="E52" s="233"/>
+      <c r="F52" s="233"/>
+      <c r="G52" s="233"/>
+      <c r="H52" s="233"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14205,28 +14205,28 @@
       </c>
     </row>
     <row r="69" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="230"/>
-      <c r="C69" s="230"/>
-      <c r="D69" s="230"/>
-      <c r="E69" s="230"/>
-      <c r="F69" s="230"/>
-      <c r="G69" s="230"/>
-      <c r="H69" s="230"/>
+      <c r="B69" s="233"/>
+      <c r="C69" s="233"/>
+      <c r="D69" s="233"/>
+      <c r="E69" s="233"/>
+      <c r="F69" s="233"/>
+      <c r="G69" s="233"/>
+      <c r="H69" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14296,36 +14296,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="230" t="s">
+      <c r="S2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230"/>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
-      <c r="AA2" s="230" t="s">
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="230"/>
-      <c r="AC2" s="230"/>
+      <c r="AB2" s="233"/>
+      <c r="AC2" s="233"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15695,35 +15695,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
-      <c r="P2" s="230" t="s">
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
+      <c r="P2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="230"/>
-      <c r="R2" s="230"/>
-      <c r="S2" s="230"/>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230" t="s">
+      <c r="Q2" s="233"/>
+      <c r="R2" s="233"/>
+      <c r="S2" s="233"/>
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16954,20 +16954,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -18278,23 +18278,23 @@
         <v>58</v>
       </c>
       <c r="C45" s="114">
-        <f>-Statement!M60</f>
+        <f>-Statement!M109</f>
         <v>1888</v>
       </c>
       <c r="D45" s="114">
-        <f>-Statement!N60</f>
+        <f>-Statement!N109</f>
         <v>2262</v>
       </c>
       <c r="E45" s="114">
-        <f>-Statement!O60</f>
+        <f>-Statement!O109</f>
         <v>1450</v>
       </c>
       <c r="F45" s="114">
-        <f>-Statement!P60</f>
+        <f>-Statement!P109</f>
         <v>1041</v>
       </c>
       <c r="G45" s="115">
-        <f>-Statement!Q60</f>
+        <f>-Statement!Q109</f>
         <v>1192</v>
       </c>
       <c r="H45" s="25">
@@ -18360,6 +18360,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18367,12 +18373,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18410,20 +18410,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="S2" s="244"/>
       <c r="T2" s="244"/>
       <c r="U2" s="244"/>
@@ -19432,16 +19432,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19504,10 +19504,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="230"/>
+      <c r="C4" s="233"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>184.79</v>
+        <v>176.25</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>195877.4</v>
+        <v>186825</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.3740000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6463000000000001</v>
+        <v>1.6396999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19592,10 +19592,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
+      <c r="B15" s="233" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="230"/>
+      <c r="C15" s="233"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.2319147666511638E-2</v>
+        <v>7.5558524456320053E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9276808523334884</v>
+        <v>0.92444147554367995</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19630,7 +19630,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1178235</v>
+        <v>0.11863649999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11195924879444408</v>
+        <v>0.11244814350924069</v>
       </c>
     </row>
   </sheetData>
@@ -19684,20 +19684,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -19890,7 +19890,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>151473.70703834851</v>
+        <v>150626.86579244063</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19944,23 +19944,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>8959.3620007709869</v>
+        <v>8955.4245725360779</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7963.3474466691287</v>
+        <v>7956.3495780345447</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7503.3863103078038</v>
+        <v>7493.4979734694343</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7087.3305393539886</v>
+        <v>7074.8798917231115</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7559.3562142793662</v>
+        <v>7542.7600143685713</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19979,14 +19979,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>89103.117000838203</v>
+        <v>88410.441942781923</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="230" t="s">
+      <c r="B13" s="233" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="230"/>
+      <c r="C13" s="233"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20002,14 +20002,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11195924879444408</v>
+        <v>0.11244814350924069</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="230" t="s">
+      <c r="B18" s="233" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="230"/>
+      <c r="C18" s="233"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20017,7 +20017,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>39072.782511381272</v>
+        <v>39022.912030131738</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20026,7 +20026,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>89103.117000838203</v>
+        <v>88410.441942781923</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>128175.89951221948</v>
+        <v>127433.35397291367</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20062,7 +20062,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>122704.89951221948</v>
+        <v>121962.35397291367</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>115.75933916247121</v>
+        <v>115.05882450274875</v>
       </c>
     </row>
   </sheetData>
@@ -20123,20 +20123,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21068,10 +21068,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="230" t="s">
+      <c r="B37" s="233" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="230"/>
+      <c r="C37" s="233"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11195924879444408</v>
+        <v>0.11244814350924069</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>191127.47905226969</v>
+        <v>190697.64592025711</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21133,14 +21133,14 @@
       </c>
       <c r="C44" s="142">
         <f ca="1">C42/C43</f>
-        <v>180.30894250214121</v>
+        <v>179.90343954741238</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="230" t="s">
+      <c r="B46" s="233" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="230"/>
+      <c r="C46" s="233"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -21196,10 +21196,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="230" t="s">
+      <c r="B54" s="233" t="s">
         <v>319</v>
       </c>
-      <c r="C54" s="230"/>
+      <c r="C54" s="233"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -21216,7 +21216,7 @@
       </c>
       <c r="C56" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11195924879444408</v>
+        <v>0.11244814350924069</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C59" s="24">
         <f ca="1">C58/(1+C56)^5-G30+G31</f>
-        <v>184327.90535698418</v>
+        <v>183913.00035921429</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="C61" s="142">
         <f ca="1">C59/C60</f>
-        <v>173.89425033677753</v>
+        <v>173.50283052756066</v>
       </c>
     </row>
   </sheetData>
@@ -21312,10 +21312,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="230"/>
+      <c r="C4" s="233"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21324,7 +21324,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>115.75933916247121</v>
+        <v>115.05882450274875</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C44</f>
-        <v>180.30894250214121</v>
+        <v>179.90343954741238</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C61</f>
-        <v>173.89425033677753</v>
+        <v>173.50283052756066</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21360,7 +21360,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>165.16732073419234</v>
+        <v>164.79296137827529</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21369,7 +21369,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>184.79</v>
+        <v>176.25</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.10618907552252638</v>
+        <v>-6.5004474449501873E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21443,20 +21443,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -21631,7 +21631,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>300839.3406956672</v>
+        <v>299157.44377062313</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21685,23 +21685,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12375.257563976988</v>
+        <v>12369.818930228013</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12987.819106517336</v>
+        <v>12976.405934787002</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13630.701766938228</v>
+        <v>13612.738548087336</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14305.406406990973</v>
+        <v>14280.275425248137</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>15013.508179421222</v>
+        <v>14980.546750425807</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21720,7 +21720,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>176966.17780453918</v>
+        <v>175590.4677103165</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21736,7 +21736,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>184.79</v>
+        <v>176.25</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>227.52169907816312</v>
+        <v>226.12832381318103</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11195924879444408</v>
+        <v>0.11244814350924069</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>194768.66</v>
+        <v>185767.5</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21829,7 +21829,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>200239.66</v>
+        <v>191238.5</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>68312.693023844738</v>
+        <v>68219.7855887763</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>176966.17780453918</v>
+        <v>175590.4677103165</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>245278.87082838392</v>
+        <v>243810.25329909282</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>239807.87082838392</v>
+        <v>238339.25329909282</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>227.52169907816312</v>
+        <v>226.12832381318103</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22355,17 +22355,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28850,7 +28850,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>184.79</v>
+        <v>176.25</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -28897,7 +28897,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>184.79</v>
+        <v>176.25</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -30399,7 +30399,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>19.620224687651973</v>
+        <v>18.71348342009124</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30436,7 +30436,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.4844296415915306</v>
+        <v>4.2771834208047368</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30473,7 +30473,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>7.140137106826014</v>
+        <v>6.8101583693819201</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30510,7 +30510,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>195877.4</v>
+        <v>186825</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30547,7 +30547,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>201348.4</v>
+        <v>192296</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30584,7 +30584,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>4.5159556811555195</v>
+        <v>4.3129233391647599</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30621,7 +30621,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>17.732135623073535</v>
+        <v>16.934918538088947</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30756,7 +30756,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="98">AC156/AC160</f>
-        <v>20.76952603117379</v>
+        <v>19.809670236454245</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30793,7 +30793,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="98"/>
-        <v>16.837989197992673</v>
+        <v>16.080971941258031</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30830,7 +30830,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="101">AC160/AC156</f>
-        <v>4.8147463668600871E-2</v>
+        <v>5.0480396092600029E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30867,7 +30867,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.0967815910352543E-2</v>
+        <v>5.3437405401838556E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30904,7 +30904,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>1.9265111748471238E-2</v>
+        <v>2.0198581560283688E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -30941,7 +30941,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>5.4804689055501045E-2</v>
+        <v>5.7460190017395961E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -30978,7 +30978,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>7.4306683670500015E-2</v>
+        <v>7.7907132343101829E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -31481,7 +31481,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-2.7930736266664761E-2</v>
+        <v>-2.9284089388465141E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -32803,15 +32803,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="230"/>
-      <c r="E4" s="230" t="s">
+      <c r="C4" s="233"/>
+      <c r="E4" s="233" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32819,7 +32819,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>184.79</v>
+        <v>176.25</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -32835,7 +32835,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>195877.4</v>
+        <v>186825</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32855,7 +32855,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>201348.4</v>
+        <v>192296</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32875,7 +32875,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>19.620224687651973</v>
+        <v>18.71348342009124</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.4844296415915306</v>
+        <v>4.2771834208047368</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32915,7 +32915,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.140137106826014</v>
+        <v>6.8101583693819201</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32935,7 +32935,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.5159556811555195</v>
+        <v>4.3129233391647599</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32944,18 +32944,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>17.732135623073535</v>
+        <v>16.934918538088947</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
+      <c r="B15" s="233" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="230"/>
-      <c r="E15" s="230" t="s">
+      <c r="C15" s="233"/>
+      <c r="E15" s="233" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="230"/>
+      <c r="F15" s="233"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33006,14 +33006,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="230" t="s">
+      <c r="B21" s="233" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="230"/>
-      <c r="E21" s="230" t="s">
+      <c r="C21" s="233"/>
+      <c r="E21" s="233" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="230"/>
+      <c r="F21" s="233"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33082,14 +33082,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="230" t="s">
+      <c r="B29" s="233" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="230"/>
-      <c r="E29" s="230" t="s">
+      <c r="C29" s="233"/>
+      <c r="E29" s="233" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="230"/>
+      <c r="F29" s="233"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33165,14 +33165,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="230" t="s">
+      <c r="B37" s="233" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="230"/>
-      <c r="E37" s="230" t="s">
+      <c r="C37" s="233"/>
+      <c r="E37" s="233" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="230"/>
+      <c r="F37" s="233"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33180,7 +33180,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.0967815910352543E-2</v>
+        <v>5.3437405401838556E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33196,7 +33196,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>4.8147463668600871E-2</v>
+        <v>5.0480396092600029E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33212,7 +33212,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.9265111748471238E-2</v>
+        <v>2.0198581560283688E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.4804689055501045E-2</v>
+        <v>5.7460190017395961E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33237,18 +33237,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>7.4306683670500015E-2</v>
+        <v>7.7907132343101829E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="230" t="s">
+      <c r="B45" s="233" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="230"/>
-      <c r="E45" s="230" t="s">
+      <c r="C45" s="233"/>
+      <c r="E45" s="233" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="230"/>
+      <c r="F45" s="233"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33281,18 +33281,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-2.7930736266664761E-2</v>
+        <v>-2.9284089388465141E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="230" t="s">
+      <c r="B51" s="233" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="230"/>
-      <c r="E51" s="230" t="s">
+      <c r="C51" s="233"/>
+      <c r="E51" s="233" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="230"/>
+      <c r="F51" s="233"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33461,7 +33461,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>184.79</v>
+        <v>176.25</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33490,7 +33490,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>195877.4</v>
+        <v>186825</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>201348.4</v>
+        <v>192296</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33548,7 +33548,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>19.620224687651973</v>
+        <v>18.71348342009124</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33577,7 +33577,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.4844296415915306</v>
+        <v>4.2771834208047368</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33606,7 +33606,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.140137106826014</v>
+        <v>6.8101583693819201</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33635,7 +33635,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.5159556811555195</v>
+        <v>4.3129233391647599</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33664,7 +33664,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>17.732135623073535</v>
+        <v>16.934918538088947</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34437,7 +34437,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.0967815910352543E-2</v>
+        <v>5.3437405401838556E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34466,7 +34466,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>4.8147463668600871E-2</v>
+        <v>5.0480396092600029E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34495,7 +34495,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.9265111748471238E-2</v>
+        <v>2.0198581560283688E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.4804689055501045E-2</v>
+        <v>5.7460190017395961E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34553,7 +34553,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>7.4306683670500015E-2</v>
+        <v>7.7907132343101829E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34789,7 +34789,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-2.7930736266664761E-2</v>
+        <v>-2.9284089388465141E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35327,14 +35327,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="236" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="F3" s="236" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="235"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35401,19 +35401,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="237">
+      <c r="C7" s="234">
         <f>Statement!AA89</f>
         <v>-0.13491674828599412</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="F7" s="237">
+      <c r="D7" s="235"/>
+      <c r="F7" s="234">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-3.4611531104836508E-2</v>
       </c>
-      <c r="G7" s="238"/>
+      <c r="G7" s="235"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35440,19 +35440,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="237">
+      <c r="C9" s="234">
         <f>Statement!AA90</f>
         <v>-0.11997126436781609</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="F9" s="237">
+      <c r="D9" s="235"/>
+      <c r="F9" s="234">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>-7.4944298156775372E-3</v>
       </c>
-      <c r="G9" s="238"/>
+      <c r="G9" s="235"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35479,19 +35479,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="237">
+      <c r="C11" s="234">
         <f>Statement!AA91</f>
         <v>-0.1473668461998803</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="F11" s="237">
+      <c r="D11" s="235"/>
+      <c r="F11" s="234">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-5.6769281694803046E-2</v>
       </c>
-      <c r="G11" s="238"/>
+      <c r="G11" s="235"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35518,19 +35518,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="237">
+      <c r="C13" s="234">
         <f>Statement!AA94</f>
         <v>2.1699819168173599E-2</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="F13" s="237">
+      <c r="D13" s="235"/>
+      <c r="F13" s="234">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.16016427104722791</v>
       </c>
-      <c r="G13" s="238"/>
+      <c r="G13" s="235"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -35557,19 +35557,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="237">
+      <c r="C15" s="234">
         <f>Statement!AA95</f>
         <v>-0.31402257872846107</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="F15" s="237">
+      <c r="D15" s="235"/>
+      <c r="F15" s="234">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.25993589743589746</v>
       </c>
-      <c r="G15" s="238"/>
+      <c r="G15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35596,19 +35596,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="237">
+      <c r="C17" s="234">
         <f>Statement!AA97</f>
         <v>-0.35685752330226367</v>
       </c>
-      <c r="D17" s="238"/>
-      <c r="F17" s="237">
+      <c r="D17" s="235"/>
+      <c r="F17" s="234">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.31294452347083929</v>
       </c>
-      <c r="G17" s="238"/>
+      <c r="G17" s="235"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -35635,22 +35635,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="237">
+      <c r="C19" s="234">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-6.4874884151992582E-3</v>
       </c>
-      <c r="D19" s="238"/>
-      <c r="F19" s="237">
+      <c r="D19" s="235"/>
+      <c r="F19" s="234">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.8565022421524667E-2</v>
       </c>
-      <c r="G19" s="238"/>
+      <c r="G19" s="235"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35677,22 +35677,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="237">
+      <c r="C21" s="234">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.35171265972296784</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="F21" s="237">
+      <c r="D21" s="235"/>
+      <c r="F21" s="234">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.28482587064676618</v>
       </c>
-      <c r="G21" s="238"/>
+      <c r="G21" s="235"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35740,22 +35740,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="237">
+      <c r="C25" s="234">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.23006134969325154</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="F25" s="237">
+      <c r="D25" s="235"/>
+      <c r="F25" s="234">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.13061047770241016</v>
       </c>
-      <c r="G25" s="238"/>
+      <c r="G25" s="235"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -35782,22 +35782,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="237">
+      <c r="C27" s="234">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.20435967302452315</v>
       </c>
-      <c r="D27" s="238"/>
-      <c r="F27" s="237">
+      <c r="D27" s="235"/>
+      <c r="F27" s="234">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.38269030239833157</v>
       </c>
-      <c r="G27" s="238"/>
+      <c r="G27" s="235"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -35824,22 +35824,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="237">
+      <c r="C29" s="234">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.2511848341232227E-2</v>
       </c>
-      <c r="D29" s="238"/>
-      <c r="F29" s="237">
+      <c r="D29" s="235"/>
+      <c r="F29" s="234">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>9.1714104996837451E-2</v>
       </c>
-      <c r="G29" s="238"/>
+      <c r="G29" s="235"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35866,22 +35866,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="237">
+      <c r="C31" s="234">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.1448223876378027</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="F31" s="237">
+      <c r="D31" s="235"/>
+      <c r="F31" s="234">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-4.1503854683704718E-2</v>
       </c>
-      <c r="G31" s="238"/>
+      <c r="G31" s="235"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -35908,25 +35908,43 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="237">
+      <c r="C33" s="234">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.13190954773869346</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="F33" s="237">
+      <c r="D33" s="235"/>
+      <c r="F33" s="234">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>4.7763457164518575E-2</v>
       </c>
-      <c r="G33" s="238"/>
+      <c r="G33" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -35937,24 +35955,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D667B5C1-6036-E141-A5F6-DC5DA9C2643A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793FCFFA-A6B8-3F49-BEE7-D059A93F6DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,7 +128,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -138,19 +159,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="406">
   <si>
     <t>Ticker</t>
   </si>
@@ -2280,6 +2310,21 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2287,15 +2332,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2307,22 +2343,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12652,7 +12682,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12691,11 +12721,9 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6396999999999999</v>
-    <v>-5.67</v>
-    <v>-3.1168000000000001E-2</v>
-    <v>0.77</v>
-    <v>4.3690000000000005E-3</v>
+    <v>1.6357999999999999</v>
+    <v>-3.53</v>
+    <v>-1.8929999999999999E-2</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12703,36 +12731,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>185.79900000000001</v>
+    <v>185.88</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46205.999901481249</v>
+    <v>46210.764783876562</v>
     <v>4</v>
-    <v>172.12</v>
-    <v>185767500000</v>
+    <v>179</v>
+    <v>192829300000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>182.17</v>
-    <v>19.788</v>
-    <v>181.92</v>
-    <v>176.25</v>
-    <v>177.02</v>
+    <v>179.51</v>
+    <v>19.900099999999998</v>
+    <v>186.48</v>
+    <v>182.95</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>18682459</v>
-    <v>22834174</v>
+    <v>6878614</v>
+    <v>22329372</v>
     <v>1991</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12746,28 +12788,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.1</v>
-    <v>2.235E-3</v>
+    <v>-0.06</v>
+    <v>-1.338E-3</v>
     <v>US</v>
-    <v>45.05</v>
+    <v>44.91</v>
     <v>Index</v>
-    <v>7</v>
-    <v>44.53</v>
+    <v>10</v>
+    <v>44.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.03</v>
-    <v>44.75</v>
+    <v>44.57</v>
     <v>44.85</v>
+    <v>44.79</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12801,8 +12843,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12824,7 +12864,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12834,6 +12873,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12869,7 +12913,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12880,16 +12924,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12990,19 +13031,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13083,9 +13118,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13093,9 +13125,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13587,18 +13616,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="230" t="s">
+      <c r="B2" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="231"/>
-      <c r="E2" s="230" t="s">
+      <c r="C2" s="236"/>
+      <c r="E2" s="235" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="231"/>
-      <c r="H2" s="230" t="s">
+      <c r="F2" s="236"/>
+      <c r="H2" s="235" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="231"/>
+      <c r="I2" s="236"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13613,7 +13642,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>186825</v>
+        <v>193927</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13621,7 +13650,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>115.05882450274875</v>
+        <v>115.07054079074922</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13637,7 +13666,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>192296</v>
+        <v>199398</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13645,7 +13674,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>179.90343954741238</v>
+        <v>174.74892984060975</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13654,7 +13683,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>176.25</v>
+        <v>182.95</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13676,16 +13705,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>177.02</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>18.71348342009124</v>
+        <v>19.424861229535843</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13693,7 +13722,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>173.50283052756066</v>
+        <v>168.34808427259546</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13702,14 +13731,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-5.67</v>
+        <v>-3.53</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>4.2771834208047368</v>
+        <v>4.4397770600636965</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13717,23 +13746,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>164.79296137827529</v>
+        <v>162.21857645983346</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.77</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>5.0480396092600029E-2</v>
+        <v>4.8631701619681632E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13741,7 +13770,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-6.5004474449501873E-2</v>
+        <v>-0.11331742847863642</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13750,30 +13779,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.1168000000000001E-2</v>
+        <v>-1.8929999999999999E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>5.3437405401838556E-2</v>
+        <v>5.1480419251566253E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>4.3690000000000005E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>5.7460190017395961E-2</v>
+        <v>5.535588133679168E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13789,7 +13818,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>2.0198581560283688E-2</v>
+        <v>1.9458868543317846E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13814,7 +13843,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6396999999999999</v>
+        <v>1.6357999999999999</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13830,7 +13859,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>22834174</v>
+        <v>22329372</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13846,7 +13875,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-2.9284089388465141E-2</v>
+        <v>-2.8211646650543761E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13859,10 +13888,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="232" t="s">
+      <c r="B17" s="237" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="232"/>
+      <c r="C17" s="237"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -13935,14 +13964,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="232" t="s">
+      <c r="B25" s="237" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="232"/>
-      <c r="E25" s="230" t="s">
+      <c r="C25" s="237"/>
+      <c r="E25" s="235" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="231"/>
+      <c r="F25" s="236"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13951,12 +13980,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.85</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13971,7 +14000,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13991,15 +14020,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="233" t="s">
+      <c r="B33" s="230" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="233"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
+      <c r="C33" s="230"/>
+      <c r="D33" s="230"/>
+      <c r="E33" s="230"/>
+      <c r="F33" s="230"/>
+      <c r="G33" s="230"/>
+      <c r="H33" s="230"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14018,24 +14047,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="233"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="233"/>
+      <c r="B39" s="230"/>
+      <c r="C39" s="230"/>
+      <c r="D39" s="230"/>
+      <c r="E39" s="230"/>
+      <c r="F39" s="230"/>
+      <c r="G39" s="230"/>
+      <c r="H39" s="230"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="233" t="s">
+      <c r="B42" s="230" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="233"/>
-      <c r="D42" s="233"/>
-      <c r="E42" s="233"/>
-      <c r="F42" s="233"/>
-      <c r="G42" s="233"/>
-      <c r="H42" s="233"/>
+      <c r="C42" s="230"/>
+      <c r="D42" s="230"/>
+      <c r="E42" s="230"/>
+      <c r="F42" s="230"/>
+      <c r="G42" s="230"/>
+      <c r="H42" s="230"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14050,24 +14079,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="233"/>
-      <c r="C49" s="233"/>
-      <c r="D49" s="233"/>
-      <c r="E49" s="233"/>
-      <c r="F49" s="233"/>
-      <c r="G49" s="233"/>
-      <c r="H49" s="233"/>
+      <c r="B49" s="230"/>
+      <c r="C49" s="230"/>
+      <c r="D49" s="230"/>
+      <c r="E49" s="230"/>
+      <c r="F49" s="230"/>
+      <c r="G49" s="230"/>
+      <c r="H49" s="230"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="233" t="s">
+      <c r="B52" s="230" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="233"/>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="233"/>
-      <c r="H52" s="233"/>
+      <c r="C52" s="230"/>
+      <c r="D52" s="230"/>
+      <c r="E52" s="230"/>
+      <c r="F52" s="230"/>
+      <c r="G52" s="230"/>
+      <c r="H52" s="230"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14205,28 +14234,28 @@
       </c>
     </row>
     <row r="69" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="233"/>
-      <c r="C69" s="233"/>
-      <c r="D69" s="233"/>
-      <c r="E69" s="233"/>
-      <c r="F69" s="233"/>
-      <c r="G69" s="233"/>
-      <c r="H69" s="233"/>
+      <c r="B69" s="230"/>
+      <c r="C69" s="230"/>
+      <c r="D69" s="230"/>
+      <c r="E69" s="230"/>
+      <c r="F69" s="230"/>
+      <c r="G69" s="230"/>
+      <c r="H69" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14296,36 +14325,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="233" t="s">
+      <c r="S2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233" t="s">
+      <c r="T2" s="230"/>
+      <c r="U2" s="230"/>
+      <c r="V2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="230"/>
+      <c r="Y2" s="230"/>
+      <c r="Z2" s="230"/>
+      <c r="AA2" s="230" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
+      <c r="AB2" s="230"/>
+      <c r="AC2" s="230"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14336,32 +14365,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
+      <c r="H4" s="234"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="234"/>
+      <c r="K4" s="234"/>
+      <c r="L4" s="234"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="240" t="s">
+      <c r="S4" s="243" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="241"/>
-      <c r="U4" s="241"/>
-      <c r="V4" s="241"/>
-      <c r="W4" s="241"/>
-      <c r="X4" s="241"/>
-      <c r="Y4" s="241"/>
-      <c r="Z4" s="241"/>
-      <c r="AA4" s="241"/>
-      <c r="AB4" s="241"/>
-      <c r="AC4" s="241"/>
+      <c r="T4" s="244"/>
+      <c r="U4" s="244"/>
+      <c r="V4" s="244"/>
+      <c r="W4" s="244"/>
+      <c r="X4" s="244"/>
+      <c r="Y4" s="244"/>
+      <c r="Z4" s="244"/>
+      <c r="AA4" s="244"/>
+      <c r="AB4" s="244"/>
+      <c r="AC4" s="244"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15045,33 +15074,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="239" t="s">
+      <c r="C13" s="234" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="234"/>
+      <c r="G13" s="234"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="234"/>
+      <c r="J13" s="234"/>
+      <c r="K13" s="234"/>
+      <c r="L13" s="234"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="240" t="s">
+      <c r="S13" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="T13" s="241"/>
-      <c r="U13" s="241"/>
-      <c r="V13" s="241"/>
-      <c r="W13" s="241"/>
-      <c r="X13" s="241"/>
-      <c r="Y13" s="241"/>
-      <c r="Z13" s="241"/>
-      <c r="AA13" s="241"/>
-      <c r="AB13" s="241"/>
-      <c r="AC13" s="241"/>
+      <c r="T13" s="244"/>
+      <c r="U13" s="244"/>
+      <c r="V13" s="244"/>
+      <c r="W13" s="244"/>
+      <c r="X13" s="244"/>
+      <c r="Y13" s="244"/>
+      <c r="Z13" s="244"/>
+      <c r="AA13" s="244"/>
+      <c r="AB13" s="244"/>
+      <c r="AC13" s="244"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15695,35 +15724,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="P2" s="233" t="s">
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
+      <c r="P2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233" t="s">
+      <c r="Q2" s="230"/>
+      <c r="R2" s="230"/>
+      <c r="S2" s="230"/>
+      <c r="T2" s="230"/>
+      <c r="U2" s="230"/>
+      <c r="V2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="230" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
+      <c r="Y2" s="230"/>
+      <c r="Z2" s="230"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15732,31 +15761,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="P4" s="241" t="s">
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
+      <c r="H4" s="234"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="234"/>
+      <c r="K4" s="234"/>
+      <c r="L4" s="234"/>
+      <c r="P4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="241"/>
-      <c r="R4" s="241"/>
-      <c r="S4" s="241"/>
-      <c r="T4" s="241"/>
-      <c r="U4" s="241"/>
-      <c r="V4" s="241"/>
-      <c r="W4" s="241"/>
-      <c r="X4" s="241"/>
-      <c r="Y4" s="241"/>
-      <c r="Z4" s="241"/>
+      <c r="Q4" s="244"/>
+      <c r="R4" s="244"/>
+      <c r="S4" s="244"/>
+      <c r="T4" s="244"/>
+      <c r="U4" s="244"/>
+      <c r="V4" s="244"/>
+      <c r="W4" s="244"/>
+      <c r="X4" s="244"/>
+      <c r="Y4" s="244"/>
+      <c r="Z4" s="244"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15951,32 +15980,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="239" t="s">
+      <c r="C9" s="234" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="239"/>
-      <c r="E9" s="239"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="239"/>
-      <c r="L9" s="239"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="234"/>
+      <c r="F9" s="234"/>
+      <c r="G9" s="234"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="234"/>
+      <c r="J9" s="234"/>
+      <c r="K9" s="234"/>
+      <c r="L9" s="234"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="241" t="s">
+      <c r="P9" s="244" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="241"/>
-      <c r="R9" s="241"/>
-      <c r="S9" s="241"/>
-      <c r="T9" s="241"/>
-      <c r="U9" s="241"/>
-      <c r="V9" s="241"/>
-      <c r="W9" s="241"/>
-      <c r="X9" s="241"/>
-      <c r="Y9" s="241"/>
-      <c r="Z9" s="241"/>
+      <c r="Q9" s="244"/>
+      <c r="R9" s="244"/>
+      <c r="S9" s="244"/>
+      <c r="T9" s="244"/>
+      <c r="U9" s="244"/>
+      <c r="V9" s="244"/>
+      <c r="W9" s="244"/>
+      <c r="X9" s="244"/>
+      <c r="Y9" s="244"/>
+      <c r="Z9" s="244"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16452,31 +16481,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="239" t="s">
+      <c r="C17" s="234" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="239"/>
-      <c r="E17" s="239"/>
-      <c r="F17" s="239"/>
-      <c r="G17" s="239"/>
-      <c r="H17" s="239"/>
-      <c r="I17" s="239"/>
-      <c r="J17" s="239"/>
-      <c r="K17" s="239"/>
-      <c r="L17" s="239"/>
-      <c r="P17" s="241" t="s">
+      <c r="D17" s="234"/>
+      <c r="E17" s="234"/>
+      <c r="F17" s="234"/>
+      <c r="G17" s="234"/>
+      <c r="H17" s="234"/>
+      <c r="I17" s="234"/>
+      <c r="J17" s="234"/>
+      <c r="K17" s="234"/>
+      <c r="L17" s="234"/>
+      <c r="P17" s="244" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="241"/>
-      <c r="R17" s="241"/>
-      <c r="S17" s="241"/>
-      <c r="T17" s="241"/>
-      <c r="U17" s="241"/>
-      <c r="V17" s="241"/>
-      <c r="W17" s="241"/>
-      <c r="X17" s="241"/>
-      <c r="Y17" s="241"/>
-      <c r="Z17" s="241"/>
+      <c r="Q17" s="244"/>
+      <c r="R17" s="244"/>
+      <c r="S17" s="244"/>
+      <c r="T17" s="244"/>
+      <c r="U17" s="244"/>
+      <c r="V17" s="244"/>
+      <c r="W17" s="244"/>
+      <c r="X17" s="244"/>
+      <c r="Y17" s="244"/>
+      <c r="Z17" s="244"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16954,60 +16983,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="231"/>
+      <c r="H3" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="244"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
-      <c r="W3" s="244"/>
-      <c r="X3" s="244"/>
-      <c r="Y3" s="244"/>
-      <c r="Z3" s="244"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="P3" s="233"/>
+      <c r="Q3" s="233"/>
+      <c r="R3" s="233"/>
+      <c r="S3" s="233"/>
+      <c r="T3" s="233"/>
+      <c r="U3" s="233"/>
+      <c r="V3" s="233"/>
+      <c r="W3" s="233"/>
+      <c r="X3" s="233"/>
+      <c r="Y3" s="233"/>
+      <c r="Z3" s="233"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="244"/>
-      <c r="T5" s="244"/>
-      <c r="U5" s="244"/>
-      <c r="V5" s="244"/>
-      <c r="W5" s="244"/>
-      <c r="X5" s="244"/>
-      <c r="Y5" s="244"/>
-      <c r="Z5" s="244"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="234"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="234"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="234"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="234"/>
+      <c r="L5" s="234"/>
+      <c r="P5" s="233"/>
+      <c r="Q5" s="233"/>
+      <c r="R5" s="233"/>
+      <c r="S5" s="233"/>
+      <c r="T5" s="233"/>
+      <c r="U5" s="233"/>
+      <c r="V5" s="233"/>
+      <c r="W5" s="233"/>
+      <c r="X5" s="233"/>
+      <c r="Y5" s="233"/>
+      <c r="Z5" s="233"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17193,30 +17222,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="239" t="s">
+      <c r="C11" s="234" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="239"/>
-      <c r="E11" s="239"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
+      <c r="D11" s="234"/>
+      <c r="E11" s="234"/>
+      <c r="F11" s="234"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="234"/>
+      <c r="I11" s="234"/>
+      <c r="J11" s="234"/>
+      <c r="K11" s="234"/>
+      <c r="L11" s="234"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="244"/>
-      <c r="Q11" s="244"/>
-      <c r="R11" s="244"/>
-      <c r="S11" s="244"/>
-      <c r="T11" s="244"/>
-      <c r="U11" s="244"/>
-      <c r="V11" s="244"/>
-      <c r="W11" s="244"/>
-      <c r="X11" s="244"/>
-      <c r="Y11" s="244"/>
-      <c r="Z11" s="244"/>
+      <c r="P11" s="233"/>
+      <c r="Q11" s="233"/>
+      <c r="R11" s="233"/>
+      <c r="S11" s="233"/>
+      <c r="T11" s="233"/>
+      <c r="U11" s="233"/>
+      <c r="V11" s="233"/>
+      <c r="W11" s="233"/>
+      <c r="X11" s="233"/>
+      <c r="Y11" s="233"/>
+      <c r="Z11" s="233"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17458,18 +17487,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="234" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="234"/>
+      <c r="G18" s="234"/>
+      <c r="H18" s="234"/>
+      <c r="I18" s="234"/>
+      <c r="J18" s="234"/>
+      <c r="K18" s="234"/>
+      <c r="L18" s="234"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17682,23 +17711,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="244"/>
-      <c r="C25" s="244"/>
+      <c r="B25" s="233"/>
+      <c r="C25" s="233"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="239" t="s">
+      <c r="C26" s="234" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
+      <c r="D26" s="234"/>
+      <c r="E26" s="234"/>
+      <c r="F26" s="234"/>
+      <c r="G26" s="234"/>
+      <c r="H26" s="234"/>
+      <c r="I26" s="234"/>
+      <c r="J26" s="234"/>
+      <c r="K26" s="234"/>
+      <c r="L26" s="234"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17890,18 +17919,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="239" t="s">
+      <c r="C33" s="234" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="239"/>
-      <c r="E33" s="239"/>
-      <c r="F33" s="239"/>
-      <c r="G33" s="239"/>
-      <c r="H33" s="239"/>
-      <c r="I33" s="239"/>
-      <c r="J33" s="239"/>
-      <c r="K33" s="239"/>
-      <c r="L33" s="239"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
+      <c r="F33" s="234"/>
+      <c r="G33" s="234"/>
+      <c r="H33" s="234"/>
+      <c r="I33" s="234"/>
+      <c r="J33" s="234"/>
+      <c r="K33" s="234"/>
+      <c r="L33" s="234"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18085,18 +18114,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="239" t="s">
+      <c r="C40" s="234" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="239"/>
-      <c r="E40" s="239"/>
-      <c r="F40" s="239"/>
-      <c r="G40" s="239"/>
-      <c r="H40" s="239"/>
-      <c r="I40" s="239"/>
-      <c r="J40" s="239"/>
-      <c r="K40" s="239"/>
-      <c r="L40" s="239"/>
+      <c r="D40" s="234"/>
+      <c r="E40" s="234"/>
+      <c r="F40" s="234"/>
+      <c r="G40" s="234"/>
+      <c r="H40" s="234"/>
+      <c r="I40" s="234"/>
+      <c r="J40" s="234"/>
+      <c r="K40" s="234"/>
+      <c r="L40" s="234"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18360,12 +18389,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18373,6 +18396,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18410,60 +18439,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="S2" s="244"/>
-      <c r="T2" s="244"/>
-      <c r="U2" s="244"/>
-      <c r="V2" s="244"/>
-      <c r="W2" s="244"/>
-      <c r="X2" s="244"/>
-      <c r="Y2" s="244"/>
-      <c r="Z2" s="244"/>
-      <c r="AA2" s="244"/>
-      <c r="AB2" s="244"/>
-      <c r="AC2" s="244"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
+      <c r="S2" s="233"/>
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233"/>
+      <c r="AB2" s="233"/>
+      <c r="AC2" s="233"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="234" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="S4" s="244"/>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
-      <c r="AA4" s="244"/>
-      <c r="AB4" s="244"/>
-      <c r="AC4" s="244"/>
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
+      <c r="H4" s="234"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="234"/>
+      <c r="K4" s="234"/>
+      <c r="L4" s="234"/>
+      <c r="S4" s="233"/>
+      <c r="T4" s="233"/>
+      <c r="U4" s="233"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="233"/>
+      <c r="X4" s="233"/>
+      <c r="Y4" s="233"/>
+      <c r="Z4" s="233"/>
+      <c r="AA4" s="233"/>
+      <c r="AB4" s="233"/>
+      <c r="AC4" s="233"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18826,18 +18855,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="239" t="s">
+      <c r="C13" s="234" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="234"/>
+      <c r="G13" s="234"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="234"/>
+      <c r="J13" s="234"/>
+      <c r="K13" s="234"/>
+      <c r="L13" s="234"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18930,18 +18959,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="234" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="234"/>
+      <c r="G18" s="234"/>
+      <c r="H18" s="234"/>
+      <c r="I18" s="234"/>
+      <c r="J18" s="234"/>
+      <c r="K18" s="234"/>
+      <c r="L18" s="234"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19133,18 +19162,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="239" t="s">
+      <c r="C25" s="234" t="s">
         <v>259</v>
       </c>
-      <c r="D25" s="239"/>
-      <c r="E25" s="239"/>
-      <c r="F25" s="239"/>
-      <c r="G25" s="239"/>
-      <c r="H25" s="239"/>
-      <c r="I25" s="239"/>
-      <c r="J25" s="239"/>
-      <c r="K25" s="239"/>
-      <c r="L25" s="239"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="234"/>
+      <c r="F25" s="234"/>
+      <c r="G25" s="234"/>
+      <c r="H25" s="234"/>
+      <c r="I25" s="234"/>
+      <c r="J25" s="234"/>
+      <c r="K25" s="234"/>
+      <c r="L25" s="234"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19282,18 +19311,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="239" t="s">
+      <c r="C31" s="234" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="239"/>
-      <c r="E31" s="239"/>
-      <c r="F31" s="239"/>
-      <c r="G31" s="239"/>
-      <c r="H31" s="239"/>
-      <c r="I31" s="239"/>
-      <c r="J31" s="239"/>
-      <c r="K31" s="239"/>
-      <c r="L31" s="239"/>
+      <c r="D31" s="234"/>
+      <c r="E31" s="234"/>
+      <c r="F31" s="234"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="234"/>
+      <c r="I31" s="234"/>
+      <c r="J31" s="234"/>
+      <c r="K31" s="234"/>
+      <c r="L31" s="234"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19432,16 +19461,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19504,10 +19533,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="230" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="230"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19524,7 +19553,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>176.25</v>
+        <v>182.95</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19533,7 +19562,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>186825</v>
+        <v>193927</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19551,7 +19580,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19560,7 +19589,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6396999999999999</v>
+        <v>1.6357999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19592,10 +19621,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="230" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="233"/>
+      <c r="C15" s="230"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19603,7 +19632,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.5558524456320053E-2</v>
+        <v>7.2993398566901055E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19612,7 +19641,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92444147554367995</v>
+        <v>0.92700660143309899</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19630,7 +19659,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11863649999999999</v>
+        <v>0.11840099999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19639,7 +19668,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11244814350924069</v>
+        <v>0.11243992111263545</v>
       </c>
     </row>
   </sheetData>
@@ -19684,60 +19713,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="231"/>
+      <c r="H3" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="244"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
-      <c r="W3" s="244"/>
-      <c r="X3" s="244"/>
-      <c r="Y3" s="244"/>
-      <c r="Z3" s="244"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="P3" s="233"/>
+      <c r="Q3" s="233"/>
+      <c r="R3" s="233"/>
+      <c r="S3" s="233"/>
+      <c r="T3" s="233"/>
+      <c r="U3" s="233"/>
+      <c r="V3" s="233"/>
+      <c r="W3" s="233"/>
+      <c r="X3" s="233"/>
+      <c r="Y3" s="233"/>
+      <c r="Z3" s="233"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="234" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="244"/>
-      <c r="T5" s="244"/>
-      <c r="U5" s="244"/>
-      <c r="V5" s="244"/>
-      <c r="W5" s="244"/>
-      <c r="X5" s="244"/>
-      <c r="Y5" s="244"/>
-      <c r="Z5" s="244"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="234"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="234"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="234"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="234"/>
+      <c r="L5" s="234"/>
+      <c r="P5" s="233"/>
+      <c r="Q5" s="233"/>
+      <c r="R5" s="233"/>
+      <c r="S5" s="233"/>
+      <c r="T5" s="233"/>
+      <c r="U5" s="233"/>
+      <c r="V5" s="233"/>
+      <c r="W5" s="233"/>
+      <c r="X5" s="233"/>
+      <c r="Y5" s="233"/>
+      <c r="Z5" s="233"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19890,7 +19919,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>150626.86579244063</v>
+        <v>150641.02996155454</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19944,23 +19973,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>8955.4245725360779</v>
+        <v>8955.4907649220258</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7956.3495780345447</v>
+        <v>7956.4671942802197</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7493.4979734694343</v>
+        <v>7493.664135164664</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7074.8798917231115</v>
+        <v>7075.0890647750984</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7542.7600143685713</v>
+        <v>7543.0387731580458</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19979,14 +20008,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>88410.441942781923</v>
+        <v>88422.023305894123</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="233" t="s">
+      <c r="B13" s="230" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="233"/>
+      <c r="C13" s="230"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20002,14 +20031,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11244814350924069</v>
+        <v>0.11243992111263545</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="230" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="233"/>
+      <c r="C18" s="230"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20017,7 +20046,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>39022.912030131738</v>
+        <v>39023.749932300059</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20026,7 +20055,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>88410.441942781923</v>
+        <v>88422.023305894123</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20035,7 +20064,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>127433.35397291367</v>
+        <v>127445.77323819418</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20062,7 +20091,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>121962.35397291367</v>
+        <v>121974.77323819418</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20080,7 +20109,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>115.05882450274875</v>
+        <v>115.07054079074922</v>
       </c>
     </row>
   </sheetData>
@@ -20101,7 +20130,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -20123,37 +20152,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="234" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
+      <c r="H4" s="234"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="234"/>
+      <c r="K4" s="234"/>
+      <c r="L4" s="234"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20342,18 +20371,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="239" t="s">
+      <c r="C10" s="234" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="239"/>
-      <c r="L10" s="239"/>
+      <c r="D10" s="234"/>
+      <c r="E10" s="234"/>
+      <c r="F10" s="234"/>
+      <c r="G10" s="234"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="234"/>
+      <c r="J10" s="234"/>
+      <c r="K10" s="234"/>
+      <c r="L10" s="234"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20547,18 +20576,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="239" t="s">
+      <c r="C16" s="234" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="239"/>
-      <c r="E16" s="239"/>
-      <c r="F16" s="239"/>
-      <c r="G16" s="239"/>
-      <c r="H16" s="239"/>
-      <c r="I16" s="239"/>
-      <c r="J16" s="239"/>
-      <c r="K16" s="239"/>
-      <c r="L16" s="239"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="234"/>
+      <c r="F16" s="234"/>
+      <c r="G16" s="234"/>
+      <c r="H16" s="234"/>
+      <c r="I16" s="234"/>
+      <c r="J16" s="234"/>
+      <c r="K16" s="234"/>
+      <c r="L16" s="234"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20692,18 +20721,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="239" t="s">
+      <c r="C21" s="234" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="239"/>
-      <c r="E21" s="239"/>
-      <c r="F21" s="239"/>
-      <c r="G21" s="239"/>
-      <c r="H21" s="239"/>
-      <c r="I21" s="239"/>
-      <c r="J21" s="239"/>
-      <c r="K21" s="239"/>
-      <c r="L21" s="239"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="234"/>
+      <c r="G21" s="234"/>
+      <c r="H21" s="234"/>
+      <c r="I21" s="234"/>
+      <c r="J21" s="234"/>
+      <c r="K21" s="234"/>
+      <c r="L21" s="234"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -20787,18 +20816,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="239" t="s">
+      <c r="C26" s="234" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
+      <c r="D26" s="234"/>
+      <c r="E26" s="234"/>
+      <c r="F26" s="234"/>
+      <c r="G26" s="234"/>
+      <c r="H26" s="234"/>
+      <c r="I26" s="234"/>
+      <c r="J26" s="234"/>
+      <c r="K26" s="234"/>
+      <c r="L26" s="234"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21068,10 +21097,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="230" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="233"/>
+      <c r="C37" s="230"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21089,7 +21118,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11244814350924069</v>
+        <v>0.11243992111263545</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21115,160 +21144,214 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>190697.64592025711</v>
+        <v>190704.86563104633</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C43" s="136">
+        <f>Statement!AC106</f>
+        <v>9799</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C44" s="136">
+        <f>Statement!AC107</f>
+        <v>15270</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="24">
+        <f ca="1">C42+C43-C44</f>
+        <v>185233.86563104633</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="88">
+      <c r="C46" s="88">
         <f>Statement!AC78</f>
         <v>1060</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="141" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="141" t="s">
         <v>201</v>
       </c>
-      <c r="C44" s="142">
-        <f ca="1">C42/C43</f>
-        <v>179.90343954741238</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="233" t="s">
+      <c r="C47" s="142">
+        <f ca="1">C45/C46</f>
+        <v>174.74892984060975</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="230" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="233"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="1" t="s">
+      <c r="C49" s="230"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="64">
+      <c r="C50" s="64">
         <f>L6</f>
         <v>57384.209765196996</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C48" s="135">
+      <c r="C51" s="135">
         <f>Overview!C29</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="39" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C49" s="105">
+      <c r="C52" s="105">
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="1" t="s">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C50" s="24">
+      <c r="C53" s="24">
         <f>L18</f>
         <v>1024.4422356918749</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C51" s="24">
-        <f>(C47*C49)/C50</f>
+      <c r="C54" s="24">
+        <f>(C50*C52)/C53</f>
         <v>336.09045644105976</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="141" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="141" t="s">
         <v>201</v>
       </c>
-      <c r="C52" s="142">
-        <f>C51/(1+C48)^5</f>
+      <c r="C55" s="142">
+        <f>C54/(1+C51)^5</f>
         <v>190.70675093537938</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="233" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="230" t="s">
         <v>319</v>
       </c>
-      <c r="C54" s="233"/>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+      <c r="C57" s="230"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C55" s="64">
+      <c r="C58" s="64">
         <f>L8</f>
         <v>12850.770513331205</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C56" s="135">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11244814350924069</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="39" t="s">
-        <v>354</v>
-      </c>
-      <c r="C57" s="105">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C58" s="24">
-        <f>(C55*C57)</f>
-        <v>321269.26283328014</v>
-      </c>
-    </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C59" s="135">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.11243992111263545</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="39" t="s">
+        <v>354</v>
+      </c>
+      <c r="C60" s="105">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C61" s="24">
+        <f>(C58*C60)</f>
+        <v>321269.26283328014</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C59" s="24">
-        <f ca="1">C58/(1+C56)^5-G30+G31</f>
-        <v>183913.00035921429</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C62" s="24">
+        <f ca="1">C61/(1+C59)^5-G30+G31</f>
+        <v>183919.96932895118</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" s="136">
+        <f>Statement!AC106</f>
+        <v>9799</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64" s="136">
+        <f>Statement!AC107</f>
+        <v>15270</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" s="24">
+        <f ca="1">C62+C63-C64</f>
+        <v>178448.96932895118</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="88">
+      <c r="C66" s="88">
         <f>Statement!AC78</f>
         <v>1060</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="141" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="141" t="s">
         <v>201</v>
       </c>
-      <c r="C61" s="142">
-        <f ca="1">C59/C60</f>
-        <v>173.50283052756066</v>
+      <c r="C67" s="142">
+        <f ca="1">C65/C66</f>
+        <v>168.34808427259546</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -21312,10 +21395,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="230" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="230"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21324,7 +21407,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>115.05882450274875</v>
+        <v>115.07054079074922</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21332,8 +21415,8 @@
         <v>209</v>
       </c>
       <c r="C6" s="133">
-        <f ca="1">Multiples!C44</f>
-        <v>179.90343954741238</v>
+        <f ca="1">Multiples!C47</f>
+        <v>174.74892984060975</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21341,7 +21424,7 @@
         <v>210</v>
       </c>
       <c r="C7" s="133">
-        <f>Multiples!C52</f>
+        <f>Multiples!C55</f>
         <v>190.70675093537938</v>
       </c>
     </row>
@@ -21350,8 +21433,8 @@
         <v>320</v>
       </c>
       <c r="C8" s="133">
-        <f ca="1">Multiples!C61</f>
-        <v>173.50283052756066</v>
+        <f ca="1">Multiples!C67</f>
+        <v>168.34808427259546</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21360,7 +21443,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>164.79296137827529</v>
+        <v>162.21857645983346</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21369,7 +21452,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>176.25</v>
+        <v>182.95</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21378,7 +21461,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-6.5004474449501873E-2</v>
+        <v>-0.11331742847863642</v>
       </c>
     </row>
   </sheetData>
@@ -21443,60 +21526,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="230" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="231"/>
+      <c r="H3" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="244"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
-      <c r="W3" s="244"/>
-      <c r="X3" s="244"/>
-      <c r="Y3" s="244"/>
-      <c r="Z3" s="244"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="P3" s="233"/>
+      <c r="Q3" s="233"/>
+      <c r="R3" s="233"/>
+      <c r="S3" s="233"/>
+      <c r="T3" s="233"/>
+      <c r="U3" s="233"/>
+      <c r="V3" s="233"/>
+      <c r="W3" s="233"/>
+      <c r="X3" s="233"/>
+      <c r="Y3" s="233"/>
+      <c r="Z3" s="233"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="234" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="244"/>
-      <c r="T5" s="244"/>
-      <c r="U5" s="244"/>
-      <c r="V5" s="244"/>
-      <c r="W5" s="244"/>
-      <c r="X5" s="244"/>
-      <c r="Y5" s="244"/>
-      <c r="Z5" s="244"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="234"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="234"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="234"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="234"/>
+      <c r="L5" s="234"/>
+      <c r="P5" s="233"/>
+      <c r="Q5" s="233"/>
+      <c r="R5" s="233"/>
+      <c r="S5" s="233"/>
+      <c r="T5" s="233"/>
+      <c r="U5" s="233"/>
+      <c r="V5" s="233"/>
+      <c r="W5" s="233"/>
+      <c r="X5" s="233"/>
+      <c r="Y5" s="233"/>
+      <c r="Z5" s="233"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21631,7 +21714,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>299157.44377062313</v>
+        <v>299185.57498481899</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21685,23 +21768,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12369.818930228013</v>
+        <v>12369.910359486572</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12976.405934787002</v>
+        <v>12976.597760967266</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13612.738548087336</v>
+        <v>13613.040398534467</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14280.275425248137</v>
+        <v>14280.69763012506</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14980.546750425807</v>
+        <v>14981.100388493287</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21720,7 +21803,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>175590.4677103165</v>
+        <v>175613.46925765538</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21736,7 +21819,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>176.25</v>
+        <v>182.95</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21745,7 +21828,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>226.12832381318103</v>
+        <v>226.15162788924292</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -21784,7 +21867,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11244814350924069</v>
+        <v>0.11243992111263545</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -21802,7 +21885,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>185767.5</v>
+        <v>192829.3</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21829,7 +21912,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>191238.5</v>
+        <v>198300.3</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21845,7 +21928,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>68219.7855887763</v>
+        <v>68221.346537606645</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -21854,7 +21937,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>175590.4677103165</v>
+        <v>175613.46925765538</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -21863,7 +21946,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>243810.25329909282</v>
+        <v>243834.81579526202</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -21890,7 +21973,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>238339.25329909282</v>
+        <v>238363.81579526202</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -21908,22 +21991,22 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>226.12832381318103</v>
+        <v>226.15162788924292</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="239" t="s">
+      <c r="C39" s="234" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="239"/>
-      <c r="E39" s="239"/>
-      <c r="F39" s="239"/>
-      <c r="G39" s="239"/>
-      <c r="H39" s="239"/>
-      <c r="I39" s="239"/>
-      <c r="J39" s="239"/>
-      <c r="K39" s="239"/>
-      <c r="L39" s="239"/>
+      <c r="D39" s="234"/>
+      <c r="E39" s="234"/>
+      <c r="F39" s="234"/>
+      <c r="G39" s="234"/>
+      <c r="H39" s="234"/>
+      <c r="I39" s="234"/>
+      <c r="J39" s="234"/>
+      <c r="K39" s="234"/>
+      <c r="L39" s="234"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -22355,17 +22438,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28850,7 +28933,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>176.25</v>
+        <v>182.95</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -28897,7 +28980,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>176.25</v>
+        <v>182.95</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -30399,7 +30482,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>18.71348342009124</v>
+        <v>19.424861229535843</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30436,7 +30519,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.2771834208047368</v>
+        <v>4.4397770600636965</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30473,7 +30556,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.8101583693819201</v>
+        <v>7.0690409854094876</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30510,7 +30593,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>186825</v>
+        <v>193927</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30547,7 +30630,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>192296</v>
+        <v>199398</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30584,7 +30667,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>4.3129233391647599</v>
+        <v>4.4722110079397117</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30621,7 +30704,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>16.934918538088947</v>
+        <v>17.560369881109644</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30756,7 +30839,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="98">AC156/AC160</f>
-        <v>19.809670236454245</v>
+        <v>20.562718693669812</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30793,7 +30876,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="98"/>
-        <v>16.080971941258031</v>
+        <v>16.674884777337901</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30830,7 +30913,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="101">AC160/AC156</f>
-        <v>5.0480396092600029E-2</v>
+        <v>4.8631701619681632E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30867,7 +30950,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.3437405401838556E-2</v>
+        <v>5.1480419251566253E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30904,7 +30987,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>2.0198581560283688E-2</v>
+        <v>1.9458868543317846E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -30941,7 +31024,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>5.7460190017395961E-2</v>
+        <v>5.535588133679168E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -30978,7 +31061,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>7.7907132343101829E-2</v>
+        <v>7.5054015170657004E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -31481,7 +31564,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-2.9284089388465141E-2</v>
+        <v>-2.8211646650543761E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -32803,15 +32886,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="230" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="233"/>
-      <c r="E4" s="233" t="s">
+      <c r="C4" s="230"/>
+      <c r="E4" s="230" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32819,7 +32902,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>176.25</v>
+        <v>182.95</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -32835,7 +32918,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>186825</v>
+        <v>193927</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32855,7 +32938,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>192296</v>
+        <v>199398</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32875,7 +32958,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>18.71348342009124</v>
+        <v>19.424861229535843</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32895,7 +32978,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.2771834208047368</v>
+        <v>4.4397770600636965</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32915,7 +32998,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>6.8101583693819201</v>
+        <v>7.0690409854094876</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32935,7 +33018,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.3129233391647599</v>
+        <v>4.4722110079397117</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32944,18 +33027,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>16.934918538088947</v>
+        <v>17.560369881109644</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="233"/>
-      <c r="E15" s="233" t="s">
+      <c r="C15" s="230"/>
+      <c r="E15" s="230" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="233"/>
+      <c r="F15" s="230"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33006,14 +33089,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="233" t="s">
+      <c r="B21" s="230" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="233"/>
-      <c r="E21" s="233" t="s">
+      <c r="C21" s="230"/>
+      <c r="E21" s="230" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="233"/>
+      <c r="F21" s="230"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33082,14 +33165,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="233" t="s">
+      <c r="B29" s="230" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="233"/>
-      <c r="E29" s="233" t="s">
+      <c r="C29" s="230"/>
+      <c r="E29" s="230" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="233"/>
+      <c r="F29" s="230"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33165,14 +33248,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="230" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="233"/>
-      <c r="E37" s="233" t="s">
+      <c r="C37" s="230"/>
+      <c r="E37" s="230" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="233"/>
+      <c r="F37" s="230"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33180,7 +33263,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.3437405401838556E-2</v>
+        <v>5.1480419251566253E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33196,7 +33279,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>5.0480396092600029E-2</v>
+        <v>4.8631701619681632E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33212,7 +33295,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>2.0198581560283688E-2</v>
+        <v>1.9458868543317846E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33228,7 +33311,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.7460190017395961E-2</v>
+        <v>5.535588133679168E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33237,18 +33320,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>7.7907132343101829E-2</v>
+        <v>7.5054015170657004E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="233" t="s">
+      <c r="B45" s="230" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="233"/>
-      <c r="E45" s="233" t="s">
+      <c r="C45" s="230"/>
+      <c r="E45" s="230" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="233"/>
+      <c r="F45" s="230"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33281,18 +33364,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-2.9284089388465141E-2</v>
+        <v>-2.8211646650543761E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="233" t="s">
+      <c r="B51" s="230" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="233"/>
-      <c r="E51" s="233" t="s">
+      <c r="C51" s="230"/>
+      <c r="E51" s="230" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="233"/>
+      <c r="F51" s="230"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33461,7 +33544,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>176.25</v>
+        <v>182.95</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33490,7 +33573,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>186825</v>
+        <v>193927</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33519,7 +33602,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>192296</v>
+        <v>199398</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33548,7 +33631,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>18.71348342009124</v>
+        <v>19.424861229535843</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33577,7 +33660,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.2771834208047368</v>
+        <v>4.4397770600636965</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33606,7 +33689,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>6.8101583693819201</v>
+        <v>7.0690409854094876</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33635,7 +33718,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.3129233391647599</v>
+        <v>4.4722110079397117</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33664,7 +33747,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>16.934918538088947</v>
+        <v>17.560369881109644</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34437,7 +34520,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.3437405401838556E-2</v>
+        <v>5.1480419251566253E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34466,7 +34549,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>5.0480396092600029E-2</v>
+        <v>4.8631701619681632E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34495,7 +34578,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>2.0198581560283688E-2</v>
+        <v>1.9458868543317846E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34524,7 +34607,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.7460190017395961E-2</v>
+        <v>5.535588133679168E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34553,7 +34636,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>7.7907132343101829E-2</v>
+        <v>7.5054015170657004E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34789,7 +34872,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-2.9284089388465141E-2</v>
+        <v>-2.8211646650543761E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35327,14 +35410,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="238" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="239"/>
+      <c r="F3" s="240" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="239"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35401,19 +35484,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="234">
+      <c r="C7" s="241">
         <f>Statement!AA89</f>
         <v>-0.13491674828599412</v>
       </c>
-      <c r="D7" s="235"/>
-      <c r="F7" s="234">
+      <c r="D7" s="242"/>
+      <c r="F7" s="241">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-3.4611531104836508E-2</v>
       </c>
-      <c r="G7" s="235"/>
+      <c r="G7" s="242"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35440,19 +35523,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="234">
+      <c r="C9" s="241">
         <f>Statement!AA90</f>
         <v>-0.11997126436781609</v>
       </c>
-      <c r="D9" s="235"/>
-      <c r="F9" s="234">
+      <c r="D9" s="242"/>
+      <c r="F9" s="241">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>-7.4944298156775372E-3</v>
       </c>
-      <c r="G9" s="235"/>
+      <c r="G9" s="242"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35479,19 +35562,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="234">
+      <c r="C11" s="241">
         <f>Statement!AA91</f>
         <v>-0.1473668461998803</v>
       </c>
-      <c r="D11" s="235"/>
-      <c r="F11" s="234">
+      <c r="D11" s="242"/>
+      <c r="F11" s="241">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-5.6769281694803046E-2</v>
       </c>
-      <c r="G11" s="235"/>
+      <c r="G11" s="242"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35518,19 +35601,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="234">
+      <c r="C13" s="241">
         <f>Statement!AA94</f>
         <v>2.1699819168173599E-2</v>
       </c>
-      <c r="D13" s="235"/>
-      <c r="F13" s="234">
+      <c r="D13" s="242"/>
+      <c r="F13" s="241">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.16016427104722791</v>
       </c>
-      <c r="G13" s="235"/>
+      <c r="G13" s="242"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -35557,19 +35640,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="234">
+      <c r="C15" s="241">
         <f>Statement!AA95</f>
         <v>-0.31402257872846107</v>
       </c>
-      <c r="D15" s="235"/>
-      <c r="F15" s="234">
+      <c r="D15" s="242"/>
+      <c r="F15" s="241">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.25993589743589746</v>
       </c>
-      <c r="G15" s="235"/>
+      <c r="G15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35596,19 +35679,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="234">
+      <c r="C17" s="241">
         <f>Statement!AA97</f>
         <v>-0.35685752330226367</v>
       </c>
-      <c r="D17" s="235"/>
-      <c r="F17" s="234">
+      <c r="D17" s="242"/>
+      <c r="F17" s="241">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.31294452347083929</v>
       </c>
-      <c r="G17" s="235"/>
+      <c r="G17" s="242"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -35635,22 +35718,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="234">
+      <c r="C19" s="241">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-6.4874884151992582E-3</v>
       </c>
-      <c r="D19" s="235"/>
-      <c r="F19" s="234">
+      <c r="D19" s="242"/>
+      <c r="F19" s="241">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.8565022421524667E-2</v>
       </c>
-      <c r="G19" s="235"/>
+      <c r="G19" s="242"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35677,22 +35760,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="234">
+      <c r="C21" s="241">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.35171265972296784</v>
       </c>
-      <c r="D21" s="235"/>
-      <c r="F21" s="234">
+      <c r="D21" s="242"/>
+      <c r="F21" s="241">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.28482587064676618</v>
       </c>
-      <c r="G21" s="235"/>
+      <c r="G21" s="242"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35740,22 +35823,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="234">
+      <c r="C25" s="241">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.23006134969325154</v>
       </c>
-      <c r="D25" s="235"/>
-      <c r="F25" s="234">
+      <c r="D25" s="242"/>
+      <c r="F25" s="241">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.13061047770241016</v>
       </c>
-      <c r="G25" s="235"/>
+      <c r="G25" s="242"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -35782,22 +35865,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="234">
+      <c r="C27" s="241">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.20435967302452315</v>
       </c>
-      <c r="D27" s="235"/>
-      <c r="F27" s="234">
+      <c r="D27" s="242"/>
+      <c r="F27" s="241">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.38269030239833157</v>
       </c>
-      <c r="G27" s="235"/>
+      <c r="G27" s="242"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -35824,22 +35907,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="234">
+      <c r="C29" s="241">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.2511848341232227E-2</v>
       </c>
-      <c r="D29" s="235"/>
-      <c r="F29" s="234">
+      <c r="D29" s="242"/>
+      <c r="F29" s="241">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>9.1714104996837451E-2</v>
       </c>
-      <c r="G29" s="235"/>
+      <c r="G29" s="242"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35866,22 +35949,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="234">
+      <c r="C31" s="241">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.1448223876378027</v>
       </c>
-      <c r="D31" s="235"/>
-      <c r="F31" s="234">
+      <c r="D31" s="242"/>
+      <c r="F31" s="241">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-4.1503854683704718E-2</v>
       </c>
-      <c r="G31" s="235"/>
+      <c r="G31" s="242"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -35908,43 +35991,25 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="234">
+      <c r="C33" s="241">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.13190954773869346</v>
       </c>
-      <c r="D33" s="235"/>
-      <c r="F33" s="234">
+      <c r="D33" s="242"/>
+      <c r="F33" s="241">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>4.7763457164518575E-2</v>
       </c>
-      <c r="G33" s="235"/>
+      <c r="G33" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -35955,6 +36020,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793FCFFA-A6B8-3F49-BEE7-D059A93F6DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7ECBE0-C6F7-9C42-95FE-DDAD16E08723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,28 +128,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -159,21 +138,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2310,21 +2280,6 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2332,6 +2287,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2343,16 +2307,22 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12682,7 +12652,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12721,9 +12691,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6357999999999999</v>
-    <v>-3.53</v>
-    <v>-1.8929999999999999E-2</v>
+    <v>1.6351</v>
+    <v>-1.95</v>
+    <v>-1.0204E-2</v>
+    <v>-0.66</v>
+    <v>-3.4889999999999999E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12731,50 +12703,36 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>185.88</v>
+    <v>190.19</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46210.764783876562</v>
+    <v>46213.885025149997</v>
     <v>4</v>
-    <v>179</v>
-    <v>192829300000</v>
+    <v>185.72</v>
+    <v>199374640000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>179.51</v>
-    <v>19.900099999999998</v>
-    <v>186.48</v>
-    <v>182.95</v>
+    <v>187.50800000000001</v>
+    <v>20.575600000000001</v>
+    <v>191.11</v>
+    <v>189.16</v>
+    <v>188.5</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>6878614</v>
-    <v>22329372</v>
+    <v>7039544</v>
+    <v>21168579</v>
     <v>1991</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12788,28 +12746,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.06</v>
-    <v>-1.338E-3</v>
+    <v>-0.3</v>
+    <v>-6.5659999999999998E-3</v>
     <v>US</v>
-    <v>44.91</v>
+    <v>45.81</v>
     <v>Index</v>
-    <v>10</v>
-    <v>44.57</v>
+    <v>7</v>
+    <v>45.29</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.57</v>
-    <v>44.85</v>
-    <v>44.79</v>
+    <v>45.77</v>
+    <v>45.69</v>
+    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>11</v>
+    <v>8</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12843,6 +12801,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12864,6 +12824,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12873,11 +12834,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12913,7 +12869,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12924,13 +12880,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13031,13 +12990,19 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
+      <v>1</v>
+      <v>1</v>
+      <v>6</v>
     </spb>
     <spb s="5">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13118,6 +13083,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13125,6 +13093,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13616,18 +13587,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="235" t="s">
+      <c r="B2" s="230" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="236"/>
-      <c r="E2" s="235" t="s">
+      <c r="C2" s="231"/>
+      <c r="E2" s="230" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="236"/>
-      <c r="H2" s="235" t="s">
+      <c r="F2" s="231"/>
+      <c r="H2" s="230" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="236"/>
+      <c r="I2" s="231"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13642,7 +13613,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>193927</v>
+        <v>200509.6</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13650,7 +13621,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>115.07054079074922</v>
+        <v>113.01609383176907</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13666,7 +13637,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>199398</v>
+        <v>205980.6</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13674,7 +13645,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>174.74892984060975</v>
+        <v>174.16181266937014</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13683,7 +13654,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>182.95</v>
+        <v>189.16</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13705,16 +13676,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="208" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>188.5</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>19.424861229535843</v>
+        <v>20.084212900677784</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13722,7 +13693,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>168.34808427259546</v>
+        <v>167.78135772110033</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13731,14 +13702,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-3.53</v>
+        <v>-1.95</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>4.4397770600636965</v>
+        <v>4.5904795227201367</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13746,23 +13717,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>162.21857645983346</v>
+        <v>161.41650378940471</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.66</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.8631701619681632E-2</v>
+        <v>4.7035154426521224E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13770,7 +13741,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.11331742847863642</v>
+        <v>-0.14666682285152929</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13779,30 +13750,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.8929999999999999E-2</v>
+        <v>-1.0204E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>5.1480419251566253E-2</v>
+        <v>4.9790350507898318E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-3.4889999999999999E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>5.535588133679168E-2</v>
+        <v>5.3538583688761035E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13818,7 +13789,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.9458868543317846E-2</v>
+        <v>1.8820046521463313E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13843,7 +13814,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6357999999999999</v>
+        <v>1.6351</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13859,7 +13830,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>22329372</v>
+        <v>21168579</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13875,7 +13846,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-2.8211646650543761E-2</v>
+        <v>-2.7285476605608906E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13888,10 +13859,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="237"/>
+      <c r="C17" s="232"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -13964,14 +13935,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="232" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="237"/>
-      <c r="E25" s="235" t="s">
+      <c r="C25" s="232"/>
+      <c r="E25" s="230" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="236"/>
+      <c r="F25" s="231"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13980,12 +13951,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="5">
+      <c r="E26" s="185" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.79</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14000,7 +13971,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14020,15 +13991,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="230" t="s">
+      <c r="B33" s="233" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="230"/>
-      <c r="D33" s="230"/>
-      <c r="E33" s="230"/>
-      <c r="F33" s="230"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="230"/>
+      <c r="C33" s="233"/>
+      <c r="D33" s="233"/>
+      <c r="E33" s="233"/>
+      <c r="F33" s="233"/>
+      <c r="G33" s="233"/>
+      <c r="H33" s="233"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14047,24 +14018,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="230"/>
-      <c r="C39" s="230"/>
-      <c r="D39" s="230"/>
-      <c r="E39" s="230"/>
-      <c r="F39" s="230"/>
-      <c r="G39" s="230"/>
-      <c r="H39" s="230"/>
+      <c r="B39" s="233"/>
+      <c r="C39" s="233"/>
+      <c r="D39" s="233"/>
+      <c r="E39" s="233"/>
+      <c r="F39" s="233"/>
+      <c r="G39" s="233"/>
+      <c r="H39" s="233"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="230" t="s">
+      <c r="B42" s="233" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="230"/>
-      <c r="D42" s="230"/>
-      <c r="E42" s="230"/>
-      <c r="F42" s="230"/>
-      <c r="G42" s="230"/>
-      <c r="H42" s="230"/>
+      <c r="C42" s="233"/>
+      <c r="D42" s="233"/>
+      <c r="E42" s="233"/>
+      <c r="F42" s="233"/>
+      <c r="G42" s="233"/>
+      <c r="H42" s="233"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14079,24 +14050,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="230"/>
-      <c r="C49" s="230"/>
-      <c r="D49" s="230"/>
-      <c r="E49" s="230"/>
-      <c r="F49" s="230"/>
-      <c r="G49" s="230"/>
-      <c r="H49" s="230"/>
+      <c r="B49" s="233"/>
+      <c r="C49" s="233"/>
+      <c r="D49" s="233"/>
+      <c r="E49" s="233"/>
+      <c r="F49" s="233"/>
+      <c r="G49" s="233"/>
+      <c r="H49" s="233"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="230" t="s">
+      <c r="B52" s="233" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="230"/>
-      <c r="D52" s="230"/>
-      <c r="E52" s="230"/>
-      <c r="F52" s="230"/>
-      <c r="G52" s="230"/>
-      <c r="H52" s="230"/>
+      <c r="C52" s="233"/>
+      <c r="D52" s="233"/>
+      <c r="E52" s="233"/>
+      <c r="F52" s="233"/>
+      <c r="G52" s="233"/>
+      <c r="H52" s="233"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14234,28 +14205,28 @@
       </c>
     </row>
     <row r="69" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="230"/>
-      <c r="C69" s="230"/>
-      <c r="D69" s="230"/>
-      <c r="E69" s="230"/>
-      <c r="F69" s="230"/>
-      <c r="G69" s="230"/>
-      <c r="H69" s="230"/>
+      <c r="B69" s="233"/>
+      <c r="C69" s="233"/>
+      <c r="D69" s="233"/>
+      <c r="E69" s="233"/>
+      <c r="F69" s="233"/>
+      <c r="G69" s="233"/>
+      <c r="H69" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14325,36 +14296,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="231"/>
-      <c r="H2" s="232" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="230" t="s">
+      <c r="S2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230"/>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
-      <c r="AA2" s="230" t="s">
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="230"/>
-      <c r="AC2" s="230"/>
+      <c r="AB2" s="233"/>
+      <c r="AC2" s="233"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14365,32 +14336,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="234" t="s">
+      <c r="C4" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="243" t="s">
+      <c r="S4" s="240" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
-      <c r="AA4" s="244"/>
-      <c r="AB4" s="244"/>
-      <c r="AC4" s="244"/>
+      <c r="T4" s="241"/>
+      <c r="U4" s="241"/>
+      <c r="V4" s="241"/>
+      <c r="W4" s="241"/>
+      <c r="X4" s="241"/>
+      <c r="Y4" s="241"/>
+      <c r="Z4" s="241"/>
+      <c r="AA4" s="241"/>
+      <c r="AB4" s="241"/>
+      <c r="AC4" s="241"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15074,33 +15045,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="234" t="s">
+      <c r="C13" s="239" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="234"/>
-      <c r="E13" s="234"/>
-      <c r="F13" s="234"/>
-      <c r="G13" s="234"/>
-      <c r="H13" s="234"/>
-      <c r="I13" s="234"/>
-      <c r="J13" s="234"/>
-      <c r="K13" s="234"/>
-      <c r="L13" s="234"/>
+      <c r="D13" s="239"/>
+      <c r="E13" s="239"/>
+      <c r="F13" s="239"/>
+      <c r="G13" s="239"/>
+      <c r="H13" s="239"/>
+      <c r="I13" s="239"/>
+      <c r="J13" s="239"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="239"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="243" t="s">
+      <c r="S13" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="T13" s="244"/>
-      <c r="U13" s="244"/>
-      <c r="V13" s="244"/>
-      <c r="W13" s="244"/>
-      <c r="X13" s="244"/>
-      <c r="Y13" s="244"/>
-      <c r="Z13" s="244"/>
-      <c r="AA13" s="244"/>
-      <c r="AB13" s="244"/>
-      <c r="AC13" s="244"/>
+      <c r="T13" s="241"/>
+      <c r="U13" s="241"/>
+      <c r="V13" s="241"/>
+      <c r="W13" s="241"/>
+      <c r="X13" s="241"/>
+      <c r="Y13" s="241"/>
+      <c r="Z13" s="241"/>
+      <c r="AA13" s="241"/>
+      <c r="AB13" s="241"/>
+      <c r="AC13" s="241"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15724,35 +15695,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="231"/>
-      <c r="H2" s="232" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
-      <c r="P2" s="230" t="s">
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
+      <c r="P2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="230"/>
-      <c r="R2" s="230"/>
-      <c r="S2" s="230"/>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230" t="s">
+      <c r="Q2" s="233"/>
+      <c r="R2" s="233"/>
+      <c r="S2" s="233"/>
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15761,31 +15732,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="234" t="s">
+      <c r="C4" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
-      <c r="P4" s="244" t="s">
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
+      <c r="P4" s="241" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="244"/>
-      <c r="S4" s="244"/>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
+      <c r="Q4" s="241"/>
+      <c r="R4" s="241"/>
+      <c r="S4" s="241"/>
+      <c r="T4" s="241"/>
+      <c r="U4" s="241"/>
+      <c r="V4" s="241"/>
+      <c r="W4" s="241"/>
+      <c r="X4" s="241"/>
+      <c r="Y4" s="241"/>
+      <c r="Z4" s="241"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15980,32 +15951,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="234" t="s">
+      <c r="C9" s="239" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="234"/>
-      <c r="E9" s="234"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="234"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="234"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="234"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="239"/>
+      <c r="F9" s="239"/>
+      <c r="G9" s="239"/>
+      <c r="H9" s="239"/>
+      <c r="I9" s="239"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="239"/>
+      <c r="L9" s="239"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="244" t="s">
+      <c r="P9" s="241" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="244"/>
-      <c r="R9" s="244"/>
-      <c r="S9" s="244"/>
-      <c r="T9" s="244"/>
-      <c r="U9" s="244"/>
-      <c r="V9" s="244"/>
-      <c r="W9" s="244"/>
-      <c r="X9" s="244"/>
-      <c r="Y9" s="244"/>
-      <c r="Z9" s="244"/>
+      <c r="Q9" s="241"/>
+      <c r="R9" s="241"/>
+      <c r="S9" s="241"/>
+      <c r="T9" s="241"/>
+      <c r="U9" s="241"/>
+      <c r="V9" s="241"/>
+      <c r="W9" s="241"/>
+      <c r="X9" s="241"/>
+      <c r="Y9" s="241"/>
+      <c r="Z9" s="241"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16481,31 +16452,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="234" t="s">
+      <c r="C17" s="239" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="234"/>
-      <c r="E17" s="234"/>
-      <c r="F17" s="234"/>
-      <c r="G17" s="234"/>
-      <c r="H17" s="234"/>
-      <c r="I17" s="234"/>
-      <c r="J17" s="234"/>
-      <c r="K17" s="234"/>
-      <c r="L17" s="234"/>
-      <c r="P17" s="244" t="s">
+      <c r="D17" s="239"/>
+      <c r="E17" s="239"/>
+      <c r="F17" s="239"/>
+      <c r="G17" s="239"/>
+      <c r="H17" s="239"/>
+      <c r="I17" s="239"/>
+      <c r="J17" s="239"/>
+      <c r="K17" s="239"/>
+      <c r="L17" s="239"/>
+      <c r="P17" s="241" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="244"/>
-      <c r="R17" s="244"/>
-      <c r="S17" s="244"/>
-      <c r="T17" s="244"/>
-      <c r="U17" s="244"/>
-      <c r="V17" s="244"/>
-      <c r="W17" s="244"/>
-      <c r="X17" s="244"/>
-      <c r="Y17" s="244"/>
-      <c r="Z17" s="244"/>
+      <c r="Q17" s="241"/>
+      <c r="R17" s="241"/>
+      <c r="S17" s="241"/>
+      <c r="T17" s="241"/>
+      <c r="U17" s="241"/>
+      <c r="V17" s="241"/>
+      <c r="W17" s="241"/>
+      <c r="X17" s="241"/>
+      <c r="Y17" s="241"/>
+      <c r="Z17" s="241"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16983,60 +16954,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
-      <c r="G3" s="231"/>
-      <c r="H3" s="232" t="s">
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
-      <c r="P3" s="233"/>
-      <c r="Q3" s="233"/>
-      <c r="R3" s="233"/>
-      <c r="S3" s="233"/>
-      <c r="T3" s="233"/>
-      <c r="U3" s="233"/>
-      <c r="V3" s="233"/>
-      <c r="W3" s="233"/>
-      <c r="X3" s="233"/>
-      <c r="Y3" s="233"/>
-      <c r="Z3" s="233"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
+      <c r="S3" s="244"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="244"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="234" t="s">
+      <c r="C5" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="234"/>
-      <c r="E5" s="234"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="234"/>
-      <c r="H5" s="234"/>
-      <c r="I5" s="234"/>
-      <c r="J5" s="234"/>
-      <c r="K5" s="234"/>
-      <c r="L5" s="234"/>
-      <c r="P5" s="233"/>
-      <c r="Q5" s="233"/>
-      <c r="R5" s="233"/>
-      <c r="S5" s="233"/>
-      <c r="T5" s="233"/>
-      <c r="U5" s="233"/>
-      <c r="V5" s="233"/>
-      <c r="W5" s="233"/>
-      <c r="X5" s="233"/>
-      <c r="Y5" s="233"/>
-      <c r="Z5" s="233"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="244"/>
+      <c r="R5" s="244"/>
+      <c r="S5" s="244"/>
+      <c r="T5" s="244"/>
+      <c r="U5" s="244"/>
+      <c r="V5" s="244"/>
+      <c r="W5" s="244"/>
+      <c r="X5" s="244"/>
+      <c r="Y5" s="244"/>
+      <c r="Z5" s="244"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17222,30 +17193,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="234" t="s">
+      <c r="C11" s="239" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="234"/>
-      <c r="E11" s="234"/>
-      <c r="F11" s="234"/>
-      <c r="G11" s="234"/>
-      <c r="H11" s="234"/>
-      <c r="I11" s="234"/>
-      <c r="J11" s="234"/>
-      <c r="K11" s="234"/>
-      <c r="L11" s="234"/>
+      <c r="D11" s="239"/>
+      <c r="E11" s="239"/>
+      <c r="F11" s="239"/>
+      <c r="G11" s="239"/>
+      <c r="H11" s="239"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="239"/>
+      <c r="K11" s="239"/>
+      <c r="L11" s="239"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="233"/>
-      <c r="Q11" s="233"/>
-      <c r="R11" s="233"/>
-      <c r="S11" s="233"/>
-      <c r="T11" s="233"/>
-      <c r="U11" s="233"/>
-      <c r="V11" s="233"/>
-      <c r="W11" s="233"/>
-      <c r="X11" s="233"/>
-      <c r="Y11" s="233"/>
-      <c r="Z11" s="233"/>
+      <c r="P11" s="244"/>
+      <c r="Q11" s="244"/>
+      <c r="R11" s="244"/>
+      <c r="S11" s="244"/>
+      <c r="T11" s="244"/>
+      <c r="U11" s="244"/>
+      <c r="V11" s="244"/>
+      <c r="W11" s="244"/>
+      <c r="X11" s="244"/>
+      <c r="Y11" s="244"/>
+      <c r="Z11" s="244"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17487,18 +17458,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="234" t="s">
+      <c r="C18" s="239" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="234"/>
-      <c r="E18" s="234"/>
-      <c r="F18" s="234"/>
-      <c r="G18" s="234"/>
-      <c r="H18" s="234"/>
-      <c r="I18" s="234"/>
-      <c r="J18" s="234"/>
-      <c r="K18" s="234"/>
-      <c r="L18" s="234"/>
+      <c r="D18" s="239"/>
+      <c r="E18" s="239"/>
+      <c r="F18" s="239"/>
+      <c r="G18" s="239"/>
+      <c r="H18" s="239"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17711,23 +17682,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="233"/>
-      <c r="C25" s="233"/>
+      <c r="B25" s="244"/>
+      <c r="C25" s="244"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="234" t="s">
+      <c r="C26" s="239" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="234"/>
-      <c r="E26" s="234"/>
-      <c r="F26" s="234"/>
-      <c r="G26" s="234"/>
-      <c r="H26" s="234"/>
-      <c r="I26" s="234"/>
-      <c r="J26" s="234"/>
-      <c r="K26" s="234"/>
-      <c r="L26" s="234"/>
+      <c r="D26" s="239"/>
+      <c r="E26" s="239"/>
+      <c r="F26" s="239"/>
+      <c r="G26" s="239"/>
+      <c r="H26" s="239"/>
+      <c r="I26" s="239"/>
+      <c r="J26" s="239"/>
+      <c r="K26" s="239"/>
+      <c r="L26" s="239"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17919,18 +17890,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="234" t="s">
+      <c r="C33" s="239" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="234"/>
-      <c r="E33" s="234"/>
-      <c r="F33" s="234"/>
-      <c r="G33" s="234"/>
-      <c r="H33" s="234"/>
-      <c r="I33" s="234"/>
-      <c r="J33" s="234"/>
-      <c r="K33" s="234"/>
-      <c r="L33" s="234"/>
+      <c r="D33" s="239"/>
+      <c r="E33" s="239"/>
+      <c r="F33" s="239"/>
+      <c r="G33" s="239"/>
+      <c r="H33" s="239"/>
+      <c r="I33" s="239"/>
+      <c r="J33" s="239"/>
+      <c r="K33" s="239"/>
+      <c r="L33" s="239"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18114,18 +18085,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="234" t="s">
+      <c r="C40" s="239" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="234"/>
-      <c r="E40" s="234"/>
-      <c r="F40" s="234"/>
-      <c r="G40" s="234"/>
-      <c r="H40" s="234"/>
-      <c r="I40" s="234"/>
-      <c r="J40" s="234"/>
-      <c r="K40" s="234"/>
-      <c r="L40" s="234"/>
+      <c r="D40" s="239"/>
+      <c r="E40" s="239"/>
+      <c r="F40" s="239"/>
+      <c r="G40" s="239"/>
+      <c r="H40" s="239"/>
+      <c r="I40" s="239"/>
+      <c r="J40" s="239"/>
+      <c r="K40" s="239"/>
+      <c r="L40" s="239"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18283,19 +18254,19 @@
       </c>
       <c r="H44" s="123">
         <f t="shared" si="13"/>
-        <v>1.2</v>
+        <v>0.85714285714285698</v>
       </c>
       <c r="I44" s="123">
         <f t="shared" si="13"/>
-        <v>1.2</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="J44" s="123">
         <f t="shared" si="13"/>
-        <v>1.2</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="K44" s="123">
         <f t="shared" si="13"/>
-        <v>1.1999999999999997</v>
+        <v>1.0714285714285714</v>
       </c>
       <c r="L44" s="123">
         <f t="shared" si="13"/>
@@ -18328,19 +18299,19 @@
       </c>
       <c r="H45" s="25">
         <f>H7*H46</f>
-        <v>1021.8447500000002</v>
+        <v>1430.5826500000005</v>
       </c>
       <c r="I45" s="25">
         <f>I7*I46</f>
-        <v>1015.1923624999999</v>
+        <v>1421.2693075</v>
       </c>
       <c r="J45" s="25">
         <f>J7*J46</f>
-        <v>1107.0399692500002</v>
+        <v>1549.8559569500003</v>
       </c>
       <c r="K45" s="25">
         <f>K7*K46</f>
-        <v>1251.1347737955</v>
+        <v>1401.2709466509598</v>
       </c>
       <c r="L45" s="25">
         <f>L7*L46</f>
@@ -18372,16 +18343,16 @@
         <v>2.6917170987264025E-2</v>
       </c>
       <c r="H46" s="97">
-        <v>2.5000000000000001E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="I46" s="97">
-        <v>2.5000000000000001E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="J46" s="97">
-        <v>2.5000000000000001E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="K46" s="97">
-        <v>2.5000000000000001E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="L46" s="97">
         <v>2.5000000000000001E-2</v>
@@ -18389,6 +18360,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18396,12 +18373,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18439,60 +18410,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="231"/>
-      <c r="H2" s="232" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233"/>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
+      <c r="S2" s="244"/>
+      <c r="T2" s="244"/>
+      <c r="U2" s="244"/>
+      <c r="V2" s="244"/>
+      <c r="W2" s="244"/>
+      <c r="X2" s="244"/>
+      <c r="Y2" s="244"/>
+      <c r="Z2" s="244"/>
+      <c r="AA2" s="244"/>
+      <c r="AB2" s="244"/>
+      <c r="AC2" s="244"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="234" t="s">
+      <c r="C4" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
-      <c r="S4" s="233"/>
-      <c r="T4" s="233"/>
-      <c r="U4" s="233"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="233"/>
-      <c r="X4" s="233"/>
-      <c r="Y4" s="233"/>
-      <c r="Z4" s="233"/>
-      <c r="AA4" s="233"/>
-      <c r="AB4" s="233"/>
-      <c r="AC4" s="233"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
+      <c r="S4" s="244"/>
+      <c r="T4" s="244"/>
+      <c r="U4" s="244"/>
+      <c r="V4" s="244"/>
+      <c r="W4" s="244"/>
+      <c r="X4" s="244"/>
+      <c r="Y4" s="244"/>
+      <c r="Z4" s="244"/>
+      <c r="AA4" s="244"/>
+      <c r="AB4" s="244"/>
+      <c r="AC4" s="244"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18855,18 +18826,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="234" t="s">
+      <c r="C13" s="239" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="234"/>
-      <c r="E13" s="234"/>
-      <c r="F13" s="234"/>
-      <c r="G13" s="234"/>
-      <c r="H13" s="234"/>
-      <c r="I13" s="234"/>
-      <c r="J13" s="234"/>
-      <c r="K13" s="234"/>
-      <c r="L13" s="234"/>
+      <c r="D13" s="239"/>
+      <c r="E13" s="239"/>
+      <c r="F13" s="239"/>
+      <c r="G13" s="239"/>
+      <c r="H13" s="239"/>
+      <c r="I13" s="239"/>
+      <c r="J13" s="239"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="239"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18959,18 +18930,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="234" t="s">
+      <c r="C18" s="239" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="234"/>
-      <c r="E18" s="234"/>
-      <c r="F18" s="234"/>
-      <c r="G18" s="234"/>
-      <c r="H18" s="234"/>
-      <c r="I18" s="234"/>
-      <c r="J18" s="234"/>
-      <c r="K18" s="234"/>
-      <c r="L18" s="234"/>
+      <c r="D18" s="239"/>
+      <c r="E18" s="239"/>
+      <c r="F18" s="239"/>
+      <c r="G18" s="239"/>
+      <c r="H18" s="239"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19091,19 +19062,19 @@
       </c>
       <c r="H21" s="88">
         <f>'WC &amp; Investments'!H45</f>
-        <v>1021.8447500000002</v>
+        <v>1430.5826500000005</v>
       </c>
       <c r="I21" s="88">
         <f>'WC &amp; Investments'!I45</f>
-        <v>1015.1923624999999</v>
+        <v>1421.2693075</v>
       </c>
       <c r="J21" s="88">
         <f>'WC &amp; Investments'!J45</f>
-        <v>1107.0399692500002</v>
+        <v>1549.8559569500003</v>
       </c>
       <c r="K21" s="88">
         <f>'WC &amp; Investments'!K45</f>
-        <v>1251.1347737955</v>
+        <v>1401.2709466509598</v>
       </c>
       <c r="L21" s="88">
         <f>'WC &amp; Investments'!L45</f>
@@ -19162,18 +19133,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="234" t="s">
+      <c r="C25" s="239" t="s">
         <v>259</v>
       </c>
-      <c r="D25" s="234"/>
-      <c r="E25" s="234"/>
-      <c r="F25" s="234"/>
-      <c r="G25" s="234"/>
-      <c r="H25" s="234"/>
-      <c r="I25" s="234"/>
-      <c r="J25" s="234"/>
-      <c r="K25" s="234"/>
-      <c r="L25" s="234"/>
+      <c r="D25" s="239"/>
+      <c r="E25" s="239"/>
+      <c r="F25" s="239"/>
+      <c r="G25" s="239"/>
+      <c r="H25" s="239"/>
+      <c r="I25" s="239"/>
+      <c r="J25" s="239"/>
+      <c r="K25" s="239"/>
+      <c r="L25" s="239"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19291,19 +19262,19 @@
       </c>
       <c r="H28" s="94">
         <f t="shared" si="7"/>
-        <v>9962.4454400547947</v>
+        <v>9553.7075400547947</v>
       </c>
       <c r="I28" s="94">
         <f t="shared" si="7"/>
-        <v>9846.3077947150741</v>
+        <v>9440.2308497150734</v>
       </c>
       <c r="J28" s="94">
         <f t="shared" si="7"/>
-        <v>10316.299001554395</v>
+        <v>9873.483013854393</v>
       </c>
       <c r="K28" s="94">
         <f t="shared" si="7"/>
-        <v>10835.230978068088</v>
+        <v>10685.09480521263</v>
       </c>
       <c r="L28" s="94">
         <f t="shared" si="7"/>
@@ -19311,18 +19282,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="234" t="s">
+      <c r="C31" s="239" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="234"/>
-      <c r="E31" s="234"/>
-      <c r="F31" s="234"/>
-      <c r="G31" s="234"/>
-      <c r="H31" s="234"/>
-      <c r="I31" s="234"/>
-      <c r="J31" s="234"/>
-      <c r="K31" s="234"/>
-      <c r="L31" s="234"/>
+      <c r="D31" s="239"/>
+      <c r="E31" s="239"/>
+      <c r="F31" s="239"/>
+      <c r="G31" s="239"/>
+      <c r="H31" s="239"/>
+      <c r="I31" s="239"/>
+      <c r="J31" s="239"/>
+      <c r="K31" s="239"/>
+      <c r="L31" s="239"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19461,16 +19432,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19533,10 +19504,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="230"/>
+      <c r="C4" s="233"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19553,7 +19524,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>182.95</v>
+        <v>189.16</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19562,7 +19533,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>193927</v>
+        <v>200509.6</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19580,7 +19551,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19589,7 +19560,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6357999999999999</v>
+        <v>1.6351</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19621,10 +19592,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
+      <c r="B15" s="233" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="230"/>
+      <c r="C15" s="233"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19632,7 +19603,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.2993398566901055E-2</v>
+        <v>7.0766652640008601E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19641,7 +19612,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92700660143309899</v>
+        <v>0.92923334735999141</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19659,7 +19630,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11840099999999999</v>
+        <v>0.11896949999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19668,7 +19639,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11243992111263545</v>
+        <v>0.1131500397034752</v>
       </c>
     </row>
   </sheetData>
@@ -19713,60 +19684,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
-      <c r="G3" s="231"/>
-      <c r="H3" s="232" t="s">
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
-      <c r="P3" s="233"/>
-      <c r="Q3" s="233"/>
-      <c r="R3" s="233"/>
-      <c r="S3" s="233"/>
-      <c r="T3" s="233"/>
-      <c r="U3" s="233"/>
-      <c r="V3" s="233"/>
-      <c r="W3" s="233"/>
-      <c r="X3" s="233"/>
-      <c r="Y3" s="233"/>
-      <c r="Z3" s="233"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
+      <c r="S3" s="244"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="244"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="234" t="s">
+      <c r="C5" s="239" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="234"/>
-      <c r="E5" s="234"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="234"/>
-      <c r="H5" s="234"/>
-      <c r="I5" s="234"/>
-      <c r="J5" s="234"/>
-      <c r="K5" s="234"/>
-      <c r="L5" s="234"/>
-      <c r="P5" s="233"/>
-      <c r="Q5" s="233"/>
-      <c r="R5" s="233"/>
-      <c r="S5" s="233"/>
-      <c r="T5" s="233"/>
-      <c r="U5" s="233"/>
-      <c r="V5" s="233"/>
-      <c r="W5" s="233"/>
-      <c r="X5" s="233"/>
-      <c r="Y5" s="233"/>
-      <c r="Z5" s="233"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="244"/>
+      <c r="R5" s="244"/>
+      <c r="S5" s="244"/>
+      <c r="T5" s="244"/>
+      <c r="U5" s="244"/>
+      <c r="V5" s="244"/>
+      <c r="W5" s="244"/>
+      <c r="X5" s="244"/>
+      <c r="Y5" s="244"/>
+      <c r="Z5" s="244"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19853,19 +19824,19 @@
       </c>
       <c r="H7" s="112">
         <f>'FCF &amp; Other'!H28</f>
-        <v>9962.4454400547947</v>
+        <v>9553.7075400547947</v>
       </c>
       <c r="I7" s="112">
         <f>'FCF &amp; Other'!I28</f>
-        <v>9846.3077947150741</v>
+        <v>9440.2308497150734</v>
       </c>
       <c r="J7" s="112">
         <f>'FCF &amp; Other'!J28</f>
-        <v>10316.299001554395</v>
+        <v>9873.483013854393</v>
       </c>
       <c r="K7" s="112">
         <f>'FCF &amp; Other'!K28</f>
-        <v>10835.230978068088</v>
+        <v>10685.09480521263</v>
       </c>
       <c r="L7" s="112">
         <f>'FCF &amp; Other'!L28</f>
@@ -19919,7 +19890,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>150641.02996155454</v>
+        <v>149427.49680514541</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19973,23 +19944,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>8955.4907649220258</v>
+        <v>8582.587431429949</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7956.4671942802197</v>
+        <v>7618.600525327136</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7493.664135164664</v>
+        <v>7158.2896076812713</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7075.0890647750984</v>
+        <v>6959.2679024986746</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7543.0387731580458</v>
+        <v>7519.0095673746537</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20008,14 +19979,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>88422.023305894123</v>
+        <v>87430.304427363517</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="230" t="s">
+      <c r="B13" s="233" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="230"/>
+      <c r="C13" s="233"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20031,14 +20002,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11243992111263545</v>
+        <v>0.1131500397034752</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="230" t="s">
+      <c r="B18" s="233" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="230"/>
+      <c r="C18" s="233"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20046,7 +20017,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>39023.749932300059</v>
+        <v>37837.755034311682</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20055,7 +20026,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>88422.023305894123</v>
+        <v>87430.304427363517</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20064,7 +20035,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>127445.77323819418</v>
+        <v>125268.05946167521</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20091,7 +20062,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>121974.77323819418</v>
+        <v>119797.05946167521</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20109,7 +20080,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>115.07054079074922</v>
+        <v>113.01609383176907</v>
       </c>
     </row>
   </sheetData>
@@ -20152,37 +20123,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="231"/>
-      <c r="H2" s="232" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="234" t="s">
+      <c r="C4" s="239" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20347,19 +20318,19 @@
       </c>
       <c r="H8" s="92">
         <f>'FCF &amp; Other'!H28</f>
-        <v>9962.4454400547947</v>
+        <v>9553.7075400547947</v>
       </c>
       <c r="I8" s="92">
         <f>'FCF &amp; Other'!I28</f>
-        <v>9846.3077947150741</v>
+        <v>9440.2308497150734</v>
       </c>
       <c r="J8" s="92">
         <f>'FCF &amp; Other'!J28</f>
-        <v>10316.299001554395</v>
+        <v>9873.483013854393</v>
       </c>
       <c r="K8" s="92">
         <f>'FCF &amp; Other'!K28</f>
-        <v>10835.230978068088</v>
+        <v>10685.09480521263</v>
       </c>
       <c r="L8" s="92">
         <f>'FCF &amp; Other'!L28</f>
@@ -20371,18 +20342,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="234" t="s">
+      <c r="C10" s="239" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="234"/>
-      <c r="E10" s="234"/>
-      <c r="F10" s="234"/>
-      <c r="G10" s="234"/>
-      <c r="H10" s="234"/>
-      <c r="I10" s="234"/>
-      <c r="J10" s="234"/>
-      <c r="K10" s="234"/>
-      <c r="L10" s="234"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="239"/>
+      <c r="F10" s="239"/>
+      <c r="G10" s="239"/>
+      <c r="H10" s="239"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20552,23 +20523,23 @@
       </c>
       <c r="H14" s="95">
         <f t="shared" si="3"/>
-        <v>-0.15512259839061682</v>
+        <v>-0.18978611719924546</v>
       </c>
       <c r="I14" s="95">
         <f t="shared" si="3"/>
-        <v>-1.1657543927194832E-2</v>
+        <v>-1.1877764717410474E-2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="3"/>
-        <v>4.7732735624168125E-2</v>
+        <v>4.5894234053862788E-2</v>
       </c>
       <c r="K14" s="95">
         <f t="shared" si="3"/>
-        <v>5.0302145802046255E-2</v>
+        <v>8.2201163481963699E-2</v>
       </c>
       <c r="L14" s="95">
         <f t="shared" si="3"/>
-        <v>0.18601721913845953</v>
+        <v>0.20268193662278686</v>
       </c>
       <c r="N14" s="91"/>
     </row>
@@ -20576,18 +20547,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="234" t="s">
+      <c r="C16" s="239" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="234"/>
-      <c r="E16" s="234"/>
-      <c r="F16" s="234"/>
-      <c r="G16" s="234"/>
-      <c r="H16" s="234"/>
-      <c r="I16" s="234"/>
-      <c r="J16" s="234"/>
-      <c r="K16" s="234"/>
-      <c r="L16" s="234"/>
+      <c r="D16" s="239"/>
+      <c r="E16" s="239"/>
+      <c r="F16" s="239"/>
+      <c r="G16" s="239"/>
+      <c r="H16" s="239"/>
+      <c r="I16" s="239"/>
+      <c r="J16" s="239"/>
+      <c r="K16" s="239"/>
+      <c r="L16" s="239"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20721,18 +20692,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="234" t="s">
+      <c r="C21" s="239" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="234"/>
-      <c r="E21" s="234"/>
-      <c r="F21" s="234"/>
-      <c r="G21" s="234"/>
-      <c r="H21" s="234"/>
-      <c r="I21" s="234"/>
-      <c r="J21" s="234"/>
-      <c r="K21" s="234"/>
-      <c r="L21" s="234"/>
+      <c r="D21" s="239"/>
+      <c r="E21" s="239"/>
+      <c r="F21" s="239"/>
+      <c r="G21" s="239"/>
+      <c r="H21" s="239"/>
+      <c r="I21" s="239"/>
+      <c r="J21" s="239"/>
+      <c r="K21" s="239"/>
+      <c r="L21" s="239"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -20816,18 +20787,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="234" t="s">
+      <c r="C26" s="239" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="234"/>
-      <c r="E26" s="234"/>
-      <c r="F26" s="234"/>
-      <c r="G26" s="234"/>
-      <c r="H26" s="234"/>
-      <c r="I26" s="234"/>
-      <c r="J26" s="234"/>
-      <c r="K26" s="234"/>
-      <c r="L26" s="234"/>
+      <c r="D26" s="239"/>
+      <c r="E26" s="239"/>
+      <c r="F26" s="239"/>
+      <c r="G26" s="239"/>
+      <c r="H26" s="239"/>
+      <c r="I26" s="239"/>
+      <c r="J26" s="239"/>
+      <c r="K26" s="239"/>
+      <c r="L26" s="239"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21097,10 +21068,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="230" t="s">
+      <c r="B37" s="233" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="230"/>
+      <c r="C37" s="233"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21118,7 +21089,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11243992111263545</v>
+        <v>0.1131500397034752</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21144,7 +21115,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>190704.86563104633</v>
+        <v>190082.52142953235</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21171,7 +21142,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>185233.86563104633</v>
+        <v>184611.52142953235</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21189,14 +21160,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>174.74892984060975</v>
+        <v>174.16181266937014</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="230" t="s">
+      <c r="B49" s="233" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="230"/>
+      <c r="C49" s="233"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21252,10 +21223,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="230" t="s">
+      <c r="B57" s="233" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="230"/>
+      <c r="C57" s="233"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21272,7 +21243,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11243992111263545</v>
+        <v>0.1131500397034752</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21298,7 +21269,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>183919.96932895118</v>
+        <v>183319.23918436636</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21325,7 +21296,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>178448.96932895118</v>
+        <v>177848.23918436636</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21343,7 +21314,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>168.34808427259546</v>
+        <v>167.78135772110033</v>
       </c>
     </row>
   </sheetData>
@@ -21395,10 +21366,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="230"/>
+      <c r="C4" s="233"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21407,7 +21378,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>115.07054079074922</v>
+        <v>113.01609383176907</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21416,7 +21387,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>174.74892984060975</v>
+        <v>174.16181266937014</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21434,7 +21405,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>168.34808427259546</v>
+        <v>167.78135772110033</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21443,7 +21414,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>162.21857645983346</v>
+        <v>161.41650378940471</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21452,7 +21423,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>182.95</v>
+        <v>189.16</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21461,7 +21432,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.11331742847863642</v>
+        <v>-0.14666682285152929</v>
       </c>
     </row>
   </sheetData>
@@ -21526,60 +21497,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
-      <c r="G3" s="231"/>
-      <c r="H3" s="232" t="s">
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
-      <c r="P3" s="233"/>
-      <c r="Q3" s="233"/>
-      <c r="R3" s="233"/>
-      <c r="S3" s="233"/>
-      <c r="T3" s="233"/>
-      <c r="U3" s="233"/>
-      <c r="V3" s="233"/>
-      <c r="W3" s="233"/>
-      <c r="X3" s="233"/>
-      <c r="Y3" s="233"/>
-      <c r="Z3" s="233"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
+      <c r="S3" s="244"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="244"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="234" t="s">
+      <c r="C5" s="239" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="234"/>
-      <c r="E5" s="234"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="234"/>
-      <c r="H5" s="234"/>
-      <c r="I5" s="234"/>
-      <c r="J5" s="234"/>
-      <c r="K5" s="234"/>
-      <c r="L5" s="234"/>
-      <c r="P5" s="233"/>
-      <c r="Q5" s="233"/>
-      <c r="R5" s="233"/>
-      <c r="S5" s="233"/>
-      <c r="T5" s="233"/>
-      <c r="U5" s="233"/>
-      <c r="V5" s="233"/>
-      <c r="W5" s="233"/>
-      <c r="X5" s="233"/>
-      <c r="Y5" s="233"/>
-      <c r="Z5" s="233"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="244"/>
+      <c r="R5" s="244"/>
+      <c r="S5" s="244"/>
+      <c r="T5" s="244"/>
+      <c r="U5" s="244"/>
+      <c r="V5" s="244"/>
+      <c r="W5" s="244"/>
+      <c r="X5" s="244"/>
+      <c r="Y5" s="244"/>
+      <c r="Z5" s="244"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21714,7 +21685,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>299185.57498481899</v>
+        <v>296775.39752349874</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21768,23 +21739,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12369.910359486572</v>
+        <v>12362.019147161202</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12976.597760967266</v>
+        <v>12960.046561719655</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13613.040398534467</v>
+        <v>13587.004265440912</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14280.69763012506</v>
+        <v>14244.291795554649</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14981.100388493287</v>
+        <v>14933.376393572596</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21803,7 +21774,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>175613.46925765538</v>
+        <v>173643.83334257829</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21819,7 +21790,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>182.95</v>
+        <v>189.16</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21828,7 +21799,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>226.15162788924292</v>
+        <v>224.1551911821891</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -21867,7 +21838,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11243992111263545</v>
+        <v>0.1131500397034752</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -21885,7 +21856,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>192829.3</v>
+        <v>199374.63999999998</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21912,7 +21883,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>198300.3</v>
+        <v>204845.63999999998</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21928,7 +21899,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>68221.346537606645</v>
+        <v>68086.738163449016</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -21937,7 +21908,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>175613.46925765538</v>
+        <v>173643.83334257829</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -21946,7 +21917,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>243834.81579526202</v>
+        <v>241730.57150602731</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -21973,7 +21944,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>238363.81579526202</v>
+        <v>236259.57150602731</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -21991,22 +21962,22 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>226.15162788924292</v>
+        <v>224.1551911821891</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="234" t="s">
+      <c r="C39" s="239" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="234"/>
-      <c r="E39" s="234"/>
-      <c r="F39" s="234"/>
-      <c r="G39" s="234"/>
-      <c r="H39" s="234"/>
-      <c r="I39" s="234"/>
-      <c r="J39" s="234"/>
-      <c r="K39" s="234"/>
-      <c r="L39" s="234"/>
+      <c r="D39" s="239"/>
+      <c r="E39" s="239"/>
+      <c r="F39" s="239"/>
+      <c r="G39" s="239"/>
+      <c r="H39" s="239"/>
+      <c r="I39" s="239"/>
+      <c r="J39" s="239"/>
+      <c r="K39" s="239"/>
+      <c r="L39" s="239"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -22438,17 +22409,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28933,7 +28904,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>182.95</v>
+        <v>189.16</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -28980,7 +28951,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>182.95</v>
+        <v>189.16</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -30482,7 +30453,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>19.424861229535843</v>
+        <v>20.084212900677784</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30519,7 +30490,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.4397770600636965</v>
+        <v>4.5904795227201367</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30556,7 +30527,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>7.0690409854094876</v>
+        <v>7.3089903951902633</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30593,7 +30564,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>193927</v>
+        <v>200509.6</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30630,7 +30601,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>199398</v>
+        <v>205980.6</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30667,7 +30638,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>4.4722110079397117</v>
+        <v>4.6198492800430628</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30704,7 +30675,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>17.560369881109644</v>
+        <v>18.14007926023778</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30839,7 +30810,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="98">AC156/AC160</f>
-        <v>20.562718693669812</v>
+        <v>21.260693457745734</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30876,7 +30847,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="98"/>
-        <v>16.674884777337901</v>
+        <v>17.225362197047751</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -30913,7 +30884,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="101">AC160/AC156</f>
-        <v>4.8631701619681632E-2</v>
+        <v>4.7035154426521224E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -30950,7 +30921,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.1480419251566253E-2</v>
+        <v>4.9790350507898318E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -30987,7 +30958,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>1.9458868543317846E-2</v>
+        <v>1.8820046521463313E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31024,7 +30995,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>5.535588133679168E-2</v>
+        <v>5.3538583688761035E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31061,7 +31032,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>7.5054015170657004E-2</v>
+        <v>7.2590040576610795E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -31564,7 +31535,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-2.8211646650543761E-2</v>
+        <v>-2.7285476605608906E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -32886,15 +32857,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="230"/>
-      <c r="E4" s="230" t="s">
+      <c r="C4" s="233"/>
+      <c r="E4" s="233" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32902,7 +32873,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>182.95</v>
+        <v>189.16</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -32918,7 +32889,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>193927</v>
+        <v>200509.6</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32938,7 +32909,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>199398</v>
+        <v>205980.6</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32958,7 +32929,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>19.424861229535843</v>
+        <v>20.084212900677784</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -32978,7 +32949,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.4397770600636965</v>
+        <v>4.5904795227201367</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -32998,7 +32969,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.0690409854094876</v>
+        <v>7.3089903951902633</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33018,7 +32989,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.4722110079397117</v>
+        <v>4.6198492800430628</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33027,18 +32998,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>17.560369881109644</v>
+        <v>18.14007926023778</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
+      <c r="B15" s="233" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="230"/>
-      <c r="E15" s="230" t="s">
+      <c r="C15" s="233"/>
+      <c r="E15" s="233" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="230"/>
+      <c r="F15" s="233"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33089,14 +33060,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="230" t="s">
+      <c r="B21" s="233" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="230"/>
-      <c r="E21" s="230" t="s">
+      <c r="C21" s="233"/>
+      <c r="E21" s="233" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="230"/>
+      <c r="F21" s="233"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33165,14 +33136,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="230" t="s">
+      <c r="B29" s="233" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="230"/>
-      <c r="E29" s="230" t="s">
+      <c r="C29" s="233"/>
+      <c r="E29" s="233" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="230"/>
+      <c r="F29" s="233"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33248,14 +33219,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="230" t="s">
+      <c r="B37" s="233" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="230"/>
-      <c r="E37" s="230" t="s">
+      <c r="C37" s="233"/>
+      <c r="E37" s="233" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="230"/>
+      <c r="F37" s="233"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33263,7 +33234,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.1480419251566253E-2</v>
+        <v>4.9790350507898318E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33279,7 +33250,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>4.8631701619681632E-2</v>
+        <v>4.7035154426521224E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33295,7 +33266,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.9458868543317846E-2</v>
+        <v>1.8820046521463313E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33311,7 +33282,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.535588133679168E-2</v>
+        <v>5.3538583688761035E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33320,18 +33291,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>7.5054015170657004E-2</v>
+        <v>7.2590040576610795E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="230" t="s">
+      <c r="B45" s="233" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="230"/>
-      <c r="E45" s="230" t="s">
+      <c r="C45" s="233"/>
+      <c r="E45" s="233" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="230"/>
+      <c r="F45" s="233"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33364,18 +33335,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-2.8211646650543761E-2</v>
+        <v>-2.7285476605608906E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="230" t="s">
+      <c r="B51" s="233" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="230"/>
-      <c r="E51" s="230" t="s">
+      <c r="C51" s="233"/>
+      <c r="E51" s="233" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="230"/>
+      <c r="F51" s="233"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33544,7 +33515,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>182.95</v>
+        <v>189.16</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33573,7 +33544,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>193927</v>
+        <v>200509.6</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33602,7 +33573,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>199398</v>
+        <v>205980.6</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33631,7 +33602,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>19.424861229535843</v>
+        <v>20.084212900677784</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33660,7 +33631,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.4397770600636965</v>
+        <v>4.5904795227201367</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33689,7 +33660,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.0690409854094876</v>
+        <v>7.3089903951902633</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33718,7 +33689,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.4722110079397117</v>
+        <v>4.6198492800430628</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33747,7 +33718,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>17.560369881109644</v>
+        <v>18.14007926023778</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34520,7 +34491,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.1480419251566253E-2</v>
+        <v>4.9790350507898318E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34549,7 +34520,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>4.8631701619681632E-2</v>
+        <v>4.7035154426521224E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34578,7 +34549,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.9458868543317846E-2</v>
+        <v>1.8820046521463313E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34607,7 +34578,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.535588133679168E-2</v>
+        <v>5.3538583688761035E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34636,7 +34607,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>7.5054015170657004E-2</v>
+        <v>7.2590040576610795E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34872,7 +34843,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-2.8211646650543761E-2</v>
+        <v>-2.7285476605608906E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35410,14 +35381,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="236" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="F3" s="240" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="239"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35484,19 +35455,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="241">
+      <c r="C7" s="234">
         <f>Statement!AA89</f>
         <v>-0.13491674828599412</v>
       </c>
-      <c r="D7" s="242"/>
-      <c r="F7" s="241">
+      <c r="D7" s="235"/>
+      <c r="F7" s="234">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-3.4611531104836508E-2</v>
       </c>
-      <c r="G7" s="242"/>
+      <c r="G7" s="235"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35523,19 +35494,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="241">
+      <c r="C9" s="234">
         <f>Statement!AA90</f>
         <v>-0.11997126436781609</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="F9" s="241">
+      <c r="D9" s="235"/>
+      <c r="F9" s="234">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>-7.4944298156775372E-3</v>
       </c>
-      <c r="G9" s="242"/>
+      <c r="G9" s="235"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35562,19 +35533,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="241">
+      <c r="C11" s="234">
         <f>Statement!AA91</f>
         <v>-0.1473668461998803</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="F11" s="241">
+      <c r="D11" s="235"/>
+      <c r="F11" s="234">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-5.6769281694803046E-2</v>
       </c>
-      <c r="G11" s="242"/>
+      <c r="G11" s="235"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35601,19 +35572,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="241">
+      <c r="C13" s="234">
         <f>Statement!AA94</f>
         <v>2.1699819168173599E-2</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="F13" s="241">
+      <c r="D13" s="235"/>
+      <c r="F13" s="234">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.16016427104722791</v>
       </c>
-      <c r="G13" s="242"/>
+      <c r="G13" s="235"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -35640,19 +35611,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="241">
+      <c r="C15" s="234">
         <f>Statement!AA95</f>
         <v>-0.31402257872846107</v>
       </c>
-      <c r="D15" s="242"/>
-      <c r="F15" s="241">
+      <c r="D15" s="235"/>
+      <c r="F15" s="234">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.25993589743589746</v>
       </c>
-      <c r="G15" s="242"/>
+      <c r="G15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35679,19 +35650,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="241">
+      <c r="C17" s="234">
         <f>Statement!AA97</f>
         <v>-0.35685752330226367</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="F17" s="241">
+      <c r="D17" s="235"/>
+      <c r="F17" s="234">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.31294452347083929</v>
       </c>
-      <c r="G17" s="242"/>
+      <c r="G17" s="235"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -35718,22 +35689,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="241">
+      <c r="C19" s="234">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-6.4874884151992582E-3</v>
       </c>
-      <c r="D19" s="242"/>
-      <c r="F19" s="241">
+      <c r="D19" s="235"/>
+      <c r="F19" s="234">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.8565022421524667E-2</v>
       </c>
-      <c r="G19" s="242"/>
+      <c r="G19" s="235"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35760,22 +35731,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="241">
+      <c r="C21" s="234">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.35171265972296784</v>
       </c>
-      <c r="D21" s="242"/>
-      <c r="F21" s="241">
+      <c r="D21" s="235"/>
+      <c r="F21" s="234">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.28482587064676618</v>
       </c>
-      <c r="G21" s="242"/>
+      <c r="G21" s="235"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35823,22 +35794,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="241">
+      <c r="C25" s="234">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.23006134969325154</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="F25" s="241">
+      <c r="D25" s="235"/>
+      <c r="F25" s="234">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.13061047770241016</v>
       </c>
-      <c r="G25" s="242"/>
+      <c r="G25" s="235"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -35865,22 +35836,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="241">
+      <c r="C27" s="234">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.20435967302452315</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="F27" s="241">
+      <c r="D27" s="235"/>
+      <c r="F27" s="234">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.38269030239833157</v>
       </c>
-      <c r="G27" s="242"/>
+      <c r="G27" s="235"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -35907,22 +35878,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="241">
+      <c r="C29" s="234">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.2511848341232227E-2</v>
       </c>
-      <c r="D29" s="242"/>
-      <c r="F29" s="241">
+      <c r="D29" s="235"/>
+      <c r="F29" s="234">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>9.1714104996837451E-2</v>
       </c>
-      <c r="G29" s="242"/>
+      <c r="G29" s="235"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35949,22 +35920,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="241">
+      <c r="C31" s="234">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.1448223876378027</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="F31" s="241">
+      <c r="D31" s="235"/>
+      <c r="F31" s="234">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-4.1503854683704718E-2</v>
       </c>
-      <c r="G31" s="242"/>
+      <c r="G31" s="235"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -35991,25 +35962,43 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="241">
+      <c r="C33" s="234">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.13190954773869346</v>
       </c>
-      <c r="D33" s="242"/>
-      <c r="F33" s="241">
+      <c r="D33" s="235"/>
+      <c r="F33" s="234">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>4.7763457164518575E-2</v>
       </c>
-      <c r="G33" s="242"/>
+      <c r="G33" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36020,24 +36009,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7ECBE0-C6F7-9C42-95FE-DDAD16E08723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FF68B2-73D2-B640-B0E8-F96D499AADF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -32,10 +32,11 @@
     <sheet name="DCF" sheetId="11" r:id="rId17"/>
     <sheet name="Multiples" sheetId="12" r:id="rId18"/>
     <sheet name="AVG target price" sheetId="13" r:id="rId19"/>
-    <sheet name="Reverse DCF" sheetId="14" r:id="rId20"/>
+    <sheet name="DDM" sheetId="21" r:id="rId20"/>
+    <sheet name="Reverse DCF" sheetId="14" r:id="rId21"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId21"/>
+    <externalReference r:id="rId22"/>
   </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -150,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="417">
   <si>
     <t>Ticker</t>
   </si>
@@ -1368,6 +1369,39 @@
   </si>
   <si>
     <t>Actual QTL Revenue</t>
+  </si>
+  <si>
+    <t>Dividend discount model</t>
+  </si>
+  <si>
+    <t>Dividend per share</t>
+  </si>
+  <si>
+    <t>Ratios</t>
+  </si>
+  <si>
+    <t>Payout</t>
+  </si>
+  <si>
+    <t>DDM valuation</t>
+  </si>
+  <si>
+    <t>Latest dividend</t>
+  </si>
+  <si>
+    <t>Year 1 growth rate</t>
+  </si>
+  <si>
+    <t>Year 1 dividend</t>
+  </si>
+  <si>
+    <t>Perpetual dividend growth</t>
+  </si>
+  <si>
+    <t>DDM price</t>
+  </si>
+  <si>
+    <t>Manual Cost of Equity</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +2005,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2280,6 +2314,11 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -12691,11 +12730,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6351</v>
+    <v>1.6361000000000001</v>
     <v>-1.95</v>
     <v>-1.0204E-2</v>
-    <v>-0.66</v>
-    <v>-3.4889999999999999E-3</v>
+    <v>-0.26</v>
+    <v>-1.374E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12707,21 +12746,21 @@
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.885025149997</v>
+    <v>46213.999990844532</v>
     <v>4</v>
     <v>185.72</v>
     <v>199374640000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>187.50800000000001</v>
-    <v>20.575600000000001</v>
+    <v>20.787700000000001</v>
     <v>191.11</v>
     <v>189.16</v>
-    <v>188.5</v>
+    <v>188.9</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>7039544</v>
+    <v>7063957</v>
     <v>21168579</v>
     <v>1991</v>
   </rv>
@@ -12746,17 +12785,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.3</v>
-    <v>-6.5659999999999998E-3</v>
+    <v>0.3</v>
+    <v>6.6090000000000003E-3</v>
     <v>US</v>
-    <v>45.81</v>
+    <v>45.71</v>
     <v>Index</v>
     <v>7</v>
-    <v>45.29</v>
+    <v>45.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.77</v>
+    <v>45.41</v>
+    <v>45.39</v>
     <v>45.69</v>
-    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12998,9 +13037,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13587,18 +13626,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="230" t="s">
+      <c r="B2" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="231"/>
-      <c r="E2" s="230" t="s">
+      <c r="C2" s="236"/>
+      <c r="E2" s="235" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="231"/>
-      <c r="H2" s="230" t="s">
+      <c r="F2" s="236"/>
+      <c r="H2" s="235" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="231"/>
+      <c r="I2" s="236"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13621,7 +13660,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>113.01609383176907</v>
+        <v>112.56890697983242</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13645,7 +13684,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>174.16181266937014</v>
+        <v>173.89749204909762</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13668,8 +13707,8 @@
         <v>PS price</v>
       </c>
       <c r="I5" s="211">
-        <f>'AVG target price'!C7</f>
-        <v>190.70675093537938</v>
+        <f ca="1">'AVG target price'!C7</f>
+        <v>191.29143781629537</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13678,7 +13717,7 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>188.5</v>
+        <v>188.9</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
@@ -13693,7 +13732,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>167.78135772110033</v>
+        <v>167.52621697415231</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13717,7 +13756,7 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>161.41650378940471</v>
+        <v>161.32101345484443</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13726,7 +13765,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.66</v>
+        <v>-0.26</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
@@ -13741,7 +13780,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.14666682285152929</v>
+        <v>-0.14717163536242103</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13766,7 +13805,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-3.4889999999999999E-3</v>
+        <v>-1.374E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
@@ -13775,6 +13814,13 @@
         <f ca="1">Statement!AC167</f>
         <v>5.3538583688761035E-2</v>
       </c>
+      <c r="H10" s="184" t="s">
+        <v>415</v>
+      </c>
+      <c r="I10" s="212">
+        <f ca="1">DDM!C26</f>
+        <v>37.142612609437698</v>
+      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="185" t="s">
@@ -13814,7 +13860,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6351</v>
+        <v>1.6361000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13859,10 +13905,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="232" t="s">
+      <c r="B17" s="237" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="232"/>
+      <c r="C17" s="237"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -13935,14 +13981,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="232" t="s">
+      <c r="B25" s="237" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="232"/>
-      <c r="E25" s="230" t="s">
+      <c r="C25" s="237"/>
+      <c r="E25" s="235" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="231"/>
+      <c r="F25" s="236"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13956,7 +14002,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.39</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13971,7 +14017,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13984,22 +14030,22 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="184" t="s">
-        <v>355</v>
+        <v>416</v>
       </c>
       <c r="C29" s="221">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="233" t="s">
+      <c r="B33" s="238" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="233"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
+      <c r="C33" s="238"/>
+      <c r="D33" s="238"/>
+      <c r="E33" s="238"/>
+      <c r="F33" s="238"/>
+      <c r="G33" s="238"/>
+      <c r="H33" s="238"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14018,24 +14064,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="233"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="233"/>
+      <c r="B39" s="238"/>
+      <c r="C39" s="238"/>
+      <c r="D39" s="238"/>
+      <c r="E39" s="238"/>
+      <c r="F39" s="238"/>
+      <c r="G39" s="238"/>
+      <c r="H39" s="238"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="233" t="s">
+      <c r="B42" s="238" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="233"/>
-      <c r="D42" s="233"/>
-      <c r="E42" s="233"/>
-      <c r="F42" s="233"/>
-      <c r="G42" s="233"/>
-      <c r="H42" s="233"/>
+      <c r="C42" s="238"/>
+      <c r="D42" s="238"/>
+      <c r="E42" s="238"/>
+      <c r="F42" s="238"/>
+      <c r="G42" s="238"/>
+      <c r="H42" s="238"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14050,24 +14096,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="233"/>
-      <c r="C49" s="233"/>
-      <c r="D49" s="233"/>
-      <c r="E49" s="233"/>
-      <c r="F49" s="233"/>
-      <c r="G49" s="233"/>
-      <c r="H49" s="233"/>
+      <c r="B49" s="238"/>
+      <c r="C49" s="238"/>
+      <c r="D49" s="238"/>
+      <c r="E49" s="238"/>
+      <c r="F49" s="238"/>
+      <c r="G49" s="238"/>
+      <c r="H49" s="238"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="233" t="s">
+      <c r="B52" s="238" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="233"/>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="233"/>
-      <c r="H52" s="233"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="238"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="238"/>
+      <c r="H52" s="238"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14205,13 +14251,13 @@
       </c>
     </row>
     <row r="69" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="233"/>
-      <c r="C69" s="233"/>
-      <c r="D69" s="233"/>
-      <c r="E69" s="233"/>
-      <c r="F69" s="233"/>
-      <c r="G69" s="233"/>
-      <c r="H69" s="233"/>
+      <c r="B69" s="238"/>
+      <c r="C69" s="238"/>
+      <c r="D69" s="238"/>
+      <c r="E69" s="238"/>
+      <c r="F69" s="238"/>
+      <c r="G69" s="238"/>
+      <c r="H69" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14296,36 +14342,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="233" t="s">
+      <c r="S2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233" t="s">
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14336,32 +14382,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="240" t="s">
+      <c r="S4" s="245" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="241"/>
-      <c r="U4" s="241"/>
-      <c r="V4" s="241"/>
-      <c r="W4" s="241"/>
-      <c r="X4" s="241"/>
-      <c r="Y4" s="241"/>
-      <c r="Z4" s="241"/>
-      <c r="AA4" s="241"/>
-      <c r="AB4" s="241"/>
-      <c r="AC4" s="241"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15045,33 +15091,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="239" t="s">
+      <c r="C13" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
+      <c r="D13" s="244"/>
+      <c r="E13" s="244"/>
+      <c r="F13" s="244"/>
+      <c r="G13" s="244"/>
+      <c r="H13" s="244"/>
+      <c r="I13" s="244"/>
+      <c r="J13" s="244"/>
+      <c r="K13" s="244"/>
+      <c r="L13" s="244"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="240" t="s">
+      <c r="S13" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="T13" s="241"/>
-      <c r="U13" s="241"/>
-      <c r="V13" s="241"/>
-      <c r="W13" s="241"/>
-      <c r="X13" s="241"/>
-      <c r="Y13" s="241"/>
-      <c r="Z13" s="241"/>
-      <c r="AA13" s="241"/>
-      <c r="AB13" s="241"/>
-      <c r="AC13" s="241"/>
+      <c r="T13" s="246"/>
+      <c r="U13" s="246"/>
+      <c r="V13" s="246"/>
+      <c r="W13" s="246"/>
+      <c r="X13" s="246"/>
+      <c r="Y13" s="246"/>
+      <c r="Z13" s="246"/>
+      <c r="AA13" s="246"/>
+      <c r="AB13" s="246"/>
+      <c r="AC13" s="246"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15695,35 +15741,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="P2" s="233" t="s">
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="P2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233" t="s">
+      <c r="Q2" s="238"/>
+      <c r="R2" s="238"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15732,31 +15778,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="P4" s="241" t="s">
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="P4" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="241"/>
-      <c r="R4" s="241"/>
-      <c r="S4" s="241"/>
-      <c r="T4" s="241"/>
-      <c r="U4" s="241"/>
-      <c r="V4" s="241"/>
-      <c r="W4" s="241"/>
-      <c r="X4" s="241"/>
-      <c r="Y4" s="241"/>
-      <c r="Z4" s="241"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15951,32 +15997,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="239" t="s">
+      <c r="C9" s="244" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="239"/>
-      <c r="E9" s="239"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="239"/>
-      <c r="L9" s="239"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="241" t="s">
+      <c r="P9" s="246" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="241"/>
-      <c r="R9" s="241"/>
-      <c r="S9" s="241"/>
-      <c r="T9" s="241"/>
-      <c r="U9" s="241"/>
-      <c r="V9" s="241"/>
-      <c r="W9" s="241"/>
-      <c r="X9" s="241"/>
-      <c r="Y9" s="241"/>
-      <c r="Z9" s="241"/>
+      <c r="Q9" s="246"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="246"/>
+      <c r="U9" s="246"/>
+      <c r="V9" s="246"/>
+      <c r="W9" s="246"/>
+      <c r="X9" s="246"/>
+      <c r="Y9" s="246"/>
+      <c r="Z9" s="246"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16452,31 +16498,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="239" t="s">
+      <c r="C17" s="244" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="239"/>
-      <c r="E17" s="239"/>
-      <c r="F17" s="239"/>
-      <c r="G17" s="239"/>
-      <c r="H17" s="239"/>
-      <c r="I17" s="239"/>
-      <c r="J17" s="239"/>
-      <c r="K17" s="239"/>
-      <c r="L17" s="239"/>
-      <c r="P17" s="241" t="s">
+      <c r="D17" s="244"/>
+      <c r="E17" s="244"/>
+      <c r="F17" s="244"/>
+      <c r="G17" s="244"/>
+      <c r="H17" s="244"/>
+      <c r="I17" s="244"/>
+      <c r="J17" s="244"/>
+      <c r="K17" s="244"/>
+      <c r="L17" s="244"/>
+      <c r="P17" s="246" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="241"/>
-      <c r="R17" s="241"/>
-      <c r="S17" s="241"/>
-      <c r="T17" s="241"/>
-      <c r="U17" s="241"/>
-      <c r="V17" s="241"/>
-      <c r="W17" s="241"/>
-      <c r="X17" s="241"/>
-      <c r="Y17" s="241"/>
-      <c r="Z17" s="241"/>
+      <c r="Q17" s="246"/>
+      <c r="R17" s="246"/>
+      <c r="S17" s="246"/>
+      <c r="T17" s="246"/>
+      <c r="U17" s="246"/>
+      <c r="V17" s="246"/>
+      <c r="W17" s="246"/>
+      <c r="X17" s="246"/>
+      <c r="Y17" s="246"/>
+      <c r="Z17" s="246"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16954,60 +17000,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="244"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
-      <c r="W3" s="244"/>
-      <c r="X3" s="244"/>
-      <c r="Y3" s="244"/>
-      <c r="Z3" s="244"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
+      <c r="P3" s="249"/>
+      <c r="Q3" s="249"/>
+      <c r="R3" s="249"/>
+      <c r="S3" s="249"/>
+      <c r="T3" s="249"/>
+      <c r="U3" s="249"/>
+      <c r="V3" s="249"/>
+      <c r="W3" s="249"/>
+      <c r="X3" s="249"/>
+      <c r="Y3" s="249"/>
+      <c r="Z3" s="249"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="244"/>
-      <c r="T5" s="244"/>
-      <c r="U5" s="244"/>
-      <c r="V5" s="244"/>
-      <c r="W5" s="244"/>
-      <c r="X5" s="244"/>
-      <c r="Y5" s="244"/>
-      <c r="Z5" s="244"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="P5" s="249"/>
+      <c r="Q5" s="249"/>
+      <c r="R5" s="249"/>
+      <c r="S5" s="249"/>
+      <c r="T5" s="249"/>
+      <c r="U5" s="249"/>
+      <c r="V5" s="249"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="249"/>
+      <c r="Y5" s="249"/>
+      <c r="Z5" s="249"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17193,30 +17239,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="239" t="s">
+      <c r="C11" s="244" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="239"/>
-      <c r="E11" s="239"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
+      <c r="D11" s="244"/>
+      <c r="E11" s="244"/>
+      <c r="F11" s="244"/>
+      <c r="G11" s="244"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="244"/>
+      <c r="J11" s="244"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="244"/>
-      <c r="Q11" s="244"/>
-      <c r="R11" s="244"/>
-      <c r="S11" s="244"/>
-      <c r="T11" s="244"/>
-      <c r="U11" s="244"/>
-      <c r="V11" s="244"/>
-      <c r="W11" s="244"/>
-      <c r="X11" s="244"/>
-      <c r="Y11" s="244"/>
-      <c r="Z11" s="244"/>
+      <c r="P11" s="249"/>
+      <c r="Q11" s="249"/>
+      <c r="R11" s="249"/>
+      <c r="S11" s="249"/>
+      <c r="T11" s="249"/>
+      <c r="U11" s="249"/>
+      <c r="V11" s="249"/>
+      <c r="W11" s="249"/>
+      <c r="X11" s="249"/>
+      <c r="Y11" s="249"/>
+      <c r="Z11" s="249"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17458,18 +17504,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="244" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+      <c r="K18" s="244"/>
+      <c r="L18" s="244"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17682,23 +17728,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="244"/>
-      <c r="C25" s="244"/>
+      <c r="B25" s="249"/>
+      <c r="C25" s="249"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="239" t="s">
+      <c r="C26" s="244" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
+      <c r="D26" s="244"/>
+      <c r="E26" s="244"/>
+      <c r="F26" s="244"/>
+      <c r="G26" s="244"/>
+      <c r="H26" s="244"/>
+      <c r="I26" s="244"/>
+      <c r="J26" s="244"/>
+      <c r="K26" s="244"/>
+      <c r="L26" s="244"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17890,18 +17936,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="239" t="s">
+      <c r="C33" s="244" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="239"/>
-      <c r="E33" s="239"/>
-      <c r="F33" s="239"/>
-      <c r="G33" s="239"/>
-      <c r="H33" s="239"/>
-      <c r="I33" s="239"/>
-      <c r="J33" s="239"/>
-      <c r="K33" s="239"/>
-      <c r="L33" s="239"/>
+      <c r="D33" s="244"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="244"/>
+      <c r="G33" s="244"/>
+      <c r="H33" s="244"/>
+      <c r="I33" s="244"/>
+      <c r="J33" s="244"/>
+      <c r="K33" s="244"/>
+      <c r="L33" s="244"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18085,18 +18131,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="239" t="s">
+      <c r="C40" s="244" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="239"/>
-      <c r="E40" s="239"/>
-      <c r="F40" s="239"/>
-      <c r="G40" s="239"/>
-      <c r="H40" s="239"/>
-      <c r="I40" s="239"/>
-      <c r="J40" s="239"/>
-      <c r="K40" s="239"/>
-      <c r="L40" s="239"/>
+      <c r="D40" s="244"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="244"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="244"/>
+      <c r="L40" s="244"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18410,60 +18456,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="S2" s="244"/>
-      <c r="T2" s="244"/>
-      <c r="U2" s="244"/>
-      <c r="V2" s="244"/>
-      <c r="W2" s="244"/>
-      <c r="X2" s="244"/>
-      <c r="Y2" s="244"/>
-      <c r="Z2" s="244"/>
-      <c r="AA2" s="244"/>
-      <c r="AB2" s="244"/>
-      <c r="AC2" s="244"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="244" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="S4" s="244"/>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
-      <c r="AA4" s="244"/>
-      <c r="AB4" s="244"/>
-      <c r="AC4" s="244"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="S4" s="249"/>
+      <c r="T4" s="249"/>
+      <c r="U4" s="249"/>
+      <c r="V4" s="249"/>
+      <c r="W4" s="249"/>
+      <c r="X4" s="249"/>
+      <c r="Y4" s="249"/>
+      <c r="Z4" s="249"/>
+      <c r="AA4" s="249"/>
+      <c r="AB4" s="249"/>
+      <c r="AC4" s="249"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18826,18 +18872,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="239" t="s">
+      <c r="C13" s="244" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
+      <c r="D13" s="244"/>
+      <c r="E13" s="244"/>
+      <c r="F13" s="244"/>
+      <c r="G13" s="244"/>
+      <c r="H13" s="244"/>
+      <c r="I13" s="244"/>
+      <c r="J13" s="244"/>
+      <c r="K13" s="244"/>
+      <c r="L13" s="244"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18930,18 +18976,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="244" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+      <c r="K18" s="244"/>
+      <c r="L18" s="244"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19133,18 +19179,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="239" t="s">
+      <c r="C25" s="244" t="s">
         <v>259</v>
       </c>
-      <c r="D25" s="239"/>
-      <c r="E25" s="239"/>
-      <c r="F25" s="239"/>
-      <c r="G25" s="239"/>
-      <c r="H25" s="239"/>
-      <c r="I25" s="239"/>
-      <c r="J25" s="239"/>
-      <c r="K25" s="239"/>
-      <c r="L25" s="239"/>
+      <c r="D25" s="244"/>
+      <c r="E25" s="244"/>
+      <c r="F25" s="244"/>
+      <c r="G25" s="244"/>
+      <c r="H25" s="244"/>
+      <c r="I25" s="244"/>
+      <c r="J25" s="244"/>
+      <c r="K25" s="244"/>
+      <c r="L25" s="244"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19282,18 +19328,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="239" t="s">
+      <c r="C31" s="244" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="239"/>
-      <c r="E31" s="239"/>
-      <c r="F31" s="239"/>
-      <c r="G31" s="239"/>
-      <c r="H31" s="239"/>
-      <c r="I31" s="239"/>
-      <c r="J31" s="239"/>
-      <c r="K31" s="239"/>
-      <c r="L31" s="239"/>
+      <c r="D31" s="244"/>
+      <c r="E31" s="244"/>
+      <c r="F31" s="244"/>
+      <c r="G31" s="244"/>
+      <c r="H31" s="244"/>
+      <c r="I31" s="244"/>
+      <c r="J31" s="244"/>
+      <c r="K31" s="244"/>
+      <c r="L31" s="244"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19504,10 +19550,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="238"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19551,7 +19597,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19560,7 +19606,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6351</v>
+        <v>1.6361000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19592,10 +19638,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="238" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="233"/>
+      <c r="C15" s="238"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19630,7 +19676,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11896949999999999</v>
+        <v>0.11931449999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19639,7 +19685,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1131500397034752</v>
+        <v>0.1134706252083144</v>
       </c>
     </row>
   </sheetData>
@@ -19684,60 +19730,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="244"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
-      <c r="W3" s="244"/>
-      <c r="X3" s="244"/>
-      <c r="Y3" s="244"/>
-      <c r="Z3" s="244"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
+      <c r="P3" s="249"/>
+      <c r="Q3" s="249"/>
+      <c r="R3" s="249"/>
+      <c r="S3" s="249"/>
+      <c r="T3" s="249"/>
+      <c r="U3" s="249"/>
+      <c r="V3" s="249"/>
+      <c r="W3" s="249"/>
+      <c r="X3" s="249"/>
+      <c r="Y3" s="249"/>
+      <c r="Z3" s="249"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="244" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="244"/>
-      <c r="T5" s="244"/>
-      <c r="U5" s="244"/>
-      <c r="V5" s="244"/>
-      <c r="W5" s="244"/>
-      <c r="X5" s="244"/>
-      <c r="Y5" s="244"/>
-      <c r="Z5" s="244"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="P5" s="249"/>
+      <c r="Q5" s="249"/>
+      <c r="R5" s="249"/>
+      <c r="S5" s="249"/>
+      <c r="T5" s="249"/>
+      <c r="U5" s="249"/>
+      <c r="V5" s="249"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="249"/>
+      <c r="Y5" s="249"/>
+      <c r="Z5" s="249"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19890,7 +19936,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>149427.49680514541</v>
+        <v>148886.02567405149</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19944,23 +19990,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>8582.587431429949</v>
+        <v>8580.1163710694509</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7618.600525327136</v>
+        <v>7614.2141297887729</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7158.2896076812713</v>
+        <v>7152.1084390597553</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>6959.2679024986746</v>
+        <v>6951.2566374632397</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7519.0095673746537</v>
+        <v>7508.1915997040569</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19979,14 +20025,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>87430.304427363517</v>
+        <v>86988.154221537072</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="233" t="s">
+      <c r="B13" s="238" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="233"/>
+      <c r="C13" s="238"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20002,14 +20048,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1131500397034752</v>
+        <v>0.1134706252083144</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="238" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="233"/>
+      <c r="C18" s="238"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20017,7 +20063,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37837.755034311682</v>
+        <v>37805.887177085278</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20026,7 +20072,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>87430.304427363517</v>
+        <v>86988.154221537072</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20035,7 +20081,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>125268.05946167521</v>
+        <v>124794.04139862236</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20062,7 +20108,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119797.05946167521</v>
+        <v>119323.04139862236</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20080,7 +20126,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>113.01609383176907</v>
+        <v>112.56890697983242</v>
       </c>
     </row>
   </sheetData>
@@ -20123,37 +20169,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="244" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20342,18 +20388,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="239" t="s">
+      <c r="C10" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="239"/>
-      <c r="L10" s="239"/>
+      <c r="D10" s="244"/>
+      <c r="E10" s="244"/>
+      <c r="F10" s="244"/>
+      <c r="G10" s="244"/>
+      <c r="H10" s="244"/>
+      <c r="I10" s="244"/>
+      <c r="J10" s="244"/>
+      <c r="K10" s="244"/>
+      <c r="L10" s="244"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20547,18 +20593,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="239" t="s">
+      <c r="C16" s="244" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="239"/>
-      <c r="E16" s="239"/>
-      <c r="F16" s="239"/>
-      <c r="G16" s="239"/>
-      <c r="H16" s="239"/>
-      <c r="I16" s="239"/>
-      <c r="J16" s="239"/>
-      <c r="K16" s="239"/>
-      <c r="L16" s="239"/>
+      <c r="D16" s="244"/>
+      <c r="E16" s="244"/>
+      <c r="F16" s="244"/>
+      <c r="G16" s="244"/>
+      <c r="H16" s="244"/>
+      <c r="I16" s="244"/>
+      <c r="J16" s="244"/>
+      <c r="K16" s="244"/>
+      <c r="L16" s="244"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20692,18 +20738,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="239" t="s">
+      <c r="C21" s="244" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="239"/>
-      <c r="E21" s="239"/>
-      <c r="F21" s="239"/>
-      <c r="G21" s="239"/>
-      <c r="H21" s="239"/>
-      <c r="I21" s="239"/>
-      <c r="J21" s="239"/>
-      <c r="K21" s="239"/>
-      <c r="L21" s="239"/>
+      <c r="D21" s="244"/>
+      <c r="E21" s="244"/>
+      <c r="F21" s="244"/>
+      <c r="G21" s="244"/>
+      <c r="H21" s="244"/>
+      <c r="I21" s="244"/>
+      <c r="J21" s="244"/>
+      <c r="K21" s="244"/>
+      <c r="L21" s="244"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -20787,18 +20833,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="239" t="s">
+      <c r="C26" s="244" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
+      <c r="D26" s="244"/>
+      <c r="E26" s="244"/>
+      <c r="F26" s="244"/>
+      <c r="G26" s="244"/>
+      <c r="H26" s="244"/>
+      <c r="I26" s="244"/>
+      <c r="J26" s="244"/>
+      <c r="K26" s="244"/>
+      <c r="L26" s="244"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21068,10 +21114,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="238" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="233"/>
+      <c r="C37" s="238"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21089,7 +21135,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1131500397034752</v>
+        <v>0.1134706252083144</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21115,7 +21161,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>190082.52142953235</v>
+        <v>189802.34157204349</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21142,7 +21188,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>184611.52142953235</v>
+        <v>184331.34157204349</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21160,14 +21206,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>174.16181266937014</v>
+        <v>173.89749204909762</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="233" t="s">
+      <c r="B49" s="238" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="233"/>
+      <c r="C49" s="238"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21183,8 +21229,8 @@
         <v>355</v>
       </c>
       <c r="C51" s="135">
-        <f>Overview!C29</f>
-        <v>0.12</v>
+        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.11931449999999999</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21218,15 +21264,15 @@
         <v>201</v>
       </c>
       <c r="C55" s="142">
-        <f>C54/(1+C51)^5</f>
-        <v>190.70675093537938</v>
+        <f ca="1">C54/(1+C51)^5</f>
+        <v>191.29143781629537</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="233" t="s">
+      <c r="B57" s="238" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="233"/>
+      <c r="C57" s="238"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21243,7 +21289,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1131500397034752</v>
+        <v>0.1134706252083144</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21269,7 +21315,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>183319.23918436636</v>
+        <v>183048.78999260144</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21296,7 +21342,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>177848.23918436636</v>
+        <v>177577.78999260144</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21314,7 +21360,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>167.78135772110033</v>
+        <v>167.52621697415231</v>
       </c>
     </row>
   </sheetData>
@@ -21366,10 +21412,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="238" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="238"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21378,7 +21424,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>113.01609383176907</v>
+        <v>112.56890697983242</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21387,7 +21433,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>174.16181266937014</v>
+        <v>173.89749204909762</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21395,8 +21441,8 @@
         <v>210</v>
       </c>
       <c r="C7" s="133">
-        <f>Multiples!C55</f>
-        <v>190.70675093537938</v>
+        <f ca="1">Multiples!C55</f>
+        <v>191.29143781629537</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21405,7 +21451,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>167.78135772110033</v>
+        <v>167.52621697415231</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21414,7 +21460,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>161.41650378940471</v>
+        <v>161.32101345484443</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21432,7 +21478,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.14666682285152929</v>
+        <v>-0.14717163536242103</v>
       </c>
     </row>
   </sheetData>
@@ -21465,6 +21511,477 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97514150-DB89-F74E-BBB8-9E97A5FA5872}">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" style="83" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="10.83203125" style="1"/>
+    <col min="13" max="14" width="9.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4"/>
+      <c r="B1" s="82" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4"/>
+      <c r="C2" s="238" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+    </row>
+    <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="86"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="244" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B5" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="12">
+        <f>Revenue!C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D5" s="12">
+        <f>Revenue!D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E5" s="12">
+        <f>Revenue!E5</f>
+        <v>2023</v>
+      </c>
+      <c r="F5" s="12">
+        <f>Revenue!F5</f>
+        <v>2024</v>
+      </c>
+      <c r="G5" s="12">
+        <f>Revenue!G5</f>
+        <v>2025</v>
+      </c>
+      <c r="H5" s="12">
+        <f>Revenue!H5</f>
+        <v>2026</v>
+      </c>
+      <c r="I5" s="12">
+        <f>Revenue!I5</f>
+        <v>2027</v>
+      </c>
+      <c r="J5" s="12">
+        <f>Revenue!J5</f>
+        <v>2028</v>
+      </c>
+      <c r="K5" s="12">
+        <f>Revenue!K5</f>
+        <v>2029</v>
+      </c>
+      <c r="L5" s="12">
+        <f>Revenue!L5</f>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B6" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="230">
+        <f>Statement!M26</f>
+        <v>7.87</v>
+      </c>
+      <c r="D6" s="230">
+        <f>Statement!N26</f>
+        <v>11.41</v>
+      </c>
+      <c r="E6" s="230">
+        <f>Statement!O26</f>
+        <v>6.52</v>
+      </c>
+      <c r="F6" s="230">
+        <f>Statement!P26</f>
+        <v>8.94</v>
+      </c>
+      <c r="G6" s="231">
+        <f>Statement!Q26</f>
+        <v>10.172850678733031</v>
+      </c>
+      <c r="H6" s="137"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="137"/>
+      <c r="K6" s="137"/>
+      <c r="L6" s="137"/>
+      <c r="N6" s="91"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B7" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C7" s="230">
+        <f>Statement!M82</f>
+        <v>2.66</v>
+      </c>
+      <c r="D7" s="230">
+        <f>Statement!N82</f>
+        <v>2.86</v>
+      </c>
+      <c r="E7" s="230">
+        <f>Statement!O82</f>
+        <v>3.1</v>
+      </c>
+      <c r="F7" s="230">
+        <f>Statement!P82</f>
+        <v>3.3</v>
+      </c>
+      <c r="G7" s="231">
+        <f>Statement!Q82</f>
+        <v>3.48</v>
+      </c>
+      <c r="H7" s="137"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="137"/>
+      <c r="L7" s="137"/>
+      <c r="N7" s="91"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="91"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C9" s="244" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
+      <c r="N9" s="91"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="12">
+        <f t="shared" ref="C10:L10" si="0">C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="F10" s="12">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="I10" s="12">
+        <f t="shared" si="0"/>
+        <v>2027</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="N10" s="91"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" s="137"/>
+      <c r="D11" s="95">
+        <f>(D6-C6)/C6</f>
+        <v>0.44980940279542564</v>
+      </c>
+      <c r="E11" s="95">
+        <f>(E6-D6)/D6</f>
+        <v>-0.4285714285714286</v>
+      </c>
+      <c r="F11" s="95">
+        <f>(F6-E6)/E6</f>
+        <v>0.37116564417177916</v>
+      </c>
+      <c r="G11" s="96">
+        <f>(G6-F6)/F6</f>
+        <v>0.13790276048467914</v>
+      </c>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="N11" s="91"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12" s="137"/>
+      <c r="D12" s="95">
+        <f>IF(C7=0,
+IF(D7=0,0,IF(D7&gt;0,1,-1)),
+(D7-C7)/ABS(C7)
+)</f>
+        <v>7.5187969924811929E-2</v>
+      </c>
+      <c r="E12" s="95">
+        <f>IF(D7=0,
+IF(E7=0,0,IF(E7&gt;0,1,-1)),
+(E7-D7)/ABS(D7)
+)</f>
+        <v>8.3916083916083989E-2</v>
+      </c>
+      <c r="F12" s="95">
+        <f>IF(E7=0,
+IF(F7=0,0,IF(F7&gt;0,1,-1)),
+(F7-E7)/ABS(E7)
+)</f>
+        <v>6.4516129032257979E-2</v>
+      </c>
+      <c r="G12" s="96">
+        <f>IF(F7=0,
+IF(G7=0,0,IF(G7&gt;0,1,-1)),
+(G7-F7)/ABS(F7)
+)</f>
+        <v>5.4545454545454598E-2</v>
+      </c>
+      <c r="H12" s="137"/>
+      <c r="I12" s="137"/>
+      <c r="J12" s="137"/>
+      <c r="K12" s="137"/>
+      <c r="L12" s="137"/>
+      <c r="N12" s="91"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="91"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C14" s="244" t="s">
+        <v>408</v>
+      </c>
+      <c r="D14" s="244"/>
+      <c r="E14" s="244"/>
+      <c r="F14" s="244"/>
+      <c r="G14" s="244"/>
+      <c r="H14" s="244"/>
+      <c r="I14" s="244"/>
+      <c r="J14" s="244"/>
+      <c r="K14" s="244"/>
+      <c r="L14" s="244"/>
+      <c r="N14" s="91"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B15" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="C15" s="12">
+        <f>C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" ref="D15:L15" si="1">D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E15" s="12">
+        <f t="shared" si="1"/>
+        <v>2023</v>
+      </c>
+      <c r="F15" s="12">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="G15" s="12">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="H15" s="12">
+        <f t="shared" si="1"/>
+        <v>2026</v>
+      </c>
+      <c r="I15" s="12">
+        <f t="shared" si="1"/>
+        <v>2027</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="1"/>
+        <v>2028</v>
+      </c>
+      <c r="K15" s="12">
+        <f t="shared" si="1"/>
+        <v>2029</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" si="1"/>
+        <v>2030</v>
+      </c>
+      <c r="N15" s="91"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C16" s="95">
+        <f>C7/C6</f>
+        <v>0.33799237611181704</v>
+      </c>
+      <c r="D16" s="95">
+        <f t="shared" ref="D16:G16" si="2">D7/D6</f>
+        <v>0.25065731814198072</v>
+      </c>
+      <c r="E16" s="95">
+        <f t="shared" si="2"/>
+        <v>0.47546012269938653</v>
+      </c>
+      <c r="F16" s="95">
+        <f t="shared" si="2"/>
+        <v>0.36912751677852351</v>
+      </c>
+      <c r="G16" s="96">
+        <f t="shared" si="2"/>
+        <v>0.34208700293568189</v>
+      </c>
+      <c r="H16" s="137"/>
+      <c r="I16" s="137"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="137"/>
+      <c r="L16" s="137"/>
+      <c r="N16" s="91"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="91"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="91"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N19" s="91"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="238" t="s">
+        <v>410</v>
+      </c>
+      <c r="C20" s="238"/>
+      <c r="N20" s="91"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C21" s="232">
+        <f>G7</f>
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C22" s="234">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23" s="39" t="s">
+        <v>413</v>
+      </c>
+      <c r="C23" s="233">
+        <f>C21*(1+C22)</f>
+        <v>3.6888000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C24" s="135">
+        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.11931449999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="39" t="s">
+        <v>414</v>
+      </c>
+      <c r="C25" s="234">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B26" s="141" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="142">
+        <f ca="1">C23/(C24-C25)</f>
+        <v>37.142612609437698</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C9:L9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0116CE1A-CCEC-514B-9208-A0DCC7740441}">
   <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -21497,60 +22014,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="244"/>
-      <c r="T3" s="244"/>
-      <c r="U3" s="244"/>
-      <c r="V3" s="244"/>
-      <c r="W3" s="244"/>
-      <c r="X3" s="244"/>
-      <c r="Y3" s="244"/>
-      <c r="Z3" s="244"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
+      <c r="P3" s="249"/>
+      <c r="Q3" s="249"/>
+      <c r="R3" s="249"/>
+      <c r="S3" s="249"/>
+      <c r="T3" s="249"/>
+      <c r="U3" s="249"/>
+      <c r="V3" s="249"/>
+      <c r="W3" s="249"/>
+      <c r="X3" s="249"/>
+      <c r="Y3" s="249"/>
+      <c r="Z3" s="249"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="244" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="244"/>
-      <c r="T5" s="244"/>
-      <c r="U5" s="244"/>
-      <c r="V5" s="244"/>
-      <c r="W5" s="244"/>
-      <c r="X5" s="244"/>
-      <c r="Y5" s="244"/>
-      <c r="Z5" s="244"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="P5" s="249"/>
+      <c r="Q5" s="249"/>
+      <c r="R5" s="249"/>
+      <c r="S5" s="249"/>
+      <c r="T5" s="249"/>
+      <c r="U5" s="249"/>
+      <c r="V5" s="249"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="249"/>
+      <c r="Y5" s="249"/>
+      <c r="Z5" s="249"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21685,7 +22202,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>296775.39752349874</v>
+        <v>295699.99096437363</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21739,23 +22256,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12362.019147161202</v>
+        <v>12358.459929648498</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12960.046561719655</v>
+        <v>12952.584838240871</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13587.004265440912</v>
+        <v>13575.271914693909</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14244.291795554649</v>
+        <v>14227.894266616973</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14933.376393572596</v>
+        <v>14911.891012873059</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21774,15 +22291,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>173643.83334257829</v>
+        <v>172765.68637562246</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="245" t="s">
+      <c r="B14" s="250" t="s">
         <v>215</v>
       </c>
-      <c r="C14" s="246"/>
+      <c r="C14" s="251"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -21799,7 +22316,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>224.1551911821891</v>
+        <v>223.26450506422748</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -21809,20 +22326,20 @@
       <c r="C17" s="158">
         <v>0.16700000000000001</v>
       </c>
-      <c r="E17" s="247" t="s">
+      <c r="E17" s="252" t="s">
         <v>218</v>
       </c>
-      <c r="F17" s="247"/>
-      <c r="G17" s="247"/>
-      <c r="H17" s="247"/>
-      <c r="I17" s="247"/>
+      <c r="F17" s="252"/>
+      <c r="G17" s="252"/>
+      <c r="H17" s="252"/>
+      <c r="I17" s="252"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="245" t="s">
+      <c r="B19" s="250" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="246"/>
+      <c r="C19" s="251"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -21838,7 +22355,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1131500397034752</v>
+        <v>0.1134706252083144</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -21888,10 +22405,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="245" t="s">
+      <c r="B28" s="250" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="246"/>
+      <c r="C28" s="251"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -21899,7 +22416,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>68086.738163449016</v>
+        <v>68026.101962073313</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -21908,7 +22425,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>173643.83334257829</v>
+        <v>172765.68637562246</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -21917,7 +22434,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>241730.57150602731</v>
+        <v>240791.78833769576</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -21944,7 +22461,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>236259.57150602731</v>
+        <v>235320.78833769576</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -21962,22 +22479,22 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>224.1551911821891</v>
+        <v>223.26450506422748</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="239" t="s">
+      <c r="C39" s="244" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="239"/>
-      <c r="E39" s="239"/>
-      <c r="F39" s="239"/>
-      <c r="G39" s="239"/>
-      <c r="H39" s="239"/>
-      <c r="I39" s="239"/>
-      <c r="J39" s="239"/>
-      <c r="K39" s="239"/>
-      <c r="L39" s="239"/>
+      <c r="D39" s="244"/>
+      <c r="E39" s="244"/>
+      <c r="F39" s="244"/>
+      <c r="G39" s="244"/>
+      <c r="H39" s="244"/>
+      <c r="I39" s="244"/>
+      <c r="J39" s="244"/>
+      <c r="K39" s="244"/>
+      <c r="L39" s="244"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -32857,15 +33374,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="238" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="233"/>
-      <c r="E4" s="233" t="s">
+      <c r="C4" s="238"/>
+      <c r="E4" s="238" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33002,14 +33519,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="238" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="233"/>
-      <c r="E15" s="233" t="s">
+      <c r="C15" s="238"/>
+      <c r="E15" s="238" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="233"/>
+      <c r="F15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33060,14 +33577,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="233" t="s">
+      <c r="B21" s="238" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="233"/>
-      <c r="E21" s="233" t="s">
+      <c r="C21" s="238"/>
+      <c r="E21" s="238" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="233"/>
+      <c r="F21" s="238"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33136,14 +33653,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="233" t="s">
+      <c r="B29" s="238" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="233"/>
-      <c r="E29" s="233" t="s">
+      <c r="C29" s="238"/>
+      <c r="E29" s="238" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="233"/>
+      <c r="F29" s="238"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33219,14 +33736,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="238" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="233"/>
-      <c r="E37" s="233" t="s">
+      <c r="C37" s="238"/>
+      <c r="E37" s="238" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="233"/>
+      <c r="F37" s="238"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33295,14 +33812,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="233" t="s">
+      <c r="B45" s="238" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="233"/>
-      <c r="E45" s="233" t="s">
+      <c r="C45" s="238"/>
+      <c r="E45" s="238" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="233"/>
+      <c r="F45" s="238"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33339,14 +33856,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="233" t="s">
+      <c r="B51" s="238" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="233"/>
-      <c r="E51" s="233" t="s">
+      <c r="C51" s="238"/>
+      <c r="E51" s="238" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="233"/>
+      <c r="F51" s="238"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35381,14 +35898,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="241" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35455,19 +35972,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="234">
+      <c r="C7" s="239">
         <f>Statement!AA89</f>
         <v>-0.13491674828599412</v>
       </c>
-      <c r="D7" s="235"/>
-      <c r="F7" s="234">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-3.4611531104836508E-2</v>
       </c>
-      <c r="G7" s="235"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35494,19 +36011,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="234">
+      <c r="C9" s="239">
         <f>Statement!AA90</f>
         <v>-0.11997126436781609</v>
       </c>
-      <c r="D9" s="235"/>
-      <c r="F9" s="234">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>-7.4944298156775372E-3</v>
       </c>
-      <c r="G9" s="235"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35533,19 +36050,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="234">
+      <c r="C11" s="239">
         <f>Statement!AA91</f>
         <v>-0.1473668461998803</v>
       </c>
-      <c r="D11" s="235"/>
-      <c r="F11" s="234">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-5.6769281694803046E-2</v>
       </c>
-      <c r="G11" s="235"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35572,19 +36089,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="234">
+      <c r="C13" s="239">
         <f>Statement!AA94</f>
         <v>2.1699819168173599E-2</v>
       </c>
-      <c r="D13" s="235"/>
-      <c r="F13" s="234">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.16016427104722791</v>
       </c>
-      <c r="G13" s="235"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -35611,19 +36128,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="234">
+      <c r="C15" s="239">
         <f>Statement!AA95</f>
         <v>-0.31402257872846107</v>
       </c>
-      <c r="D15" s="235"/>
-      <c r="F15" s="234">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.25993589743589746</v>
       </c>
-      <c r="G15" s="235"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35650,19 +36167,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="234">
+      <c r="C17" s="239">
         <f>Statement!AA97</f>
         <v>-0.35685752330226367</v>
       </c>
-      <c r="D17" s="235"/>
-      <c r="F17" s="234">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.31294452347083929</v>
       </c>
-      <c r="G17" s="235"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -35689,22 +36206,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="234">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-6.4874884151992582E-3</v>
       </c>
-      <c r="D19" s="235"/>
-      <c r="F19" s="234">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.8565022421524667E-2</v>
       </c>
-      <c r="G19" s="235"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35731,22 +36248,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="234">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.35171265972296784</v>
       </c>
-      <c r="D21" s="235"/>
-      <c r="F21" s="234">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.28482587064676618</v>
       </c>
-      <c r="G21" s="235"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35794,22 +36311,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="234">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.23006134969325154</v>
       </c>
-      <c r="D25" s="235"/>
-      <c r="F25" s="234">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.13061047770241016</v>
       </c>
-      <c r="G25" s="235"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -35836,22 +36353,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="234">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.20435967302452315</v>
       </c>
-      <c r="D27" s="235"/>
-      <c r="F27" s="234">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.38269030239833157</v>
       </c>
-      <c r="G27" s="235"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -35878,22 +36395,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="234">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.2511848341232227E-2</v>
       </c>
-      <c r="D29" s="235"/>
-      <c r="F29" s="234">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>9.1714104996837451E-2</v>
       </c>
-      <c r="G29" s="235"/>
+      <c r="G29" s="240"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35920,22 +36437,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="234">
+      <c r="C31" s="239">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.1448223876378027</v>
       </c>
-      <c r="D31" s="235"/>
-      <c r="F31" s="234">
+      <c r="D31" s="240"/>
+      <c r="F31" s="239">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-4.1503854683704718E-2</v>
       </c>
-      <c r="G31" s="235"/>
+      <c r="G31" s="240"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -35962,22 +36479,22 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="234">
+      <c r="C33" s="239">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.13190954773869346</v>
       </c>
-      <c r="D33" s="235"/>
-      <c r="F33" s="234">
+      <c r="D33" s="240"/>
+      <c r="F33" s="239">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>4.7763457164518575E-2</v>
       </c>
-      <c r="G33" s="235"/>
+      <c r="G33" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FF68B2-73D2-B640-B0E8-F96D499AADF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA1C443-7810-1B42-A5E4-C9490AECE6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2319,6 +2319,9 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2328,15 +2331,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2344,6 +2338,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12730,11 +12730,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6361000000000001</v>
-    <v>-1.95</v>
-    <v>-1.0204E-2</v>
-    <v>-0.26</v>
-    <v>-1.374E-3</v>
+    <v>1.6363000000000001</v>
+    <v>-7.37</v>
+    <v>-4.1409000000000001E-2</v>
+    <v>-0.89280000000000004</v>
+    <v>-5.2329999999999998E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12742,26 +12742,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>190.19</v>
+    <v>173.96</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999990844532</v>
+    <v>46219.999902441406</v>
     <v>4</v>
-    <v>185.72</v>
-    <v>199374640000</v>
+    <v>168.99</v>
+    <v>179822940000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>187.50800000000001</v>
-    <v>20.787700000000001</v>
-    <v>191.11</v>
-    <v>189.16</v>
-    <v>188.9</v>
+    <v>173.08</v>
+    <v>18.5579</v>
+    <v>177.98</v>
+    <v>170.61</v>
+    <v>169.71719999999999</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>7063957</v>
-    <v>21168579</v>
+    <v>15951600</v>
+    <v>19871783</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -12785,16 +12785,16 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.3</v>
-    <v>6.6090000000000003E-3</v>
+    <v>0.24</v>
+    <v>5.2810000000000001E-3</v>
     <v>US</v>
-    <v>45.71</v>
+    <v>45.96</v>
     <v>Index</v>
     <v>7</v>
-    <v>45.39</v>
+    <v>45.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.41</v>
-    <v>45.39</v>
+    <v>45.82</v>
+    <v>45.45</v>
     <v>45.69</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
@@ -13626,18 +13626,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="235" t="s">
+      <c r="B2" s="236" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="236"/>
-      <c r="E2" s="235" t="s">
+      <c r="C2" s="237"/>
+      <c r="E2" s="236" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="236"/>
-      <c r="H2" s="235" t="s">
+      <c r="F2" s="237"/>
+      <c r="H2" s="236" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="236"/>
+      <c r="I2" s="237"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>200509.6</v>
+        <v>180846.6</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>112.56890697983242</v>
+        <v>113.37700576422391</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>205980.6</v>
+        <v>186317.6</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>173.89749204909762</v>
+        <v>174.37406444931298</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>189.16</v>
+        <v>170.61</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13708,7 +13708,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>191.29143781629537</v>
+        <v>191.28374747809156</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13717,14 +13717,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>188.9</v>
+        <v>169.71719999999999</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>20.084212900677784</v>
+        <v>18.114651950648323</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>167.52621697415231</v>
+        <v>167.98623798212512</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13741,14 +13741,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.95</v>
+        <v>-7.37</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>4.5904795227201367</v>
+        <v>4.1403135513389859</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>161.32101345484443</v>
+        <v>161.75526391843837</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13765,14 +13765,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.26</v>
+        <v>-0.89280000000000004</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.7035154426521224E-2</v>
+        <v>5.2149169517148784E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.14717163536242103</v>
+        <v>-5.1900451799786876E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13789,14 +13789,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.0204E-2</v>
+        <v>-4.1409000000000001E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>4.9790350507898318E-2</v>
+        <v>5.5203931200246442E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13805,21 +13805,21 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.374E-3</v>
+        <v>-5.2329999999999998E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>5.3538583688761035E-2</v>
+        <v>5.9359700431194172E-2</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>415</v>
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>37.142612609437698</v>
+        <v>37.139247005995564</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.8820046521463313E-2</v>
+        <v>2.0866303264755876E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6361000000000001</v>
+        <v>1.6363000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13876,7 +13876,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>21168579</v>
+        <v>19871783</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13892,7 +13892,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-2.7285476605608906E-2</v>
+        <v>-3.0252158459158202E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13905,10 +13905,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="238" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="237"/>
+      <c r="C17" s="238"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -13981,14 +13981,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="238" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="237"/>
-      <c r="E25" s="235" t="s">
+      <c r="C25" s="238"/>
+      <c r="E25" s="236" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="236"/>
+      <c r="F25" s="237"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14037,15 +14037,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="238" t="s">
+      <c r="B33" s="235" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="238"/>
-      <c r="D33" s="238"/>
-      <c r="E33" s="238"/>
-      <c r="F33" s="238"/>
-      <c r="G33" s="238"/>
-      <c r="H33" s="238"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14064,24 +14064,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="238"/>
-      <c r="C39" s="238"/>
-      <c r="D39" s="238"/>
-      <c r="E39" s="238"/>
-      <c r="F39" s="238"/>
-      <c r="G39" s="238"/>
-      <c r="H39" s="238"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="238" t="s">
+      <c r="B42" s="235" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="238"/>
-      <c r="D42" s="238"/>
-      <c r="E42" s="238"/>
-      <c r="F42" s="238"/>
-      <c r="G42" s="238"/>
-      <c r="H42" s="238"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14096,24 +14096,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="238"/>
-      <c r="C49" s="238"/>
-      <c r="D49" s="238"/>
-      <c r="E49" s="238"/>
-      <c r="F49" s="238"/>
-      <c r="G49" s="238"/>
-      <c r="H49" s="238"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="235"/>
+      <c r="E49" s="235"/>
+      <c r="F49" s="235"/>
+      <c r="G49" s="235"/>
+      <c r="H49" s="235"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="238" t="s">
+      <c r="B52" s="235" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="238"/>
-      <c r="D52" s="238"/>
-      <c r="E52" s="238"/>
-      <c r="F52" s="238"/>
-      <c r="G52" s="238"/>
-      <c r="H52" s="238"/>
+      <c r="C52" s="235"/>
+      <c r="D52" s="235"/>
+      <c r="E52" s="235"/>
+      <c r="F52" s="235"/>
+      <c r="G52" s="235"/>
+      <c r="H52" s="235"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14251,28 +14251,28 @@
       </c>
     </row>
     <row r="69" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="238"/>
-      <c r="C69" s="238"/>
-      <c r="D69" s="238"/>
-      <c r="E69" s="238"/>
-      <c r="F69" s="238"/>
-      <c r="G69" s="238"/>
-      <c r="H69" s="238"/>
+      <c r="B69" s="235"/>
+      <c r="C69" s="235"/>
+      <c r="D69" s="235"/>
+      <c r="E69" s="235"/>
+      <c r="F69" s="235"/>
+      <c r="G69" s="235"/>
+      <c r="H69" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14342,36 +14342,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="238" t="s">
+      <c r="S2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="238" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15741,35 +15741,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="P2" s="238" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -17000,20 +17000,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="247"/>
       <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -18406,12 +18406,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18419,6 +18413,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18456,20 +18456,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="S2" s="249"/>
       <c r="T2" s="249"/>
       <c r="U2" s="249"/>
@@ -19478,16 +19478,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19550,10 +19550,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="235" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19570,7 +19570,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>189.16</v>
+        <v>170.61</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19579,7 +19579,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>200509.6</v>
+        <v>180846.6</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19606,7 +19606,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6361000000000001</v>
+        <v>1.6363000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19638,10 +19638,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="238"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.0766652640008601E-2</v>
+        <v>7.7861843413561116E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92923334735999141</v>
+        <v>0.92213815658643894</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19676,7 +19676,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11931449999999999</v>
+        <v>0.1193235</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19685,7 +19685,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1134706252083144</v>
+        <v>0.11289300714523912</v>
       </c>
     </row>
   </sheetData>
@@ -19730,20 +19730,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="247"/>
       <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -19936,7 +19936,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>148886.02567405149</v>
+        <v>149864.47959845426</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19990,23 +19990,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>8580.1163710694509</v>
+        <v>8584.5696564862847</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7614.2141297887729</v>
+        <v>7622.120099097081</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7152.1084390597553</v>
+        <v>7163.2505656236099</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>6951.2566374632397</v>
+        <v>6965.6993499456967</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7508.1915997040569</v>
+        <v>7527.6964904421047</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20025,14 +20025,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>86988.154221537072</v>
+        <v>87787.289948482561</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="238" t="s">
+      <c r="B13" s="235" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="238"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20048,14 +20048,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1134706252083144</v>
+        <v>0.11289300714523912</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="238" t="s">
+      <c r="B18" s="235" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="238"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37805.887177085278</v>
+        <v>37863.336161594772</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20072,7 +20072,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>86988.154221537072</v>
+        <v>87787.289948482561</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>124794.04139862236</v>
+        <v>125650.62611007734</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20108,7 +20108,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119323.04139862236</v>
+        <v>120179.62611007734</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>112.56890697983242</v>
+        <v>113.37700576422391</v>
       </c>
     </row>
   </sheetData>
@@ -20169,20 +20169,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21114,10 +21114,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="238" t="s">
+      <c r="B37" s="235" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="238"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21135,7 +21135,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1134706252083144</v>
+        <v>0.11289300714523912</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21161,7 +21161,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>189802.34157204349</v>
+        <v>190307.50831627176</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21188,7 +21188,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>184331.34157204349</v>
+        <v>184836.50831627176</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21206,14 +21206,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>173.89749204909762</v>
+        <v>174.37406444931298</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="238" t="s">
+      <c r="B49" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="238"/>
+      <c r="C49" s="235"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C51" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11931449999999999</v>
+        <v>0.1193235</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21265,14 +21265,14 @@
       </c>
       <c r="C55" s="142">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>191.29143781629537</v>
+        <v>191.28374747809156</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="238" t="s">
+      <c r="B57" s="235" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="238"/>
+      <c r="C57" s="235"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1134706252083144</v>
+        <v>0.11289300714523912</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21315,7 +21315,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>183048.78999260144</v>
+        <v>183536.41226105264</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>177577.78999260144</v>
+        <v>178065.41226105264</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21360,7 +21360,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>167.52621697415231</v>
+        <v>167.98623798212512</v>
       </c>
     </row>
   </sheetData>
@@ -21412,10 +21412,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>112.56890697983242</v>
+        <v>113.37700576422391</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21433,7 +21433,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>173.89749204909762</v>
+        <v>174.37406444931298</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C55</f>
-        <v>191.29143781629537</v>
+        <v>191.28374747809156</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>167.52621697415231</v>
+        <v>167.98623798212512</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21460,7 +21460,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>161.32101345484443</v>
+        <v>161.75526391843837</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>189.16</v>
+        <v>170.61</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21478,7 +21478,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.14717163536242103</v>
+        <v>-5.1900451799786876E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21534,20 +21534,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21910,10 +21910,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="238" t="s">
+      <c r="B20" s="235" t="s">
         <v>410</v>
       </c>
-      <c r="C20" s="238"/>
+      <c r="C20" s="235"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21948,7 +21948,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11931449999999999</v>
+        <v>0.1193235</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C23/(C24-C25)</f>
-        <v>37.142612609437698</v>
+        <v>37.139247005995564</v>
       </c>
     </row>
   </sheetData>
@@ -22014,20 +22014,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="247"/>
       <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -22202,7 +22202,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>295699.99096437363</v>
+        <v>297643.28158077016</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22256,23 +22256,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12358.459929648498</v>
+        <v>12364.874265655035</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12952.584838240871</v>
+        <v>12966.033729544541</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13575.271914693909</v>
+        <v>13596.420559055367</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14227.894266616973</v>
+        <v>14257.455739720423</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14911.891012873059</v>
+        <v>14950.629343007738</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22291,7 +22291,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>172765.68637562246</v>
+        <v>174352.83618479542</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22307,7 +22307,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>189.16</v>
+        <v>170.61</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>223.26450506422748</v>
+        <v>224.87405106430597</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22355,7 +22355,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1134706252083144</v>
+        <v>0.11289300714523912</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22373,7 +22373,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>199374.63999999998</v>
+        <v>179822.94</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>204845.63999999998</v>
+        <v>185293.94</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>68026.101962073313</v>
+        <v>68135.413636983096</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22425,7 +22425,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>172765.68637562246</v>
+        <v>174352.83618479542</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>240791.78833769576</v>
+        <v>242488.2498217785</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>235320.78833769576</v>
+        <v>237017.2498217785</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22479,7 +22479,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>223.26450506422748</v>
+        <v>224.87405106430597</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22926,17 +22926,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29421,7 +29421,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>189.16</v>
+        <v>170.61</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29468,7 +29468,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>189.16</v>
+        <v>170.61</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -30970,7 +30970,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>20.084212900677784</v>
+        <v>18.114651950648323</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31007,7 +31007,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.5904795227201367</v>
+        <v>4.1403135513389859</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31044,7 +31044,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>7.3089903951902633</v>
+        <v>6.5922333015616994</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31081,7 +31081,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>200509.6</v>
+        <v>180846.6</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31118,7 +31118,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>205980.6</v>
+        <v>186317.6</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31155,7 +31155,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>4.6198492800430628</v>
+        <v>4.1788364060467416</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31192,7 +31192,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>18.14007926023778</v>
+        <v>16.408419198590931</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31327,7 +31327,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="98">AC156/AC160</f>
-        <v>21.260693457745734</v>
+        <v>19.175760788887711</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31364,7 +31364,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="98"/>
-        <v>17.225362197047751</v>
+        <v>15.581021434468411</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31401,7 +31401,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="101">AC160/AC156</f>
-        <v>4.7035154426521224E-2</v>
+        <v>5.2149169517148784E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31438,7 +31438,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>4.9790350507898318E-2</v>
+        <v>5.5203931200246442E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31475,7 +31475,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>1.8820046521463313E-2</v>
+        <v>2.0866303264755876E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31512,7 +31512,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>5.3538583688761035E-2</v>
+        <v>5.9359700431194172E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31549,7 +31549,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>7.2590040576610795E-2</v>
+        <v>8.0482574734609333E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32052,7 +32052,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-2.7285476605608906E-2</v>
+        <v>-3.0252158459158202E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33374,15 +33374,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="235" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="238"/>
-      <c r="E4" s="238" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33390,7 +33390,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>189.16</v>
+        <v>170.61</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33406,7 +33406,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>200509.6</v>
+        <v>180846.6</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33426,7 +33426,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>205980.6</v>
+        <v>186317.6</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>20.084212900677784</v>
+        <v>18.114651950648323</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -33466,7 +33466,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.5904795227201367</v>
+        <v>4.1403135513389859</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -33486,7 +33486,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.3089903951902633</v>
+        <v>6.5922333015616994</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33506,7 +33506,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.6198492800430628</v>
+        <v>4.1788364060467416</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33515,18 +33515,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>18.14007926023778</v>
+        <v>16.408419198590931</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="238"/>
-      <c r="E15" s="238" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="238"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33577,14 +33577,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="238" t="s">
+      <c r="B21" s="235" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="238"/>
-      <c r="E21" s="238" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="238"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33653,14 +33653,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="238" t="s">
+      <c r="B29" s="235" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="238"/>
-      <c r="E29" s="238" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="238"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33736,14 +33736,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="238" t="s">
+      <c r="B37" s="235" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="238"/>
-      <c r="E37" s="238" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="238"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33751,7 +33751,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>4.9790350507898318E-2</v>
+        <v>5.5203931200246442E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33767,7 +33767,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>4.7035154426521224E-2</v>
+        <v>5.2149169517148784E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33783,7 +33783,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.8820046521463313E-2</v>
+        <v>2.0866303264755876E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.3538583688761035E-2</v>
+        <v>5.9359700431194172E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33808,18 +33808,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>7.2590040576610795E-2</v>
+        <v>8.0482574734609333E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="238" t="s">
+      <c r="B45" s="235" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="238"/>
-      <c r="E45" s="238" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="238"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33852,18 +33852,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-2.7285476605608906E-2</v>
+        <v>-3.0252158459158202E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="238" t="s">
+      <c r="B51" s="235" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="238"/>
-      <c r="E51" s="238" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="238"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34032,7 +34032,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>189.16</v>
+        <v>170.61</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34061,7 +34061,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>200509.6</v>
+        <v>180846.6</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34090,7 +34090,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>205980.6</v>
+        <v>186317.6</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34119,7 +34119,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>20.084212900677784</v>
+        <v>18.114651950648323</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34148,7 +34148,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.5904795227201367</v>
+        <v>4.1403135513389859</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34177,7 +34177,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>7.3089903951902633</v>
+        <v>6.5922333015616994</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.6198492800430628</v>
+        <v>4.1788364060467416</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34235,7 +34235,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>18.14007926023778</v>
+        <v>16.408419198590931</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35008,7 +35008,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>4.9790350507898318E-2</v>
+        <v>5.5203931200246442E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35037,7 +35037,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>4.7035154426521224E-2</v>
+        <v>5.2149169517148784E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35066,7 +35066,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.8820046521463313E-2</v>
+        <v>2.0866303264755876E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35095,7 +35095,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.3538583688761035E-2</v>
+        <v>5.9359700431194172E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35124,7 +35124,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>7.2590040576610795E-2</v>
+        <v>8.0482574734609333E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35360,7 +35360,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-2.7285476605608906E-2</v>
+        <v>-3.0252158459158202E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35898,14 +35898,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="239" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="240"/>
+      <c r="F3" s="241" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35972,19 +35972,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="242">
         <f>Statement!AA89</f>
         <v>-0.13491674828599412</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="243"/>
+      <c r="F7" s="242">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-3.4611531104836508E-2</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="243"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -36011,19 +36011,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="242">
         <f>Statement!AA90</f>
         <v>-0.11997126436781609</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="243"/>
+      <c r="F9" s="242">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>-7.4944298156775372E-3</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="243"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -36050,19 +36050,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="242">
         <f>Statement!AA91</f>
         <v>-0.1473668461998803</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="243"/>
+      <c r="F11" s="242">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-5.6769281694803046E-2</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="243"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -36089,19 +36089,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="242">
         <f>Statement!AA94</f>
         <v>2.1699819168173599E-2</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="243"/>
+      <c r="F13" s="242">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.16016427104722791</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="243"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -36128,19 +36128,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="242">
         <f>Statement!AA95</f>
         <v>-0.31402257872846107</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="243"/>
+      <c r="F15" s="242">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.25993589743589746</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -36167,19 +36167,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="242">
         <f>Statement!AA97</f>
         <v>-0.35685752330226367</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="243"/>
+      <c r="F17" s="242">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.31294452347083929</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="243"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36206,22 +36206,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="242">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-6.4874884151992582E-3</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="243"/>
+      <c r="F19" s="242">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.8565022421524667E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="243"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36248,22 +36248,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="242">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.35171265972296784</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="243"/>
+      <c r="F21" s="242">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.28482587064676618</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="243"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36311,22 +36311,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="242">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.23006134969325154</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="243"/>
+      <c r="F25" s="242">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.13061047770241016</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="243"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -36353,22 +36353,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="242">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.20435967302452315</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="243"/>
+      <c r="F27" s="242">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.38269030239833157</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="243"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -36395,22 +36395,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="242">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.2511848341232227E-2</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="243"/>
+      <c r="F29" s="242">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>9.1714104996837451E-2</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="243"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36437,22 +36437,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="239">
+      <c r="C31" s="242">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.1448223876378027</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="F31" s="239">
+      <c r="D31" s="243"/>
+      <c r="F31" s="242">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-4.1503854683704718E-2</v>
       </c>
-      <c r="G31" s="240"/>
+      <c r="G31" s="243"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36479,43 +36479,25 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="239">
+      <c r="C33" s="242">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.13190954773869346</v>
       </c>
-      <c r="D33" s="240"/>
-      <c r="F33" s="239">
+      <c r="D33" s="243"/>
+      <c r="F33" s="242">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>4.7763457164518575E-2</v>
       </c>
-      <c r="G33" s="240"/>
+      <c r="G33" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36526,6 +36508,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA1C443-7810-1B42-A5E4-C9490AECE6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C805D51-EB34-BC49-AF3E-530ED7511110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -129,7 +129,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -139,12 +160,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2319,7 +2349,22 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2344,21 +2389,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12691,7 +12721,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12730,11 +12760,9 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6363000000000001</v>
-    <v>-7.37</v>
-    <v>-4.1409000000000001E-2</v>
-    <v>-0.89280000000000004</v>
-    <v>-5.2329999999999998E-3</v>
+    <v>1.6667000000000001</v>
+    <v>-3.1549999999999998</v>
+    <v>-2.0811000000000003E-2</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12742,36 +12770,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>173.96</v>
+    <v>153.72999999999999</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46219.999902441406</v>
+    <v>46234.712151758591</v>
     <v>4</v>
-    <v>168.99</v>
-    <v>179822940000</v>
+    <v>146.15</v>
+    <v>156461030000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>173.08</v>
-    <v>18.5579</v>
-    <v>177.98</v>
-    <v>170.61</v>
-    <v>169.71719999999999</v>
+    <v>153.22999999999999</v>
+    <v>17.180299999999999</v>
+    <v>151.6</v>
+    <v>148.44499999999999</v>
     <v>1054000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>15951600</v>
-    <v>19871783</v>
+    <v>6421645</v>
+    <v>16447152</v>
     <v>1991</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12783,30 +12825,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>46.87</v>
+    <v>47.14</v>
     <v>39.47</v>
-    <v>0.24</v>
-    <v>5.2810000000000001E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>45.96</v>
+    <v>46.86</v>
     <v>Index</v>
-    <v>7</v>
-    <v>45.61</v>
+    <v>10</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.82</v>
-    <v>45.45</v>
-    <v>45.69</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12840,8 +12882,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12863,7 +12903,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12873,6 +12912,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12908,7 +12952,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12919,16 +12963,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13029,19 +13070,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13122,9 +13157,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13132,9 +13164,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13626,18 +13655,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="236" t="s">
+      <c r="B2" s="241" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="237"/>
-      <c r="E2" s="236" t="s">
+      <c r="C2" s="242"/>
+      <c r="E2" s="241" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="237"/>
-      <c r="H2" s="236" t="s">
+      <c r="F2" s="242"/>
+      <c r="H2" s="241" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="237"/>
+      <c r="I2" s="242"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13652,7 +13681,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>180846.6</v>
+        <v>157351.69999999998</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13660,7 +13689,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>113.37700576422391</v>
+        <v>111.67082074155307</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13676,7 +13705,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>186317.6</v>
+        <v>162822.69999999998</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13684,7 +13713,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>174.37406444931298</v>
+        <v>173.36216020720786</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13693,7 +13722,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>170.61</v>
+        <v>148.44499999999999</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13708,23 +13737,23 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>191.28374747809156</v>
+        <v>189.3237912426618</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>169.71719999999999</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>18.114651950648323</v>
+        <v>15.761265510896138</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13732,7 +13761,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>167.98623798212512</v>
+        <v>167.00947724395647</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13741,14 +13770,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-7.37</v>
+        <v>-3.1549999999999998</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>4.1403135513389859</v>
+        <v>3.6024198178800519</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13756,23 +13785,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>161.75526391843837</v>
+        <v>160.34156235884481</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.89280000000000004</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>5.2149169517148784E-2</v>
+        <v>5.9935799867430736E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13780,7 +13809,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-5.1900451799786876E-2</v>
+        <v>8.0141212966720457E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13789,37 +13818,37 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-4.1409000000000001E-2</v>
+        <v>-2.0811000000000003E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>5.5203931200246442E-2</v>
+        <v>6.3446681950042411E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-5.2329999999999998E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>5.9359700431194172E-2</v>
+        <v>6.8222968039112389E-2</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>415</v>
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>37.139247005995564</v>
+        <v>36.295833476825592</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13835,7 +13864,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>2.0866303264755876E-2</v>
+        <v>2.398194617535114E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13860,7 +13889,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6363000000000001</v>
+        <v>1.6667000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13876,7 +13905,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>19871783</v>
+        <v>16447152</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13892,7 +13921,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.0252158459158202E-2</v>
+        <v>-3.4769246217231847E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13905,10 +13934,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="238" t="s">
+      <c r="B17" s="243" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="238"/>
+      <c r="C17" s="243"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -13981,14 +14010,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="238" t="s">
+      <c r="B25" s="243" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="238"/>
-      <c r="E25" s="236" t="s">
+      <c r="C25" s="243"/>
+      <c r="E25" s="241" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="237"/>
+      <c r="F25" s="242"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13997,12 +14026,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.69</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14017,7 +14046,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14037,15 +14066,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="238" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="238"/>
+      <c r="D33" s="238"/>
+      <c r="E33" s="238"/>
+      <c r="F33" s="238"/>
+      <c r="G33" s="238"/>
+      <c r="H33" s="238"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14064,24 +14093,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="238"/>
+      <c r="C39" s="238"/>
+      <c r="D39" s="238"/>
+      <c r="E39" s="238"/>
+      <c r="F39" s="238"/>
+      <c r="G39" s="238"/>
+      <c r="H39" s="238"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="238" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="238"/>
+      <c r="D42" s="238"/>
+      <c r="E42" s="238"/>
+      <c r="F42" s="238"/>
+      <c r="G42" s="238"/>
+      <c r="H42" s="238"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14096,24 +14125,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="235"/>
-      <c r="C49" s="235"/>
-      <c r="D49" s="235"/>
-      <c r="E49" s="235"/>
-      <c r="F49" s="235"/>
-      <c r="G49" s="235"/>
-      <c r="H49" s="235"/>
+      <c r="B49" s="238"/>
+      <c r="C49" s="238"/>
+      <c r="D49" s="238"/>
+      <c r="E49" s="238"/>
+      <c r="F49" s="238"/>
+      <c r="G49" s="238"/>
+      <c r="H49" s="238"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="238" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="235"/>
-      <c r="D52" s="235"/>
-      <c r="E52" s="235"/>
-      <c r="F52" s="235"/>
-      <c r="G52" s="235"/>
-      <c r="H52" s="235"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="238"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="238"/>
+      <c r="H52" s="238"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14251,13 +14280,13 @@
       </c>
     </row>
     <row r="69" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="235"/>
-      <c r="C69" s="235"/>
-      <c r="D69" s="235"/>
-      <c r="E69" s="235"/>
-      <c r="F69" s="235"/>
-      <c r="G69" s="235"/>
-      <c r="H69" s="235"/>
+      <c r="B69" s="238"/>
+      <c r="C69" s="238"/>
+      <c r="D69" s="238"/>
+      <c r="E69" s="238"/>
+      <c r="F69" s="238"/>
+      <c r="G69" s="238"/>
+      <c r="H69" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14342,36 +14371,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14382,32 +14411,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="245" t="s">
+      <c r="S4" s="236" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="237"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="237"/>
+      <c r="Y4" s="237"/>
+      <c r="Z4" s="237"/>
+      <c r="AA4" s="237"/>
+      <c r="AB4" s="237"/>
+      <c r="AC4" s="237"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15091,33 +15120,33 @@
       <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="244" t="s">
+      <c r="C13" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="244"/>
-      <c r="I13" s="244"/>
-      <c r="J13" s="244"/>
-      <c r="K13" s="244"/>
-      <c r="L13" s="244"/>
+      <c r="D13" s="235"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="235"/>
+      <c r="H13" s="235"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="235"/>
+      <c r="K13" s="235"/>
+      <c r="L13" s="235"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="91"/>
-      <c r="S13" s="245" t="s">
+      <c r="S13" s="236" t="s">
         <v>114</v>
       </c>
-      <c r="T13" s="246"/>
-      <c r="U13" s="246"/>
-      <c r="V13" s="246"/>
-      <c r="W13" s="246"/>
-      <c r="X13" s="246"/>
-      <c r="Y13" s="246"/>
-      <c r="Z13" s="246"/>
-      <c r="AA13" s="246"/>
-      <c r="AB13" s="246"/>
-      <c r="AC13" s="246"/>
+      <c r="T13" s="237"/>
+      <c r="U13" s="237"/>
+      <c r="V13" s="237"/>
+      <c r="W13" s="237"/>
+      <c r="X13" s="237"/>
+      <c r="Y13" s="237"/>
+      <c r="Z13" s="237"/>
+      <c r="AA13" s="237"/>
+      <c r="AB13" s="237"/>
+      <c r="AC13" s="237"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15741,35 +15770,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="P2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="238"/>
+      <c r="R2" s="238"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15778,31 +15807,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="P4" s="246" t="s">
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
+      <c r="P4" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="237"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="237"/>
+      <c r="Y4" s="237"/>
+      <c r="Z4" s="237"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15997,32 +16026,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="235" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="235"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="246" t="s">
+      <c r="P9" s="237" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="246"/>
-      <c r="S9" s="246"/>
-      <c r="T9" s="246"/>
-      <c r="U9" s="246"/>
-      <c r="V9" s="246"/>
-      <c r="W9" s="246"/>
-      <c r="X9" s="246"/>
-      <c r="Y9" s="246"/>
-      <c r="Z9" s="246"/>
+      <c r="Q9" s="237"/>
+      <c r="R9" s="237"/>
+      <c r="S9" s="237"/>
+      <c r="T9" s="237"/>
+      <c r="U9" s="237"/>
+      <c r="V9" s="237"/>
+      <c r="W9" s="237"/>
+      <c r="X9" s="237"/>
+      <c r="Y9" s="237"/>
+      <c r="Z9" s="237"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16498,31 +16527,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="244" t="s">
+      <c r="C17" s="235" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
-      <c r="J17" s="244"/>
-      <c r="K17" s="244"/>
-      <c r="L17" s="244"/>
-      <c r="P17" s="246" t="s">
+      <c r="D17" s="235"/>
+      <c r="E17" s="235"/>
+      <c r="F17" s="235"/>
+      <c r="G17" s="235"/>
+      <c r="H17" s="235"/>
+      <c r="I17" s="235"/>
+      <c r="J17" s="235"/>
+      <c r="K17" s="235"/>
+      <c r="L17" s="235"/>
+      <c r="P17" s="237" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="246"/>
-      <c r="R17" s="246"/>
-      <c r="S17" s="246"/>
-      <c r="T17" s="246"/>
-      <c r="U17" s="246"/>
-      <c r="V17" s="246"/>
-      <c r="W17" s="246"/>
-      <c r="X17" s="246"/>
-      <c r="Y17" s="246"/>
-      <c r="Z17" s="246"/>
+      <c r="Q17" s="237"/>
+      <c r="R17" s="237"/>
+      <c r="S17" s="237"/>
+      <c r="T17" s="237"/>
+      <c r="U17" s="237"/>
+      <c r="V17" s="237"/>
+      <c r="W17" s="237"/>
+      <c r="X17" s="237"/>
+      <c r="Y17" s="237"/>
+      <c r="Z17" s="237"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17000,20 +17029,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -17031,18 +17060,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -17239,18 +17268,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="235" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="235"/>
+      <c r="E11" s="235"/>
+      <c r="F11" s="235"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
+      <c r="K11" s="235"/>
+      <c r="L11" s="235"/>
       <c r="N11" s="91"/>
       <c r="P11" s="249"/>
       <c r="Q11" s="249"/>
@@ -17504,18 +17533,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="235" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="235"/>
+      <c r="E18" s="235"/>
+      <c r="F18" s="235"/>
+      <c r="G18" s="235"/>
+      <c r="H18" s="235"/>
+      <c r="I18" s="235"/>
+      <c r="J18" s="235"/>
+      <c r="K18" s="235"/>
+      <c r="L18" s="235"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17733,18 +17762,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="244" t="s">
+      <c r="C26" s="235" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="244"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="244"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="244"/>
+      <c r="D26" s="235"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="235"/>
+      <c r="G26" s="235"/>
+      <c r="H26" s="235"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235"/>
+      <c r="L26" s="235"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17936,18 +17965,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="244" t="s">
+      <c r="C33" s="235" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="244"/>
-      <c r="E33" s="244"/>
-      <c r="F33" s="244"/>
-      <c r="G33" s="244"/>
-      <c r="H33" s="244"/>
-      <c r="I33" s="244"/>
-      <c r="J33" s="244"/>
-      <c r="K33" s="244"/>
-      <c r="L33" s="244"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
+      <c r="I33" s="235"/>
+      <c r="J33" s="235"/>
+      <c r="K33" s="235"/>
+      <c r="L33" s="235"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18131,18 +18160,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="244" t="s">
+      <c r="C40" s="235" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="244"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
-      <c r="G40" s="244"/>
-      <c r="H40" s="244"/>
-      <c r="I40" s="244"/>
-      <c r="J40" s="244"/>
-      <c r="K40" s="244"/>
-      <c r="L40" s="244"/>
+      <c r="D40" s="235"/>
+      <c r="E40" s="235"/>
+      <c r="F40" s="235"/>
+      <c r="G40" s="235"/>
+      <c r="H40" s="235"/>
+      <c r="I40" s="235"/>
+      <c r="J40" s="235"/>
+      <c r="K40" s="235"/>
+      <c r="L40" s="235"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18456,20 +18485,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
       <c r="S2" s="249"/>
       <c r="T2" s="249"/>
       <c r="U2" s="249"/>
@@ -18487,18 +18516,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="235" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
       <c r="S4" s="249"/>
       <c r="T4" s="249"/>
       <c r="U4" s="249"/>
@@ -18872,18 +18901,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="244" t="s">
+      <c r="C13" s="235" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="244"/>
-      <c r="I13" s="244"/>
-      <c r="J13" s="244"/>
-      <c r="K13" s="244"/>
-      <c r="L13" s="244"/>
+      <c r="D13" s="235"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="235"/>
+      <c r="H13" s="235"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="235"/>
+      <c r="K13" s="235"/>
+      <c r="L13" s="235"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18976,18 +19005,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="235" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="235"/>
+      <c r="E18" s="235"/>
+      <c r="F18" s="235"/>
+      <c r="G18" s="235"/>
+      <c r="H18" s="235"/>
+      <c r="I18" s="235"/>
+      <c r="J18" s="235"/>
+      <c r="K18" s="235"/>
+      <c r="L18" s="235"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19179,18 +19208,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="244" t="s">
+      <c r="C25" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="E25" s="244"/>
-      <c r="F25" s="244"/>
-      <c r="G25" s="244"/>
-      <c r="H25" s="244"/>
-      <c r="I25" s="244"/>
-      <c r="J25" s="244"/>
-      <c r="K25" s="244"/>
-      <c r="L25" s="244"/>
+      <c r="D25" s="235"/>
+      <c r="E25" s="235"/>
+      <c r="F25" s="235"/>
+      <c r="G25" s="235"/>
+      <c r="H25" s="235"/>
+      <c r="I25" s="235"/>
+      <c r="J25" s="235"/>
+      <c r="K25" s="235"/>
+      <c r="L25" s="235"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19328,18 +19357,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="244" t="s">
+      <c r="C31" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="244"/>
-      <c r="E31" s="244"/>
-      <c r="F31" s="244"/>
-      <c r="G31" s="244"/>
-      <c r="H31" s="244"/>
-      <c r="I31" s="244"/>
-      <c r="J31" s="244"/>
-      <c r="K31" s="244"/>
-      <c r="L31" s="244"/>
+      <c r="D31" s="235"/>
+      <c r="E31" s="235"/>
+      <c r="F31" s="235"/>
+      <c r="G31" s="235"/>
+      <c r="H31" s="235"/>
+      <c r="I31" s="235"/>
+      <c r="J31" s="235"/>
+      <c r="K31" s="235"/>
+      <c r="L31" s="235"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19550,10 +19579,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="238"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19570,7 +19599,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>170.61</v>
+        <v>148.44499999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19579,7 +19608,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>180846.6</v>
+        <v>157351.69999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19597,7 +19626,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19606,7 +19635,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6363000000000001</v>
+        <v>1.6667000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19638,10 +19667,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="238" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="238"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19649,7 +19678,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.7861843413561116E-2</v>
+        <v>8.8459330431805511E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19658,7 +19687,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92213815658643894</v>
+        <v>0.91154066956819446</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19676,7 +19705,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1193235</v>
+        <v>0.1216315</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19685,7 +19714,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11289300714523912</v>
+        <v>0.11412161245399621</v>
       </c>
     </row>
   </sheetData>
@@ -19730,20 +19759,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -19761,18 +19790,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="235" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -19936,7 +19965,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>149864.47959845426</v>
+        <v>147798.49032650495</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19990,23 +20019,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>8584.5696564862847</v>
+        <v>8575.1029629624754</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7622.120099097081</v>
+        <v>7605.3186769058484</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7163.2505656236099</v>
+        <v>7139.5787169027972</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>6965.6993499456967</v>
+        <v>6935.0242449607895</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7527.6964904421047</v>
+        <v>7486.2818351437536</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20025,14 +20054,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>87787.289948482561</v>
+        <v>86100.763549170602</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="238" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="238"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20048,14 +20077,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11289300714523912</v>
+        <v>0.11412161245399621</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="238" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="238"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20063,7 +20092,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37863.336161594772</v>
+        <v>37741.306436875668</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20072,7 +20101,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>87787.289948482561</v>
+        <v>86100.763549170602</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20081,7 +20110,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>125650.62611007734</v>
+        <v>123842.06998604626</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20108,7 +20137,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>120179.62611007734</v>
+        <v>118371.06998604626</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20126,7 +20155,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>113.37700576422391</v>
+        <v>111.67082074155307</v>
       </c>
     </row>
   </sheetData>
@@ -20169,37 +20198,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="235" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20388,18 +20417,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="244" t="s">
+      <c r="C10" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="244"/>
-      <c r="E10" s="244"/>
-      <c r="F10" s="244"/>
-      <c r="G10" s="244"/>
-      <c r="H10" s="244"/>
-      <c r="I10" s="244"/>
-      <c r="J10" s="244"/>
-      <c r="K10" s="244"/>
-      <c r="L10" s="244"/>
+      <c r="D10" s="235"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="235"/>
+      <c r="L10" s="235"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20593,18 +20622,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="244" t="s">
+      <c r="C16" s="235" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="244"/>
-      <c r="E16" s="244"/>
-      <c r="F16" s="244"/>
-      <c r="G16" s="244"/>
-      <c r="H16" s="244"/>
-      <c r="I16" s="244"/>
-      <c r="J16" s="244"/>
-      <c r="K16" s="244"/>
-      <c r="L16" s="244"/>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="235"/>
+      <c r="H16" s="235"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="235"/>
+      <c r="L16" s="235"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20738,18 +20767,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="244" t="s">
+      <c r="C21" s="235" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="244"/>
-      <c r="E21" s="244"/>
-      <c r="F21" s="244"/>
-      <c r="G21" s="244"/>
-      <c r="H21" s="244"/>
-      <c r="I21" s="244"/>
-      <c r="J21" s="244"/>
-      <c r="K21" s="244"/>
-      <c r="L21" s="244"/>
+      <c r="D21" s="235"/>
+      <c r="E21" s="235"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="235"/>
+      <c r="H21" s="235"/>
+      <c r="I21" s="235"/>
+      <c r="J21" s="235"/>
+      <c r="K21" s="235"/>
+      <c r="L21" s="235"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -20833,18 +20862,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="244" t="s">
+      <c r="C26" s="235" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="244"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="244"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="244"/>
+      <c r="D26" s="235"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="235"/>
+      <c r="G26" s="235"/>
+      <c r="H26" s="235"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235"/>
+      <c r="L26" s="235"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21114,10 +21143,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="238" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="238"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21135,7 +21164,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11289300714523912</v>
+        <v>0.11412161245399621</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21161,7 +21190,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>190307.50831627176</v>
+        <v>189234.88981964035</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21188,7 +21217,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>184836.50831627176</v>
+        <v>183763.88981964035</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21206,14 +21235,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>174.37406444931298</v>
+        <v>173.36216020720786</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="235" t="s">
+      <c r="B49" s="238" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="235"/>
+      <c r="C49" s="238"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21230,7 +21259,7 @@
       </c>
       <c r="C51" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1193235</v>
+        <v>0.1216315</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21265,14 +21294,14 @@
       </c>
       <c r="C55" s="142">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>191.28374747809156</v>
+        <v>189.3237912426618</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="235" t="s">
+      <c r="B57" s="238" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="235"/>
+      <c r="C57" s="238"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21289,7 +21318,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11289300714523912</v>
+        <v>0.11412161245399621</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21315,7 +21344,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>183536.41226105264</v>
+        <v>182501.04587859387</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21342,7 +21371,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>178065.41226105264</v>
+        <v>177030.04587859387</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21360,7 +21389,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>167.98623798212512</v>
+        <v>167.00947724395647</v>
       </c>
     </row>
   </sheetData>
@@ -21412,10 +21441,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="238"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21424,7 +21453,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>113.37700576422391</v>
+        <v>111.67082074155307</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21433,7 +21462,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>174.37406444931298</v>
+        <v>173.36216020720786</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21442,7 +21471,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C55</f>
-        <v>191.28374747809156</v>
+        <v>189.3237912426618</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21451,7 +21480,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>167.98623798212512</v>
+        <v>167.00947724395647</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21460,7 +21489,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>161.75526391843837</v>
+        <v>160.34156235884481</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21469,7 +21498,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>170.61</v>
+        <v>148.44499999999999</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21478,7 +21507,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-5.1900451799786876E-2</v>
+        <v>8.0141212966720457E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21534,37 +21563,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="235" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21677,18 +21706,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="235"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21809,18 +21838,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="244" t="s">
+      <c r="C14" s="235" t="s">
         <v>408</v>
       </c>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
-      <c r="H14" s="244"/>
-      <c r="I14" s="244"/>
-      <c r="J14" s="244"/>
-      <c r="K14" s="244"/>
-      <c r="L14" s="244"/>
+      <c r="D14" s="235"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="235"/>
+      <c r="G14" s="235"/>
+      <c r="H14" s="235"/>
+      <c r="I14" s="235"/>
+      <c r="J14" s="235"/>
+      <c r="K14" s="235"/>
+      <c r="L14" s="235"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -21910,10 +21939,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="235" t="s">
+      <c r="B20" s="238" t="s">
         <v>410</v>
       </c>
-      <c r="C20" s="235"/>
+      <c r="C20" s="238"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21948,7 +21977,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1193235</v>
+        <v>0.1216315</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -21965,7 +21994,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C23/(C24-C25)</f>
-        <v>37.139247005995564</v>
+        <v>36.295833476825592</v>
       </c>
     </row>
   </sheetData>
@@ -22014,20 +22043,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -22045,18 +22074,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="235" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -22202,7 +22231,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>297643.28158077016</v>
+        <v>293540.05559779349</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22256,23 +22285,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12364.874265655035</v>
+        <v>12351.238815094628</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12966.033729544541</v>
+        <v>12937.452730556917</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13596.420559055367</v>
+        <v>13551.489503290954</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14257.455739720423</v>
+        <v>14194.66966043938</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14950.629343007738</v>
+        <v>14868.376403941949</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22291,7 +22320,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>174352.83618479542</v>
+        <v>171003.25492772355</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22307,7 +22336,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>170.61</v>
+        <v>148.44499999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22316,7 +22345,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>224.87405106430597</v>
+        <v>221.47578941275842</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22355,7 +22384,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11289300714523912</v>
+        <v>0.11412161245399621</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22373,7 +22402,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>179822.94</v>
+        <v>156461.03</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22400,7 +22429,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>185293.94</v>
+        <v>161932.03</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22416,7 +22445,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>68135.413636983096</v>
+        <v>67903.227113323825</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22425,7 +22454,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>174352.83618479542</v>
+        <v>171003.25492772355</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22434,7 +22463,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>242488.2498217785</v>
+        <v>238906.48204104736</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22461,7 +22490,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>237017.2498217785</v>
+        <v>233435.48204104736</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22479,22 +22508,22 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>224.87405106430597</v>
+        <v>221.47578941275842</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="244" t="s">
+      <c r="C39" s="235" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="244"/>
-      <c r="E39" s="244"/>
-      <c r="F39" s="244"/>
-      <c r="G39" s="244"/>
-      <c r="H39" s="244"/>
-      <c r="I39" s="244"/>
-      <c r="J39" s="244"/>
-      <c r="K39" s="244"/>
-      <c r="L39" s="244"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
+      <c r="I39" s="235"/>
+      <c r="J39" s="235"/>
+      <c r="K39" s="235"/>
+      <c r="L39" s="235"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -27170,7 +27199,9 @@
       <c r="T74" s="21">
         <v>1114</v>
       </c>
-      <c r="U74" s="21"/>
+      <c r="U74" s="21">
+        <v>1111</v>
+      </c>
       <c r="V74" s="21">
         <v>1106</v>
       </c>
@@ -27234,7 +27265,7 @@
       </c>
       <c r="U75" s="25">
         <f t="shared" ref="U75" si="30">U74*U85</f>
-        <v>0</v>
+        <v>1111</v>
       </c>
       <c r="V75" s="25">
         <f t="shared" ref="V75" si="31">V74*V85</f>
@@ -27434,7 +27465,7 @@
       </c>
       <c r="U78" s="25">
         <f t="shared" si="40"/>
-        <v>14</v>
+        <v>1125</v>
       </c>
       <c r="V78" s="25">
         <f t="shared" si="40"/>
@@ -29411,17 +29442,33 @@
       <c r="Q115" s="63">
         <v>169.2</v>
       </c>
-      <c r="T115" s="68"/>
-      <c r="U115" s="68"/>
-      <c r="V115" s="68"/>
-      <c r="W115" s="68"/>
-      <c r="X115" s="68"/>
-      <c r="Y115" s="68"/>
-      <c r="Z115" s="68"/>
-      <c r="AA115" s="68"/>
+      <c r="T115" s="63">
+        <v>215.47</v>
+      </c>
+      <c r="U115" s="63">
+        <v>170.13</v>
+      </c>
+      <c r="V115" s="63">
+        <v>157.24</v>
+      </c>
+      <c r="W115" s="63">
+        <v>152.72</v>
+      </c>
+      <c r="X115" s="63">
+        <v>158.54</v>
+      </c>
+      <c r="Y115" s="63">
+        <v>169.2</v>
+      </c>
+      <c r="Z115" s="63">
+        <v>174.81</v>
+      </c>
+      <c r="AA115" s="63">
+        <v>127.11</v>
+      </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>170.61</v>
+        <v>148.44499999999999</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29458,17 +29505,41 @@
         <f>Q115/Q85</f>
         <v>169.2</v>
       </c>
-      <c r="T116" s="68"/>
-      <c r="U116" s="68"/>
-      <c r="V116" s="68"/>
-      <c r="W116" s="68"/>
-      <c r="X116" s="68"/>
-      <c r="Y116" s="68"/>
-      <c r="Z116" s="68"/>
-      <c r="AA116" s="68"/>
+      <c r="T116" s="65">
+        <f t="shared" ref="T116:AA116" si="70">T115/T85</f>
+        <v>215.47</v>
+      </c>
+      <c r="U116" s="65">
+        <f t="shared" si="70"/>
+        <v>170.13</v>
+      </c>
+      <c r="V116" s="65">
+        <f t="shared" si="70"/>
+        <v>157.24</v>
+      </c>
+      <c r="W116" s="65">
+        <f t="shared" si="70"/>
+        <v>152.72</v>
+      </c>
+      <c r="X116" s="65">
+        <f t="shared" si="70"/>
+        <v>158.54</v>
+      </c>
+      <c r="Y116" s="65">
+        <f t="shared" si="70"/>
+        <v>169.2</v>
+      </c>
+      <c r="Z116" s="65">
+        <f t="shared" si="70"/>
+        <v>174.81</v>
+      </c>
+      <c r="AA116" s="65">
+        <f t="shared" si="70"/>
+        <v>127.11</v>
+      </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>170.61</v>
+        <v>148.44499999999999</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -29582,19 +29653,19 @@
         <v>94</v>
       </c>
       <c r="M122" s="76">
-        <f t="shared" ref="M122:P122" si="70">M120*M121</f>
+        <f t="shared" ref="M122:P122" si="71">M120*M121</f>
         <v>0.21927740058195924</v>
       </c>
       <c r="N122" s="76">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.26494470967478678</v>
       </c>
       <c r="O122" s="76">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.14378918495297807</v>
       </c>
       <c r="P122" s="76">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.18330492801972659</v>
       </c>
       <c r="Q122" s="76">
@@ -29656,19 +29727,19 @@
         <v>96</v>
       </c>
       <c r="M124" s="76">
-        <f t="shared" ref="M124:P124" si="71">M122*M123</f>
+        <f t="shared" ref="M124:P124" si="72">M122*M123</f>
         <v>0.90884422110552765</v>
       </c>
       <c r="N124" s="76">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.7209237772719701</v>
       </c>
       <c r="O124" s="76">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.34006765210138556</v>
       </c>
       <c r="P124" s="76">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.38479104818451698</v>
       </c>
       <c r="Q124" s="76">
@@ -29830,35 +29901,35 @@
       <c r="P130" s="49"/>
       <c r="Q130" s="49"/>
       <c r="T130" s="25">
-        <f t="shared" ref="T130:AA130" si="72">U5</f>
+        <f t="shared" ref="T130:AA130" si="73">U5</f>
         <v>10244</v>
       </c>
       <c r="U130" s="25">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>11669</v>
       </c>
       <c r="V130" s="25">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>10979</v>
       </c>
       <c r="W130" s="25">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>10465</v>
       </c>
       <c r="X130" s="25">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>11270</v>
       </c>
       <c r="Y130" s="25">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>12252</v>
       </c>
       <c r="Z130" s="25">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>10599</v>
       </c>
       <c r="AA130" s="25">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AC130" s="49"/>
@@ -29883,35 +29954,35 @@
       <c r="P131" s="49"/>
       <c r="Q131" s="49"/>
       <c r="T131" s="227" t="str">
-        <f t="shared" ref="T131:AA131" si="73">IF(T130&gt;T129, "BEAT", IF(T130&lt;T128, "MISSED", "MET"))</f>
+        <f t="shared" ref="T131:AA131" si="74">IF(T130&gt;T129, "BEAT", IF(T130&lt;T128, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U131" s="227" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>BEAT</v>
       </c>
       <c r="V131" s="227" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MET</v>
       </c>
       <c r="W131" s="227" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MET</v>
       </c>
       <c r="X131" s="227" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>BEAT</v>
       </c>
       <c r="Y131" s="227" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MET</v>
       </c>
       <c r="Z131" s="227" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MET</v>
       </c>
       <c r="AA131" s="227" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>MISSED</v>
       </c>
       <c r="AC131" s="49"/>
@@ -30026,27 +30097,27 @@
       <c r="P134" s="49"/>
       <c r="Q134" s="49"/>
       <c r="T134" s="25">
-        <f t="shared" ref="T134:Y134" si="74">U193</f>
+        <f t="shared" ref="T134:Y134" si="75">U193</f>
         <v>8678</v>
       </c>
       <c r="U134" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>10084</v>
       </c>
       <c r="V134" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>9469</v>
       </c>
       <c r="W134" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>8993</v>
       </c>
       <c r="X134" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>9821</v>
       </c>
       <c r="Y134" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>10613</v>
       </c>
       <c r="Z134" s="25">
@@ -30079,35 +30150,35 @@
       <c r="P135" s="49"/>
       <c r="Q135" s="49"/>
       <c r="T135" s="227" t="str">
-        <f t="shared" ref="T135:AA135" si="75">IF(T134&gt;T133, "BEAT", IF(T134&lt;T132, "MISSED", "MET"))</f>
+        <f t="shared" ref="T135:AA135" si="76">IF(T134&gt;T133, "BEAT", IF(T134&lt;T132, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U135" s="227" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>BEAT</v>
       </c>
       <c r="V135" s="227" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MET</v>
       </c>
       <c r="W135" s="227" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MET</v>
       </c>
       <c r="X135" s="227" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>BEAT</v>
       </c>
       <c r="Y135" s="227" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MET</v>
       </c>
       <c r="Z135" s="227" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MET</v>
       </c>
       <c r="AA135" s="227" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>MISSED</v>
       </c>
       <c r="AC135" s="49"/>
@@ -30222,27 +30293,27 @@
       <c r="P138" s="49"/>
       <c r="Q138" s="49"/>
       <c r="T138" s="25">
-        <f t="shared" ref="T138:Y138" si="76">U194</f>
+        <f t="shared" ref="T138:Y138" si="77">U194</f>
         <v>1015</v>
       </c>
       <c r="U138" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>1535</v>
       </c>
       <c r="V138" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>1319</v>
       </c>
       <c r="W138" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>1318</v>
       </c>
       <c r="X138" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>1409</v>
       </c>
       <c r="Y138" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>1592</v>
       </c>
       <c r="Z138" s="25">
@@ -30275,35 +30346,35 @@
       <c r="P139" s="49"/>
       <c r="Q139" s="49"/>
       <c r="T139" s="227" t="str">
-        <f t="shared" ref="T139:AA139" si="77">IF(T138&gt;T137, "BEAT", IF(T138&lt;T136, "MISSED", "MET"))</f>
+        <f t="shared" ref="T139:AA139" si="78">IF(T138&gt;T137, "BEAT", IF(T138&lt;T136, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="U139" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="V139" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="W139" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="X139" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="Y139" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="Z139" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="AA139" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MISSED</v>
       </c>
       <c r="AC139" s="49"/>
@@ -30392,55 +30463,55 @@
         <v>131</v>
       </c>
       <c r="M144" s="118">
-        <f t="shared" ref="M144:Q145" si="78">M30/M5*365</f>
+        <f t="shared" ref="M144:Q145" si="79">M30/M5*365</f>
         <v>38.91839957099446</v>
       </c>
       <c r="N144" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>46.599434389140271</v>
       </c>
       <c r="O144" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>32.434254606365158</v>
       </c>
       <c r="P144" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>36.807273753914075</v>
       </c>
       <c r="Q144" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>35.565328335290403</v>
       </c>
       <c r="T144" s="118">
-        <f t="shared" ref="T144:AA144" si="79">T30/T5*90</f>
+        <f t="shared" ref="T144:AA144" si="80">T30/T5*90</f>
         <v>28.246566592143086</v>
       </c>
       <c r="U144" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>34.518742678641154</v>
       </c>
       <c r="V144" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>27.380238238066674</v>
       </c>
       <c r="W144" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>30.322433737134528</v>
       </c>
       <c r="X144" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>29.326325848064979</v>
       </c>
       <c r="Y144" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>34.45874001774623</v>
       </c>
       <c r="Z144" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>30.506856023506366</v>
       </c>
       <c r="AA144" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>36.911972827625249</v>
       </c>
       <c r="AC144" s="118">
@@ -30453,55 +30524,55 @@
         <v>132</v>
       </c>
       <c r="M145" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>82.612536811106438</v>
       </c>
       <c r="N145" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>124.08004074411623</v>
       </c>
       <c r="O145" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>147.7112609490201</v>
       </c>
       <c r="P145" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>137.42057444314187</v>
       </c>
       <c r="Q145" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>120.68041341574629</v>
       </c>
       <c r="T145" s="118">
-        <f t="shared" ref="T145:AA145" si="80">T31/T6*365</f>
+        <f t="shared" ref="T145:AA145" si="81">T31/T6*365</f>
         <v>526.42549113560131</v>
       </c>
       <c r="U145" s="118">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>524.82538616521151</v>
       </c>
       <c r="V145" s="118">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>445.76535555124974</v>
       </c>
       <c r="W145" s="118">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>458.07980554992912</v>
       </c>
       <c r="X145" s="118">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>502.25141120277902</v>
       </c>
       <c r="Y145" s="118">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>473.27438903238624</v>
       </c>
       <c r="Z145" s="118">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>436.91181752873564</v>
       </c>
       <c r="AA145" s="118">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>548.84081632653067</v>
       </c>
       <c r="AC145" s="118">
@@ -30534,35 +30605,35 @@
         <v>51.611865437227685</v>
       </c>
       <c r="T146" s="118">
-        <f t="shared" ref="T146:AA146" si="81">T38/T6*90</f>
+        <f t="shared" ref="T146:AA146" si="82">T38/T6*90</f>
         <v>55.759463344513655</v>
       </c>
       <c r="U146" s="118">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>52.061786433848219</v>
       </c>
       <c r="V146" s="118">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>45.008719240457275</v>
       </c>
       <c r="W146" s="118">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>45.191411788535554</v>
       </c>
       <c r="X146" s="118">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>45.664350846721668</v>
       </c>
       <c r="Y146" s="118">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>49.908603218756205</v>
       </c>
       <c r="Z146" s="118">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>43.787715517241381</v>
       </c>
       <c r="AA146" s="118">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>54.60612244897959</v>
       </c>
       <c r="AC146" s="118">
@@ -30579,55 +30650,55 @@
         <v>51.151606694820003</v>
       </c>
       <c r="N147" s="118">
-        <f t="shared" ref="N147:Q147" si="82">N144+N145-N146</f>
+        <f t="shared" ref="N147:Q147" si="83">N144+N145-N146</f>
         <v>96.399734608944073</v>
       </c>
       <c r="O147" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>136.16794923110521</v>
       </c>
       <c r="P147" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>118.9429712920149</v>
       </c>
       <c r="Q147" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>104.633876313809</v>
       </c>
       <c r="T147" s="118">
-        <f t="shared" ref="T147" si="83">T144+T145-T146</f>
+        <f t="shared" ref="T147" si="84">T144+T145-T146</f>
         <v>498.91259438323067</v>
       </c>
       <c r="U147" s="118">
-        <f t="shared" ref="U147" si="84">U144+U145-U146</f>
+        <f t="shared" ref="U147" si="85">U144+U145-U146</f>
         <v>507.28234241000445</v>
       </c>
       <c r="V147" s="118">
-        <f t="shared" ref="V147" si="85">V144+V145-V146</f>
+        <f t="shared" ref="V147" si="86">V144+V145-V146</f>
         <v>428.13687454885917</v>
       </c>
       <c r="W147" s="118">
-        <f t="shared" ref="W147" si="86">W144+W145-W146</f>
+        <f t="shared" ref="W147" si="87">W144+W145-W146</f>
         <v>443.21082749852809</v>
       </c>
       <c r="X147" s="118">
-        <f t="shared" ref="X147" si="87">X144+X145-X146</f>
+        <f t="shared" ref="X147" si="88">X144+X145-X146</f>
         <v>485.91338620412233</v>
       </c>
       <c r="Y147" s="118">
-        <f t="shared" ref="Y147" si="88">Y144+Y145-Y146</f>
+        <f t="shared" ref="Y147" si="89">Y144+Y145-Y146</f>
         <v>457.82452583137626</v>
       </c>
       <c r="Z147" s="118">
-        <f t="shared" ref="Z147:AA147" si="89">Z144+Z145-Z146</f>
+        <f t="shared" ref="Z147:AA147" si="90">Z144+Z145-Z146</f>
         <v>423.63095803500062</v>
       </c>
       <c r="AA147" s="118">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>531.14666670517636</v>
       </c>
       <c r="AC147" s="118">
-        <f t="shared" ref="AC147" si="90">AC144+AC145-AC146</f>
+        <f t="shared" ref="AC147" si="91">AC144+AC145-AC146</f>
         <v>115.36831157787066</v>
       </c>
     </row>
@@ -30656,35 +30727,35 @@
         <v>0.69843440535697443</v>
       </c>
       <c r="T148" s="118">
-        <f t="shared" ref="T148:AA148" si="91">T107/T49</f>
+        <f t="shared" ref="T148:AA148" si="92">T107/T49</f>
         <v>0.58994730441832188</v>
       </c>
       <c r="U148" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.55697647864809319</v>
       </c>
       <c r="V148" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.54229910714285712</v>
       </c>
       <c r="W148" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.52737305251009814</v>
       </c>
       <c r="X148" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.54349663714212204</v>
       </c>
       <c r="Y148" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.69843440535697443</v>
       </c>
       <c r="Z148" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.64217917045897799</v>
       </c>
       <c r="AA148" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.55979177359043919</v>
       </c>
       <c r="AC148" s="118">
@@ -30717,35 +30788,35 @@
         <v>0.21956050174478922</v>
       </c>
       <c r="T149" s="179">
-        <f t="shared" ref="T149:AA149" si="92">(T107-T106)/T49</f>
+        <f t="shared" ref="T149:AA149" si="93">(T107-T106)/T49</f>
         <v>6.169436562626672E-2</v>
       </c>
       <c r="U149" s="179">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5.0772626931567331E-2</v>
       </c>
       <c r="V149" s="179">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.011904761904762E-2</v>
       </c>
       <c r="W149" s="179">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>2.8022215810732835E-2</v>
       </c>
       <c r="X149" s="179">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.17556690800837957</v>
       </c>
       <c r="Y149" s="179">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.21956050174478922</v>
       </c>
       <c r="Z149" s="179">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.12980540025137607</v>
       </c>
       <c r="AA149" s="179">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.20056455751887969</v>
       </c>
       <c r="AC149" s="179">
@@ -30778,35 +30849,35 @@
         <v>1.5824584426946631</v>
       </c>
       <c r="T150" s="118">
-        <f t="shared" ref="T150:AA150" si="93">(T106+T30)/T40</f>
+        <f t="shared" ref="T150:AA150" si="94">(T106+T30)/T40</f>
         <v>1.6394788139940495</v>
       </c>
       <c r="U150" s="118">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.6402322924600152</v>
       </c>
       <c r="V150" s="118">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.7937512557765722</v>
       </c>
       <c r="W150" s="118">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.838327745180218</v>
       </c>
       <c r="X150" s="118">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.7206410256410256</v>
       </c>
       <c r="Y150" s="118">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.5824584426946631</v>
       </c>
       <c r="Z150" s="118">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.6264508246792915</v>
       </c>
       <c r="AA150" s="118">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.4483464728166273</v>
       </c>
       <c r="AC150" s="118">
@@ -30839,35 +30910,35 @@
         <v>2.8164916885389326</v>
       </c>
       <c r="T151" s="118">
-        <f t="shared" ref="T151:AA151" si="94">T32/T40</f>
+        <f t="shared" ref="T151:AA151" si="95">T32/T40</f>
         <v>2.3937621832358675</v>
       </c>
       <c r="U151" s="118">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.402037319116527</v>
       </c>
       <c r="V151" s="118">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.6185453084187262</v>
       </c>
       <c r="W151" s="118">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.732606873428332</v>
       </c>
       <c r="X151" s="118">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>3.193974358974359</v>
       </c>
       <c r="Y151" s="118">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.8164916885389326</v>
       </c>
       <c r="Z151" s="118">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.5053960496843821</v>
       </c>
       <c r="AA151" s="118">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.3663356199447119</v>
       </c>
       <c r="AC151" s="118">
@@ -30900,35 +30971,35 @@
         <v>18.606927710843372</v>
       </c>
       <c r="T152" s="181">
-        <f t="shared" ref="T152:AA152" si="95">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T152:AA152" si="96">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>13.220238095238095</v>
       </c>
       <c r="U152" s="181">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>14.5</v>
       </c>
       <c r="V152" s="181">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>21.809815950920246</v>
       </c>
       <c r="W152" s="181">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>19.141104294478527</v>
       </c>
       <c r="X152" s="181">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>16.44047619047619</v>
       </c>
       <c r="Y152" s="181">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>17.064327485380115</v>
       </c>
       <c r="Z152" s="181">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>19.917159763313609</v>
       </c>
       <c r="AA152" s="181">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>13.502923976608187</v>
       </c>
       <c r="AC152" s="181">
@@ -30970,7 +31041,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>18.114651950648323</v>
+        <v>15.761265510896138</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31007,7 +31078,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.1403135513389859</v>
+        <v>3.6024198178800519</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31034,17 +31105,41 @@
         <f>Q116/(Statement!Q49/Statement!Q75)</f>
         <v>8.5453739507686493</v>
       </c>
-      <c r="T155" s="49"/>
-      <c r="U155" s="49"/>
-      <c r="V155" s="49"/>
-      <c r="W155" s="49"/>
-      <c r="X155" s="49"/>
-      <c r="Y155" s="49"/>
-      <c r="Z155" s="49"/>
-      <c r="AA155" s="49"/>
+      <c r="T155" s="72">
+        <f>T116/(Statement!T49/Statement!T75)</f>
+        <v>9.7297762464531825</v>
+      </c>
+      <c r="U155" s="72">
+        <f>U116/(Statement!U49/Statement!U75)</f>
+        <v>7.1939723681205754</v>
+      </c>
+      <c r="V155" s="72">
+        <f>V116/(Statement!V49/Statement!V75)</f>
+        <v>6.4697708333333335</v>
+      </c>
+      <c r="W155" s="72">
+        <f>W116/(Statement!W49/Statement!W75)</f>
+        <v>6.0475533756491631</v>
+      </c>
+      <c r="X155" s="72">
+        <f>X116/(Statement!X49/Statement!X75)</f>
+        <v>6.2870616340181558</v>
+      </c>
+      <c r="Y155" s="72">
+        <f>Y116/(Statement!Y49/Statement!Y75)</f>
+        <v>8.5453739507686493</v>
+      </c>
+      <c r="Z155" s="72">
+        <f>Z116/(Statement!Z49/Statement!Z75)</f>
+        <v>8.084005981016773</v>
+      </c>
+      <c r="AA155" s="72">
+        <f>AA116/(Statement!AA49/Statement!AA75)</f>
+        <v>4.9114282572036077</v>
+      </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.5922333015616994</v>
+        <v>5.7357955128675124</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31071,17 +31166,41 @@
         <f>Statement!Q116*Statement!Q78</f>
         <v>182736</v>
       </c>
-      <c r="T156" s="49"/>
-      <c r="U156" s="49"/>
-      <c r="V156" s="49"/>
-      <c r="W156" s="49"/>
-      <c r="X156" s="49"/>
-      <c r="Y156" s="49"/>
-      <c r="Z156" s="49"/>
-      <c r="AA156" s="49"/>
+      <c r="T156" s="143">
+        <f>Statement!T116*Statement!T78</f>
+        <v>243912.04</v>
+      </c>
+      <c r="U156" s="143">
+        <f>Statement!U116*Statement!U78</f>
+        <v>191396.25</v>
+      </c>
+      <c r="V156" s="143">
+        <f>Statement!V116*Statement!V78</f>
+        <v>175794.32</v>
+      </c>
+      <c r="W156" s="143">
+        <f>Statement!W116*Statement!W78</f>
+        <v>169213.76</v>
+      </c>
+      <c r="X156" s="143">
+        <f>Statement!X116*Statement!X78</f>
+        <v>172174.44</v>
+      </c>
+      <c r="Y156" s="143">
+        <f>Statement!Y116*Statement!Y78</f>
+        <v>182736</v>
+      </c>
+      <c r="Z156" s="143">
+        <f>Statement!Z116*Statement!Z78</f>
+        <v>188095.56</v>
+      </c>
+      <c r="AA156" s="143">
+        <f>Statement!AA116*Statement!AA78</f>
+        <v>134736.6</v>
+      </c>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>180846.6</v>
+        <v>157351.69999999998</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31108,17 +31227,41 @@
         <f>Q156+Q107-Q106+Q48+Q45</f>
         <v>187392</v>
       </c>
-      <c r="T157" s="49"/>
-      <c r="U157" s="49"/>
-      <c r="V157" s="49"/>
-      <c r="W157" s="49"/>
-      <c r="X157" s="49"/>
-      <c r="Y157" s="49"/>
-      <c r="Z157" s="49"/>
-      <c r="AA157" s="49"/>
+      <c r="T157" s="143">
+        <f t="shared" ref="T157:AA157" si="97">T156+T107-T106+T48+T45</f>
+        <v>245434.04</v>
+      </c>
+      <c r="U157" s="143">
+        <f t="shared" si="97"/>
+        <v>192730.25</v>
+      </c>
+      <c r="V157" s="143">
+        <f t="shared" si="97"/>
+        <v>176066.32</v>
+      </c>
+      <c r="W157" s="143">
+        <f t="shared" si="97"/>
+        <v>169990.76</v>
+      </c>
+      <c r="X157" s="143">
+        <f t="shared" si="97"/>
+        <v>176951.44</v>
+      </c>
+      <c r="Y157" s="143">
+        <f t="shared" si="97"/>
+        <v>187392</v>
+      </c>
+      <c r="Z157" s="143">
+        <f t="shared" si="97"/>
+        <v>191090.56</v>
+      </c>
+      <c r="AA157" s="143">
+        <f t="shared" si="97"/>
+        <v>140207.6</v>
+      </c>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>186317.6</v>
+        <v>162822.69999999998</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31155,7 +31298,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>4.1788364060467416</v>
+        <v>3.6518795137487099</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31192,7 +31335,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>16.408419198590931</v>
+        <v>14.339295464553059</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31220,35 +31363,35 @@
         <v>10037</v>
       </c>
       <c r="T160" s="64">
-        <f t="shared" ref="T160:AA160" si="96">T59-T54+T109+T65</f>
+        <f t="shared" ref="T160:AA160" si="98">T59-T54+T109+T65</f>
         <v>0</v>
       </c>
       <c r="U160" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="V160" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3551</v>
       </c>
       <c r="W160" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1638</v>
       </c>
       <c r="X160" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1922</v>
       </c>
       <c r="Y160" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2926</v>
       </c>
       <c r="Z160" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3528</v>
       </c>
       <c r="AA160" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1055</v>
       </c>
       <c r="AC160" s="64">
@@ -31302,19 +31445,19 @@
         <v>21.811802433786685</v>
       </c>
       <c r="N162" s="72">
-        <f t="shared" ref="N162:Q162" si="97">N156/N160</f>
+        <f t="shared" ref="N162:Q162" si="99">N156/N160</f>
         <v>28.638486362689985</v>
       </c>
       <c r="O162" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>16.404203665987779</v>
       </c>
       <c r="P162" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>22.482820392341125</v>
       </c>
       <c r="Q162" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>18.206236923383482</v>
       </c>
       <c r="T162" s="49"/>
@@ -31326,8 +31469,8 @@
       <c r="Z162" s="49"/>
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
-        <f t="shared" ref="AC162:AC163" ca="1" si="98">AC156/AC160</f>
-        <v>19.175760788887711</v>
+        <f t="shared" ref="AC162:AC163" ca="1" si="100">AC156/AC160</f>
+        <v>16.684519139009648</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31339,19 +31482,19 @@
         <v>19.834913152264804</v>
       </c>
       <c r="N163" s="72">
-        <f t="shared" ref="N163:Q163" si="99">N157/N161</f>
+        <f t="shared" ref="N163:Q163" si="101">N157/N161</f>
         <v>27.867839537332323</v>
       </c>
       <c r="O163" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>11.081541471136106</v>
       </c>
       <c r="P163" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>17.214522225380236</v>
       </c>
       <c r="Q163" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>15.89200834223236</v>
       </c>
       <c r="T163" s="49"/>
@@ -31363,8 +31506,8 @@
       <c r="Z163" s="49"/>
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
-        <f t="shared" ca="1" si="98"/>
-        <v>15.581021434468411</v>
+        <f t="shared" ca="1" si="100"/>
+        <v>13.616233671526574</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31376,19 +31519,19 @@
         <v>4.5846738390174974E-2</v>
       </c>
       <c r="N164" s="74">
-        <f t="shared" ref="N164:Q164" si="100">N160/N156</f>
+        <f t="shared" ref="N164:Q164" si="102">N160/N156</f>
         <v>3.4918046552306369E-2</v>
       </c>
       <c r="O164" s="74">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>6.0959984426027604E-2</v>
       </c>
       <c r="P164" s="74">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>4.4478405402404698E-2</v>
       </c>
       <c r="Q164" s="74">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>5.4926232378951056E-2</v>
       </c>
       <c r="T164" s="49"/>
@@ -31400,8 +31543,8 @@
       <c r="Z164" s="49"/>
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
-        <f t="shared" ref="AC164" ca="1" si="101">AC160/AC156</f>
-        <v>5.2149169517148784E-2</v>
+        <f t="shared" ref="AC164" ca="1" si="103">AC160/AC156</f>
+        <v>5.9935799867430736E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31438,7 +31581,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.5203931200246442E-2</v>
+        <v>6.3446681950042411E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31475,7 +31618,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>2.0866303264755876E-2</v>
+        <v>2.398194617535114E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31512,7 +31655,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>5.9359700431194172E-2</v>
+        <v>6.8222968039112389E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31549,7 +31692,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>8.0482574734609333E-2</v>
+        <v>9.2499795045112326E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -31799,35 +31942,35 @@
         <v>9.4817927170868348</v>
       </c>
       <c r="T175" s="72">
-        <f t="shared" ref="T175:AA175" si="102">T106/T75</f>
+        <f t="shared" ref="T175:AA175" si="104">T106/T75</f>
         <v>11.6983842010772</v>
       </c>
-      <c r="U175" s="72" t="e">
-        <f t="shared" si="102"/>
-        <v>#DIV/0!</v>
+      <c r="U175" s="72">
+        <f t="shared" si="104"/>
+        <v>11.971197119711972</v>
       </c>
       <c r="V175" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>12.933996383363471</v>
       </c>
       <c r="W175" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>12.610200364298725</v>
       </c>
       <c r="X175" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>9.2780352177942547</v>
       </c>
       <c r="Y175" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>9.4817927170868348</v>
       </c>
       <c r="Z175" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>11.079662605435802</v>
       </c>
       <c r="AA175" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>9.2969639468690701</v>
       </c>
       <c r="AC175" s="72">
@@ -31860,35 +32003,35 @@
         <v>0.19861547245218383</v>
       </c>
       <c r="T176" s="154" t="e">
-        <f t="shared" ref="T176:AA176" si="103">T54/T59</f>
+        <f t="shared" ref="T176:AA176" si="105">T54/T59</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U176" s="154" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V176" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.16546762589928057</v>
       </c>
       <c r="W176" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.27486296006264682</v>
       </c>
       <c r="X176" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.22921739130434782</v>
       </c>
       <c r="Y176" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.16591591591591592</v>
       </c>
       <c r="Z176" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.17885196374622356</v>
       </c>
       <c r="AA176" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.35157207023274806</v>
       </c>
       <c r="AC176" s="154">
@@ -31921,35 +32064,35 @@
         <v>6.284436816909042E-2</v>
       </c>
       <c r="T177" s="154">
-        <f t="shared" ref="T177:AA177" si="104">T54/T5</f>
+        <f t="shared" ref="T177:AA177" si="106">T54/T5</f>
         <v>0</v>
       </c>
       <c r="U177" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="V177" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>6.5044134030336792E-2</v>
       </c>
       <c r="W177" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>6.3940249567355861E-2</v>
       </c>
       <c r="X177" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>6.2971810797897751E-2</v>
       </c>
       <c r="Y177" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>5.8828748890860691E-2</v>
       </c>
       <c r="Z177" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>7.2477962781586677E-2</v>
       </c>
       <c r="AA177" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>8.1234078686668557E-2</v>
       </c>
       <c r="AC177" s="154">
@@ -31982,35 +32125,35 @@
         <v>-4.3473389355742293</v>
       </c>
       <c r="T178" s="72">
-        <f t="shared" ref="T178:AA178" si="105">(T106-T107)/T75</f>
+        <f t="shared" ref="T178:AA178" si="107">(T106-T107)/T75</f>
         <v>-1.3662477558348294</v>
       </c>
-      <c r="U178" s="72" t="e">
-        <f t="shared" si="105"/>
-        <v>#DIV/0!</v>
+      <c r="U178" s="72">
+        <f t="shared" si="107"/>
+        <v>-1.2007200720072007</v>
       </c>
       <c r="V178" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>-0.24593128390596744</v>
       </c>
       <c r="W178" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>-0.70765027322404372</v>
       </c>
       <c r="X178" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>-4.4272474513438365</v>
       </c>
       <c r="Y178" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>-4.3473389355742293</v>
       </c>
       <c r="Z178" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>-2.8069353327085285</v>
       </c>
       <c r="AA178" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>-5.1907020872865273</v>
       </c>
       <c r="AC178" s="72">
@@ -32052,7 +32195,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.0252158459158202E-2</v>
+        <v>-3.4769246217231847E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -32080,35 +32223,35 @@
         <v>2.6917170987264025E-2</v>
       </c>
       <c r="T180" s="154">
-        <f t="shared" ref="T180:AA180" si="106">-T109/T5</f>
+        <f t="shared" ref="T180:AA180" si="108">-T109/T5</f>
         <v>0</v>
       </c>
       <c r="U180" s="154">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="V180" s="154">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.3738109520952951E-2</v>
       </c>
       <c r="W180" s="154">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.9491756990618454E-2</v>
       </c>
       <c r="X180" s="154">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.8093645484949834E-2</v>
       </c>
       <c r="Y180" s="154">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>3.6113575865128658E-2</v>
       </c>
       <c r="Z180" s="154">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>4.4809010773751226E-2</v>
       </c>
       <c r="AA180" s="154">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>5.0287762996509104E-2</v>
       </c>
       <c r="AC180" s="154">
@@ -32141,35 +32284,35 @@
         <v>8.5069940051384532E-2</v>
       </c>
       <c r="T181" s="154" t="e">
-        <f t="shared" ref="T181:AA181" si="107">-(T109/T59)</f>
+        <f t="shared" ref="T181:AA181" si="109">-(T109/T59)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U181" s="154" t="e">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V181" s="154">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>6.0388053193808591E-2</v>
       </c>
       <c r="W181" s="154">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>8.3790133124510571E-2</v>
       </c>
       <c r="X181" s="154">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.10226086956521739</v>
       </c>
       <c r="Y181" s="154">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.10185185185185185</v>
       </c>
       <c r="Z181" s="154">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.11057401812688822</v>
       </c>
       <c r="AA181" s="154">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.21763985300122499</v>
       </c>
       <c r="AC181" s="154">
@@ -32202,35 +32345,35 @@
         <v>0.74406991260923849</v>
       </c>
       <c r="T182" s="154" t="e">
-        <f t="shared" ref="T182:AA182" si="108">-T109/T53</f>
+        <f t="shared" ref="T182:AA182" si="110">-T109/T53</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U182" s="154" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V182" s="154">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.63532110091743121</v>
       </c>
       <c r="W182" s="154">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.53904282115869018</v>
       </c>
       <c r="X182" s="154">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.7386934673366834</v>
       </c>
       <c r="Y182" s="154">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1.0970350404312668</v>
       </c>
       <c r="Z182" s="154">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1.3969465648854962</v>
       </c>
       <c r="AA182" s="154">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1.2905569007263922</v>
       </c>
       <c r="AC182" s="154">
@@ -32247,19 +32390,19 @@
         <v>0.81391852570320078</v>
       </c>
       <c r="N183" s="72">
-        <f t="shared" ref="N183:Q183" si="109">N5/N37</f>
+        <f t="shared" ref="N183:Q183" si="111">N5/N37</f>
         <v>0.90178316399396086</v>
       </c>
       <c r="O183" s="72">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.70180250783699061</v>
       </c>
       <c r="P183" s="72">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.70642201834862384</v>
       </c>
       <c r="Q183" s="72">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.88315417904792293</v>
       </c>
       <c r="T183" s="49"/>
@@ -32271,7 +32414,7 @@
       <c r="Z183" s="49"/>
       <c r="AA183" s="49"/>
       <c r="AC183" s="72">
-        <f t="shared" ref="AC183" si="110">AC5/AC37</f>
+        <f t="shared" ref="AC183" si="112">AC5/AC37</f>
         <v>0.78034864183702046</v>
       </c>
     </row>
@@ -32284,19 +32427,19 @@
         <v>1.608438042700991</v>
       </c>
       <c r="N184" s="72">
-        <f t="shared" ref="N184:Q184" si="111">IF(AND(N12&gt;0,N107&gt;0),N107/N12,"N/A")</f>
+        <f t="shared" ref="N184:Q184" si="113">IF(AND(N12&gt;0,N107&gt;0),N107/N12,"N/A")</f>
         <v>0.97616645649432532</v>
       </c>
       <c r="O184" s="72">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>1.9771443246019518</v>
       </c>
       <c r="P184" s="72">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>1.4530831099195711</v>
       </c>
       <c r="Q184" s="72">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>1.1987859166329422</v>
       </c>
       <c r="T184" s="49"/>
@@ -32308,7 +32451,7 @@
       <c r="Z184" s="49"/>
       <c r="AA184" s="49"/>
       <c r="AC184" s="72">
-        <f t="shared" ref="AC184" si="112">IF(AND(AC12&gt;0,AC107&gt;0),AC107/AC12,"N/A")</f>
+        <f t="shared" ref="AC184" si="114">IF(AND(AC12&gt;0,AC107&gt;0),AC107/AC12,"N/A")</f>
         <v>1.344782034346103</v>
       </c>
     </row>
@@ -32321,19 +32464,19 @@
         <v>0.34027990601695779</v>
       </c>
       <c r="N185" s="228">
-        <f t="shared" ref="N185:Q185" si="113">IF(AND(N12&gt;0,N107&gt;0),(N107-N106)/N12,"N/A")</f>
+        <f t="shared" ref="N185:Q185" si="115">IF(AND(N12&gt;0,N107&gt;0),(N107-N106)/N12,"N/A")</f>
         <v>0.57377049180327866</v>
       </c>
       <c r="O185" s="228">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0.52311248073959937</v>
       </c>
       <c r="P185" s="228">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0.13245953728527454</v>
       </c>
       <c r="Q185" s="228">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0.37685147713476325</v>
       </c>
       <c r="T185" s="49"/>
@@ -32345,7 +32488,7 @@
       <c r="Z185" s="49"/>
       <c r="AA185" s="49"/>
       <c r="AC185" s="228">
-        <f t="shared" ref="AC185" si="114">IF(AND(AC12&gt;0,AC107&gt;0),(AC107-AC106)/AC12,"N/A")</f>
+        <f t="shared" ref="AC185" si="116">IF(AND(AC12&gt;0,AC107&gt;0),(AC107-AC106)/AC12,"N/A")</f>
         <v>0.48181417877586968</v>
       </c>
     </row>
@@ -32358,19 +32501,19 @@
         <v>2.5273699269633312</v>
       </c>
       <c r="N186" s="228">
-        <f t="shared" ref="N186:Q186" si="115">N5/(N107+N111-N106)</f>
+        <f t="shared" ref="N186:Q186" si="117">N5/(N107+N111-N106)</f>
         <v>1.6302142883487627</v>
       </c>
       <c r="O186" s="228">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>1.3962190606119664</v>
       </c>
       <c r="P186" s="228">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>1.4112576064908722</v>
       </c>
       <c r="Q186" s="228">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>1.7123192328512875</v>
       </c>
       <c r="T186" s="49"/>
@@ -32382,7 +32525,7 @@
       <c r="Z186" s="49"/>
       <c r="AA186" s="49"/>
       <c r="AC186" s="228">
-        <f t="shared" ref="AC186" si="116">AC5/(AC107+AC111-AC106)</f>
+        <f t="shared" ref="AC186" si="118">AC5/(AC107+AC111-AC106)</f>
         <v>1.3614461510275122</v>
       </c>
     </row>
@@ -32512,7 +32655,7 @@
         <v>1326</v>
       </c>
       <c r="AC191" s="62">
-        <f t="shared" ref="AC191:AC194" si="117">SUM(X191:AA191)</f>
+        <f t="shared" ref="AC191:AC194" si="119">SUM(X191:AA191)</f>
         <v>4464</v>
       </c>
     </row>
@@ -32570,7 +32713,7 @@
         <v>1726</v>
       </c>
       <c r="AC192" s="62">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>6902</v>
       </c>
     </row>
@@ -32630,7 +32773,7 @@
         <v>9076</v>
       </c>
       <c r="AC193" s="62">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>38503</v>
       </c>
     </row>
@@ -32690,7 +32833,7 @@
         <v>1382</v>
       </c>
       <c r="AC194" s="62">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>5701</v>
       </c>
     </row>
@@ -32754,61 +32897,61 @@
       <c r="K198" s="81"/>
       <c r="L198" s="81"/>
       <c r="M198" s="81">
-        <f t="shared" ref="M198:Q201" si="118">IF(L190=0,
+        <f t="shared" ref="M198:Q201" si="120">IF(L190=0,
 IF(M190=0,0,IF(M190&gt;0,1,-1)),
 (M190-L190)/ABS(L190)
 )</f>
         <v>1</v>
       </c>
       <c r="N198" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.48704693998811643</v>
       </c>
       <c r="O198" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>-9.8173972110121063E-2</v>
       </c>
       <c r="P198" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.10159503766061143</v>
       </c>
       <c r="Q198" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.11784579495636086</v>
       </c>
       <c r="T198" s="81">
-        <f t="shared" ref="T198:AA201" si="119">IF(S190=0,
+        <f t="shared" ref="T198:AA201" si="121">IF(S190=0,
 IF(T190=0,0,IF(T190&gt;0,1,-1)),
 (T190-S190)/ABS(S190)
 )</f>
         <v>1</v>
       </c>
       <c r="U198" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>3.3395490761145959E-2</v>
       </c>
       <c r="V198" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.24245406824146981</v>
       </c>
       <c r="W198" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-8.5159757063638764E-2</v>
       </c>
       <c r="X198" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-8.6736902871987306E-2</v>
       </c>
       <c r="Y198" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.10003160556257902</v>
       </c>
       <c r="Z198" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.12397644016664272</v>
       </c>
       <c r="AA198" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-0.23006134969325154</v>
       </c>
       <c r="AC198" s="49"/>
@@ -32818,55 +32961,55 @@
         <v>388</v>
       </c>
       <c r="M199" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>1</v>
       </c>
       <c r="N199" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.40717948717948715</v>
       </c>
       <c r="O199" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.36443148688046645</v>
       </c>
       <c r="P199" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.55448717948717952</v>
       </c>
       <c r="Q199" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.35979381443298969</v>
       </c>
       <c r="T199" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>1</v>
       </c>
       <c r="U199" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.10850801479654747</v>
       </c>
       <c r="V199" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="W199" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-2.0811654526534861E-3</v>
       </c>
       <c r="X199" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>2.6068821689259645E-2</v>
       </c>
       <c r="Y199" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>7.0121951219512202E-2</v>
       </c>
       <c r="Z199" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>4.5584045584045586E-2</v>
       </c>
       <c r="AA199" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.20435967302452315</v>
       </c>
       <c r="AC199" s="49"/>
@@ -32876,55 +33019,55 @@
         <v>389</v>
       </c>
       <c r="M200" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>1</v>
       </c>
       <c r="N200" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.37420886075949367</v>
       </c>
       <c r="O200" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>-0.14507772020725387</v>
       </c>
       <c r="P200" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>-8.7037037037037038E-2</v>
       </c>
       <c r="Q200" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.22017333579199705</v>
       </c>
       <c r="T200" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>1</v>
       </c>
       <c r="U200" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.23841059602649006</v>
       </c>
       <c r="V200" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-7.9619726678550204E-2</v>
       </c>
       <c r="W200" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>2.0658489347966429E-2</v>
       </c>
       <c r="X200" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>6.3251106894370648E-2</v>
       </c>
       <c r="Y200" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>7.4955383700178471E-2</v>
       </c>
       <c r="Z200" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-6.5855008301051468E-2</v>
       </c>
       <c r="AA200" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>2.2511848341232227E-2</v>
       </c>
       <c r="AC200" s="49"/>
@@ -32934,55 +33077,55 @@
         <v>390</v>
       </c>
       <c r="M201" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>1</v>
       </c>
       <c r="N201" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.39446315555720046</v>
       </c>
       <c r="O201" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>-0.19361944953154445</v>
       </c>
       <c r="P201" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>9.2620630636561119E-2</v>
       </c>
       <c r="Q201" s="81">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0.15577177973249789</v>
       </c>
       <c r="T201" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>1</v>
       </c>
       <c r="U201" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>7.5474036435741729E-2</v>
       </c>
       <c r="V201" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.16201889836367828</v>
       </c>
       <c r="W201" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-6.0987703292344306E-2</v>
       </c>
       <c r="X201" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-5.0269299820466788E-2</v>
       </c>
       <c r="Y201" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>9.2071611253196933E-2</v>
       </c>
       <c r="Z201" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>8.064351898991956E-2</v>
       </c>
       <c r="AA201" s="81">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>-0.1448223876378027</v>
       </c>
       <c r="AC201" s="49"/>
@@ -32992,91 +33135,91 @@
         <v>391</v>
       </c>
       <c r="M202" s="81">
-        <f t="shared" ref="M202" si="120">IF(L194=0,
+        <f t="shared" ref="M202" si="122">IF(L194=0,
 IF(M194=0,0,IF(M194&gt;0,1,-1)),
 (M194-L194)/ABS(L194)
 )</f>
         <v>1</v>
       </c>
       <c r="N202" s="81">
-        <f t="shared" ref="N202" si="121">IF(M194=0,
+        <f t="shared" ref="N202" si="123">IF(M194=0,
 IF(N194=0,0,IF(N194&gt;0,1,-1)),
 (N194-M194)/ABS(M194)
 )</f>
         <v>6.0126582278481012E-3</v>
       </c>
       <c r="O202" s="81">
-        <f t="shared" ref="O202" si="122">IF(N194=0,
+        <f t="shared" ref="O202" si="124">IF(N194=0,
 IF(O194=0,0,IF(O194&gt;0,1,-1)),
 (O194-N194)/ABS(N194)
 )</f>
         <v>-0.16546083674111356</v>
       </c>
       <c r="P202" s="81">
-        <f t="shared" ref="P202" si="123">IF(O194=0,
+        <f t="shared" ref="P202" si="125">IF(O194=0,
 IF(P194=0,0,IF(P194&gt;0,1,-1)),
 (P194-O194)/ABS(O194)
 )</f>
         <v>5.0131926121372031E-2</v>
       </c>
       <c r="Q202" s="81">
-        <f t="shared" ref="Q202" si="124">IF(P194=0,
+        <f t="shared" ref="Q202" si="126">IF(P194=0,
 IF(Q194=0,0,IF(Q194&gt;0,1,-1)),
 (Q194-P194)/ABS(P194)
 )</f>
         <v>1.7946877243359654E-3</v>
       </c>
       <c r="T202" s="81">
-        <f t="shared" ref="T202" si="125">IF(S194=0,
+        <f t="shared" ref="T202" si="127">IF(S194=0,
 IF(T194=0,0,IF(T194&gt;0,1,-1)),
 (T194-S194)/ABS(S194)
 )</f>
         <v>1</v>
       </c>
       <c r="U202" s="81">
-        <f t="shared" ref="U202" si="126">IF(T194=0,
+        <f t="shared" ref="U202" si="128">IF(T194=0,
 IF(U194=0,0,IF(U194&gt;0,1,-1)),
 (U194-T194)/ABS(T194)
 )</f>
         <v>-0.20267085624509035</v>
       </c>
       <c r="V202" s="81">
-        <f t="shared" ref="V202" si="127">IF(U194=0,
+        <f t="shared" ref="V202" si="129">IF(U194=0,
 IF(V194=0,0,IF(V194&gt;0,1,-1)),
 (V194-U194)/ABS(U194)
 )</f>
         <v>0.51231527093596063</v>
       </c>
       <c r="W202" s="81">
-        <f t="shared" ref="W202" si="128">IF(V194=0,
+        <f t="shared" ref="W202" si="130">IF(V194=0,
 IF(W194=0,0,IF(W194&gt;0,1,-1)),
 (W194-V194)/ABS(V194)
 )</f>
         <v>-0.14071661237785016</v>
       </c>
       <c r="X202" s="81">
-        <f t="shared" ref="X202" si="129">IF(W194=0,
+        <f t="shared" ref="X202" si="131">IF(W194=0,
 IF(X194=0,0,IF(X194&gt;0,1,-1)),
 (X194-W194)/ABS(W194)
 )</f>
         <v>-7.5815011372251705E-4</v>
       </c>
       <c r="Y202" s="81">
-        <f t="shared" ref="Y202" si="130">IF(X194=0,
+        <f t="shared" ref="Y202" si="132">IF(X194=0,
 IF(Y194=0,0,IF(Y194&gt;0,1,-1)),
 (Y194-X194)/ABS(X194)
 )</f>
         <v>6.9044006069802738E-2</v>
       </c>
       <c r="Z202" s="81">
-        <f t="shared" ref="Z202" si="131">IF(Y194=0,
+        <f t="shared" ref="Z202" si="133">IF(Y194=0,
 IF(Z194=0,0,IF(Z194&gt;0,1,-1)),
 (Z194-Y194)/ABS(Y194)
 )</f>
         <v>0.12987934705464868</v>
       </c>
       <c r="AA202" s="81">
-        <f t="shared" ref="AA202" si="132">IF(Z194=0,
+        <f t="shared" ref="AA202" si="134">IF(Z194=0,
 IF(AA194=0,0,IF(AA194&gt;0,1,-1)),
 (AA194-Z194)/ABS(Z194)
 )</f>
@@ -33219,15 +33362,15 @@
         <v>90.521362414102185</v>
       </c>
       <c r="O210" s="143">
-        <f t="shared" ref="O210:Q210" si="133">100*(1+((O116-$M116)/ABS($M116)))</f>
+        <f t="shared" ref="O210:Q210" si="135">100*(1+((O116-$M116)/ABS($M116)))</f>
         <v>80.430236032267715</v>
       </c>
       <c r="P210" s="143">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>127.07648640573647</v>
       </c>
       <c r="Q210" s="143">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>126.38183447863757</v>
       </c>
       <c r="T210" s="49"/>
@@ -33252,15 +33395,15 @@
         <v>131.68086754453913</v>
       </c>
       <c r="O211" s="143">
-        <f t="shared" ref="O211:Q211" si="134">100*(1+((O5-$M5)/ABS($M5)))</f>
+        <f t="shared" ref="O211:Q211" si="136">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>106.71512840374189</v>
       </c>
       <c r="P211" s="143">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>116.07579097896681</v>
       </c>
       <c r="Q211" s="143">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>131.93112077697671</v>
       </c>
       <c r="T211" s="49"/>
@@ -33285,15 +33428,15 @@
         <v>144.98094027954255</v>
       </c>
       <c r="O212" s="143">
-        <f t="shared" ref="O212:Q212" si="135">100*(1+((O26-$M26)/ABS($M26)))</f>
+        <f t="shared" ref="O212:Q212" si="137">100*(1+((O26-$M26)/ABS($M26)))</f>
         <v>82.846251588310025</v>
       </c>
       <c r="P212" s="143">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>113.59593392630241</v>
       </c>
       <c r="Q212" s="143">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>129.26112679457472</v>
       </c>
       <c r="T212" s="49"/>
@@ -33374,15 +33517,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="238"/>
+      <c r="E4" s="238" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33390,7 +33533,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>170.61</v>
+        <v>148.44499999999999</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33406,7 +33549,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>180846.6</v>
+        <v>157351.69999999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33426,7 +33569,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>186317.6</v>
+        <v>162822.69999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33446,7 +33589,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>18.114651950648323</v>
+        <v>15.761265510896138</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -33466,7 +33609,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.1403135513389859</v>
+        <v>3.6024198178800519</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -33486,7 +33629,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>6.5922333015616994</v>
+        <v>5.7357955128675124</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33506,7 +33649,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.1788364060467416</v>
+        <v>3.6518795137487099</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33515,18 +33658,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>16.408419198590931</v>
+        <v>14.339295464553059</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="238" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="238"/>
+      <c r="E15" s="238" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33577,14 +33720,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="238" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="238"/>
+      <c r="E21" s="238" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="238"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33653,14 +33796,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="238" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="238"/>
+      <c r="E29" s="238" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="238"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33736,14 +33879,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="238" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="238"/>
+      <c r="E37" s="238" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="238"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33751,7 +33894,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.5203931200246442E-2</v>
+        <v>6.3446681950042411E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -33767,7 +33910,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>5.2149169517148784E-2</v>
+        <v>5.9935799867430736E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -33783,7 +33926,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>2.0866303264755876E-2</v>
+        <v>2.398194617535114E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -33799,7 +33942,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.9359700431194172E-2</v>
+        <v>6.8222968039112389E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33808,18 +33951,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>8.0482574734609333E-2</v>
+        <v>9.2499795045112326E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="238" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="238"/>
+      <c r="E45" s="238" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="238"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33852,18 +33995,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-3.0252158459158202E-2</v>
+        <v>-3.4769246217231847E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="238" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="238"/>
+      <c r="E51" s="238" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="238"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34032,7 +34175,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>170.61</v>
+        <v>148.44499999999999</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34061,7 +34204,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>180846.6</v>
+        <v>157351.69999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34090,7 +34233,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>186317.6</v>
+        <v>162822.69999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34119,7 +34262,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>18.114651950648323</v>
+        <v>15.761265510896138</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34148,7 +34291,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.1403135513389859</v>
+        <v>3.6024198178800519</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34177,7 +34320,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>6.5922333015616994</v>
+        <v>5.7357955128675124</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34206,7 +34349,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.1788364060467416</v>
+        <v>3.6518795137487099</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34235,7 +34378,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>16.408419198590931</v>
+        <v>14.339295464553059</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35008,7 +35151,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.5203931200246442E-2</v>
+        <v>6.3446681950042411E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35037,7 +35180,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>5.2149169517148784E-2</v>
+        <v>5.9935799867430736E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35066,7 +35209,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>2.0866303264755876E-2</v>
+        <v>2.398194617535114E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35095,7 +35238,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.9359700431194172E-2</v>
+        <v>6.8222968039112389E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35124,7 +35267,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>8.0482574734609333E-2</v>
+        <v>9.2499795045112326E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35360,7 +35503,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-3.0252158459158202E-2</v>
+        <v>-3.4769246217231847E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35898,14 +36041,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="244" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="245"/>
+      <c r="F3" s="246" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="245"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35972,19 +36115,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="242">
+      <c r="C7" s="247">
         <f>Statement!AA89</f>
         <v>-0.13491674828599412</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="F7" s="242">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-3.4611531104836508E-2</v>
       </c>
-      <c r="G7" s="243"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -36011,19 +36154,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="242">
+      <c r="C9" s="247">
         <f>Statement!AA90</f>
         <v>-0.11997126436781609</v>
       </c>
-      <c r="D9" s="243"/>
-      <c r="F9" s="242">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>-7.4944298156775372E-3</v>
       </c>
-      <c r="G9" s="243"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -36050,19 +36193,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="242">
+      <c r="C11" s="247">
         <f>Statement!AA91</f>
         <v>-0.1473668461998803</v>
       </c>
-      <c r="D11" s="243"/>
-      <c r="F11" s="242">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-5.6769281694803046E-2</v>
       </c>
-      <c r="G11" s="243"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -36089,19 +36232,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="242">
+      <c r="C13" s="247">
         <f>Statement!AA94</f>
         <v>2.1699819168173599E-2</v>
       </c>
-      <c r="D13" s="243"/>
-      <c r="F13" s="242">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.16016427104722791</v>
       </c>
-      <c r="G13" s="243"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -36128,19 +36271,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="242">
+      <c r="C15" s="247">
         <f>Statement!AA95</f>
         <v>-0.31402257872846107</v>
       </c>
-      <c r="D15" s="243"/>
-      <c r="F15" s="242">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.25993589743589746</v>
       </c>
-      <c r="G15" s="243"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -36167,19 +36310,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="242">
+      <c r="C17" s="247">
         <f>Statement!AA97</f>
         <v>-0.35685752330226367</v>
       </c>
-      <c r="D17" s="243"/>
-      <c r="F17" s="242">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.31294452347083929</v>
       </c>
-      <c r="G17" s="243"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36206,22 +36349,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="242">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-6.4874884151992582E-3</v>
       </c>
-      <c r="D19" s="243"/>
-      <c r="F19" s="242">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.8565022421524667E-2</v>
       </c>
-      <c r="G19" s="243"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36248,22 +36391,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="242">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.35171265972296784</v>
       </c>
-      <c r="D21" s="243"/>
-      <c r="F21" s="242">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.28482587064676618</v>
       </c>
-      <c r="G21" s="243"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36311,22 +36454,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="242">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.23006134969325154</v>
       </c>
-      <c r="D25" s="243"/>
-      <c r="F25" s="242">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.13061047770241016</v>
       </c>
-      <c r="G25" s="243"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -36353,22 +36496,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="242">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.20435967302452315</v>
       </c>
-      <c r="D27" s="243"/>
-      <c r="F27" s="242">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.38269030239833157</v>
       </c>
-      <c r="G27" s="243"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -36395,22 +36538,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="242">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.2511848341232227E-2</v>
       </c>
-      <c r="D29" s="243"/>
-      <c r="F29" s="242">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>9.1714104996837451E-2</v>
       </c>
-      <c r="G29" s="243"/>
+      <c r="G29" s="248"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36437,22 +36580,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="242">
+      <c r="C31" s="247">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-0.1448223876378027</v>
       </c>
-      <c r="D31" s="243"/>
-      <c r="F31" s="242">
+      <c r="D31" s="248"/>
+      <c r="F31" s="247">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-4.1503854683704718E-2</v>
       </c>
-      <c r="G31" s="243"/>
+      <c r="G31" s="248"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36479,22 +36622,22 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="242">
+      <c r="C33" s="247">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-0.13190954773869346</v>
       </c>
-      <c r="D33" s="243"/>
-      <c r="F33" s="242">
+      <c r="D33" s="248"/>
+      <c r="F33" s="247">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>4.7763457164518575E-2</v>
       </c>
-      <c r="G33" s="243"/>
+      <c r="G33" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="28">
